--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,6 +1021,6674 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125692134</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500001</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6792610</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125693022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500026</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6792635</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125684146</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>500023</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6792383</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125690295</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>500031</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6792511</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125685885</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>500002</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6792449</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125684984</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>500076</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6792415</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125684196</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>500039</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6792388</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125684736</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>500077</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6792400</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125690957</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>500003</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6792577</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125691010</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>500009</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6792567</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125693671</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>500087</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6792574</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125685734</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>499996</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6792435</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125686316</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78683</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>499963</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6792480</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125684537</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>500039</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6792388</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125685190</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>500040</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6792406</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125684610</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>500047</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6792395</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125690007</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79536</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>499989</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6792563</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125693249</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79536</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>500047</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6792612</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125689064</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79536</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>499942</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6792546</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125690154</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>499990</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6792543</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125685512</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>499996</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6792394</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125687486</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79536</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>499947</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6792525</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125685121</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>500063</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6792423</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125689757</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79536</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>499951</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6792574</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125693372</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>500078</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6792594</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125693403</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78684</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>500078</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6792594</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125693241</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>500047</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6792612</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125686874</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>500013</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6792493</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125685335</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>500063</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6792381</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125686343</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>499963</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6792480</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125690119</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>499990</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6792543</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125692802</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79536</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>499954</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6792650</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125691576</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>500028</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6792566</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125683895</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>500326</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6792440</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125685863</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79536</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>499996</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6792435</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125687294</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>499945</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6792497</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125690170</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>500018</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6792528</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125693794</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56836</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>500087</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6792574</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125685407</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>500063</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6792381</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125684974</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>500076</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6792407</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125690589</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>500043</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6792510</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125687400</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>499947</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6792525</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125685428</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>499996</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6792394</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125686648</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78684</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>499990</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6792488</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125686792</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>499990</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6792488</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125686894</v>
+      </c>
+      <c r="B50" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>500010</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6792501</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125686732</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78683</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>499990</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6792488</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125689836</v>
+      </c>
+      <c r="B52" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>499951</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6792574</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125684967</v>
+      </c>
+      <c r="B53" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>500076</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6792407</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125687215</v>
+      </c>
+      <c r="B54" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>499945</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6792497</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125686800</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>500007</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6792490</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125693564</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78683</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>500087</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6792574</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125685110</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>500063</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6792423</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125685313</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78684</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>500063</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6792381</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Muljöbilder</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125685693</v>
+      </c>
+      <c r="B59" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>500002</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6792449</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125684006</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>500326</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6792440</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125683878</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>499954</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6792394</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125685808</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78684</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>499996</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6792435</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125686463</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>499969</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6792489</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125688845</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>499970</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6792544</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125687329</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>499947</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6792525</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125686305</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78684</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>499963</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6792480</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125685660</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>499989</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6792445</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125686924</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>500010</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6792501</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1023,32 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125686800</v>
+        <v>125686874</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500007</v>
+        <v>500013</v>
       </c>
       <c r="R5" t="n">
-        <v>6792490</v>
+        <v>6792493</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,6 +1094,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,32 +1125,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125686732</v>
+        <v>125687215</v>
       </c>
       <c r="B6" t="n">
-        <v>78725</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499990</v>
+        <v>499945</v>
       </c>
       <c r="R6" t="n">
-        <v>6792488</v>
+        <v>6792497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,11 +1196,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,32 +1222,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125685630</v>
+        <v>125689836</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499996</v>
+        <v>499951</v>
       </c>
       <c r="R7" t="n">
-        <v>6792394</v>
+        <v>6792574</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125685407</v>
+        <v>125687486</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,21 +1330,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500063</v>
+        <v>499947</v>
       </c>
       <c r="R8" t="n">
-        <v>6792381</v>
+        <v>6792525</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,32 +1416,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125693671</v>
+        <v>125686800</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500087</v>
+        <v>500007</v>
       </c>
       <c r="R9" t="n">
-        <v>6792574</v>
+        <v>6792490</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,32 +1513,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125686874</v>
+        <v>125686732</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>78725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500013</v>
+        <v>499990</v>
       </c>
       <c r="R10" t="n">
-        <v>6792493</v>
+        <v>6792488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,32 +1615,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125687215</v>
+        <v>125685630</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499945</v>
+        <v>499996</v>
       </c>
       <c r="R11" t="n">
-        <v>6792497</v>
+        <v>6792394</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,32 +1712,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125689836</v>
+        <v>125685407</v>
       </c>
       <c r="B12" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499951</v>
+        <v>500063</v>
       </c>
       <c r="R12" t="n">
-        <v>6792574</v>
+        <v>6792381</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1809,32 +1809,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125687486</v>
+        <v>125693671</v>
       </c>
       <c r="B13" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499947</v>
+        <v>500087</v>
       </c>
       <c r="R13" t="n">
-        <v>6792525</v>
+        <v>6792574</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3309,32 +3309,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125683895</v>
+        <v>125693241</v>
       </c>
       <c r="B28" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500326</v>
+        <v>500047</v>
       </c>
       <c r="R28" t="n">
-        <v>6792440</v>
+        <v>6792612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3380,11 +3380,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3411,32 +3406,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125686305</v>
+        <v>125683895</v>
       </c>
       <c r="B29" t="n">
-        <v>78726</v>
+        <v>8447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3446,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499963</v>
+        <v>500326</v>
       </c>
       <c r="R29" t="n">
-        <v>6792480</v>
+        <v>6792440</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,10 +3508,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125693249</v>
+        <v>125686343</v>
       </c>
       <c r="B30" t="n">
-        <v>79556</v>
+        <v>79585</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3519,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3543,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500047</v>
+        <v>499963</v>
       </c>
       <c r="R30" t="n">
-        <v>6792612</v>
+        <v>6792480</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,10 +3605,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125686343</v>
+        <v>125685148</v>
       </c>
       <c r="B31" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3621,21 +3616,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3645,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499963</v>
+        <v>500040</v>
       </c>
       <c r="R31" t="n">
-        <v>6792480</v>
+        <v>6792406</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125685148</v>
+        <v>125686305</v>
       </c>
       <c r="B32" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3718,21 +3713,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3742,10 +3737,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500040</v>
+        <v>499963</v>
       </c>
       <c r="R32" t="n">
-        <v>6792406</v>
+        <v>6792480</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3778,6 +3773,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3804,10 +3804,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125693241</v>
+        <v>125693249</v>
       </c>
       <c r="B33" t="n">
-        <v>57648</v>
+        <v>79556</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3815,21 +3815,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -5978,32 +5978,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685813</v>
+        <v>125683878</v>
       </c>
       <c r="B55" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499996</v>
+        <v>499954</v>
       </c>
       <c r="R55" t="n">
-        <v>6792435</v>
+        <v>6792394</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,6 +6049,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6075,32 +6080,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125683878</v>
+        <v>125685885</v>
       </c>
       <c r="B56" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6110,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499954</v>
+        <v>500002</v>
       </c>
       <c r="R56" t="n">
-        <v>6792394</v>
+        <v>6792449</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6146,11 +6151,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6177,7 +6177,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125685885</v>
+        <v>125690170</v>
       </c>
       <c r="B57" t="n">
         <v>78967</v>
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>500002</v>
+        <v>500018</v>
       </c>
       <c r="R57" t="n">
-        <v>6792449</v>
+        <v>6792528</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125690170</v>
+        <v>125685813</v>
       </c>
       <c r="B58" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>500018</v>
+        <v>499996</v>
       </c>
       <c r="R58" t="n">
-        <v>6792528</v>
+        <v>6792435</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7365,32 +7365,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125892998</v>
+        <v>125888195</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500188</v>
+        <v>500310</v>
       </c>
       <c r="R69" t="n">
-        <v>6792496</v>
+        <v>6792516</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,6 +7436,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7462,32 +7467,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125893046</v>
+        <v>125889107</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7497,10 +7502,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500207</v>
+        <v>500285</v>
       </c>
       <c r="R70" t="n">
-        <v>6792488</v>
+        <v>6792489</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7559,32 +7564,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125888195</v>
+        <v>125892998</v>
       </c>
       <c r="B71" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7594,10 +7599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500310</v>
+        <v>500188</v>
       </c>
       <c r="R71" t="n">
-        <v>6792516</v>
+        <v>6792496</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7630,11 +7635,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7661,32 +7661,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125889107</v>
+        <v>125893046</v>
       </c>
       <c r="B72" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500285</v>
+        <v>500207</v>
       </c>
       <c r="R72" t="n">
-        <v>6792489</v>
+        <v>6792488</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125896683</v>
+        <v>125894466</v>
       </c>
       <c r="B90" t="n">
         <v>8447</v>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>500384</v>
+        <v>500128</v>
       </c>
       <c r="R90" t="n">
-        <v>6792529</v>
+        <v>6792590</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9514,7 +9514,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125894466</v>
+        <v>125896683</v>
       </c>
       <c r="B91" t="n">
         <v>8447</v>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R91" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11071,50 +11071,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125896426</v>
+        <v>125893643</v>
       </c>
       <c r="B107" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500351</v>
+        <v>500237</v>
       </c>
       <c r="R107" t="n">
-        <v>6792369</v>
+        <v>6792567</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11173,10 +11168,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125896524</v>
+        <v>125896426</v>
       </c>
       <c r="B108" t="n">
-        <v>79585</v>
+        <v>57648</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11184,34 +11179,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500384</v>
+        <v>500351</v>
       </c>
       <c r="R108" t="n">
-        <v>6792529</v>
+        <v>6792369</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11270,30 +11270,34 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125894266</v>
+        <v>125896524</v>
       </c>
       <c r="B109" t="n">
-        <v>98244</v>
+        <v>79585</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>223597</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11301,10 +11305,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R109" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11363,10 +11367,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125893643</v>
+        <v>125894266</v>
       </c>
       <c r="B110" t="n">
-        <v>8447</v>
+        <v>98244</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11374,23 +11378,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>223597</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11398,10 +11398,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500237</v>
+        <v>500128</v>
       </c>
       <c r="R110" t="n">
-        <v>6792567</v>
+        <v>6792590</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12741,32 +12741,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125896611</v>
+        <v>125891471</v>
       </c>
       <c r="B124" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12776,10 +12776,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500384</v>
+        <v>500181</v>
       </c>
       <c r="R124" t="n">
-        <v>6792529</v>
+        <v>6792401</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12812,11 +12812,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12843,10 +12838,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125896030</v>
+        <v>125892207</v>
       </c>
       <c r="B125" t="n">
-        <v>57651</v>
+        <v>79585</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12854,39 +12849,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500351</v>
+        <v>500158</v>
       </c>
       <c r="R125" t="n">
-        <v>6792369</v>
+        <v>6792441</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12945,10 +12935,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125894132</v>
+        <v>125896611</v>
       </c>
       <c r="B126" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12956,21 +12946,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12980,10 +12970,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R126" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13016,6 +13006,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13042,45 +13037,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125891471</v>
+        <v>125896030</v>
       </c>
       <c r="B127" t="n">
-        <v>8447</v>
+        <v>57651</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500181</v>
+        <v>500351</v>
       </c>
       <c r="R127" t="n">
-        <v>6792401</v>
+        <v>6792369</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13139,10 +13139,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125892207</v>
+        <v>125894132</v>
       </c>
       <c r="B128" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13150,21 +13150,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13174,10 +13174,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>500158</v>
+        <v>500128</v>
       </c>
       <c r="R128" t="n">
-        <v>6792441</v>
+        <v>6792590</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125892160</v>
+        <v>125889379</v>
       </c>
       <c r="B140" t="n">
-        <v>79556</v>
+        <v>78726</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R140" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14410,10 +14410,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125896535</v>
+        <v>125889266</v>
       </c>
       <c r="B141" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14421,21 +14421,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14445,10 +14445,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500384</v>
+        <v>500257</v>
       </c>
       <c r="R141" t="n">
-        <v>6792529</v>
+        <v>6792475</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14481,6 +14481,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14507,7 +14512,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125896642</v>
+        <v>125892160</v>
       </c>
       <c r="B142" t="n">
         <v>79556</v>
@@ -14542,10 +14547,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>500384</v>
+        <v>500145</v>
       </c>
       <c r="R142" t="n">
-        <v>6792529</v>
+        <v>6792446</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14604,10 +14609,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125896454</v>
+        <v>125896535</v>
       </c>
       <c r="B143" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14615,21 +14620,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14639,10 +14644,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500374</v>
+        <v>500384</v>
       </c>
       <c r="R143" t="n">
-        <v>6792515</v>
+        <v>6792529</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14675,11 +14680,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14706,7 +14706,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125892643</v>
+        <v>125896642</v>
       </c>
       <c r="B144" t="n">
         <v>79556</v>
@@ -14741,10 +14741,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500151</v>
+        <v>500384</v>
       </c>
       <c r="R144" t="n">
-        <v>6792458</v>
+        <v>6792529</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14803,10 +14803,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125889379</v>
+        <v>125896454</v>
       </c>
       <c r="B145" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14814,21 +14814,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14838,10 +14838,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500257</v>
+        <v>500374</v>
       </c>
       <c r="R145" t="n">
-        <v>6792475</v>
+        <v>6792515</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14874,6 +14874,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14900,10 +14905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125889266</v>
+        <v>125892643</v>
       </c>
       <c r="B146" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14911,21 +14916,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14935,10 +14940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500257</v>
+        <v>500151</v>
       </c>
       <c r="R146" t="n">
-        <v>6792475</v>
+        <v>6792458</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14971,11 +14976,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15002,32 +15002,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125896772</v>
+        <v>125891864</v>
       </c>
       <c r="B147" t="n">
-        <v>92502</v>
+        <v>78967</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15037,10 +15037,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500384</v>
+        <v>500126</v>
       </c>
       <c r="R147" t="n">
-        <v>6792529</v>
+        <v>6792397</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15073,6 +15073,11 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15099,50 +15104,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125888369</v>
+        <v>125896772</v>
       </c>
       <c r="B148" t="n">
-        <v>57648</v>
+        <v>92502</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500310</v>
+        <v>500384</v>
       </c>
       <c r="R148" t="n">
-        <v>6792516</v>
+        <v>6792529</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15201,10 +15201,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125888908</v>
+        <v>125888369</v>
       </c>
       <c r="B149" t="n">
-        <v>79556</v>
+        <v>57648</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15212,34 +15212,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500306</v>
+        <v>500310</v>
       </c>
       <c r="R149" t="n">
-        <v>6792466</v>
+        <v>6792516</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15298,32 +15303,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125892001</v>
+        <v>125888908</v>
       </c>
       <c r="B150" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15333,10 +15338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500111</v>
+        <v>500306</v>
       </c>
       <c r="R150" t="n">
-        <v>6792428</v>
+        <v>6792466</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15395,32 +15400,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125891864</v>
+        <v>125892001</v>
       </c>
       <c r="B151" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15430,10 +15435,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500126</v>
+        <v>500111</v>
       </c>
       <c r="R151" t="n">
-        <v>6792397</v>
+        <v>6792428</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15466,11 +15471,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15497,32 +15497,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125888498</v>
+        <v>125891609</v>
       </c>
       <c r="B152" t="n">
-        <v>8447</v>
+        <v>78726</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500311</v>
+        <v>500153</v>
       </c>
       <c r="R152" t="n">
-        <v>6792509</v>
+        <v>6792391</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15594,32 +15594,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125889396</v>
+        <v>125888498</v>
       </c>
       <c r="B153" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15629,10 +15629,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500257</v>
+        <v>500311</v>
       </c>
       <c r="R153" t="n">
-        <v>6792475</v>
+        <v>6792509</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15691,10 +15691,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125891609</v>
+        <v>125889396</v>
       </c>
       <c r="B154" t="n">
-        <v>78726</v>
+        <v>79556</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15702,21 +15702,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500153</v>
+        <v>500257</v>
       </c>
       <c r="R154" t="n">
-        <v>6792391</v>
+        <v>6792475</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1023,32 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125686874</v>
+        <v>125686800</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500013</v>
+        <v>500007</v>
       </c>
       <c r="R5" t="n">
-        <v>6792493</v>
+        <v>6792490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,11 +1094,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,32 +1120,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125687215</v>
+        <v>125686732</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>78725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499945</v>
+        <v>499990</v>
       </c>
       <c r="R6" t="n">
-        <v>6792497</v>
+        <v>6792488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1191,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,32 +1222,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125689836</v>
+        <v>125685630</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499951</v>
+        <v>499996</v>
       </c>
       <c r="R7" t="n">
-        <v>6792574</v>
+        <v>6792394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125687486</v>
+        <v>125685407</v>
       </c>
       <c r="B8" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,21 +1330,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499947</v>
+        <v>500063</v>
       </c>
       <c r="R8" t="n">
-        <v>6792525</v>
+        <v>6792381</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,32 +1416,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125686800</v>
+        <v>125686874</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500007</v>
+        <v>500013</v>
       </c>
       <c r="R9" t="n">
-        <v>6792490</v>
+        <v>6792493</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,6 +1487,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,32 +1518,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125686732</v>
+        <v>125693671</v>
       </c>
       <c r="B10" t="n">
-        <v>78725</v>
+        <v>8447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499990</v>
+        <v>500087</v>
       </c>
       <c r="R10" t="n">
-        <v>6792488</v>
+        <v>6792574</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,11 +1589,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,32 +1615,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125685630</v>
+        <v>125687215</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499996</v>
+        <v>499945</v>
       </c>
       <c r="R11" t="n">
-        <v>6792394</v>
+        <v>6792497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,32 +1712,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125685407</v>
+        <v>125689836</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500063</v>
+        <v>499951</v>
       </c>
       <c r="R12" t="n">
-        <v>6792381</v>
+        <v>6792574</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1809,32 +1809,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125693671</v>
+        <v>125687486</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500087</v>
+        <v>499947</v>
       </c>
       <c r="R13" t="n">
-        <v>6792574</v>
+        <v>6792525</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2207,32 +2207,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125685313</v>
+        <v>125684253</v>
       </c>
       <c r="B17" t="n">
-        <v>78726</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500063</v>
+        <v>500039</v>
       </c>
       <c r="R17" t="n">
-        <v>6792381</v>
+        <v>6792388</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,11 +2278,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Muljöbilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2309,10 +2304,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125692802</v>
+        <v>125685313</v>
       </c>
       <c r="B18" t="n">
-        <v>79556</v>
+        <v>78726</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2320,21 +2315,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2344,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499954</v>
+        <v>500063</v>
       </c>
       <c r="R18" t="n">
-        <v>6792650</v>
+        <v>6792381</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,6 +2375,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Muljöbilder</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,32 +2406,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125684253</v>
+        <v>125692802</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500039</v>
+        <v>499954</v>
       </c>
       <c r="R19" t="n">
-        <v>6792388</v>
+        <v>6792650</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125685512</v>
+        <v>125693794</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>56843</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3014,34 +3014,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499996</v>
+        <v>500087</v>
       </c>
       <c r="R25" t="n">
-        <v>6792394</v>
+        <v>6792574</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3074,11 +3079,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3105,32 +3105,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125689285</v>
+        <v>125685512</v>
       </c>
       <c r="B26" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499942</v>
+        <v>499996</v>
       </c>
       <c r="R26" t="n">
-        <v>6792546</v>
+        <v>6792394</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3207,50 +3207,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125693794</v>
+        <v>125689285</v>
       </c>
       <c r="B27" t="n">
-        <v>56843</v>
+        <v>79556</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500087</v>
+        <v>499942</v>
       </c>
       <c r="R27" t="n">
-        <v>6792574</v>
+        <v>6792546</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3283,6 +3278,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3406,32 +3406,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125683895</v>
+        <v>125686343</v>
       </c>
       <c r="B29" t="n">
-        <v>8447</v>
+        <v>79585</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500326</v>
+        <v>499963</v>
       </c>
       <c r="R29" t="n">
-        <v>6792440</v>
+        <v>6792480</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3477,11 +3477,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3508,10 +3503,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125686343</v>
+        <v>125685148</v>
       </c>
       <c r="B30" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3519,21 +3514,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3543,10 +3538,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499963</v>
+        <v>500040</v>
       </c>
       <c r="R30" t="n">
-        <v>6792480</v>
+        <v>6792406</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3605,32 +3600,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125685148</v>
+        <v>125683895</v>
       </c>
       <c r="B31" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3640,10 +3635,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500040</v>
+        <v>500326</v>
       </c>
       <c r="R31" t="n">
-        <v>6792406</v>
+        <v>6792440</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3676,6 +3671,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3901,32 +3901,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125684693</v>
+        <v>125687329</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500077</v>
+        <v>499947</v>
       </c>
       <c r="R34" t="n">
-        <v>6792400</v>
+        <v>6792525</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3998,32 +3998,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125687329</v>
+        <v>125684693</v>
       </c>
       <c r="B35" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499947</v>
+        <v>500077</v>
       </c>
       <c r="R35" t="n">
-        <v>6792525</v>
+        <v>6792400</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5279,32 +5279,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125689757</v>
+        <v>125685110</v>
       </c>
       <c r="B48" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499951</v>
+        <v>500063</v>
       </c>
       <c r="R48" t="n">
-        <v>6792574</v>
+        <v>6792423</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,32 +5381,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125685110</v>
+        <v>125689757</v>
       </c>
       <c r="B49" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500063</v>
+        <v>499951</v>
       </c>
       <c r="R49" t="n">
-        <v>6792423</v>
+        <v>6792574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,32 +5580,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125684626</v>
+        <v>125685693</v>
       </c>
       <c r="B51" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500047</v>
+        <v>500002</v>
       </c>
       <c r="R51" t="n">
-        <v>6792395</v>
+        <v>6792449</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5651,6 +5651,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5677,32 +5682,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125690154</v>
+        <v>125686894</v>
       </c>
       <c r="B52" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5712,10 +5717,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499990</v>
+        <v>500010</v>
       </c>
       <c r="R52" t="n">
-        <v>6792543</v>
+        <v>6792501</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5748,11 +5753,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5779,32 +5779,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685693</v>
+        <v>125684626</v>
       </c>
       <c r="B53" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500002</v>
+        <v>500047</v>
       </c>
       <c r="R53" t="n">
-        <v>6792449</v>
+        <v>6792395</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5850,11 +5850,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5881,32 +5876,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125686894</v>
+        <v>125690154</v>
       </c>
       <c r="B54" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5916,10 +5911,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>500010</v>
+        <v>499990</v>
       </c>
       <c r="R54" t="n">
-        <v>6792501</v>
+        <v>6792543</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5952,6 +5947,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5978,32 +5978,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125683878</v>
+        <v>125685885</v>
       </c>
       <c r="B55" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499954</v>
+        <v>500002</v>
       </c>
       <c r="R55" t="n">
-        <v>6792394</v>
+        <v>6792449</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,11 +6049,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6080,7 +6075,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125685885</v>
+        <v>125690170</v>
       </c>
       <c r="B56" t="n">
         <v>78967</v>
@@ -6115,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>500002</v>
+        <v>500018</v>
       </c>
       <c r="R56" t="n">
-        <v>6792449</v>
+        <v>6792528</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6177,32 +6172,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125690170</v>
+        <v>125683878</v>
       </c>
       <c r="B57" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6212,10 +6207,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>500018</v>
+        <v>499954</v>
       </c>
       <c r="R57" t="n">
-        <v>6792528</v>
+        <v>6792394</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6248,6 +6243,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125894731</v>
+        <v>125888195</v>
       </c>
       <c r="B68" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,39 +7274,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500128</v>
+        <v>500310</v>
       </c>
       <c r="R68" t="n">
-        <v>6792590</v>
+        <v>6792516</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7339,6 +7334,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7365,10 +7365,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125888195</v>
+        <v>125894731</v>
       </c>
       <c r="B69" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7376,34 +7376,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500310</v>
+        <v>500128</v>
       </c>
       <c r="R69" t="n">
-        <v>6792516</v>
+        <v>6792590</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,11 +7441,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7467,32 +7467,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125889107</v>
+        <v>125892998</v>
       </c>
       <c r="B70" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7502,10 +7502,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500285</v>
+        <v>500188</v>
       </c>
       <c r="R70" t="n">
-        <v>6792489</v>
+        <v>6792496</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7564,7 +7564,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125892998</v>
+        <v>125893046</v>
       </c>
       <c r="B71" t="n">
         <v>8447</v>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500188</v>
+        <v>500207</v>
       </c>
       <c r="R71" t="n">
-        <v>6792496</v>
+        <v>6792488</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7661,32 +7661,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125893046</v>
+        <v>125889107</v>
       </c>
       <c r="B72" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500207</v>
+        <v>500285</v>
       </c>
       <c r="R72" t="n">
-        <v>6792488</v>
+        <v>6792489</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7758,10 +7758,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125891809</v>
+        <v>125890555</v>
       </c>
       <c r="B73" t="n">
-        <v>79556</v>
+        <v>79585</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7769,21 +7769,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>500166</v>
+        <v>500282</v>
       </c>
       <c r="R73" t="n">
-        <v>6792387</v>
+        <v>6792389</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7855,32 +7855,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125890092</v>
+        <v>125893261</v>
       </c>
       <c r="B74" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500242</v>
+        <v>500271</v>
       </c>
       <c r="R74" t="n">
-        <v>6792408</v>
+        <v>6792529</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7952,7 +7952,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125890234</v>
+        <v>125896279</v>
       </c>
       <c r="B75" t="n">
         <v>8447</v>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>500242</v>
+        <v>500351</v>
       </c>
       <c r="R75" t="n">
-        <v>6792408</v>
+        <v>6792369</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8049,32 +8049,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125890555</v>
+        <v>125895125</v>
       </c>
       <c r="B76" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>500282</v>
+        <v>499985</v>
       </c>
       <c r="R76" t="n">
-        <v>6792389</v>
+        <v>6792633</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125896279</v>
+        <v>125890234</v>
       </c>
       <c r="B77" t="n">
         <v>8447</v>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>500351</v>
+        <v>500242</v>
       </c>
       <c r="R77" t="n">
-        <v>6792369</v>
+        <v>6792408</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8243,32 +8243,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125895125</v>
+        <v>125890092</v>
       </c>
       <c r="B78" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>499985</v>
+        <v>500242</v>
       </c>
       <c r="R78" t="n">
-        <v>6792633</v>
+        <v>6792408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8340,32 +8340,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125893261</v>
+        <v>125891809</v>
       </c>
       <c r="B79" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500271</v>
+        <v>500166</v>
       </c>
       <c r="R79" t="n">
-        <v>6792529</v>
+        <v>6792387</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8437,45 +8437,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125892266</v>
+        <v>125888740</v>
       </c>
       <c r="B80" t="n">
-        <v>8447</v>
+        <v>57811</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500158</v>
+        <v>500306</v>
       </c>
       <c r="R80" t="n">
-        <v>6792441</v>
+        <v>6792466</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8534,10 +8539,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125895109</v>
+        <v>125889155</v>
       </c>
       <c r="B81" t="n">
-        <v>79585</v>
+        <v>79556</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8545,21 +8550,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8569,10 +8574,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>499985</v>
+        <v>500275</v>
       </c>
       <c r="R81" t="n">
-        <v>6792633</v>
+        <v>6792487</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8631,10 +8636,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125892653</v>
+        <v>125891598</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8642,21 +8647,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8666,10 +8671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500151</v>
+        <v>500153</v>
       </c>
       <c r="R82" t="n">
-        <v>6792458</v>
+        <v>6792391</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8728,32 +8733,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125891598</v>
+        <v>125892266</v>
       </c>
       <c r="B83" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8763,10 +8768,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>500153</v>
+        <v>500158</v>
       </c>
       <c r="R83" t="n">
-        <v>6792391</v>
+        <v>6792441</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8825,32 +8830,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125890407</v>
+        <v>125888709</v>
       </c>
       <c r="B84" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8860,10 +8865,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500242</v>
+        <v>500311</v>
       </c>
       <c r="R84" t="n">
-        <v>6792408</v>
+        <v>6792502</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8896,11 +8901,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8927,10 +8927,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125888740</v>
+        <v>125892215</v>
       </c>
       <c r="B85" t="n">
-        <v>57811</v>
+        <v>79556</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8938,39 +8938,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500306</v>
+        <v>500158</v>
       </c>
       <c r="R85" t="n">
-        <v>6792466</v>
+        <v>6792441</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9029,32 +9024,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125888709</v>
+        <v>125890407</v>
       </c>
       <c r="B86" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9064,10 +9059,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500311</v>
+        <v>500242</v>
       </c>
       <c r="R86" t="n">
-        <v>6792502</v>
+        <v>6792408</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9100,6 +9095,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9126,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125889155</v>
+        <v>125892653</v>
       </c>
       <c r="B87" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9137,21 +9137,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500275</v>
+        <v>500151</v>
       </c>
       <c r="R87" t="n">
-        <v>6792487</v>
+        <v>6792458</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9320,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125892215</v>
+        <v>125895109</v>
       </c>
       <c r="B89" t="n">
-        <v>79556</v>
+        <v>79585</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,21 +9331,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500158</v>
+        <v>499985</v>
       </c>
       <c r="R89" t="n">
-        <v>6792441</v>
+        <v>6792633</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125894466</v>
+        <v>125896683</v>
       </c>
       <c r="B90" t="n">
         <v>8447</v>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R90" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9514,7 +9514,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125896683</v>
+        <v>125894466</v>
       </c>
       <c r="B91" t="n">
         <v>8447</v>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>500384</v>
+        <v>500128</v>
       </c>
       <c r="R91" t="n">
-        <v>6792529</v>
+        <v>6792590</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9611,7 +9611,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125895107</v>
+        <v>125889879</v>
       </c>
       <c r="B92" t="n">
         <v>78726</v>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>499985</v>
+        <v>500237</v>
       </c>
       <c r="R92" t="n">
-        <v>6792633</v>
+        <v>6792422</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,32 +9708,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125888352</v>
+        <v>125895107</v>
       </c>
       <c r="B93" t="n">
-        <v>8447</v>
+        <v>78726</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>500310</v>
+        <v>499985</v>
       </c>
       <c r="R93" t="n">
-        <v>6792516</v>
+        <v>6792633</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125889879</v>
+        <v>125889889</v>
       </c>
       <c r="B94" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9902,32 +9902,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125889889</v>
+        <v>125888352</v>
       </c>
       <c r="B95" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>500237</v>
+        <v>500310</v>
       </c>
       <c r="R95" t="n">
-        <v>6792422</v>
+        <v>6792516</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10096,32 +10096,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125890971</v>
+        <v>125889556</v>
       </c>
       <c r="B97" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>500282</v>
+        <v>500218</v>
       </c>
       <c r="R97" t="n">
-        <v>6792389</v>
+        <v>6792438</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10193,32 +10193,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125889556</v>
+        <v>125890971</v>
       </c>
       <c r="B98" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>500218</v>
+        <v>500282</v>
       </c>
       <c r="R98" t="n">
-        <v>6792438</v>
+        <v>6792389</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10290,7 +10290,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125894957</v>
+        <v>125889725</v>
       </c>
       <c r="B99" t="n">
         <v>8447</v>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>500037</v>
+        <v>500234</v>
       </c>
       <c r="R99" t="n">
-        <v>6792660</v>
+        <v>6792439</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10387,32 +10387,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125892219</v>
+        <v>125894957</v>
       </c>
       <c r="B100" t="n">
-        <v>78726</v>
+        <v>8447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>500158</v>
+        <v>500037</v>
       </c>
       <c r="R100" t="n">
-        <v>6792441</v>
+        <v>6792660</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10484,32 +10484,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125889725</v>
+        <v>125893327</v>
       </c>
       <c r="B101" t="n">
-        <v>8447</v>
+        <v>78726</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>500234</v>
+        <v>500271</v>
       </c>
       <c r="R101" t="n">
-        <v>6792439</v>
+        <v>6792529</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10581,7 +10581,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125893327</v>
+        <v>125892219</v>
       </c>
       <c r="B102" t="n">
         <v>78726</v>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>500271</v>
+        <v>500158</v>
       </c>
       <c r="R102" t="n">
-        <v>6792529</v>
+        <v>6792441</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10775,10 +10775,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125891964</v>
+        <v>125896058</v>
       </c>
       <c r="B104" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500111</v>
+        <v>500351</v>
       </c>
       <c r="R104" t="n">
-        <v>6792428</v>
+        <v>6792369</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,6 +10846,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10872,32 +10877,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125889615</v>
+        <v>125891964</v>
       </c>
       <c r="B105" t="n">
-        <v>8447</v>
+        <v>79585</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10907,10 +10912,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500202</v>
+        <v>500111</v>
       </c>
       <c r="R105" t="n">
-        <v>6792435</v>
+        <v>6792428</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10969,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125896058</v>
+        <v>125889615</v>
       </c>
       <c r="B106" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11004,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500351</v>
+        <v>500202</v>
       </c>
       <c r="R106" t="n">
-        <v>6792369</v>
+        <v>6792435</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11040,11 +11045,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11071,32 +11071,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125893643</v>
+        <v>125892433</v>
       </c>
       <c r="B107" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500237</v>
+        <v>500160</v>
       </c>
       <c r="R107" t="n">
-        <v>6792567</v>
+        <v>6792451</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11270,10 +11270,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125896524</v>
+        <v>125889496</v>
       </c>
       <c r="B109" t="n">
-        <v>79585</v>
+        <v>57648</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11281,34 +11281,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500384</v>
+        <v>500257</v>
       </c>
       <c r="R109" t="n">
-        <v>6792529</v>
+        <v>6792475</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11367,30 +11372,34 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125894266</v>
+        <v>125896524</v>
       </c>
       <c r="B110" t="n">
-        <v>98244</v>
+        <v>79585</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223597</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11398,10 +11407,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R110" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11460,10 +11469,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125889496</v>
+        <v>125889090</v>
       </c>
       <c r="B111" t="n">
-        <v>57648</v>
+        <v>79585</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11471,39 +11480,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500257</v>
+        <v>500285</v>
       </c>
       <c r="R111" t="n">
-        <v>6792475</v>
+        <v>6792489</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11562,34 +11566,30 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125889090</v>
+        <v>125894266</v>
       </c>
       <c r="B112" t="n">
-        <v>79585</v>
+        <v>98251</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>223597</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11597,10 +11597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500285</v>
+        <v>500128</v>
       </c>
       <c r="R112" t="n">
-        <v>6792489</v>
+        <v>6792590</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11659,32 +11659,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125892433</v>
+        <v>125893643</v>
       </c>
       <c r="B113" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500160</v>
+        <v>500237</v>
       </c>
       <c r="R113" t="n">
-        <v>6792451</v>
+        <v>6792567</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,32 +11756,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125892154</v>
+        <v>125896458</v>
       </c>
       <c r="B114" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500145</v>
+        <v>500374</v>
       </c>
       <c r="R114" t="n">
-        <v>6792446</v>
+        <v>6792515</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11853,32 +11853,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125890126</v>
+        <v>125889235</v>
       </c>
       <c r="B115" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500242</v>
+        <v>500275</v>
       </c>
       <c r="R115" t="n">
-        <v>6792408</v>
+        <v>6792487</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11950,32 +11950,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125896458</v>
+        <v>125890126</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>79585</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500374</v>
+        <v>500242</v>
       </c>
       <c r="R116" t="n">
-        <v>6792515</v>
+        <v>6792408</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12047,32 +12047,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125889235</v>
+        <v>125893637</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500275</v>
+        <v>500246</v>
       </c>
       <c r="R117" t="n">
-        <v>6792487</v>
+        <v>6792558</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12118,6 +12118,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12144,10 +12149,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125894500</v>
+        <v>125892154</v>
       </c>
       <c r="B118" t="n">
-        <v>78725</v>
+        <v>79585</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12155,21 +12160,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12179,10 +12184,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>500128</v>
+        <v>500145</v>
       </c>
       <c r="R118" t="n">
-        <v>6792590</v>
+        <v>6792446</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12241,10 +12246,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125893637</v>
+        <v>125894500</v>
       </c>
       <c r="B119" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12252,21 +12257,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12276,10 +12281,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>500246</v>
+        <v>500128</v>
       </c>
       <c r="R119" t="n">
-        <v>6792558</v>
+        <v>6792590</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12312,11 +12317,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125888695</v>
+        <v>125893148</v>
       </c>
       <c r="B120" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500311</v>
+        <v>500251</v>
       </c>
       <c r="R120" t="n">
-        <v>6792502</v>
+        <v>6792496</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,11 +12414,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12542,32 +12537,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12577,10 +12572,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R122" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12613,6 +12608,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12741,45 +12741,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125891471</v>
+        <v>125896030</v>
       </c>
       <c r="B124" t="n">
-        <v>8447</v>
+        <v>57651</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500181</v>
+        <v>500351</v>
       </c>
       <c r="R124" t="n">
-        <v>6792401</v>
+        <v>6792369</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12838,10 +12843,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125892207</v>
+        <v>125896611</v>
       </c>
       <c r="B125" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12849,21 +12854,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12873,10 +12878,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500158</v>
+        <v>500384</v>
       </c>
       <c r="R125" t="n">
-        <v>6792441</v>
+        <v>6792529</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12909,6 +12914,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12935,10 +12945,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125896611</v>
+        <v>125892207</v>
       </c>
       <c r="B126" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12946,21 +12956,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12970,10 +12980,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500384</v>
+        <v>500158</v>
       </c>
       <c r="R126" t="n">
-        <v>6792529</v>
+        <v>6792441</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13006,11 +13016,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13037,50 +13042,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125896030</v>
+        <v>125891471</v>
       </c>
       <c r="B127" t="n">
-        <v>57651</v>
+        <v>8447</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500351</v>
+        <v>500181</v>
       </c>
       <c r="R127" t="n">
-        <v>6792369</v>
+        <v>6792401</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13236,10 +13236,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125892025</v>
+        <v>125894564</v>
       </c>
       <c r="B129" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13247,21 +13247,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13271,10 +13271,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>500111</v>
+        <v>500128</v>
       </c>
       <c r="R129" t="n">
-        <v>6792428</v>
+        <v>6792590</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13307,11 +13307,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13338,10 +13333,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125894564</v>
+        <v>125892025</v>
       </c>
       <c r="B130" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13349,21 +13344,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13373,10 +13368,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>500128</v>
+        <v>500111</v>
       </c>
       <c r="R130" t="n">
-        <v>6792590</v>
+        <v>6792428</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13409,6 +13404,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13537,7 +13537,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125891649</v>
+        <v>125893307</v>
       </c>
       <c r="B132" t="n">
         <v>79585</v>
@@ -13572,10 +13572,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500166</v>
+        <v>500271</v>
       </c>
       <c r="R132" t="n">
-        <v>6792387</v>
+        <v>6792529</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13634,32 +13634,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125890887</v>
+        <v>125891649</v>
       </c>
       <c r="B133" t="n">
-        <v>8447</v>
+        <v>79585</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13669,10 +13669,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500282</v>
+        <v>500166</v>
       </c>
       <c r="R133" t="n">
-        <v>6792389</v>
+        <v>6792387</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13731,32 +13731,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125893307</v>
+        <v>125890887</v>
       </c>
       <c r="B134" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500271</v>
+        <v>500282</v>
       </c>
       <c r="R134" t="n">
-        <v>6792529</v>
+        <v>6792389</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125889379</v>
+        <v>125896454</v>
       </c>
       <c r="B140" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500257</v>
+        <v>500374</v>
       </c>
       <c r="R140" t="n">
-        <v>6792475</v>
+        <v>6792515</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14384,6 +14384,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14512,10 +14517,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125892160</v>
+        <v>125896535</v>
       </c>
       <c r="B142" t="n">
-        <v>79556</v>
+        <v>78726</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14523,21 +14528,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14547,10 +14552,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>500145</v>
+        <v>500384</v>
       </c>
       <c r="R142" t="n">
-        <v>6792446</v>
+        <v>6792529</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14609,7 +14614,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125896535</v>
+        <v>125889379</v>
       </c>
       <c r="B143" t="n">
         <v>78726</v>
@@ -14644,10 +14649,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500384</v>
+        <v>500257</v>
       </c>
       <c r="R143" t="n">
-        <v>6792529</v>
+        <v>6792475</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14803,10 +14808,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125896454</v>
+        <v>125892643</v>
       </c>
       <c r="B145" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14814,21 +14819,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14838,10 +14843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500374</v>
+        <v>500151</v>
       </c>
       <c r="R145" t="n">
-        <v>6792515</v>
+        <v>6792458</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14874,11 +14879,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14905,7 +14905,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125892643</v>
+        <v>125892160</v>
       </c>
       <c r="B146" t="n">
         <v>79556</v>
@@ -14940,10 +14940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500151</v>
+        <v>500145</v>
       </c>
       <c r="R146" t="n">
-        <v>6792458</v>
+        <v>6792446</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15002,10 +15002,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125891864</v>
+        <v>125888369</v>
       </c>
       <c r="B147" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15013,34 +15013,39 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500126</v>
+        <v>500310</v>
       </c>
       <c r="R147" t="n">
-        <v>6792397</v>
+        <v>6792516</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15073,11 +15078,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15107,7 +15107,7 @@
         <v>125896772</v>
       </c>
       <c r="B148" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15201,10 +15201,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125888369</v>
+        <v>125891864</v>
       </c>
       <c r="B149" t="n">
-        <v>57648</v>
+        <v>78967</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15212,39 +15212,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500310</v>
+        <v>500126</v>
       </c>
       <c r="R149" t="n">
-        <v>6792516</v>
+        <v>6792397</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15277,6 +15272,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15303,32 +15303,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125888908</v>
+        <v>125892001</v>
       </c>
       <c r="B150" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15338,10 +15338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500306</v>
+        <v>500111</v>
       </c>
       <c r="R150" t="n">
-        <v>6792466</v>
+        <v>6792428</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15400,32 +15400,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125892001</v>
+        <v>125888908</v>
       </c>
       <c r="B151" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15435,10 +15435,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500111</v>
+        <v>500306</v>
       </c>
       <c r="R151" t="n">
-        <v>6792428</v>
+        <v>6792466</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15497,10 +15497,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125891609</v>
+        <v>125889396</v>
       </c>
       <c r="B152" t="n">
-        <v>78726</v>
+        <v>79556</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15508,21 +15508,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500153</v>
+        <v>500257</v>
       </c>
       <c r="R152" t="n">
-        <v>6792391</v>
+        <v>6792475</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15691,10 +15691,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125889396</v>
+        <v>125891609</v>
       </c>
       <c r="B154" t="n">
-        <v>79556</v>
+        <v>78726</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15702,21 +15702,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500257</v>
+        <v>500153</v>
       </c>
       <c r="R154" t="n">
-        <v>6792475</v>
+        <v>6792391</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15788,32 +15788,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125888924</v>
+        <v>125895017</v>
       </c>
       <c r="B155" t="n">
-        <v>78726</v>
+        <v>78991</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15823,10 +15823,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>500306</v>
+        <v>499985</v>
       </c>
       <c r="R155" t="n">
-        <v>6792466</v>
+        <v>6792633</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15982,32 +15982,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125895017</v>
+        <v>125888924</v>
       </c>
       <c r="B157" t="n">
-        <v>78991</v>
+        <v>78726</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16017,10 +16017,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>499985</v>
+        <v>500306</v>
       </c>
       <c r="R157" t="n">
-        <v>6792633</v>
+        <v>6792466</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16184,7 +16184,7 @@
         <v>125892942</v>
       </c>
       <c r="B159" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -3406,32 +3406,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125686343</v>
+        <v>125683895</v>
       </c>
       <c r="B29" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499963</v>
+        <v>500326</v>
       </c>
       <c r="R29" t="n">
-        <v>6792480</v>
+        <v>6792440</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3477,6 +3477,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3503,10 +3508,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125685148</v>
+        <v>125686305</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,21 +3519,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3538,10 +3543,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500040</v>
+        <v>499963</v>
       </c>
       <c r="R30" t="n">
-        <v>6792406</v>
+        <v>6792480</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3574,6 +3579,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3600,32 +3610,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125683895</v>
+        <v>125693249</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3635,10 +3645,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500326</v>
+        <v>500047</v>
       </c>
       <c r="R31" t="n">
-        <v>6792440</v>
+        <v>6792612</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3671,11 +3681,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3702,10 +3707,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125686305</v>
+        <v>125686343</v>
       </c>
       <c r="B32" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3713,21 +3718,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3773,11 +3778,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3804,10 +3804,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125693249</v>
+        <v>125685148</v>
       </c>
       <c r="B33" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3815,21 +3815,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500047</v>
+        <v>500040</v>
       </c>
       <c r="R33" t="n">
-        <v>6792612</v>
+        <v>6792406</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3998,10 +3998,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125684693</v>
+        <v>125685808</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500077</v>
+        <v>499996</v>
       </c>
       <c r="R35" t="n">
-        <v>6792400</v>
+        <v>6792435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4069,6 +4069,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,10 +4100,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125685808</v>
+        <v>125684693</v>
       </c>
       <c r="B36" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4106,21 +4111,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4130,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499996</v>
+        <v>500077</v>
       </c>
       <c r="R36" t="n">
-        <v>6792435</v>
+        <v>6792400</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4166,11 +4171,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5978,10 +5978,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685885</v>
+        <v>125685813</v>
       </c>
       <c r="B55" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5989,21 +5989,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>500002</v>
+        <v>499996</v>
       </c>
       <c r="R55" t="n">
-        <v>6792449</v>
+        <v>6792435</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6075,32 +6075,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125690170</v>
+        <v>125683878</v>
       </c>
       <c r="B56" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6110,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>500018</v>
+        <v>499954</v>
       </c>
       <c r="R56" t="n">
-        <v>6792528</v>
+        <v>6792394</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6146,6 +6146,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6172,32 +6177,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125683878</v>
+        <v>125685885</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6207,10 +6212,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499954</v>
+        <v>500002</v>
       </c>
       <c r="R57" t="n">
-        <v>6792394</v>
+        <v>6792449</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6243,11 +6248,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125685813</v>
+        <v>125690170</v>
       </c>
       <c r="B58" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499996</v>
+        <v>500018</v>
       </c>
       <c r="R58" t="n">
-        <v>6792435</v>
+        <v>6792528</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7855,32 +7855,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125893261</v>
+        <v>125890092</v>
       </c>
       <c r="B74" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500271</v>
+        <v>500242</v>
       </c>
       <c r="R74" t="n">
-        <v>6792529</v>
+        <v>6792408</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7952,32 +7952,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125896279</v>
+        <v>125891809</v>
       </c>
       <c r="B75" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>500351</v>
+        <v>500166</v>
       </c>
       <c r="R75" t="n">
-        <v>6792369</v>
+        <v>6792387</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125895125</v>
+        <v>125893261</v>
       </c>
       <c r="B76" t="n">
         <v>8447</v>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>499985</v>
+        <v>500271</v>
       </c>
       <c r="R76" t="n">
-        <v>6792633</v>
+        <v>6792529</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125890234</v>
+        <v>125896279</v>
       </c>
       <c r="B77" t="n">
         <v>8447</v>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>500242</v>
+        <v>500351</v>
       </c>
       <c r="R77" t="n">
-        <v>6792408</v>
+        <v>6792369</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8243,32 +8243,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125890092</v>
+        <v>125895125</v>
       </c>
       <c r="B78" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>500242</v>
+        <v>499985</v>
       </c>
       <c r="R78" t="n">
-        <v>6792408</v>
+        <v>6792633</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8340,32 +8340,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125891809</v>
+        <v>125890234</v>
       </c>
       <c r="B79" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500166</v>
+        <v>500242</v>
       </c>
       <c r="R79" t="n">
-        <v>6792387</v>
+        <v>6792408</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8437,50 +8437,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125888740</v>
+        <v>125892266</v>
       </c>
       <c r="B80" t="n">
-        <v>57811</v>
+        <v>8447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500306</v>
+        <v>500158</v>
       </c>
       <c r="R80" t="n">
-        <v>6792466</v>
+        <v>6792441</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8539,10 +8534,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125889155</v>
+        <v>125890407</v>
       </c>
       <c r="B81" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8550,21 +8545,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8574,10 +8569,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500275</v>
+        <v>500242</v>
       </c>
       <c r="R81" t="n">
-        <v>6792487</v>
+        <v>6792408</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8610,6 +8605,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8636,10 +8636,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125891598</v>
+        <v>125892653</v>
       </c>
       <c r="B82" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8647,21 +8647,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500153</v>
+        <v>500151</v>
       </c>
       <c r="R82" t="n">
-        <v>6792391</v>
+        <v>6792458</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8733,32 +8733,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125892266</v>
+        <v>125889406</v>
       </c>
       <c r="B83" t="n">
-        <v>8447</v>
+        <v>79585</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>500158</v>
+        <v>500257</v>
       </c>
       <c r="R83" t="n">
-        <v>6792441</v>
+        <v>6792475</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8830,32 +8830,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125888709</v>
+        <v>125895109</v>
       </c>
       <c r="B84" t="n">
-        <v>8447</v>
+        <v>79585</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500311</v>
+        <v>499985</v>
       </c>
       <c r="R84" t="n">
-        <v>6792502</v>
+        <v>6792633</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8927,10 +8927,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125892215</v>
+        <v>125888740</v>
       </c>
       <c r="B85" t="n">
-        <v>79556</v>
+        <v>57811</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8938,34 +8938,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500158</v>
+        <v>500306</v>
       </c>
       <c r="R85" t="n">
-        <v>6792441</v>
+        <v>6792466</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9024,32 +9029,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125890407</v>
+        <v>125888709</v>
       </c>
       <c r="B86" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9059,10 +9064,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500242</v>
+        <v>500311</v>
       </c>
       <c r="R86" t="n">
-        <v>6792408</v>
+        <v>6792502</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9095,11 +9100,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9126,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125892653</v>
+        <v>125891598</v>
       </c>
       <c r="B87" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9137,21 +9137,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500151</v>
+        <v>500153</v>
       </c>
       <c r="R87" t="n">
-        <v>6792458</v>
+        <v>6792391</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125889406</v>
+        <v>125892215</v>
       </c>
       <c r="B88" t="n">
-        <v>79585</v>
+        <v>79556</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9234,21 +9234,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9258,10 +9258,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500257</v>
+        <v>500158</v>
       </c>
       <c r="R88" t="n">
-        <v>6792475</v>
+        <v>6792441</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9320,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125895109</v>
+        <v>125889155</v>
       </c>
       <c r="B89" t="n">
-        <v>79585</v>
+        <v>79556</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,21 +9331,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>499985</v>
+        <v>500275</v>
       </c>
       <c r="R89" t="n">
-        <v>6792633</v>
+        <v>6792487</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125892224</v>
+        <v>125889615</v>
       </c>
       <c r="B103" t="n">
-        <v>78725</v>
+        <v>8447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500158</v>
+        <v>500202</v>
       </c>
       <c r="R103" t="n">
-        <v>6792441</v>
+        <v>6792435</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10775,10 +10775,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125896058</v>
+        <v>125892224</v>
       </c>
       <c r="B104" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500351</v>
+        <v>500158</v>
       </c>
       <c r="R104" t="n">
-        <v>6792369</v>
+        <v>6792441</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,11 +10846,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10877,10 +10872,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125891964</v>
+        <v>125896058</v>
       </c>
       <c r="B105" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10888,21 +10883,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10912,10 +10907,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500111</v>
+        <v>500351</v>
       </c>
       <c r="R105" t="n">
-        <v>6792428</v>
+        <v>6792369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10948,6 +10943,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125889615</v>
+        <v>125891964</v>
       </c>
       <c r="B106" t="n">
-        <v>8447</v>
+        <v>79585</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500202</v>
+        <v>500111</v>
       </c>
       <c r="R106" t="n">
-        <v>6792435</v>
+        <v>6792428</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125892433</v>
+        <v>125896426</v>
       </c>
       <c r="B107" t="n">
-        <v>79556</v>
+        <v>57648</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11082,34 +11082,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500160</v>
+        <v>500351</v>
       </c>
       <c r="R107" t="n">
-        <v>6792451</v>
+        <v>6792369</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11168,7 +11173,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125896426</v>
+        <v>125889496</v>
       </c>
       <c r="B108" t="n">
         <v>57648</v>
@@ -11199,7 +11204,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -11208,10 +11213,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500351</v>
+        <v>500257</v>
       </c>
       <c r="R108" t="n">
-        <v>6792369</v>
+        <v>6792475</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11270,10 +11275,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125889496</v>
+        <v>125896524</v>
       </c>
       <c r="B109" t="n">
-        <v>57648</v>
+        <v>79585</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11281,39 +11286,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500257</v>
+        <v>500384</v>
       </c>
       <c r="R109" t="n">
-        <v>6792475</v>
+        <v>6792529</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11372,7 +11372,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125896524</v>
+        <v>125889090</v>
       </c>
       <c r="B110" t="n">
         <v>79585</v>
@@ -11407,10 +11407,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500384</v>
+        <v>500285</v>
       </c>
       <c r="R110" t="n">
-        <v>6792529</v>
+        <v>6792489</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11469,32 +11469,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125889090</v>
+        <v>125893643</v>
       </c>
       <c r="B111" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11504,10 +11504,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500285</v>
+        <v>500237</v>
       </c>
       <c r="R111" t="n">
-        <v>6792489</v>
+        <v>6792567</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11659,32 +11659,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125893643</v>
+        <v>125892433</v>
       </c>
       <c r="B113" t="n">
-        <v>8447</v>
+        <v>79556</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500237</v>
+        <v>500160</v>
       </c>
       <c r="R113" t="n">
-        <v>6792567</v>
+        <v>6792451</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,32 +11756,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125896458</v>
+        <v>125890126</v>
       </c>
       <c r="B114" t="n">
-        <v>8447</v>
+        <v>79585</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500374</v>
+        <v>500242</v>
       </c>
       <c r="R114" t="n">
-        <v>6792515</v>
+        <v>6792408</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11853,32 +11853,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125889235</v>
+        <v>125893637</v>
       </c>
       <c r="B115" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500275</v>
+        <v>500246</v>
       </c>
       <c r="R115" t="n">
-        <v>6792487</v>
+        <v>6792558</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11924,6 +11924,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11950,7 +11955,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125890126</v>
+        <v>125892154</v>
       </c>
       <c r="B116" t="n">
         <v>79585</v>
@@ -11985,10 +11990,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500242</v>
+        <v>500145</v>
       </c>
       <c r="R116" t="n">
-        <v>6792408</v>
+        <v>6792446</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12047,10 +12052,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125893637</v>
+        <v>125894500</v>
       </c>
       <c r="B117" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12058,21 +12063,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12082,10 +12087,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500246</v>
+        <v>500128</v>
       </c>
       <c r="R117" t="n">
-        <v>6792558</v>
+        <v>6792590</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12118,11 +12123,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12149,32 +12149,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125892154</v>
+        <v>125896458</v>
       </c>
       <c r="B118" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12184,10 +12184,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>500145</v>
+        <v>500374</v>
       </c>
       <c r="R118" t="n">
-        <v>6792446</v>
+        <v>6792515</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12246,32 +12246,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125894500</v>
+        <v>125889235</v>
       </c>
       <c r="B119" t="n">
-        <v>78725</v>
+        <v>8447</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>500128</v>
+        <v>500275</v>
       </c>
       <c r="R119" t="n">
-        <v>6792590</v>
+        <v>6792487</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13435,50 +13435,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125891498</v>
+        <v>125890887</v>
       </c>
       <c r="B131" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>500166</v>
+        <v>500282</v>
       </c>
       <c r="R131" t="n">
-        <v>6792413</v>
+        <v>6792389</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13537,32 +13532,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125893307</v>
+        <v>125893186</v>
       </c>
       <c r="B132" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13572,10 +13567,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500271</v>
+        <v>500247</v>
       </c>
       <c r="R132" t="n">
-        <v>6792529</v>
+        <v>6792519</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13634,10 +13629,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125891649</v>
+        <v>125892751</v>
       </c>
       <c r="B133" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13645,21 +13640,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13669,10 +13664,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500166</v>
+        <v>500151</v>
       </c>
       <c r="R133" t="n">
-        <v>6792387</v>
+        <v>6792458</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13731,45 +13726,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125890887</v>
+        <v>125891498</v>
       </c>
       <c r="B134" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500282</v>
+        <v>500166</v>
       </c>
       <c r="R134" t="n">
-        <v>6792389</v>
+        <v>6792413</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13828,32 +13828,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125893186</v>
+        <v>125893307</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>79585</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13863,10 +13863,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500247</v>
+        <v>500271</v>
       </c>
       <c r="R135" t="n">
-        <v>6792519</v>
+        <v>6792529</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13925,10 +13925,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125892751</v>
+        <v>125891649</v>
       </c>
       <c r="B136" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13936,21 +13936,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13960,10 +13960,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500151</v>
+        <v>500166</v>
       </c>
       <c r="R136" t="n">
-        <v>6792458</v>
+        <v>6792387</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125896454</v>
+        <v>125892643</v>
       </c>
       <c r="B140" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500374</v>
+        <v>500151</v>
       </c>
       <c r="R140" t="n">
-        <v>6792515</v>
+        <v>6792458</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14384,11 +14384,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14415,10 +14410,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125889266</v>
+        <v>125892160</v>
       </c>
       <c r="B141" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14426,21 +14421,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14450,10 +14445,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R141" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14486,11 +14481,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14808,10 +14798,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125892643</v>
+        <v>125896454</v>
       </c>
       <c r="B145" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14819,21 +14809,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14843,10 +14833,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500151</v>
+        <v>500374</v>
       </c>
       <c r="R145" t="n">
-        <v>6792458</v>
+        <v>6792515</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14879,6 +14869,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14905,10 +14900,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125892160</v>
+        <v>125889266</v>
       </c>
       <c r="B146" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14916,21 +14911,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14940,10 +14935,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R146" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14976,6 +14971,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15497,32 +15497,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125889396</v>
+        <v>125888498</v>
       </c>
       <c r="B152" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500257</v>
+        <v>500311</v>
       </c>
       <c r="R152" t="n">
-        <v>6792475</v>
+        <v>6792509</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15594,32 +15594,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125888498</v>
+        <v>125891609</v>
       </c>
       <c r="B153" t="n">
-        <v>8447</v>
+        <v>78726</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15629,10 +15629,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500311</v>
+        <v>500153</v>
       </c>
       <c r="R153" t="n">
-        <v>6792509</v>
+        <v>6792391</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15691,10 +15691,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125891609</v>
+        <v>125889396</v>
       </c>
       <c r="B154" t="n">
-        <v>78726</v>
+        <v>79556</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15702,21 +15702,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500153</v>
+        <v>500257</v>
       </c>
       <c r="R154" t="n">
-        <v>6792391</v>
+        <v>6792475</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -2503,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125684537</v>
+        <v>125690007</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500039</v>
+        <v>499989</v>
       </c>
       <c r="R20" t="n">
-        <v>6792388</v>
+        <v>6792563</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125690007</v>
+        <v>125684537</v>
       </c>
       <c r="B21" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499989</v>
+        <v>500039</v>
       </c>
       <c r="R21" t="n">
-        <v>6792563</v>
+        <v>6792388</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3901,32 +3901,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125687329</v>
+        <v>125684693</v>
       </c>
       <c r="B34" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499947</v>
+        <v>500077</v>
       </c>
       <c r="R34" t="n">
-        <v>6792525</v>
+        <v>6792400</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3998,32 +3998,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125685808</v>
+        <v>125687329</v>
       </c>
       <c r="B35" t="n">
-        <v>78726</v>
+        <v>8447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499996</v>
+        <v>499947</v>
       </c>
       <c r="R35" t="n">
-        <v>6792435</v>
+        <v>6792525</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4069,11 +4069,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4100,10 +4095,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125684693</v>
+        <v>125685808</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4111,21 +4106,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4135,10 +4130,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500077</v>
+        <v>499996</v>
       </c>
       <c r="R36" t="n">
-        <v>6792400</v>
+        <v>6792435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4171,6 +4166,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5085,32 +5085,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125686463</v>
+        <v>125685110</v>
       </c>
       <c r="B46" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499969</v>
+        <v>500063</v>
       </c>
       <c r="R46" t="n">
-        <v>6792489</v>
+        <v>6792423</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5156,6 +5156,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5182,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125690957</v>
+        <v>125689757</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5193,21 +5198,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5217,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>500003</v>
+        <v>499951</v>
       </c>
       <c r="R47" t="n">
-        <v>6792577</v>
+        <v>6792574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5253,6 +5258,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5279,32 +5289,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125685110</v>
+        <v>125686463</v>
       </c>
       <c r="B48" t="n">
-        <v>8447</v>
+        <v>79585</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5314,10 +5324,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>500063</v>
+        <v>499969</v>
       </c>
       <c r="R48" t="n">
-        <v>6792423</v>
+        <v>6792489</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5350,11 +5360,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5381,10 +5386,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125689757</v>
+        <v>125690957</v>
       </c>
       <c r="B49" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,21 +5397,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5421,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499951</v>
+        <v>500003</v>
       </c>
       <c r="R49" t="n">
-        <v>6792574</v>
+        <v>6792577</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5452,11 +5457,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7266,7 +7266,7 @@
         <v>125888195</v>
       </c>
       <c r="B68" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>125889107</v>
       </c>
       <c r="B72" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7758,32 +7758,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125890555</v>
+        <v>125893261</v>
       </c>
       <c r="B73" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>500282</v>
+        <v>500271</v>
       </c>
       <c r="R73" t="n">
-        <v>6792389</v>
+        <v>6792529</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7855,32 +7855,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125890092</v>
+        <v>125896279</v>
       </c>
       <c r="B74" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500242</v>
+        <v>500351</v>
       </c>
       <c r="R74" t="n">
-        <v>6792408</v>
+        <v>6792369</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7952,32 +7952,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125891809</v>
+        <v>125895125</v>
       </c>
       <c r="B75" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>500166</v>
+        <v>499985</v>
       </c>
       <c r="R75" t="n">
-        <v>6792387</v>
+        <v>6792633</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125893261</v>
+        <v>125890234</v>
       </c>
       <c r="B76" t="n">
         <v>8447</v>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>500271</v>
+        <v>500242</v>
       </c>
       <c r="R76" t="n">
-        <v>6792529</v>
+        <v>6792408</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8146,32 +8146,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125896279</v>
+        <v>125890092</v>
       </c>
       <c r="B77" t="n">
-        <v>8447</v>
+        <v>79557</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>500351</v>
+        <v>500242</v>
       </c>
       <c r="R77" t="n">
-        <v>6792369</v>
+        <v>6792408</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8243,32 +8243,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125895125</v>
+        <v>125891809</v>
       </c>
       <c r="B78" t="n">
-        <v>8447</v>
+        <v>79557</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>499985</v>
+        <v>500166</v>
       </c>
       <c r="R78" t="n">
-        <v>6792633</v>
+        <v>6792387</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8340,32 +8340,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125890234</v>
+        <v>125890555</v>
       </c>
       <c r="B79" t="n">
-        <v>8447</v>
+        <v>79586</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500242</v>
+        <v>500282</v>
       </c>
       <c r="R79" t="n">
-        <v>6792408</v>
+        <v>6792389</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8437,32 +8437,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125892266</v>
+        <v>125889406</v>
       </c>
       <c r="B80" t="n">
-        <v>8447</v>
+        <v>79586</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8472,10 +8472,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500158</v>
+        <v>500257</v>
       </c>
       <c r="R80" t="n">
-        <v>6792441</v>
+        <v>6792475</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8534,10 +8534,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125890407</v>
+        <v>125895109</v>
       </c>
       <c r="B81" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8545,21 +8545,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500242</v>
+        <v>499985</v>
       </c>
       <c r="R81" t="n">
-        <v>6792408</v>
+        <v>6792633</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8605,11 +8605,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8636,10 +8631,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125892653</v>
+        <v>125890407</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8671,10 +8666,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500151</v>
+        <v>500242</v>
       </c>
       <c r="R82" t="n">
-        <v>6792458</v>
+        <v>6792408</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8707,6 +8702,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8733,10 +8733,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125889406</v>
+        <v>125892653</v>
       </c>
       <c r="B83" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8744,21 +8744,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>500257</v>
+        <v>500151</v>
       </c>
       <c r="R83" t="n">
-        <v>6792475</v>
+        <v>6792458</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8830,10 +8830,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125895109</v>
+        <v>125888740</v>
       </c>
       <c r="B84" t="n">
-        <v>79585</v>
+        <v>57811</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8841,34 +8841,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>499985</v>
+        <v>500306</v>
       </c>
       <c r="R84" t="n">
-        <v>6792633</v>
+        <v>6792466</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8927,50 +8932,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125888740</v>
+        <v>125888709</v>
       </c>
       <c r="B85" t="n">
-        <v>57811</v>
+        <v>8447</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500306</v>
+        <v>500311</v>
       </c>
       <c r="R85" t="n">
-        <v>6792466</v>
+        <v>6792502</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9029,7 +9029,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125888709</v>
+        <v>125892266</v>
       </c>
       <c r="B86" t="n">
         <v>8447</v>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500311</v>
+        <v>500158</v>
       </c>
       <c r="R86" t="n">
-        <v>6792502</v>
+        <v>6792441</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9126,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125891598</v>
+        <v>125892215</v>
       </c>
       <c r="B87" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500153</v>
+        <v>500158</v>
       </c>
       <c r="R87" t="n">
-        <v>6792391</v>
+        <v>6792441</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125892215</v>
+        <v>125889155</v>
       </c>
       <c r="B88" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9258,10 +9258,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500158</v>
+        <v>500275</v>
       </c>
       <c r="R88" t="n">
-        <v>6792441</v>
+        <v>6792487</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9320,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125889155</v>
+        <v>125891598</v>
       </c>
       <c r="B89" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500275</v>
+        <v>500153</v>
       </c>
       <c r="R89" t="n">
-        <v>6792487</v>
+        <v>6792391</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9611,32 +9611,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125889879</v>
+        <v>125888352</v>
       </c>
       <c r="B92" t="n">
-        <v>78726</v>
+        <v>8447</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>500237</v>
+        <v>500310</v>
       </c>
       <c r="R92" t="n">
-        <v>6792422</v>
+        <v>6792516</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125895107</v>
+        <v>125896400</v>
       </c>
       <c r="B93" t="n">
-        <v>78726</v>
+        <v>79557</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,21 +9719,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>499985</v>
+        <v>500351</v>
       </c>
       <c r="R93" t="n">
-        <v>6792633</v>
+        <v>6792369</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125889889</v>
+        <v>125889879</v>
       </c>
       <c r="B94" t="n">
-        <v>79585</v>
+        <v>78727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9902,32 +9902,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125888352</v>
+        <v>125895107</v>
       </c>
       <c r="B95" t="n">
-        <v>8447</v>
+        <v>78727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>500310</v>
+        <v>499985</v>
       </c>
       <c r="R95" t="n">
-        <v>6792516</v>
+        <v>6792633</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,10 +9999,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125896400</v>
+        <v>125889889</v>
       </c>
       <c r="B96" t="n">
-        <v>79556</v>
+        <v>79586</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>500351</v>
+        <v>500237</v>
       </c>
       <c r="R96" t="n">
-        <v>6792369</v>
+        <v>6792422</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10196,7 +10196,7 @@
         <v>125890971</v>
       </c>
       <c r="B98" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>125893327</v>
       </c>
       <c r="B101" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>125892219</v>
       </c>
       <c r="B102" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>125892224</v>
       </c>
       <c r="B104" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10872,10 +10872,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125896058</v>
+        <v>125891964</v>
       </c>
       <c r="B105" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10883,21 +10883,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10907,10 +10907,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500351</v>
+        <v>500111</v>
       </c>
       <c r="R105" t="n">
-        <v>6792369</v>
+        <v>6792428</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10943,11 +10943,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10974,10 +10969,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125891964</v>
+        <v>125896058</v>
       </c>
       <c r="B106" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10985,21 +10980,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11004,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500111</v>
+        <v>500351</v>
       </c>
       <c r="R106" t="n">
-        <v>6792428</v>
+        <v>6792369</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11045,6 +11040,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11071,10 +11071,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125896426</v>
+        <v>125896524</v>
       </c>
       <c r="B107" t="n">
-        <v>57648</v>
+        <v>79586</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11082,39 +11082,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500351</v>
+        <v>500384</v>
       </c>
       <c r="R107" t="n">
-        <v>6792369</v>
+        <v>6792529</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11173,50 +11168,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125889496</v>
+        <v>125893643</v>
       </c>
       <c r="B108" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500257</v>
+        <v>500237</v>
       </c>
       <c r="R108" t="n">
-        <v>6792475</v>
+        <v>6792567</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11275,10 +11265,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125896524</v>
+        <v>125896426</v>
       </c>
       <c r="B109" t="n">
-        <v>79585</v>
+        <v>57648</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11286,34 +11276,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500384</v>
+        <v>500351</v>
       </c>
       <c r="R109" t="n">
-        <v>6792529</v>
+        <v>6792369</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11372,10 +11367,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125889090</v>
+        <v>125889496</v>
       </c>
       <c r="B110" t="n">
-        <v>79585</v>
+        <v>57648</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11383,34 +11378,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500285</v>
+        <v>500257</v>
       </c>
       <c r="R110" t="n">
-        <v>6792489</v>
+        <v>6792475</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11469,32 +11469,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125893643</v>
+        <v>125889090</v>
       </c>
       <c r="B111" t="n">
-        <v>8447</v>
+        <v>79586</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11504,10 +11504,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500237</v>
+        <v>500285</v>
       </c>
       <c r="R111" t="n">
-        <v>6792567</v>
+        <v>6792489</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11569,7 +11569,7 @@
         <v>125894266</v>
       </c>
       <c r="B112" t="n">
-        <v>98251</v>
+        <v>98252</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>125892433</v>
       </c>
       <c r="B113" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>125890126</v>
       </c>
       <c r="B114" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11853,10 +11853,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125893637</v>
+        <v>125892154</v>
       </c>
       <c r="B115" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11864,21 +11864,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500246</v>
+        <v>500145</v>
       </c>
       <c r="R115" t="n">
-        <v>6792558</v>
+        <v>6792446</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11924,11 +11924,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11955,10 +11950,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125892154</v>
+        <v>125894500</v>
       </c>
       <c r="B116" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11966,21 +11961,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11990,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500145</v>
+        <v>500128</v>
       </c>
       <c r="R116" t="n">
-        <v>6792446</v>
+        <v>6792590</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12052,10 +12047,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125894500</v>
+        <v>125893637</v>
       </c>
       <c r="B117" t="n">
-        <v>78725</v>
+        <v>78968</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12063,21 +12058,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12087,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500128</v>
+        <v>500246</v>
       </c>
       <c r="R117" t="n">
-        <v>6792590</v>
+        <v>6792558</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12123,6 +12118,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B120" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R120" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,6 +12414,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12440,32 +12445,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125889503</v>
+        <v>125892496</v>
       </c>
       <c r="B121" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12475,10 +12480,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R121" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12511,6 +12516,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12537,32 +12547,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125888695</v>
+        <v>125893148</v>
       </c>
       <c r="B122" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12572,10 +12582,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500311</v>
+        <v>500251</v>
       </c>
       <c r="R122" t="n">
-        <v>6792502</v>
+        <v>6792496</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12608,11 +12618,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12639,32 +12644,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125892496</v>
+        <v>125889503</v>
       </c>
       <c r="B123" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12674,10 +12679,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R123" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12710,11 +12715,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12741,10 +12741,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125896030</v>
+        <v>125896611</v>
       </c>
       <c r="B124" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12752,39 +12752,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500351</v>
+        <v>500384</v>
       </c>
       <c r="R124" t="n">
-        <v>6792369</v>
+        <v>6792529</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12817,6 +12812,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12843,10 +12843,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125896611</v>
+        <v>125894132</v>
       </c>
       <c r="B125" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12854,21 +12854,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12878,10 +12878,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500384</v>
+        <v>500128</v>
       </c>
       <c r="R125" t="n">
-        <v>6792529</v>
+        <v>6792590</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12914,11 +12914,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12948,7 +12943,7 @@
         <v>125892207</v>
       </c>
       <c r="B126" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13042,45 +13037,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125891471</v>
+        <v>125896030</v>
       </c>
       <c r="B127" t="n">
-        <v>8447</v>
+        <v>57651</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500181</v>
+        <v>500351</v>
       </c>
       <c r="R127" t="n">
-        <v>6792401</v>
+        <v>6792369</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13139,32 +13139,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125894132</v>
+        <v>125891471</v>
       </c>
       <c r="B128" t="n">
-        <v>78726</v>
+        <v>8447</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13174,10 +13174,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>500128</v>
+        <v>500181</v>
       </c>
       <c r="R128" t="n">
-        <v>6792590</v>
+        <v>6792401</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13239,7 +13239,7 @@
         <v>125894564</v>
       </c>
       <c r="B129" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>125892025</v>
       </c>
       <c r="B130" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13435,32 +13435,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125890887</v>
+        <v>125893307</v>
       </c>
       <c r="B131" t="n">
-        <v>8447</v>
+        <v>79586</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>500282</v>
+        <v>500271</v>
       </c>
       <c r="R131" t="n">
-        <v>6792389</v>
+        <v>6792529</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13532,32 +13532,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125893186</v>
+        <v>125891649</v>
       </c>
       <c r="B132" t="n">
-        <v>8447</v>
+        <v>79586</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13567,10 +13567,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500247</v>
+        <v>500166</v>
       </c>
       <c r="R132" t="n">
-        <v>6792519</v>
+        <v>6792387</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13629,32 +13629,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125892751</v>
+        <v>125890887</v>
       </c>
       <c r="B133" t="n">
-        <v>78726</v>
+        <v>8447</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500151</v>
+        <v>500282</v>
       </c>
       <c r="R133" t="n">
-        <v>6792458</v>
+        <v>6792389</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13726,50 +13726,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125891498</v>
+        <v>125893186</v>
       </c>
       <c r="B134" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500166</v>
+        <v>500247</v>
       </c>
       <c r="R134" t="n">
-        <v>6792413</v>
+        <v>6792519</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13828,10 +13823,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125893307</v>
+        <v>125891498</v>
       </c>
       <c r="B135" t="n">
-        <v>79585</v>
+        <v>57648</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13839,34 +13834,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500271</v>
+        <v>500166</v>
       </c>
       <c r="R135" t="n">
-        <v>6792529</v>
+        <v>6792413</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13925,10 +13925,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125891649</v>
+        <v>125892751</v>
       </c>
       <c r="B136" t="n">
-        <v>79585</v>
+        <v>78727</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13936,21 +13936,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13960,10 +13960,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500166</v>
+        <v>500151</v>
       </c>
       <c r="R136" t="n">
-        <v>6792387</v>
+        <v>6792458</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14119,10 +14119,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125889010</v>
+        <v>125892352</v>
       </c>
       <c r="B138" t="n">
-        <v>78726</v>
+        <v>79557</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14130,21 +14130,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14154,10 +14154,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>500286</v>
+        <v>500165</v>
       </c>
       <c r="R138" t="n">
-        <v>6792459</v>
+        <v>6792432</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14216,10 +14216,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125892352</v>
+        <v>125889010</v>
       </c>
       <c r="B139" t="n">
-        <v>79556</v>
+        <v>78727</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14227,21 +14227,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>500165</v>
+        <v>500286</v>
       </c>
       <c r="R139" t="n">
-        <v>6792432</v>
+        <v>6792459</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125892643</v>
+        <v>125896454</v>
       </c>
       <c r="B140" t="n">
-        <v>79556</v>
+        <v>78968</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500151</v>
+        <v>500374</v>
       </c>
       <c r="R140" t="n">
-        <v>6792458</v>
+        <v>6792515</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14384,6 +14384,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14410,10 +14415,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125892160</v>
+        <v>125889266</v>
       </c>
       <c r="B141" t="n">
-        <v>79556</v>
+        <v>78968</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14421,21 +14426,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14445,10 +14450,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R141" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14481,6 +14486,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14510,7 +14520,7 @@
         <v>125896535</v>
       </c>
       <c r="B142" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14604,10 +14614,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125889379</v>
+        <v>125896642</v>
       </c>
       <c r="B143" t="n">
-        <v>78726</v>
+        <v>79557</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14615,21 +14625,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14639,10 +14649,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500257</v>
+        <v>500384</v>
       </c>
       <c r="R143" t="n">
-        <v>6792475</v>
+        <v>6792529</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14701,10 +14711,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125896642</v>
+        <v>125892643</v>
       </c>
       <c r="B144" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14736,10 +14746,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500384</v>
+        <v>500151</v>
       </c>
       <c r="R144" t="n">
-        <v>6792529</v>
+        <v>6792458</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14798,10 +14808,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125896454</v>
+        <v>125889379</v>
       </c>
       <c r="B145" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14809,21 +14819,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14833,10 +14843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500374</v>
+        <v>500257</v>
       </c>
       <c r="R145" t="n">
-        <v>6792515</v>
+        <v>6792475</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14869,11 +14879,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14900,10 +14905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125889266</v>
+        <v>125892160</v>
       </c>
       <c r="B146" t="n">
-        <v>78967</v>
+        <v>79557</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14911,21 +14916,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14935,10 +14940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R146" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14971,11 +14976,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15107,7 +15107,7 @@
         <v>125896772</v>
       </c>
       <c r="B148" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>125891864</v>
       </c>
       <c r="B149" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>125888908</v>
       </c>
       <c r="B151" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15497,32 +15497,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125888498</v>
+        <v>125889396</v>
       </c>
       <c r="B152" t="n">
-        <v>8447</v>
+        <v>79557</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500311</v>
+        <v>500257</v>
       </c>
       <c r="R152" t="n">
-        <v>6792509</v>
+        <v>6792475</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15597,7 +15597,7 @@
         <v>125891609</v>
       </c>
       <c r="B153" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15691,32 +15691,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125889396</v>
+        <v>125888498</v>
       </c>
       <c r="B154" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500257</v>
+        <v>500311</v>
       </c>
       <c r="R154" t="n">
-        <v>6792475</v>
+        <v>6792509</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15791,7 +15791,7 @@
         <v>125895017</v>
       </c>
       <c r="B155" t="n">
-        <v>78991</v>
+        <v>78992</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>125895229</v>
       </c>
       <c r="B156" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>125888924</v>
       </c>
       <c r="B157" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16079,10 +16079,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125889676</v>
+        <v>125892637</v>
       </c>
       <c r="B158" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16090,21 +16090,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16114,10 +16114,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500202</v>
+        <v>500151</v>
       </c>
       <c r="R158" t="n">
-        <v>6792435</v>
+        <v>6792458</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16150,11 +16150,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16181,10 +16176,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125892942</v>
+        <v>125889676</v>
       </c>
       <c r="B159" t="n">
-        <v>91247</v>
+        <v>78968</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16192,21 +16187,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16216,10 +16211,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500171</v>
+        <v>500202</v>
       </c>
       <c r="R159" t="n">
-        <v>6792489</v>
+        <v>6792435</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16252,6 +16247,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16278,10 +16278,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125892637</v>
+        <v>125892942</v>
       </c>
       <c r="B160" t="n">
-        <v>79585</v>
+        <v>91248</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16289,21 +16289,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16313,10 +16313,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>500151</v>
+        <v>500171</v>
       </c>
       <c r="R160" t="n">
-        <v>6792458</v>
+        <v>6792489</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>125686800</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125686732</v>
+        <v>125685630</v>
       </c>
       <c r="B6" t="n">
-        <v>78725</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499990</v>
+        <v>499996</v>
       </c>
       <c r="R6" t="n">
-        <v>6792488</v>
+        <v>6792394</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,11 +1191,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125685630</v>
+        <v>125685407</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499996</v>
+        <v>500063</v>
       </c>
       <c r="R7" t="n">
-        <v>6792394</v>
+        <v>6792381</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125685407</v>
+        <v>125686732</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500063</v>
+        <v>499990</v>
       </c>
       <c r="R8" t="n">
-        <v>6792381</v>
+        <v>6792488</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,6 +1385,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,32 +1416,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125686874</v>
+        <v>125687486</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>79557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500013</v>
+        <v>499947</v>
       </c>
       <c r="R9" t="n">
-        <v>6792493</v>
+        <v>6792525</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,11 +1487,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,7 +1513,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125693671</v>
+        <v>125686874</v>
       </c>
       <c r="B10" t="n">
         <v>8447</v>
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500087</v>
+        <v>500013</v>
       </c>
       <c r="R10" t="n">
-        <v>6792574</v>
+        <v>6792493</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,6 +1584,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,32 +1809,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125687486</v>
+        <v>125693671</v>
       </c>
       <c r="B13" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499947</v>
+        <v>500087</v>
       </c>
       <c r="R13" t="n">
-        <v>6792525</v>
+        <v>6792574</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,7 +1909,7 @@
         <v>125684974</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>125693564</v>
       </c>
       <c r="B15" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>125685313</v>
       </c>
       <c r="B18" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>125692802</v>
       </c>
       <c r="B19" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>125690007</v>
       </c>
       <c r="B20" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>125684537</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>125686792</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>125686316</v>
       </c>
       <c r="B23" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>125690119</v>
       </c>
       <c r="B24" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>125689285</v>
       </c>
       <c r="B27" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125693241</v>
+        <v>125686343</v>
       </c>
       <c r="B28" t="n">
-        <v>57648</v>
+        <v>79586</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3320,21 +3320,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500047</v>
+        <v>499963</v>
       </c>
       <c r="R28" t="n">
-        <v>6792612</v>
+        <v>6792480</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3406,32 +3406,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125683895</v>
+        <v>125693241</v>
       </c>
       <c r="B29" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500326</v>
+        <v>500047</v>
       </c>
       <c r="R29" t="n">
-        <v>6792440</v>
+        <v>6792612</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3477,11 +3477,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3508,32 +3503,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125686305</v>
+        <v>125683895</v>
       </c>
       <c r="B30" t="n">
-        <v>78726</v>
+        <v>8447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3543,10 +3538,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499963</v>
+        <v>500326</v>
       </c>
       <c r="R30" t="n">
-        <v>6792480</v>
+        <v>6792440</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,10 +3605,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125693249</v>
+        <v>125685148</v>
       </c>
       <c r="B31" t="n">
-        <v>79556</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3621,21 +3616,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3645,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500047</v>
+        <v>500040</v>
       </c>
       <c r="R31" t="n">
-        <v>6792612</v>
+        <v>6792406</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125686343</v>
+        <v>125686305</v>
       </c>
       <c r="B32" t="n">
-        <v>79585</v>
+        <v>78727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3718,21 +3713,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3778,6 +3773,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3804,10 +3804,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125685148</v>
+        <v>125693249</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>79557</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3815,21 +3815,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500040</v>
+        <v>500047</v>
       </c>
       <c r="R33" t="n">
-        <v>6792406</v>
+        <v>6792612</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3904,7 +3904,7 @@
         <v>125684693</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>125685808</v>
       </c>
       <c r="B36" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>125691930</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>125684984</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4391,10 +4391,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125686924</v>
+        <v>125687294</v>
       </c>
       <c r="B39" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4402,21 +4402,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500010</v>
+        <v>499945</v>
       </c>
       <c r="R39" t="n">
-        <v>6792501</v>
+        <v>6792497</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4488,10 +4488,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687294</v>
+        <v>125686924</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4499,21 +4499,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499945</v>
+        <v>500010</v>
       </c>
       <c r="R40" t="n">
-        <v>6792497</v>
+        <v>6792501</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4588,7 +4588,7 @@
         <v>125690589</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>125693372</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,10 +4784,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125688845</v>
+        <v>125690295</v>
       </c>
       <c r="B43" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499970</v>
+        <v>500031</v>
       </c>
       <c r="R43" t="n">
-        <v>6792544</v>
+        <v>6792511</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4855,11 +4855,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4886,10 +4881,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125690295</v>
+        <v>125688845</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4897,21 +4892,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4921,10 +4916,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500031</v>
+        <v>499970</v>
       </c>
       <c r="R44" t="n">
-        <v>6792511</v>
+        <v>6792544</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4957,6 +4952,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5085,32 +5085,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125685110</v>
+        <v>125690957</v>
       </c>
       <c r="B46" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500063</v>
+        <v>500003</v>
       </c>
       <c r="R46" t="n">
-        <v>6792423</v>
+        <v>6792577</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5156,11 +5156,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5187,10 +5182,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125689757</v>
+        <v>125686463</v>
       </c>
       <c r="B47" t="n">
-        <v>79556</v>
+        <v>79586</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,21 +5193,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499951</v>
+        <v>499969</v>
       </c>
       <c r="R47" t="n">
-        <v>6792574</v>
+        <v>6792489</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5258,11 +5253,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5289,32 +5279,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125686463</v>
+        <v>125685110</v>
       </c>
       <c r="B48" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5324,10 +5314,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499969</v>
+        <v>500063</v>
       </c>
       <c r="R48" t="n">
-        <v>6792489</v>
+        <v>6792423</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5360,6 +5350,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5386,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125690957</v>
+        <v>125689757</v>
       </c>
       <c r="B49" t="n">
-        <v>78967</v>
+        <v>79557</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5397,21 +5392,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5421,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500003</v>
+        <v>499951</v>
       </c>
       <c r="R49" t="n">
-        <v>6792577</v>
+        <v>6792574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5457,6 +5452,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5486,7 +5486,7 @@
         <v>125684146</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125685693</v>
+        <v>125686894</v>
       </c>
       <c r="B51" t="n">
         <v>8447</v>
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500002</v>
+        <v>500010</v>
       </c>
       <c r="R51" t="n">
-        <v>6792449</v>
+        <v>6792501</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5651,11 +5651,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5682,7 +5677,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125686894</v>
+        <v>125685693</v>
       </c>
       <c r="B52" t="n">
         <v>8447</v>
@@ -5717,10 +5712,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500010</v>
+        <v>500002</v>
       </c>
       <c r="R52" t="n">
-        <v>6792501</v>
+        <v>6792449</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5753,6 +5748,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5782,7 +5782,7 @@
         <v>125684626</v>
       </c>
       <c r="B53" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>125690154</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5978,32 +5978,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685813</v>
+        <v>125683878</v>
       </c>
       <c r="B55" t="n">
-        <v>79556</v>
+        <v>8447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499996</v>
+        <v>499954</v>
       </c>
       <c r="R55" t="n">
-        <v>6792435</v>
+        <v>6792394</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,6 +6049,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6075,32 +6080,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125683878</v>
+        <v>125685813</v>
       </c>
       <c r="B56" t="n">
-        <v>8447</v>
+        <v>79557</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6110,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499954</v>
+        <v>499996</v>
       </c>
       <c r="R56" t="n">
-        <v>6792394</v>
+        <v>6792435</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6146,11 +6151,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6180,7 +6180,7 @@
         <v>125685885</v>
       </c>
       <c r="B57" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>125690170</v>
       </c>
       <c r="B58" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125686648</v>
+        <v>125687400</v>
       </c>
       <c r="B59" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6382,21 +6382,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499990</v>
+        <v>499947</v>
       </c>
       <c r="R59" t="n">
-        <v>6792488</v>
+        <v>6792525</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6442,11 +6442,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6473,10 +6468,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125687400</v>
+        <v>125686648</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6484,21 +6479,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6508,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>499947</v>
+        <v>499990</v>
       </c>
       <c r="R60" t="n">
-        <v>6792525</v>
+        <v>6792488</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6544,6 +6539,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6573,7 +6573,7 @@
         <v>125691010</v>
       </c>
       <c r="B61" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>125685121</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>125693022</v>
       </c>
       <c r="B63" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>125693403</v>
       </c>
       <c r="B64" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>125685734</v>
       </c>
       <c r="B65" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>125685660</v>
       </c>
       <c r="B66" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>125685335</v>
       </c>
       <c r="B67" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7263,10 +7263,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125888195</v>
+        <v>125889107</v>
       </c>
       <c r="B68" t="n">
-        <v>78968</v>
+        <v>79557</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,21 +7274,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500310</v>
+        <v>500285</v>
       </c>
       <c r="R68" t="n">
-        <v>6792516</v>
+        <v>6792489</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,11 +7334,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7365,50 +7360,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125894731</v>
+        <v>125892998</v>
       </c>
       <c r="B69" t="n">
-        <v>57651</v>
+        <v>8447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500128</v>
+        <v>500188</v>
       </c>
       <c r="R69" t="n">
-        <v>6792590</v>
+        <v>6792496</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7467,7 +7457,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125892998</v>
+        <v>125893046</v>
       </c>
       <c r="B70" t="n">
         <v>8447</v>
@@ -7502,10 +7492,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500188</v>
+        <v>500207</v>
       </c>
       <c r="R70" t="n">
-        <v>6792496</v>
+        <v>6792488</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7564,32 +7554,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125893046</v>
+        <v>125888195</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7599,10 +7589,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500207</v>
+        <v>500310</v>
       </c>
       <c r="R71" t="n">
-        <v>6792488</v>
+        <v>6792516</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7635,6 +7625,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7661,10 +7656,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125889107</v>
+        <v>125894731</v>
       </c>
       <c r="B72" t="n">
-        <v>79557</v>
+        <v>57651</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7672,34 +7667,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500285</v>
+        <v>500128</v>
       </c>
       <c r="R72" t="n">
-        <v>6792489</v>
+        <v>6792590</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8437,10 +8437,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125889406</v>
+        <v>125888740</v>
       </c>
       <c r="B80" t="n">
-        <v>79586</v>
+        <v>57811</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8448,34 +8448,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500257</v>
+        <v>500306</v>
       </c>
       <c r="R80" t="n">
-        <v>6792475</v>
+        <v>6792466</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8534,32 +8539,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125895109</v>
+        <v>125892266</v>
       </c>
       <c r="B81" t="n">
-        <v>79586</v>
+        <v>8447</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8569,10 +8574,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>499985</v>
+        <v>500158</v>
       </c>
       <c r="R81" t="n">
-        <v>6792633</v>
+        <v>6792441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8631,32 +8636,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125890407</v>
+        <v>125888709</v>
       </c>
       <c r="B82" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8666,10 +8671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500242</v>
+        <v>500311</v>
       </c>
       <c r="R82" t="n">
-        <v>6792408</v>
+        <v>6792502</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8702,11 +8707,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8733,7 +8733,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125892653</v>
+        <v>125890407</v>
       </c>
       <c r="B83" t="n">
         <v>78968</v>
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>500151</v>
+        <v>500242</v>
       </c>
       <c r="R83" t="n">
-        <v>6792458</v>
+        <v>6792408</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8804,6 +8804,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8830,10 +8835,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125888740</v>
+        <v>125892653</v>
       </c>
       <c r="B84" t="n">
-        <v>57811</v>
+        <v>78968</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8841,39 +8846,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500306</v>
+        <v>500151</v>
       </c>
       <c r="R84" t="n">
-        <v>6792466</v>
+        <v>6792458</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8932,32 +8932,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125888709</v>
+        <v>125889406</v>
       </c>
       <c r="B85" t="n">
-        <v>8447</v>
+        <v>79586</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8967,10 +8967,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500311</v>
+        <v>500257</v>
       </c>
       <c r="R85" t="n">
-        <v>6792502</v>
+        <v>6792475</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9029,32 +9029,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125892266</v>
+        <v>125895109</v>
       </c>
       <c r="B86" t="n">
-        <v>8447</v>
+        <v>79586</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500158</v>
+        <v>499985</v>
       </c>
       <c r="R86" t="n">
-        <v>6792441</v>
+        <v>6792633</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9611,32 +9611,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125888352</v>
+        <v>125889889</v>
       </c>
       <c r="B92" t="n">
-        <v>8447</v>
+        <v>79586</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>500310</v>
+        <v>500237</v>
       </c>
       <c r="R92" t="n">
-        <v>6792516</v>
+        <v>6792422</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,32 +9708,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125896400</v>
+        <v>125888352</v>
       </c>
       <c r="B93" t="n">
-        <v>79557</v>
+        <v>8447</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>500351</v>
+        <v>500310</v>
       </c>
       <c r="R93" t="n">
-        <v>6792369</v>
+        <v>6792516</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125889879</v>
+        <v>125896400</v>
       </c>
       <c r="B94" t="n">
-        <v>78727</v>
+        <v>79557</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>500237</v>
+        <v>500351</v>
       </c>
       <c r="R94" t="n">
-        <v>6792422</v>
+        <v>6792369</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,7 +9902,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125895107</v>
+        <v>125889879</v>
       </c>
       <c r="B95" t="n">
         <v>78727</v>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>499985</v>
+        <v>500237</v>
       </c>
       <c r="R95" t="n">
-        <v>6792633</v>
+        <v>6792422</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,10 +9999,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125889889</v>
+        <v>125895107</v>
       </c>
       <c r="B96" t="n">
-        <v>79586</v>
+        <v>78727</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>500237</v>
+        <v>499985</v>
       </c>
       <c r="R96" t="n">
-        <v>6792422</v>
+        <v>6792633</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125889615</v>
+        <v>125892224</v>
       </c>
       <c r="B103" t="n">
-        <v>8447</v>
+        <v>78726</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500202</v>
+        <v>500158</v>
       </c>
       <c r="R103" t="n">
-        <v>6792435</v>
+        <v>6792441</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10775,10 +10775,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125892224</v>
+        <v>125896058</v>
       </c>
       <c r="B104" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500158</v>
+        <v>500351</v>
       </c>
       <c r="R104" t="n">
-        <v>6792441</v>
+        <v>6792369</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,6 +10846,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10969,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125896058</v>
+        <v>125889615</v>
       </c>
       <c r="B106" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11004,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500351</v>
+        <v>500202</v>
       </c>
       <c r="R106" t="n">
-        <v>6792369</v>
+        <v>6792435</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11040,11 +11045,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11168,32 +11168,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125893643</v>
+        <v>125889090</v>
       </c>
       <c r="B108" t="n">
-        <v>8447</v>
+        <v>79586</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500237</v>
+        <v>500285</v>
       </c>
       <c r="R108" t="n">
-        <v>6792567</v>
+        <v>6792489</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11469,32 +11469,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125889090</v>
+        <v>125893643</v>
       </c>
       <c r="B111" t="n">
-        <v>79586</v>
+        <v>8447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11504,10 +11504,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500285</v>
+        <v>500237</v>
       </c>
       <c r="R111" t="n">
-        <v>6792489</v>
+        <v>6792567</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11566,30 +11566,34 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125894266</v>
+        <v>125892433</v>
       </c>
       <c r="B112" t="n">
-        <v>98252</v>
+        <v>79557</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>223597</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11597,10 +11601,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500128</v>
+        <v>500160</v>
       </c>
       <c r="R112" t="n">
-        <v>6792590</v>
+        <v>6792451</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11659,34 +11663,30 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125892433</v>
+        <v>125894266</v>
       </c>
       <c r="B113" t="n">
-        <v>79557</v>
+        <v>98254</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>223597</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500160</v>
+        <v>500128</v>
       </c>
       <c r="R113" t="n">
-        <v>6792451</v>
+        <v>6792590</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,10 +11756,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125890126</v>
+        <v>125893637</v>
       </c>
       <c r="B114" t="n">
-        <v>79586</v>
+        <v>78968</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500242</v>
+        <v>500246</v>
       </c>
       <c r="R114" t="n">
-        <v>6792408</v>
+        <v>6792558</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11827,6 +11827,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11853,7 +11858,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125892154</v>
+        <v>125890126</v>
       </c>
       <c r="B115" t="n">
         <v>79586</v>
@@ -11888,10 +11893,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500145</v>
+        <v>500242</v>
       </c>
       <c r="R115" t="n">
-        <v>6792446</v>
+        <v>6792408</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11950,10 +11955,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125894500</v>
+        <v>125892154</v>
       </c>
       <c r="B116" t="n">
-        <v>78726</v>
+        <v>79586</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11961,21 +11966,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11985,10 +11990,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500128</v>
+        <v>500145</v>
       </c>
       <c r="R116" t="n">
-        <v>6792590</v>
+        <v>6792446</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12047,10 +12052,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125893637</v>
+        <v>125894500</v>
       </c>
       <c r="B117" t="n">
-        <v>78968</v>
+        <v>78726</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12058,21 +12063,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12082,10 +12087,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500246</v>
+        <v>500128</v>
       </c>
       <c r="R117" t="n">
-        <v>6792558</v>
+        <v>6792590</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12118,11 +12123,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12343,7 +12343,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125888695</v>
+        <v>125892496</v>
       </c>
       <c r="B120" t="n">
         <v>78968</v>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500311</v>
+        <v>500145</v>
       </c>
       <c r="R120" t="n">
-        <v>6792502</v>
+        <v>6792446</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12445,7 +12445,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125892496</v>
+        <v>125888695</v>
       </c>
       <c r="B121" t="n">
         <v>78968</v>
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500145</v>
+        <v>500311</v>
       </c>
       <c r="R121" t="n">
-        <v>6792446</v>
+        <v>6792502</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12520,7 +12520,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12741,32 +12741,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125896611</v>
+        <v>125891471</v>
       </c>
       <c r="B124" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12776,10 +12776,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500384</v>
+        <v>500181</v>
       </c>
       <c r="R124" t="n">
-        <v>6792529</v>
+        <v>6792401</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12812,11 +12812,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12843,10 +12838,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125894132</v>
+        <v>125896611</v>
       </c>
       <c r="B125" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12854,21 +12849,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12878,10 +12873,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R125" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12914,6 +12909,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13139,32 +13139,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125891471</v>
+        <v>125894132</v>
       </c>
       <c r="B128" t="n">
-        <v>8447</v>
+        <v>78727</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13174,10 +13174,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>500181</v>
+        <v>500128</v>
       </c>
       <c r="R128" t="n">
-        <v>6792401</v>
+        <v>6792590</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13629,45 +13629,50 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125890887</v>
+        <v>125891498</v>
       </c>
       <c r="B133" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500282</v>
+        <v>500166</v>
       </c>
       <c r="R133" t="n">
-        <v>6792389</v>
+        <v>6792413</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13726,7 +13731,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125893186</v>
+        <v>125890887</v>
       </c>
       <c r="B134" t="n">
         <v>8447</v>
@@ -13761,10 +13766,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500247</v>
+        <v>500282</v>
       </c>
       <c r="R134" t="n">
-        <v>6792519</v>
+        <v>6792389</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13823,50 +13828,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125891498</v>
+        <v>125893186</v>
       </c>
       <c r="B135" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500166</v>
+        <v>500247</v>
       </c>
       <c r="R135" t="n">
-        <v>6792413</v>
+        <v>6792519</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125896454</v>
+        <v>125896535</v>
       </c>
       <c r="B140" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500374</v>
+        <v>500384</v>
       </c>
       <c r="R140" t="n">
-        <v>6792515</v>
+        <v>6792529</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14384,11 +14384,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14415,10 +14410,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125889266</v>
+        <v>125896642</v>
       </c>
       <c r="B141" t="n">
-        <v>78968</v>
+        <v>79557</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14426,21 +14421,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14450,10 +14445,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500257</v>
+        <v>500384</v>
       </c>
       <c r="R141" t="n">
-        <v>6792475</v>
+        <v>6792529</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14486,11 +14481,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14517,10 +14507,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125896535</v>
+        <v>125892643</v>
       </c>
       <c r="B142" t="n">
-        <v>78727</v>
+        <v>79557</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14528,21 +14518,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14552,10 +14542,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>500384</v>
+        <v>500151</v>
       </c>
       <c r="R142" t="n">
-        <v>6792529</v>
+        <v>6792458</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14614,10 +14604,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125896642</v>
+        <v>125889379</v>
       </c>
       <c r="B143" t="n">
-        <v>79557</v>
+        <v>78727</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14625,21 +14615,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14649,10 +14639,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500384</v>
+        <v>500257</v>
       </c>
       <c r="R143" t="n">
-        <v>6792529</v>
+        <v>6792475</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14711,7 +14701,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125892643</v>
+        <v>125892160</v>
       </c>
       <c r="B144" t="n">
         <v>79557</v>
@@ -14746,10 +14736,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500151</v>
+        <v>500145</v>
       </c>
       <c r="R144" t="n">
-        <v>6792458</v>
+        <v>6792446</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14808,10 +14798,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125889379</v>
+        <v>125896454</v>
       </c>
       <c r="B145" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14819,21 +14809,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14843,10 +14833,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500257</v>
+        <v>500374</v>
       </c>
       <c r="R145" t="n">
-        <v>6792475</v>
+        <v>6792515</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14879,6 +14869,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14905,10 +14900,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125892160</v>
+        <v>125889266</v>
       </c>
       <c r="B146" t="n">
-        <v>79557</v>
+        <v>78968</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14916,21 +14911,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14940,10 +14935,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R146" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14976,6 +14971,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15002,50 +15002,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125888369</v>
+        <v>125896772</v>
       </c>
       <c r="B147" t="n">
-        <v>57648</v>
+        <v>92518</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500310</v>
+        <v>500384</v>
       </c>
       <c r="R147" t="n">
-        <v>6792516</v>
+        <v>6792529</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15104,32 +15099,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125896772</v>
+        <v>125891864</v>
       </c>
       <c r="B148" t="n">
-        <v>92510</v>
+        <v>78968</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15139,10 +15134,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500384</v>
+        <v>500126</v>
       </c>
       <c r="R148" t="n">
-        <v>6792529</v>
+        <v>6792397</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15175,6 +15170,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15201,10 +15201,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125891864</v>
+        <v>125888369</v>
       </c>
       <c r="B149" t="n">
-        <v>78968</v>
+        <v>57648</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15212,34 +15212,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500126</v>
+        <v>500310</v>
       </c>
       <c r="R149" t="n">
-        <v>6792397</v>
+        <v>6792516</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15272,11 +15277,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15497,32 +15497,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125889396</v>
+        <v>125888498</v>
       </c>
       <c r="B152" t="n">
-        <v>79557</v>
+        <v>8447</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500257</v>
+        <v>500311</v>
       </c>
       <c r="R152" t="n">
-        <v>6792475</v>
+        <v>6792509</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15594,10 +15594,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125891609</v>
+        <v>125889396</v>
       </c>
       <c r="B153" t="n">
-        <v>78727</v>
+        <v>79557</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15605,21 +15605,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15629,10 +15629,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500153</v>
+        <v>500257</v>
       </c>
       <c r="R153" t="n">
-        <v>6792391</v>
+        <v>6792475</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15691,32 +15691,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125888498</v>
+        <v>125891609</v>
       </c>
       <c r="B154" t="n">
-        <v>8447</v>
+        <v>78727</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500311</v>
+        <v>500153</v>
       </c>
       <c r="R154" t="n">
-        <v>6792509</v>
+        <v>6792391</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16079,10 +16079,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125892637</v>
+        <v>125889676</v>
       </c>
       <c r="B158" t="n">
-        <v>79586</v>
+        <v>78968</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16090,21 +16090,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16114,10 +16114,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500151</v>
+        <v>500202</v>
       </c>
       <c r="R158" t="n">
-        <v>6792458</v>
+        <v>6792435</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16150,6 +16150,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16176,10 +16181,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125889676</v>
+        <v>125892942</v>
       </c>
       <c r="B159" t="n">
-        <v>78968</v>
+        <v>91248</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16187,21 +16192,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16211,10 +16216,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500202</v>
+        <v>500171</v>
       </c>
       <c r="R159" t="n">
-        <v>6792435</v>
+        <v>6792489</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16247,11 +16252,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16278,10 +16278,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125892942</v>
+        <v>125892637</v>
       </c>
       <c r="B160" t="n">
-        <v>91248</v>
+        <v>79586</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16289,21 +16289,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16313,10 +16313,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>500171</v>
+        <v>500151</v>
       </c>
       <c r="R160" t="n">
-        <v>6792489</v>
+        <v>6792458</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1023,32 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125686800</v>
+        <v>125686874</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500007</v>
+        <v>500013</v>
       </c>
       <c r="R5" t="n">
-        <v>6792490</v>
+        <v>6792493</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,6 +1094,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,32 +1125,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125685630</v>
+        <v>125687215</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499996</v>
+        <v>499945</v>
       </c>
       <c r="R6" t="n">
-        <v>6792394</v>
+        <v>6792497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,32 +1222,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125685407</v>
+        <v>125689836</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500063</v>
+        <v>499951</v>
       </c>
       <c r="R7" t="n">
-        <v>6792381</v>
+        <v>6792574</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,32 +1319,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125686732</v>
+        <v>125693671</v>
       </c>
       <c r="B8" t="n">
-        <v>78726</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499990</v>
+        <v>500087</v>
       </c>
       <c r="R8" t="n">
-        <v>6792488</v>
+        <v>6792574</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,11 +1390,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,32 +1513,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125686874</v>
+        <v>125686800</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500013</v>
+        <v>500007</v>
       </c>
       <c r="R10" t="n">
-        <v>6792493</v>
+        <v>6792490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,11 +1584,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,32 +1610,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125687215</v>
+        <v>125685630</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499945</v>
+        <v>499996</v>
       </c>
       <c r="R11" t="n">
-        <v>6792497</v>
+        <v>6792394</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,32 +1707,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125689836</v>
+        <v>125685407</v>
       </c>
       <c r="B12" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499951</v>
+        <v>500063</v>
       </c>
       <c r="R12" t="n">
-        <v>6792574</v>
+        <v>6792381</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1809,32 +1804,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125693671</v>
+        <v>125686732</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>78726</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1844,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500087</v>
+        <v>499990</v>
       </c>
       <c r="R13" t="n">
-        <v>6792574</v>
+        <v>6792488</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1880,6 +1875,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3309,32 +3309,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125686343</v>
+        <v>125683895</v>
       </c>
       <c r="B28" t="n">
-        <v>79586</v>
+        <v>8447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499963</v>
+        <v>500326</v>
       </c>
       <c r="R28" t="n">
-        <v>6792480</v>
+        <v>6792440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3380,6 +3380,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,32 +3508,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125683895</v>
+        <v>125685148</v>
       </c>
       <c r="B30" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3538,10 +3543,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500326</v>
+        <v>500040</v>
       </c>
       <c r="R30" t="n">
-        <v>6792440</v>
+        <v>6792406</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3574,11 +3579,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3605,10 +3605,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125685148</v>
+        <v>125686343</v>
       </c>
       <c r="B31" t="n">
-        <v>78968</v>
+        <v>79586</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3616,21 +3616,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500040</v>
+        <v>499963</v>
       </c>
       <c r="R31" t="n">
-        <v>6792406</v>
+        <v>6792480</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3901,32 +3901,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125684693</v>
+        <v>125687329</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500077</v>
+        <v>499947</v>
       </c>
       <c r="R34" t="n">
-        <v>6792400</v>
+        <v>6792525</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3998,32 +3998,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125687329</v>
+        <v>125684693</v>
       </c>
       <c r="B35" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499947</v>
+        <v>500077</v>
       </c>
       <c r="R35" t="n">
-        <v>6792525</v>
+        <v>6792400</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5279,32 +5279,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125685110</v>
+        <v>125689757</v>
       </c>
       <c r="B48" t="n">
-        <v>8447</v>
+        <v>79557</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>500063</v>
+        <v>499951</v>
       </c>
       <c r="R48" t="n">
-        <v>6792423</v>
+        <v>6792574</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,32 +5381,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125689757</v>
+        <v>125685110</v>
       </c>
       <c r="B49" t="n">
-        <v>79557</v>
+        <v>8447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499951</v>
+        <v>500063</v>
       </c>
       <c r="R49" t="n">
-        <v>6792574</v>
+        <v>6792423</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5978,32 +5978,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125683878</v>
+        <v>125685885</v>
       </c>
       <c r="B55" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499954</v>
+        <v>500002</v>
       </c>
       <c r="R55" t="n">
-        <v>6792394</v>
+        <v>6792449</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,11 +6049,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6080,10 +6075,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125685813</v>
+        <v>125690170</v>
       </c>
       <c r="B56" t="n">
-        <v>79557</v>
+        <v>78968</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6091,21 +6086,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6115,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499996</v>
+        <v>500018</v>
       </c>
       <c r="R56" t="n">
-        <v>6792435</v>
+        <v>6792528</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6177,32 +6172,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125685885</v>
+        <v>125683878</v>
       </c>
       <c r="B57" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6212,10 +6207,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>500002</v>
+        <v>499954</v>
       </c>
       <c r="R57" t="n">
-        <v>6792449</v>
+        <v>6792394</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6248,6 +6243,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125690170</v>
+        <v>125685813</v>
       </c>
       <c r="B58" t="n">
-        <v>78968</v>
+        <v>79557</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>500018</v>
+        <v>499996</v>
       </c>
       <c r="R58" t="n">
-        <v>6792528</v>
+        <v>6792435</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125685121</v>
+        <v>125693403</v>
       </c>
       <c r="B62" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6678,21 +6678,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>500063</v>
+        <v>500078</v>
       </c>
       <c r="R62" t="n">
-        <v>6792423</v>
+        <v>6792594</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6764,7 +6764,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125693022</v>
+        <v>125685121</v>
       </c>
       <c r="B63" t="n">
         <v>78968</v>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>500026</v>
+        <v>500063</v>
       </c>
       <c r="R63" t="n">
-        <v>6792635</v>
+        <v>6792423</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6861,10 +6861,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125693403</v>
+        <v>125693022</v>
       </c>
       <c r="B64" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6872,21 +6872,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6896,10 +6896,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>500078</v>
+        <v>500026</v>
       </c>
       <c r="R64" t="n">
-        <v>6792594</v>
+        <v>6792635</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7263,10 +7263,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125889107</v>
+        <v>125888195</v>
       </c>
       <c r="B68" t="n">
-        <v>79557</v>
+        <v>78968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,21 +7274,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500285</v>
+        <v>500310</v>
       </c>
       <c r="R68" t="n">
-        <v>6792489</v>
+        <v>6792516</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,6 +7334,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7360,45 +7365,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125892998</v>
+        <v>125894731</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>57651</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500188</v>
+        <v>500128</v>
       </c>
       <c r="R69" t="n">
-        <v>6792496</v>
+        <v>6792590</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7457,7 +7467,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125893046</v>
+        <v>125892998</v>
       </c>
       <c r="B70" t="n">
         <v>8447</v>
@@ -7492,10 +7502,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500207</v>
+        <v>500188</v>
       </c>
       <c r="R70" t="n">
-        <v>6792488</v>
+        <v>6792496</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7554,32 +7564,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125888195</v>
+        <v>125893046</v>
       </c>
       <c r="B71" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7589,10 +7599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500310</v>
+        <v>500207</v>
       </c>
       <c r="R71" t="n">
-        <v>6792516</v>
+        <v>6792488</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7625,11 +7635,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7656,10 +7661,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125894731</v>
+        <v>125889107</v>
       </c>
       <c r="B72" t="n">
-        <v>57651</v>
+        <v>79557</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7667,39 +7672,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500128</v>
+        <v>500285</v>
       </c>
       <c r="R72" t="n">
-        <v>6792590</v>
+        <v>6792489</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -12741,32 +12741,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125891471</v>
+        <v>125896611</v>
       </c>
       <c r="B124" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12776,10 +12776,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500181</v>
+        <v>500384</v>
       </c>
       <c r="R124" t="n">
-        <v>6792401</v>
+        <v>6792529</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12812,6 +12812,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12838,10 +12843,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125896611</v>
+        <v>125892207</v>
       </c>
       <c r="B125" t="n">
-        <v>78968</v>
+        <v>79586</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12849,21 +12854,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12873,10 +12878,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500384</v>
+        <v>500158</v>
       </c>
       <c r="R125" t="n">
-        <v>6792529</v>
+        <v>6792441</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12909,11 +12914,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12940,32 +12940,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125892207</v>
+        <v>125891471</v>
       </c>
       <c r="B126" t="n">
-        <v>79586</v>
+        <v>8447</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12975,10 +12975,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500158</v>
+        <v>500181</v>
       </c>
       <c r="R126" t="n">
-        <v>6792441</v>
+        <v>6792401</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125896535</v>
+        <v>125896454</v>
       </c>
       <c r="B140" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500384</v>
+        <v>500374</v>
       </c>
       <c r="R140" t="n">
-        <v>6792529</v>
+        <v>6792515</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14384,6 +14384,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14410,10 +14415,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125896642</v>
+        <v>125889266</v>
       </c>
       <c r="B141" t="n">
-        <v>79557</v>
+        <v>78968</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14421,21 +14426,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14445,10 +14450,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500384</v>
+        <v>500257</v>
       </c>
       <c r="R141" t="n">
-        <v>6792529</v>
+        <v>6792475</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14481,6 +14486,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14507,10 +14517,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125892643</v>
+        <v>125896535</v>
       </c>
       <c r="B142" t="n">
-        <v>79557</v>
+        <v>78727</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14518,21 +14528,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14542,10 +14552,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>500151</v>
+        <v>500384</v>
       </c>
       <c r="R142" t="n">
-        <v>6792458</v>
+        <v>6792529</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14604,10 +14614,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125889379</v>
+        <v>125896642</v>
       </c>
       <c r="B143" t="n">
-        <v>78727</v>
+        <v>79557</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14615,21 +14625,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14639,10 +14649,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500257</v>
+        <v>500384</v>
       </c>
       <c r="R143" t="n">
-        <v>6792475</v>
+        <v>6792529</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14701,7 +14711,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125892160</v>
+        <v>125892643</v>
       </c>
       <c r="B144" t="n">
         <v>79557</v>
@@ -14736,10 +14746,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500145</v>
+        <v>500151</v>
       </c>
       <c r="R144" t="n">
-        <v>6792446</v>
+        <v>6792458</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14798,10 +14808,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125896454</v>
+        <v>125889379</v>
       </c>
       <c r="B145" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14809,21 +14819,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14833,10 +14843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500374</v>
+        <v>500257</v>
       </c>
       <c r="R145" t="n">
-        <v>6792515</v>
+        <v>6792475</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14869,11 +14879,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14900,10 +14905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125889266</v>
+        <v>125892160</v>
       </c>
       <c r="B146" t="n">
-        <v>78968</v>
+        <v>79557</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14911,21 +14916,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14935,10 +14940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R146" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14971,11 +14976,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD146" t="b">

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1125,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125687215</v>
+        <v>125693671</v>
       </c>
       <c r="B6" t="n">
         <v>8447</v>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499945</v>
+        <v>500087</v>
       </c>
       <c r="R6" t="n">
-        <v>6792497</v>
+        <v>6792574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125689836</v>
+        <v>125687215</v>
       </c>
       <c r="B7" t="n">
         <v>8447</v>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499951</v>
+        <v>499945</v>
       </c>
       <c r="R7" t="n">
-        <v>6792574</v>
+        <v>6792497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125693671</v>
+        <v>125689836</v>
       </c>
       <c r="B8" t="n">
         <v>8447</v>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500087</v>
+        <v>499951</v>
       </c>
       <c r="R8" t="n">
         <v>6792574</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125687486</v>
+        <v>125686800</v>
       </c>
       <c r="B9" t="n">
-        <v>79557</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,21 +1427,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499947</v>
+        <v>500007</v>
       </c>
       <c r="R9" t="n">
-        <v>6792525</v>
+        <v>6792490</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125686800</v>
+        <v>125686732</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,21 +1524,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500007</v>
+        <v>499990</v>
       </c>
       <c r="R10" t="n">
-        <v>6792490</v>
+        <v>6792488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,6 +1584,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,7 +1618,7 @@
         <v>125685630</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         <v>125685407</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,10 +1809,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125686732</v>
+        <v>125687486</v>
       </c>
       <c r="B13" t="n">
-        <v>78726</v>
+        <v>79561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1815,21 +1820,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1839,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499990</v>
+        <v>499947</v>
       </c>
       <c r="R13" t="n">
-        <v>6792488</v>
+        <v>6792525</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1875,11 +1880,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,7 +1909,7 @@
         <v>125684974</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>125693564</v>
       </c>
       <c r="B15" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,32 +2207,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125684253</v>
+        <v>125685313</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500039</v>
+        <v>500063</v>
       </c>
       <c r="R17" t="n">
-        <v>6792388</v>
+        <v>6792381</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,6 +2278,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Muljöbilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2304,10 +2309,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125685313</v>
+        <v>125692802</v>
       </c>
       <c r="B18" t="n">
-        <v>78727</v>
+        <v>79561</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2315,21 +2320,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2339,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500063</v>
+        <v>499954</v>
       </c>
       <c r="R18" t="n">
-        <v>6792381</v>
+        <v>6792650</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,11 +2380,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Muljöbilder</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,32 +2406,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125692802</v>
+        <v>125684253</v>
       </c>
       <c r="B19" t="n">
-        <v>79557</v>
+        <v>8447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499954</v>
+        <v>500039</v>
       </c>
       <c r="R19" t="n">
-        <v>6792650</v>
+        <v>6792388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125690007</v>
+        <v>125684537</v>
       </c>
       <c r="B20" t="n">
-        <v>79557</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499989</v>
+        <v>500039</v>
       </c>
       <c r="R20" t="n">
-        <v>6792563</v>
+        <v>6792388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125684537</v>
+        <v>125690007</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>79561</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500039</v>
+        <v>499989</v>
       </c>
       <c r="R21" t="n">
-        <v>6792388</v>
+        <v>6792563</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,7 +2710,7 @@
         <v>125686792</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>125686316</v>
       </c>
       <c r="B23" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>125690119</v>
       </c>
       <c r="B24" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>125689285</v>
       </c>
       <c r="B27" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3309,32 +3309,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125683895</v>
+        <v>125686343</v>
       </c>
       <c r="B28" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500326</v>
+        <v>499963</v>
       </c>
       <c r="R28" t="n">
-        <v>6792440</v>
+        <v>6792480</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3380,11 +3380,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3508,10 +3503,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125685148</v>
+        <v>125686305</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3519,21 +3514,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3543,10 +3538,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500040</v>
+        <v>499963</v>
       </c>
       <c r="R30" t="n">
-        <v>6792406</v>
+        <v>6792480</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3579,6 +3574,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3605,10 +3605,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125686343</v>
+        <v>125693249</v>
       </c>
       <c r="B31" t="n">
-        <v>79586</v>
+        <v>79561</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3616,21 +3616,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499963</v>
+        <v>500047</v>
       </c>
       <c r="R31" t="n">
-        <v>6792480</v>
+        <v>6792612</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,32 +3702,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125686305</v>
+        <v>125683895</v>
       </c>
       <c r="B32" t="n">
-        <v>78727</v>
+        <v>8447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499963</v>
+        <v>500326</v>
       </c>
       <c r="R32" t="n">
-        <v>6792480</v>
+        <v>6792440</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3804,10 +3804,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125693249</v>
+        <v>125685148</v>
       </c>
       <c r="B33" t="n">
-        <v>79557</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3815,21 +3815,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500047</v>
+        <v>500040</v>
       </c>
       <c r="R33" t="n">
-        <v>6792612</v>
+        <v>6792406</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3901,32 +3901,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125687329</v>
+        <v>125684693</v>
       </c>
       <c r="B34" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499947</v>
+        <v>500077</v>
       </c>
       <c r="R34" t="n">
-        <v>6792525</v>
+        <v>6792400</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3998,32 +3998,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125684693</v>
+        <v>125687329</v>
       </c>
       <c r="B35" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500077</v>
+        <v>499947</v>
       </c>
       <c r="R35" t="n">
-        <v>6792400</v>
+        <v>6792525</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4098,7 +4098,7 @@
         <v>125685808</v>
       </c>
       <c r="B36" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>125691930</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>125684984</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4391,10 +4391,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687294</v>
+        <v>125686924</v>
       </c>
       <c r="B39" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4402,21 +4402,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499945</v>
+        <v>500010</v>
       </c>
       <c r="R39" t="n">
-        <v>6792497</v>
+        <v>6792501</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4488,10 +4488,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125686924</v>
+        <v>125687294</v>
       </c>
       <c r="B40" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4499,21 +4499,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500010</v>
+        <v>499945</v>
       </c>
       <c r="R40" t="n">
-        <v>6792501</v>
+        <v>6792497</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4585,10 +4585,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125690589</v>
+        <v>125693372</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>500043</v>
+        <v>500078</v>
       </c>
       <c r="R41" t="n">
-        <v>6792510</v>
+        <v>6792594</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4656,11 +4656,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4687,10 +4682,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125693372</v>
+        <v>125688845</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4698,21 +4693,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4722,10 +4717,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>500078</v>
+        <v>499970</v>
       </c>
       <c r="R42" t="n">
-        <v>6792594</v>
+        <v>6792544</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4758,6 +4753,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4787,7 +4787,7 @@
         <v>125690295</v>
       </c>
       <c r="B43" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125688845</v>
+        <v>125690589</v>
       </c>
       <c r="B44" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4892,21 +4892,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499970</v>
+        <v>500043</v>
       </c>
       <c r="R44" t="n">
-        <v>6792544</v>
+        <v>6792510</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5085,10 +5085,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125690957</v>
+        <v>125686463</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500003</v>
+        <v>499969</v>
       </c>
       <c r="R46" t="n">
-        <v>6792577</v>
+        <v>6792489</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125686463</v>
+        <v>125690957</v>
       </c>
       <c r="B47" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5193,21 +5193,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499969</v>
+        <v>500003</v>
       </c>
       <c r="R47" t="n">
-        <v>6792489</v>
+        <v>6792577</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5279,32 +5279,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125689757</v>
+        <v>125685110</v>
       </c>
       <c r="B48" t="n">
-        <v>79557</v>
+        <v>8447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499951</v>
+        <v>500063</v>
       </c>
       <c r="R48" t="n">
-        <v>6792574</v>
+        <v>6792423</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,32 +5381,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125685110</v>
+        <v>125689757</v>
       </c>
       <c r="B49" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500063</v>
+        <v>499951</v>
       </c>
       <c r="R49" t="n">
-        <v>6792423</v>
+        <v>6792574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
         <v>125684146</v>
       </c>
       <c r="B50" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,32 +5580,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125686894</v>
+        <v>125684626</v>
       </c>
       <c r="B51" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500010</v>
+        <v>500047</v>
       </c>
       <c r="R51" t="n">
-        <v>6792501</v>
+        <v>6792395</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5779,32 +5779,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125684626</v>
+        <v>125686894</v>
       </c>
       <c r="B53" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500047</v>
+        <v>500010</v>
       </c>
       <c r="R53" t="n">
-        <v>6792395</v>
+        <v>6792501</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5879,7 +5879,7 @@
         <v>125690154</v>
       </c>
       <c r="B54" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5978,10 +5978,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685885</v>
+        <v>125690170</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>500002</v>
+        <v>500018</v>
       </c>
       <c r="R55" t="n">
-        <v>6792449</v>
+        <v>6792528</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6075,32 +6075,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125690170</v>
+        <v>125683878</v>
       </c>
       <c r="B56" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6110,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>500018</v>
+        <v>499954</v>
       </c>
       <c r="R56" t="n">
-        <v>6792528</v>
+        <v>6792394</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6146,6 +6146,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6172,32 +6177,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125683878</v>
+        <v>125685813</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6207,10 +6212,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499954</v>
+        <v>499996</v>
       </c>
       <c r="R57" t="n">
-        <v>6792394</v>
+        <v>6792435</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6243,11 +6248,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125685813</v>
+        <v>125685885</v>
       </c>
       <c r="B58" t="n">
-        <v>79557</v>
+        <v>78972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499996</v>
+        <v>500002</v>
       </c>
       <c r="R58" t="n">
-        <v>6792435</v>
+        <v>6792449</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6374,7 +6374,7 @@
         <v>125687400</v>
       </c>
       <c r="B59" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>125686648</v>
       </c>
       <c r="B60" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>125691010</v>
       </c>
       <c r="B61" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125693403</v>
+        <v>125685121</v>
       </c>
       <c r="B62" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6678,21 +6678,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>500078</v>
+        <v>500063</v>
       </c>
       <c r="R62" t="n">
-        <v>6792594</v>
+        <v>6792423</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6764,10 +6764,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125685121</v>
+        <v>125693022</v>
       </c>
       <c r="B63" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>500063</v>
+        <v>500026</v>
       </c>
       <c r="R63" t="n">
-        <v>6792423</v>
+        <v>6792635</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6861,10 +6861,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125693022</v>
+        <v>125693403</v>
       </c>
       <c r="B64" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6872,21 +6872,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6896,10 +6896,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>500026</v>
+        <v>500078</v>
       </c>
       <c r="R64" t="n">
-        <v>6792635</v>
+        <v>6792594</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
         <v>125685734</v>
       </c>
       <c r="B65" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>125685660</v>
       </c>
       <c r="B66" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>125685335</v>
       </c>
       <c r="B67" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7263,32 +7263,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125888195</v>
+        <v>125892998</v>
       </c>
       <c r="B68" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500310</v>
+        <v>500188</v>
       </c>
       <c r="R68" t="n">
-        <v>6792516</v>
+        <v>6792496</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,11 +7334,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7365,50 +7360,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125894731</v>
+        <v>125893046</v>
       </c>
       <c r="B69" t="n">
-        <v>57651</v>
+        <v>8447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500128</v>
+        <v>500207</v>
       </c>
       <c r="R69" t="n">
-        <v>6792590</v>
+        <v>6792488</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7467,32 +7457,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125892998</v>
+        <v>125888195</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7502,10 +7492,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500188</v>
+        <v>500310</v>
       </c>
       <c r="R70" t="n">
-        <v>6792496</v>
+        <v>6792516</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7538,6 +7528,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7564,45 +7559,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125893046</v>
+        <v>125894731</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>57651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500207</v>
+        <v>500128</v>
       </c>
       <c r="R71" t="n">
-        <v>6792488</v>
+        <v>6792590</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7664,7 +7664,7 @@
         <v>125889107</v>
       </c>
       <c r="B72" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>125890092</v>
       </c>
       <c r="B77" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>125891809</v>
       </c>
       <c r="B78" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>125890555</v>
       </c>
       <c r="B79" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8437,10 +8437,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125888740</v>
+        <v>125890407</v>
       </c>
       <c r="B80" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8448,39 +8448,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500306</v>
+        <v>500242</v>
       </c>
       <c r="R80" t="n">
-        <v>6792466</v>
+        <v>6792408</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8513,6 +8508,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8539,32 +8539,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125892266</v>
+        <v>125892653</v>
       </c>
       <c r="B81" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8574,10 +8574,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500158</v>
+        <v>500151</v>
       </c>
       <c r="R81" t="n">
-        <v>6792441</v>
+        <v>6792458</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8636,32 +8636,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125888709</v>
+        <v>125889406</v>
       </c>
       <c r="B82" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500311</v>
+        <v>500257</v>
       </c>
       <c r="R82" t="n">
-        <v>6792502</v>
+        <v>6792475</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8733,10 +8733,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125890407</v>
+        <v>125895109</v>
       </c>
       <c r="B83" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8744,21 +8744,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>500242</v>
+        <v>499985</v>
       </c>
       <c r="R83" t="n">
-        <v>6792408</v>
+        <v>6792633</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8804,11 +8804,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8835,10 +8830,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125892653</v>
+        <v>125888740</v>
       </c>
       <c r="B84" t="n">
-        <v>78968</v>
+        <v>57811</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8846,34 +8841,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500151</v>
+        <v>500306</v>
       </c>
       <c r="R84" t="n">
-        <v>6792458</v>
+        <v>6792466</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8932,32 +8932,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125889406</v>
+        <v>125892266</v>
       </c>
       <c r="B85" t="n">
-        <v>79586</v>
+        <v>8447</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8967,10 +8967,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500257</v>
+        <v>500158</v>
       </c>
       <c r="R85" t="n">
-        <v>6792475</v>
+        <v>6792441</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9029,32 +9029,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125895109</v>
+        <v>125888709</v>
       </c>
       <c r="B86" t="n">
-        <v>79586</v>
+        <v>8447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>499985</v>
+        <v>500311</v>
       </c>
       <c r="R86" t="n">
-        <v>6792633</v>
+        <v>6792502</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9129,7 +9129,7 @@
         <v>125892215</v>
       </c>
       <c r="B87" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>125889155</v>
       </c>
       <c r="B88" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>125891598</v>
       </c>
       <c r="B89" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>125889889</v>
       </c>
       <c r="B92" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9708,32 +9708,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125888352</v>
+        <v>125896400</v>
       </c>
       <c r="B93" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>500310</v>
+        <v>500351</v>
       </c>
       <c r="R93" t="n">
-        <v>6792516</v>
+        <v>6792369</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125896400</v>
+        <v>125889879</v>
       </c>
       <c r="B94" t="n">
-        <v>79557</v>
+        <v>78731</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>500351</v>
+        <v>500237</v>
       </c>
       <c r="R94" t="n">
-        <v>6792369</v>
+        <v>6792422</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125889879</v>
+        <v>125895107</v>
       </c>
       <c r="B95" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>500237</v>
+        <v>499985</v>
       </c>
       <c r="R95" t="n">
-        <v>6792422</v>
+        <v>6792633</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,32 +9999,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125895107</v>
+        <v>125888352</v>
       </c>
       <c r="B96" t="n">
-        <v>78727</v>
+        <v>8447</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>499985</v>
+        <v>500310</v>
       </c>
       <c r="R96" t="n">
-        <v>6792633</v>
+        <v>6792516</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10196,7 +10196,7 @@
         <v>125890971</v>
       </c>
       <c r="B98" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>125893327</v>
       </c>
       <c r="B101" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>125892219</v>
       </c>
       <c r="B102" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125892224</v>
+        <v>125889615</v>
       </c>
       <c r="B103" t="n">
-        <v>78726</v>
+        <v>8447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500158</v>
+        <v>500202</v>
       </c>
       <c r="R103" t="n">
-        <v>6792441</v>
+        <v>6792435</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10775,10 +10775,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125896058</v>
+        <v>125892224</v>
       </c>
       <c r="B104" t="n">
-        <v>78968</v>
+        <v>78730</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500351</v>
+        <v>500158</v>
       </c>
       <c r="R104" t="n">
-        <v>6792369</v>
+        <v>6792441</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,11 +10846,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10877,10 +10872,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125891964</v>
+        <v>125896058</v>
       </c>
       <c r="B105" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10888,21 +10883,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10912,10 +10907,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500111</v>
+        <v>500351</v>
       </c>
       <c r="R105" t="n">
-        <v>6792428</v>
+        <v>6792369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10948,6 +10943,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125889615</v>
+        <v>125891964</v>
       </c>
       <c r="B106" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500202</v>
+        <v>500111</v>
       </c>
       <c r="R106" t="n">
-        <v>6792435</v>
+        <v>6792428</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11074,7 +11074,7 @@
         <v>125896524</v>
       </c>
       <c r="B107" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>125889090</v>
       </c>
       <c r="B108" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11566,34 +11566,30 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125892433</v>
+        <v>125894266</v>
       </c>
       <c r="B112" t="n">
-        <v>79557</v>
+        <v>98258</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>223597</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11601,10 +11597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500160</v>
+        <v>500128</v>
       </c>
       <c r="R112" t="n">
-        <v>6792451</v>
+        <v>6792590</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11663,30 +11659,34 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125894266</v>
+        <v>125892433</v>
       </c>
       <c r="B113" t="n">
-        <v>98254</v>
+        <v>79561</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>223597</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500128</v>
+        <v>500160</v>
       </c>
       <c r="R113" t="n">
-        <v>6792590</v>
+        <v>6792451</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,10 +11756,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125893637</v>
+        <v>125890126</v>
       </c>
       <c r="B114" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500246</v>
+        <v>500242</v>
       </c>
       <c r="R114" t="n">
-        <v>6792558</v>
+        <v>6792408</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11827,11 +11827,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11858,10 +11853,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125890126</v>
+        <v>125893637</v>
       </c>
       <c r="B115" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11869,21 +11864,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11893,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500242</v>
+        <v>500246</v>
       </c>
       <c r="R115" t="n">
-        <v>6792408</v>
+        <v>6792558</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11929,6 +11924,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11958,7 +11958,7 @@
         <v>125892154</v>
       </c>
       <c r="B116" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>125894500</v>
       </c>
       <c r="B117" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125892496</v>
+        <v>125893148</v>
       </c>
       <c r="B120" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500145</v>
+        <v>500251</v>
       </c>
       <c r="R120" t="n">
-        <v>6792446</v>
+        <v>6792496</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,11 +12414,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12445,32 +12440,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125888695</v>
+        <v>125889503</v>
       </c>
       <c r="B121" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12480,10 +12475,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500311</v>
+        <v>500257</v>
       </c>
       <c r="R121" t="n">
-        <v>6792502</v>
+        <v>6792475</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12516,11 +12511,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12547,32 +12537,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12582,10 +12572,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R122" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12618,6 +12608,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12644,32 +12639,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125889503</v>
+        <v>125892496</v>
       </c>
       <c r="B123" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12679,10 +12674,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R123" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12715,6 +12710,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12741,32 +12741,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125896611</v>
+        <v>125891471</v>
       </c>
       <c r="B124" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12776,10 +12776,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500384</v>
+        <v>500181</v>
       </c>
       <c r="R124" t="n">
-        <v>6792529</v>
+        <v>6792401</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12812,11 +12812,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12843,10 +12838,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125892207</v>
+        <v>125894132</v>
       </c>
       <c r="B125" t="n">
-        <v>79586</v>
+        <v>78731</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12854,21 +12849,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12878,10 +12873,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500158</v>
+        <v>500128</v>
       </c>
       <c r="R125" t="n">
-        <v>6792441</v>
+        <v>6792590</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12940,32 +12935,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125891471</v>
+        <v>125896611</v>
       </c>
       <c r="B126" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12975,10 +12970,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500181</v>
+        <v>500384</v>
       </c>
       <c r="R126" t="n">
-        <v>6792401</v>
+        <v>6792529</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13011,6 +13006,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13037,10 +13037,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125896030</v>
+        <v>125892207</v>
       </c>
       <c r="B127" t="n">
-        <v>57651</v>
+        <v>79590</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13048,39 +13048,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500351</v>
+        <v>500158</v>
       </c>
       <c r="R127" t="n">
-        <v>6792369</v>
+        <v>6792441</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13139,10 +13134,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125894132</v>
+        <v>125896030</v>
       </c>
       <c r="B128" t="n">
-        <v>78727</v>
+        <v>57651</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13150,34 +13145,39 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>500128</v>
+        <v>500351</v>
       </c>
       <c r="R128" t="n">
-        <v>6792590</v>
+        <v>6792369</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13239,7 +13239,7 @@
         <v>125894564</v>
       </c>
       <c r="B129" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>125892025</v>
       </c>
       <c r="B130" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13435,10 +13435,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125893307</v>
+        <v>125891498</v>
       </c>
       <c r="B131" t="n">
-        <v>79586</v>
+        <v>57648</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13446,34 +13446,39 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>500271</v>
+        <v>500166</v>
       </c>
       <c r="R131" t="n">
-        <v>6792529</v>
+        <v>6792413</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13532,32 +13537,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125891649</v>
+        <v>125890887</v>
       </c>
       <c r="B132" t="n">
-        <v>79586</v>
+        <v>8447</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13567,10 +13572,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500166</v>
+        <v>500282</v>
       </c>
       <c r="R132" t="n">
-        <v>6792387</v>
+        <v>6792389</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13629,50 +13634,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125891498</v>
+        <v>125893186</v>
       </c>
       <c r="B133" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500166</v>
+        <v>500247</v>
       </c>
       <c r="R133" t="n">
-        <v>6792413</v>
+        <v>6792519</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13731,32 +13731,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125890887</v>
+        <v>125892751</v>
       </c>
       <c r="B134" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500282</v>
+        <v>500151</v>
       </c>
       <c r="R134" t="n">
-        <v>6792389</v>
+        <v>6792458</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13828,32 +13828,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125893186</v>
+        <v>125893307</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13863,10 +13863,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500247</v>
+        <v>500271</v>
       </c>
       <c r="R135" t="n">
-        <v>6792519</v>
+        <v>6792529</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13925,10 +13925,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125892751</v>
+        <v>125891649</v>
       </c>
       <c r="B136" t="n">
-        <v>78727</v>
+        <v>79590</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13936,21 +13936,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13960,10 +13960,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500151</v>
+        <v>500166</v>
       </c>
       <c r="R136" t="n">
-        <v>6792458</v>
+        <v>6792387</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14022,32 +14022,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125889773</v>
+        <v>125892352</v>
       </c>
       <c r="B137" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14057,10 +14057,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>500237</v>
+        <v>500165</v>
       </c>
       <c r="R137" t="n">
-        <v>6792422</v>
+        <v>6792432</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14119,10 +14119,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125892352</v>
+        <v>125889010</v>
       </c>
       <c r="B138" t="n">
-        <v>79557</v>
+        <v>78731</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14130,21 +14130,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14154,10 +14154,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>500165</v>
+        <v>500286</v>
       </c>
       <c r="R138" t="n">
-        <v>6792432</v>
+        <v>6792459</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14216,32 +14216,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125889010</v>
+        <v>125889773</v>
       </c>
       <c r="B139" t="n">
-        <v>78727</v>
+        <v>8447</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>500286</v>
+        <v>500237</v>
       </c>
       <c r="R139" t="n">
-        <v>6792459</v>
+        <v>6792422</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14316,7 +14316,7 @@
         <v>125896454</v>
       </c>
       <c r="B140" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>125889266</v>
       </c>
       <c r="B141" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>125896535</v>
       </c>
       <c r="B142" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>125896642</v>
       </c>
       <c r="B143" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>125892643</v>
       </c>
       <c r="B144" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>125889379</v>
       </c>
       <c r="B145" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>125892160</v>
       </c>
       <c r="B146" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>125896772</v>
       </c>
       <c r="B147" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>125891864</v>
       </c>
       <c r="B148" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15201,50 +15201,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125888369</v>
+        <v>125892001</v>
       </c>
       <c r="B149" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500310</v>
+        <v>500111</v>
       </c>
       <c r="R149" t="n">
-        <v>6792516</v>
+        <v>6792428</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15303,45 +15298,50 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125892001</v>
+        <v>125888369</v>
       </c>
       <c r="B150" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500111</v>
+        <v>500310</v>
       </c>
       <c r="R150" t="n">
-        <v>6792428</v>
+        <v>6792516</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15403,7 +15403,7 @@
         <v>125888908</v>
       </c>
       <c r="B151" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15497,32 +15497,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125888498</v>
+        <v>125889396</v>
       </c>
       <c r="B152" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500311</v>
+        <v>500257</v>
       </c>
       <c r="R152" t="n">
-        <v>6792509</v>
+        <v>6792475</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15594,10 +15594,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125889396</v>
+        <v>125891609</v>
       </c>
       <c r="B153" t="n">
-        <v>79557</v>
+        <v>78731</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15605,21 +15605,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15629,10 +15629,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500257</v>
+        <v>500153</v>
       </c>
       <c r="R153" t="n">
-        <v>6792475</v>
+        <v>6792391</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15691,32 +15691,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125891609</v>
+        <v>125888498</v>
       </c>
       <c r="B154" t="n">
-        <v>78727</v>
+        <v>8447</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500153</v>
+        <v>500311</v>
       </c>
       <c r="R154" t="n">
-        <v>6792391</v>
+        <v>6792509</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15791,7 +15791,7 @@
         <v>125895017</v>
       </c>
       <c r="B155" t="n">
-        <v>78992</v>
+        <v>78996</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>125895229</v>
       </c>
       <c r="B156" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>125888924</v>
       </c>
       <c r="B157" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>125889676</v>
       </c>
       <c r="B158" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>125892942</v>
       </c>
       <c r="B159" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>125892637</v>
       </c>
       <c r="B160" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1906,10 +1906,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125684974</v>
+        <v>125693564</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1917,21 +1917,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500076</v>
+        <v>500087</v>
       </c>
       <c r="R14" t="n">
-        <v>6792407</v>
+        <v>6792574</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,10 +2003,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125693564</v>
+        <v>125684006</v>
       </c>
       <c r="B15" t="n">
-        <v>78730</v>
+        <v>57648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2014,34 +2014,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500087</v>
+        <v>500326</v>
       </c>
       <c r="R15" t="n">
-        <v>6792574</v>
+        <v>6792440</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2074,6 +2079,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2100,50 +2110,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125684006</v>
+        <v>125684253</v>
       </c>
       <c r="B16" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500326</v>
+        <v>500039</v>
       </c>
       <c r="R16" t="n">
-        <v>6792440</v>
+        <v>6792388</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,11 +2181,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,32 +2406,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125684253</v>
+        <v>125684974</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500039</v>
+        <v>500076</v>
       </c>
       <c r="R19" t="n">
-        <v>6792388</v>
+        <v>6792407</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125693241</v>
+        <v>125686305</v>
       </c>
       <c r="B29" t="n">
-        <v>57648</v>
+        <v>78731</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500047</v>
+        <v>499963</v>
       </c>
       <c r="R29" t="n">
-        <v>6792612</v>
+        <v>6792480</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3477,6 +3477,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3503,10 +3508,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125686305</v>
+        <v>125693249</v>
       </c>
       <c r="B30" t="n">
-        <v>78731</v>
+        <v>79561</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,21 +3519,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3538,10 +3543,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499963</v>
+        <v>500047</v>
       </c>
       <c r="R30" t="n">
-        <v>6792480</v>
+        <v>6792612</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3574,11 +3579,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3605,10 +3605,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125693249</v>
+        <v>125685148</v>
       </c>
       <c r="B31" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3616,21 +3616,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500047</v>
+        <v>500040</v>
       </c>
       <c r="R31" t="n">
-        <v>6792612</v>
+        <v>6792406</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,32 +3702,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125683895</v>
+        <v>125693241</v>
       </c>
       <c r="B32" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500326</v>
+        <v>500047</v>
       </c>
       <c r="R32" t="n">
-        <v>6792440</v>
+        <v>6792612</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3773,11 +3773,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3804,32 +3799,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125685148</v>
+        <v>125683895</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3839,10 +3834,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500040</v>
+        <v>500326</v>
       </c>
       <c r="R33" t="n">
-        <v>6792406</v>
+        <v>6792440</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3875,6 +3870,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5978,32 +5978,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125690170</v>
+        <v>125683878</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>500018</v>
+        <v>499954</v>
       </c>
       <c r="R55" t="n">
-        <v>6792528</v>
+        <v>6792394</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,6 +6049,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6075,32 +6080,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125683878</v>
+        <v>125685813</v>
       </c>
       <c r="B56" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6110,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499954</v>
+        <v>499996</v>
       </c>
       <c r="R56" t="n">
-        <v>6792394</v>
+        <v>6792435</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6146,11 +6151,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6177,10 +6177,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125685813</v>
+        <v>125690170</v>
       </c>
       <c r="B57" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6188,21 +6188,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499996</v>
+        <v>500018</v>
       </c>
       <c r="R57" t="n">
-        <v>6792435</v>
+        <v>6792528</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7758,32 +7758,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125893261</v>
+        <v>125890555</v>
       </c>
       <c r="B73" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>500271</v>
+        <v>500282</v>
       </c>
       <c r="R73" t="n">
-        <v>6792529</v>
+        <v>6792389</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7855,7 +7855,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125896279</v>
+        <v>125893261</v>
       </c>
       <c r="B74" t="n">
         <v>8447</v>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500351</v>
+        <v>500271</v>
       </c>
       <c r="R74" t="n">
-        <v>6792369</v>
+        <v>6792529</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7952,7 +7952,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125895125</v>
+        <v>125896279</v>
       </c>
       <c r="B75" t="n">
         <v>8447</v>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>499985</v>
+        <v>500351</v>
       </c>
       <c r="R75" t="n">
-        <v>6792633</v>
+        <v>6792369</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125890234</v>
+        <v>125895125</v>
       </c>
       <c r="B76" t="n">
         <v>8447</v>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>500242</v>
+        <v>499985</v>
       </c>
       <c r="R76" t="n">
-        <v>6792408</v>
+        <v>6792633</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8146,32 +8146,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125890092</v>
+        <v>125890234</v>
       </c>
       <c r="B77" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8243,7 +8243,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125891809</v>
+        <v>125890092</v>
       </c>
       <c r="B78" t="n">
         <v>79561</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>500166</v>
+        <v>500242</v>
       </c>
       <c r="R78" t="n">
-        <v>6792387</v>
+        <v>6792408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8340,10 +8340,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125890555</v>
+        <v>125891809</v>
       </c>
       <c r="B79" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8351,21 +8351,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500282</v>
+        <v>500166</v>
       </c>
       <c r="R79" t="n">
-        <v>6792389</v>
+        <v>6792387</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125889615</v>
+        <v>125892224</v>
       </c>
       <c r="B103" t="n">
-        <v>8447</v>
+        <v>78730</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500202</v>
+        <v>500158</v>
       </c>
       <c r="R103" t="n">
-        <v>6792435</v>
+        <v>6792441</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10775,10 +10775,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125892224</v>
+        <v>125896058</v>
       </c>
       <c r="B104" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500158</v>
+        <v>500351</v>
       </c>
       <c r="R104" t="n">
-        <v>6792441</v>
+        <v>6792369</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,6 +10846,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10872,10 +10877,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125896058</v>
+        <v>125891964</v>
       </c>
       <c r="B105" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10883,21 +10888,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10907,10 +10912,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500351</v>
+        <v>500111</v>
       </c>
       <c r="R105" t="n">
-        <v>6792369</v>
+        <v>6792428</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10943,11 +10948,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125891964</v>
+        <v>125889615</v>
       </c>
       <c r="B106" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500111</v>
+        <v>500202</v>
       </c>
       <c r="R106" t="n">
-        <v>6792428</v>
+        <v>6792435</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12741,32 +12741,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125891471</v>
+        <v>125896611</v>
       </c>
       <c r="B124" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12776,10 +12776,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500181</v>
+        <v>500384</v>
       </c>
       <c r="R124" t="n">
-        <v>6792401</v>
+        <v>6792529</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12812,6 +12812,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12838,10 +12843,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125894132</v>
+        <v>125892207</v>
       </c>
       <c r="B125" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12849,21 +12854,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12873,10 +12878,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500128</v>
+        <v>500158</v>
       </c>
       <c r="R125" t="n">
-        <v>6792590</v>
+        <v>6792441</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12935,10 +12940,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125896611</v>
+        <v>125896030</v>
       </c>
       <c r="B126" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12946,34 +12951,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500384</v>
+        <v>500351</v>
       </c>
       <c r="R126" t="n">
-        <v>6792529</v>
+        <v>6792369</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13006,11 +13016,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13037,32 +13042,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125892207</v>
+        <v>125891471</v>
       </c>
       <c r="B127" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13072,10 +13077,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500158</v>
+        <v>500181</v>
       </c>
       <c r="R127" t="n">
-        <v>6792441</v>
+        <v>6792401</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13134,10 +13139,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125896030</v>
+        <v>125894132</v>
       </c>
       <c r="B128" t="n">
-        <v>57651</v>
+        <v>78731</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13145,39 +13150,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>500351</v>
+        <v>500128</v>
       </c>
       <c r="R128" t="n">
-        <v>6792369</v>
+        <v>6792590</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15201,45 +15201,50 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125892001</v>
+        <v>125888369</v>
       </c>
       <c r="B149" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500111</v>
+        <v>500310</v>
       </c>
       <c r="R149" t="n">
-        <v>6792428</v>
+        <v>6792516</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15298,10 +15303,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125888369</v>
+        <v>125888908</v>
       </c>
       <c r="B150" t="n">
-        <v>57648</v>
+        <v>79561</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15309,39 +15314,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500310</v>
+        <v>500306</v>
       </c>
       <c r="R150" t="n">
-        <v>6792516</v>
+        <v>6792466</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15400,32 +15400,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125888908</v>
+        <v>125892001</v>
       </c>
       <c r="B151" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15435,10 +15435,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500306</v>
+        <v>500111</v>
       </c>
       <c r="R151" t="n">
-        <v>6792466</v>
+        <v>6792428</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15497,32 +15497,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125889396</v>
+        <v>125888498</v>
       </c>
       <c r="B152" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500257</v>
+        <v>500311</v>
       </c>
       <c r="R152" t="n">
-        <v>6792475</v>
+        <v>6792509</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15594,10 +15594,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125891609</v>
+        <v>125889396</v>
       </c>
       <c r="B153" t="n">
-        <v>78731</v>
+        <v>79561</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15605,21 +15605,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15629,10 +15629,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500153</v>
+        <v>500257</v>
       </c>
       <c r="R153" t="n">
-        <v>6792391</v>
+        <v>6792475</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15691,32 +15691,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125888498</v>
+        <v>125891609</v>
       </c>
       <c r="B154" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500311</v>
+        <v>500153</v>
       </c>
       <c r="R154" t="n">
-        <v>6792509</v>
+        <v>6792391</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1023,32 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125686874</v>
+        <v>125685630</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500013</v>
+        <v>499996</v>
       </c>
       <c r="R5" t="n">
-        <v>6792493</v>
+        <v>6792394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,11 +1094,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,32 +1120,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125693671</v>
+        <v>125686732</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500087</v>
+        <v>499990</v>
       </c>
       <c r="R6" t="n">
-        <v>6792574</v>
+        <v>6792488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1191,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,32 +1222,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125687215</v>
+        <v>125686800</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499945</v>
+        <v>500007</v>
       </c>
       <c r="R7" t="n">
-        <v>6792497</v>
+        <v>6792490</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,32 +1319,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125689836</v>
+        <v>125685407</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499951</v>
+        <v>500063</v>
       </c>
       <c r="R8" t="n">
-        <v>6792574</v>
+        <v>6792381</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,32 +1416,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125686800</v>
+        <v>125686874</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500007</v>
+        <v>500013</v>
       </c>
       <c r="R9" t="n">
-        <v>6792490</v>
+        <v>6792493</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,6 +1487,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,32 +1518,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125686732</v>
+        <v>125693671</v>
       </c>
       <c r="B10" t="n">
-        <v>78730</v>
+        <v>8447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499990</v>
+        <v>500087</v>
       </c>
       <c r="R10" t="n">
-        <v>6792488</v>
+        <v>6792574</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,11 +1589,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,32 +1615,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125685630</v>
+        <v>125687215</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499996</v>
+        <v>499945</v>
       </c>
       <c r="R11" t="n">
-        <v>6792394</v>
+        <v>6792497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,32 +1712,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125685407</v>
+        <v>125689836</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500063</v>
+        <v>499951</v>
       </c>
       <c r="R12" t="n">
-        <v>6792381</v>
+        <v>6792574</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125693564</v>
+        <v>125684006</v>
       </c>
       <c r="B14" t="n">
-        <v>78730</v>
+        <v>57648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1917,34 +1917,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500087</v>
+        <v>500326</v>
       </c>
       <c r="R14" t="n">
-        <v>6792574</v>
+        <v>6792440</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1977,6 +1982,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,50 +2013,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125684006</v>
+        <v>125684253</v>
       </c>
       <c r="B15" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500326</v>
+        <v>500039</v>
       </c>
       <c r="R15" t="n">
-        <v>6792440</v>
+        <v>6792388</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,11 +2084,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2110,32 +2110,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125684253</v>
+        <v>125684974</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500039</v>
+        <v>500076</v>
       </c>
       <c r="R16" t="n">
-        <v>6792388</v>
+        <v>6792407</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125685313</v>
+        <v>125693564</v>
       </c>
       <c r="B17" t="n">
-        <v>78731</v>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2218,21 +2218,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500063</v>
+        <v>500087</v>
       </c>
       <c r="R17" t="n">
-        <v>6792381</v>
+        <v>6792574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,11 +2278,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Muljöbilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2309,10 +2304,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125692802</v>
+        <v>125685313</v>
       </c>
       <c r="B18" t="n">
-        <v>79561</v>
+        <v>78731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2320,21 +2315,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2344,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499954</v>
+        <v>500063</v>
       </c>
       <c r="R18" t="n">
-        <v>6792650</v>
+        <v>6792381</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,6 +2375,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Muljöbilder</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125684974</v>
+        <v>125692802</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500076</v>
+        <v>499954</v>
       </c>
       <c r="R19" t="n">
-        <v>6792407</v>
+        <v>6792650</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125684537</v>
+        <v>125690007</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500039</v>
+        <v>499989</v>
       </c>
       <c r="R20" t="n">
-        <v>6792388</v>
+        <v>6792563</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125690007</v>
+        <v>125684537</v>
       </c>
       <c r="B21" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499989</v>
+        <v>500039</v>
       </c>
       <c r="R21" t="n">
-        <v>6792563</v>
+        <v>6792388</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2707,10 +2707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125686792</v>
+        <v>125686316</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2718,21 +2718,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499990</v>
+        <v>499963</v>
       </c>
       <c r="R22" t="n">
-        <v>6792488</v>
+        <v>6792480</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125686316</v>
+        <v>125690119</v>
       </c>
       <c r="B23" t="n">
-        <v>78730</v>
+        <v>79590</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2815,21 +2815,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499963</v>
+        <v>499990</v>
       </c>
       <c r="R23" t="n">
-        <v>6792480</v>
+        <v>6792543</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2875,6 +2875,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2901,10 +2906,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125690119</v>
+        <v>125686792</v>
       </c>
       <c r="B24" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2912,21 +2917,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2939,7 +2944,7 @@
         <v>499990</v>
       </c>
       <c r="R24" t="n">
-        <v>6792543</v>
+        <v>6792488</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2972,11 +2977,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3105,32 +3105,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125685512</v>
+        <v>125689285</v>
       </c>
       <c r="B26" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499996</v>
+        <v>499942</v>
       </c>
       <c r="R26" t="n">
-        <v>6792394</v>
+        <v>6792546</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3207,32 +3207,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125689285</v>
+        <v>125685512</v>
       </c>
       <c r="B27" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499942</v>
+        <v>499996</v>
       </c>
       <c r="R27" t="n">
-        <v>6792546</v>
+        <v>6792394</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125686343</v>
+        <v>125693241</v>
       </c>
       <c r="B28" t="n">
-        <v>79590</v>
+        <v>57648</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3320,21 +3320,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499963</v>
+        <v>500047</v>
       </c>
       <c r="R28" t="n">
-        <v>6792480</v>
+        <v>6792612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3406,32 +3406,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125686305</v>
+        <v>125683895</v>
       </c>
       <c r="B29" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499963</v>
+        <v>500326</v>
       </c>
       <c r="R29" t="n">
-        <v>6792480</v>
+        <v>6792440</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125693249</v>
+        <v>125686305</v>
       </c>
       <c r="B30" t="n">
-        <v>79561</v>
+        <v>78731</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500047</v>
+        <v>499963</v>
       </c>
       <c r="R30" t="n">
-        <v>6792612</v>
+        <v>6792480</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3579,6 +3579,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3605,10 +3610,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125685148</v>
+        <v>125693249</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3616,21 +3621,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3640,10 +3645,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500040</v>
+        <v>500047</v>
       </c>
       <c r="R31" t="n">
-        <v>6792406</v>
+        <v>6792612</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,10 +3707,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125693241</v>
+        <v>125686343</v>
       </c>
       <c r="B32" t="n">
-        <v>57648</v>
+        <v>79590</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3713,21 +3718,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3737,10 +3742,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500047</v>
+        <v>499963</v>
       </c>
       <c r="R32" t="n">
-        <v>6792612</v>
+        <v>6792480</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3799,32 +3804,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125683895</v>
+        <v>125685148</v>
       </c>
       <c r="B33" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3834,10 +3839,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500326</v>
+        <v>500040</v>
       </c>
       <c r="R33" t="n">
-        <v>6792440</v>
+        <v>6792406</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3870,11 +3875,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3901,10 +3901,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125684693</v>
+        <v>125685808</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3912,21 +3912,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500077</v>
+        <v>499996</v>
       </c>
       <c r="R34" t="n">
-        <v>6792400</v>
+        <v>6792435</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3972,6 +3972,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3998,32 +4003,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125687329</v>
+        <v>125684693</v>
       </c>
       <c r="B35" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4038,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499947</v>
+        <v>500077</v>
       </c>
       <c r="R35" t="n">
-        <v>6792525</v>
+        <v>6792400</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4095,32 +4100,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125685808</v>
+        <v>125687329</v>
       </c>
       <c r="B36" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4130,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499996</v>
+        <v>499947</v>
       </c>
       <c r="R36" t="n">
-        <v>6792435</v>
+        <v>6792525</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4166,11 +4171,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4197,7 +4197,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125691930</v>
+        <v>125684984</v>
       </c>
       <c r="B37" t="n">
         <v>78972</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500001</v>
+        <v>500076</v>
       </c>
       <c r="R37" t="n">
-        <v>6792610</v>
+        <v>6792415</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125684984</v>
+        <v>125691930</v>
       </c>
       <c r="B38" t="n">
         <v>78972</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500076</v>
+        <v>500001</v>
       </c>
       <c r="R38" t="n">
-        <v>6792415</v>
+        <v>6792610</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4391,10 +4391,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125686924</v>
+        <v>125687294</v>
       </c>
       <c r="B39" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4402,21 +4402,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500010</v>
+        <v>499945</v>
       </c>
       <c r="R39" t="n">
-        <v>6792501</v>
+        <v>6792497</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4488,10 +4488,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687294</v>
+        <v>125686924</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4499,21 +4499,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499945</v>
+        <v>500010</v>
       </c>
       <c r="R40" t="n">
-        <v>6792497</v>
+        <v>6792501</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4585,7 +4585,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125693372</v>
+        <v>125690589</v>
       </c>
       <c r="B41" t="n">
         <v>78972</v>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>500078</v>
+        <v>500043</v>
       </c>
       <c r="R41" t="n">
-        <v>6792594</v>
+        <v>6792510</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4656,6 +4656,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4682,10 +4687,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125688845</v>
+        <v>125693372</v>
       </c>
       <c r="B42" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4693,21 +4698,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4717,10 +4722,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499970</v>
+        <v>500078</v>
       </c>
       <c r="R42" t="n">
-        <v>6792544</v>
+        <v>6792594</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4753,11 +4758,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4784,10 +4784,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125690295</v>
+        <v>125688845</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500031</v>
+        <v>499970</v>
       </c>
       <c r="R43" t="n">
-        <v>6792511</v>
+        <v>6792544</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4855,6 +4855,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4881,7 +4886,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125690589</v>
+        <v>125690295</v>
       </c>
       <c r="B44" t="n">
         <v>78972</v>
@@ -4916,10 +4921,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500043</v>
+        <v>500031</v>
       </c>
       <c r="R44" t="n">
-        <v>6792510</v>
+        <v>6792511</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4952,11 +4957,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5677,32 +5677,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125685693</v>
+        <v>125690154</v>
       </c>
       <c r="B52" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5712,10 +5712,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500002</v>
+        <v>499990</v>
       </c>
       <c r="R52" t="n">
-        <v>6792449</v>
+        <v>6792543</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5779,7 +5779,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125686894</v>
+        <v>125685693</v>
       </c>
       <c r="B53" t="n">
         <v>8447</v>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500010</v>
+        <v>500002</v>
       </c>
       <c r="R53" t="n">
-        <v>6792501</v>
+        <v>6792449</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5850,6 +5850,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5876,32 +5881,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125690154</v>
+        <v>125686894</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5911,10 +5916,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499990</v>
+        <v>500010</v>
       </c>
       <c r="R54" t="n">
-        <v>6792543</v>
+        <v>6792501</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5947,11 +5952,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5978,32 +5978,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125683878</v>
+        <v>125690170</v>
       </c>
       <c r="B55" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499954</v>
+        <v>500018</v>
       </c>
       <c r="R55" t="n">
-        <v>6792394</v>
+        <v>6792528</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,11 +6049,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6080,10 +6075,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125685813</v>
+        <v>125685885</v>
       </c>
       <c r="B56" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6091,21 +6086,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6115,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499996</v>
+        <v>500002</v>
       </c>
       <c r="R56" t="n">
-        <v>6792435</v>
+        <v>6792449</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6177,10 +6172,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125690170</v>
+        <v>125685813</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6188,21 +6183,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6212,10 +6207,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>500018</v>
+        <v>499996</v>
       </c>
       <c r="R57" t="n">
-        <v>6792528</v>
+        <v>6792435</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6274,32 +6269,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125685885</v>
+        <v>125683878</v>
       </c>
       <c r="B58" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6304,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>500002</v>
+        <v>499954</v>
       </c>
       <c r="R58" t="n">
-        <v>6792449</v>
+        <v>6792394</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6345,6 +6340,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6958,7 +6958,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125685734</v>
+        <v>125685660</v>
       </c>
       <c r="B65" t="n">
         <v>78972</v>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>499996</v>
+        <v>499989</v>
       </c>
       <c r="R65" t="n">
-        <v>6792435</v>
+        <v>6792445</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7029,11 +7029,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7060,7 +7055,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125685660</v>
+        <v>125685734</v>
       </c>
       <c r="B66" t="n">
         <v>78972</v>
@@ -7095,10 +7090,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>499989</v>
+        <v>499996</v>
       </c>
       <c r="R66" t="n">
-        <v>6792445</v>
+        <v>6792435</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7131,6 +7126,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7263,32 +7263,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125892998</v>
+        <v>125888195</v>
       </c>
       <c r="B68" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500188</v>
+        <v>500310</v>
       </c>
       <c r="R68" t="n">
-        <v>6792496</v>
+        <v>6792516</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,6 +7334,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7360,45 +7365,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125893046</v>
+        <v>125894731</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>57651</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500207</v>
+        <v>500128</v>
       </c>
       <c r="R69" t="n">
-        <v>6792488</v>
+        <v>6792590</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7457,32 +7467,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125888195</v>
+        <v>125892998</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7492,10 +7502,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500310</v>
+        <v>500188</v>
       </c>
       <c r="R70" t="n">
-        <v>6792516</v>
+        <v>6792496</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7528,11 +7538,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7559,50 +7564,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125894731</v>
+        <v>125893046</v>
       </c>
       <c r="B71" t="n">
-        <v>57651</v>
+        <v>8447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500128</v>
+        <v>500207</v>
       </c>
       <c r="R71" t="n">
-        <v>6792590</v>
+        <v>6792488</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9611,32 +9611,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125889889</v>
+        <v>125888352</v>
       </c>
       <c r="B92" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>500237</v>
+        <v>500310</v>
       </c>
       <c r="R92" t="n">
-        <v>6792422</v>
+        <v>6792516</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125896400</v>
+        <v>125889879</v>
       </c>
       <c r="B93" t="n">
-        <v>79561</v>
+        <v>78731</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,21 +9719,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>500351</v>
+        <v>500237</v>
       </c>
       <c r="R93" t="n">
-        <v>6792369</v>
+        <v>6792422</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,7 +9805,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125889879</v>
+        <v>125895107</v>
       </c>
       <c r="B94" t="n">
         <v>78731</v>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>500237</v>
+        <v>499985</v>
       </c>
       <c r="R94" t="n">
-        <v>6792422</v>
+        <v>6792633</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125895107</v>
+        <v>125896400</v>
       </c>
       <c r="B95" t="n">
-        <v>78731</v>
+        <v>79561</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>499985</v>
+        <v>500351</v>
       </c>
       <c r="R95" t="n">
-        <v>6792633</v>
+        <v>6792369</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,32 +9999,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125888352</v>
+        <v>125889889</v>
       </c>
       <c r="B96" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>500310</v>
+        <v>500237</v>
       </c>
       <c r="R96" t="n">
-        <v>6792516</v>
+        <v>6792422</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125892224</v>
+        <v>125889615</v>
       </c>
       <c r="B103" t="n">
-        <v>78730</v>
+        <v>8447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500158</v>
+        <v>500202</v>
       </c>
       <c r="R103" t="n">
-        <v>6792441</v>
+        <v>6792435</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10877,10 +10877,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125891964</v>
+        <v>125892224</v>
       </c>
       <c r="B105" t="n">
-        <v>79590</v>
+        <v>78730</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10888,21 +10888,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500111</v>
+        <v>500158</v>
       </c>
       <c r="R105" t="n">
-        <v>6792428</v>
+        <v>6792441</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125889615</v>
+        <v>125891964</v>
       </c>
       <c r="B106" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500202</v>
+        <v>500111</v>
       </c>
       <c r="R106" t="n">
-        <v>6792435</v>
+        <v>6792428</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11566,30 +11566,34 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125894266</v>
+        <v>125892433</v>
       </c>
       <c r="B112" t="n">
-        <v>98258</v>
+        <v>79561</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>223597</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11597,10 +11601,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500128</v>
+        <v>500160</v>
       </c>
       <c r="R112" t="n">
-        <v>6792590</v>
+        <v>6792451</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11659,34 +11663,30 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125892433</v>
+        <v>125894266</v>
       </c>
       <c r="B113" t="n">
-        <v>79561</v>
+        <v>98259</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>223597</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500160</v>
+        <v>500128</v>
       </c>
       <c r="R113" t="n">
-        <v>6792451</v>
+        <v>6792590</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,10 +11756,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125890126</v>
+        <v>125893637</v>
       </c>
       <c r="B114" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500242</v>
+        <v>500246</v>
       </c>
       <c r="R114" t="n">
-        <v>6792408</v>
+        <v>6792558</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11827,6 +11827,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11853,32 +11858,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125893637</v>
+        <v>125896458</v>
       </c>
       <c r="B115" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11893,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500246</v>
+        <v>500374</v>
       </c>
       <c r="R115" t="n">
-        <v>6792558</v>
+        <v>6792515</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11924,11 +11929,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11955,32 +11955,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125892154</v>
+        <v>125889235</v>
       </c>
       <c r="B116" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11990,10 +11990,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500145</v>
+        <v>500275</v>
       </c>
       <c r="R116" t="n">
-        <v>6792446</v>
+        <v>6792487</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12052,10 +12052,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125894500</v>
+        <v>125890126</v>
       </c>
       <c r="B117" t="n">
-        <v>78730</v>
+        <v>79590</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12063,21 +12063,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12087,10 +12087,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500128</v>
+        <v>500242</v>
       </c>
       <c r="R117" t="n">
-        <v>6792590</v>
+        <v>6792408</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12149,32 +12149,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125896458</v>
+        <v>125892154</v>
       </c>
       <c r="B118" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12184,10 +12184,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>500374</v>
+        <v>500145</v>
       </c>
       <c r="R118" t="n">
-        <v>6792515</v>
+        <v>6792446</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12246,32 +12246,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125889235</v>
+        <v>125894500</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>78730</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>500275</v>
+        <v>500128</v>
       </c>
       <c r="R119" t="n">
-        <v>6792487</v>
+        <v>6792590</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B120" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R120" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,6 +12414,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12440,32 +12445,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125889503</v>
+        <v>125892496</v>
       </c>
       <c r="B121" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12475,10 +12480,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R121" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12511,6 +12516,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12537,32 +12547,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125888695</v>
+        <v>125893148</v>
       </c>
       <c r="B122" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12572,10 +12582,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500311</v>
+        <v>500251</v>
       </c>
       <c r="R122" t="n">
-        <v>6792502</v>
+        <v>6792496</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12608,11 +12618,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12639,32 +12644,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125892496</v>
+        <v>125889503</v>
       </c>
       <c r="B123" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12674,10 +12679,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R123" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12710,11 +12715,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12741,32 +12741,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125896611</v>
+        <v>125891471</v>
       </c>
       <c r="B124" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12776,10 +12776,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500384</v>
+        <v>500181</v>
       </c>
       <c r="R124" t="n">
-        <v>6792529</v>
+        <v>6792401</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12812,11 +12812,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12843,10 +12838,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125892207</v>
+        <v>125894132</v>
       </c>
       <c r="B125" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12854,21 +12849,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12878,10 +12873,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500158</v>
+        <v>500128</v>
       </c>
       <c r="R125" t="n">
-        <v>6792441</v>
+        <v>6792590</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12940,10 +12935,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125896030</v>
+        <v>125892207</v>
       </c>
       <c r="B126" t="n">
-        <v>57651</v>
+        <v>79590</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12951,39 +12946,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500351</v>
+        <v>500158</v>
       </c>
       <c r="R126" t="n">
-        <v>6792369</v>
+        <v>6792441</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13042,45 +13032,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125891471</v>
+        <v>125896030</v>
       </c>
       <c r="B127" t="n">
-        <v>8447</v>
+        <v>57651</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500181</v>
+        <v>500351</v>
       </c>
       <c r="R127" t="n">
-        <v>6792401</v>
+        <v>6792369</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13139,10 +13134,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125894132</v>
+        <v>125896611</v>
       </c>
       <c r="B128" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13150,21 +13145,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13174,10 +13169,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R128" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13210,6 +13205,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13236,10 +13236,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125894564</v>
+        <v>125892025</v>
       </c>
       <c r="B129" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13247,21 +13247,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13271,10 +13271,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>500128</v>
+        <v>500111</v>
       </c>
       <c r="R129" t="n">
-        <v>6792590</v>
+        <v>6792428</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13307,6 +13307,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13333,10 +13338,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125892025</v>
+        <v>125894564</v>
       </c>
       <c r="B130" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13344,21 +13349,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13368,10 +13373,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>500111</v>
+        <v>500128</v>
       </c>
       <c r="R130" t="n">
-        <v>6792428</v>
+        <v>6792590</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13404,11 +13409,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13435,10 +13435,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125891498</v>
+        <v>125893307</v>
       </c>
       <c r="B131" t="n">
-        <v>57648</v>
+        <v>79590</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13446,39 +13446,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>500166</v>
+        <v>500271</v>
       </c>
       <c r="R131" t="n">
-        <v>6792413</v>
+        <v>6792529</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13537,32 +13532,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125890887</v>
+        <v>125891649</v>
       </c>
       <c r="B132" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13572,10 +13567,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500282</v>
+        <v>500166</v>
       </c>
       <c r="R132" t="n">
-        <v>6792389</v>
+        <v>6792387</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13634,7 +13629,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125893186</v>
+        <v>125890887</v>
       </c>
       <c r="B133" t="n">
         <v>8447</v>
@@ -13669,10 +13664,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500247</v>
+        <v>500282</v>
       </c>
       <c r="R133" t="n">
-        <v>6792519</v>
+        <v>6792389</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13731,32 +13726,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125892751</v>
+        <v>125893186</v>
       </c>
       <c r="B134" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13766,10 +13761,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500151</v>
+        <v>500247</v>
       </c>
       <c r="R134" t="n">
-        <v>6792458</v>
+        <v>6792519</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13828,10 +13823,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125893307</v>
+        <v>125892751</v>
       </c>
       <c r="B135" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13839,21 +13834,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13863,10 +13858,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500271</v>
+        <v>500151</v>
       </c>
       <c r="R135" t="n">
-        <v>6792529</v>
+        <v>6792458</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13925,10 +13920,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125891649</v>
+        <v>125891498</v>
       </c>
       <c r="B136" t="n">
-        <v>79590</v>
+        <v>57648</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13936,24 +13931,29 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
@@ -13963,7 +13963,7 @@
         <v>500166</v>
       </c>
       <c r="R136" t="n">
-        <v>6792387</v>
+        <v>6792413</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14022,32 +14022,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125892352</v>
+        <v>125889773</v>
       </c>
       <c r="B137" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14057,10 +14057,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>500165</v>
+        <v>500237</v>
       </c>
       <c r="R137" t="n">
-        <v>6792432</v>
+        <v>6792422</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14216,32 +14216,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125889773</v>
+        <v>125892352</v>
       </c>
       <c r="B139" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>500237</v>
+        <v>500165</v>
       </c>
       <c r="R139" t="n">
-        <v>6792422</v>
+        <v>6792432</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125896454</v>
+        <v>125896535</v>
       </c>
       <c r="B140" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500374</v>
+        <v>500384</v>
       </c>
       <c r="R140" t="n">
-        <v>6792515</v>
+        <v>6792529</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14384,11 +14384,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14415,10 +14410,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125889266</v>
+        <v>125889379</v>
       </c>
       <c r="B141" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14426,21 +14421,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14486,11 +14481,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14517,10 +14507,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125896535</v>
+        <v>125896642</v>
       </c>
       <c r="B142" t="n">
-        <v>78731</v>
+        <v>79561</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14528,21 +14518,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14614,7 +14604,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125896642</v>
+        <v>125892643</v>
       </c>
       <c r="B143" t="n">
         <v>79561</v>
@@ -14649,10 +14639,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500384</v>
+        <v>500151</v>
       </c>
       <c r="R143" t="n">
-        <v>6792529</v>
+        <v>6792458</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14711,7 +14701,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125892643</v>
+        <v>125892160</v>
       </c>
       <c r="B144" t="n">
         <v>79561</v>
@@ -14746,10 +14736,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500151</v>
+        <v>500145</v>
       </c>
       <c r="R144" t="n">
-        <v>6792458</v>
+        <v>6792446</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14808,10 +14798,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125889379</v>
+        <v>125896454</v>
       </c>
       <c r="B145" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14819,21 +14809,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14843,10 +14833,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500257</v>
+        <v>500374</v>
       </c>
       <c r="R145" t="n">
-        <v>6792475</v>
+        <v>6792515</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14879,6 +14869,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14905,10 +14900,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125892160</v>
+        <v>125889266</v>
       </c>
       <c r="B146" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14916,21 +14911,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14940,10 +14935,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R146" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14976,6 +14971,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15002,45 +15002,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125896772</v>
+        <v>125888369</v>
       </c>
       <c r="B147" t="n">
-        <v>92522</v>
+        <v>57648</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500384</v>
+        <v>500310</v>
       </c>
       <c r="R147" t="n">
-        <v>6792529</v>
+        <v>6792516</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15099,32 +15104,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125891864</v>
+        <v>125896772</v>
       </c>
       <c r="B148" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15134,10 +15139,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500126</v>
+        <v>500384</v>
       </c>
       <c r="R148" t="n">
-        <v>6792397</v>
+        <v>6792529</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15170,11 +15175,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15201,10 +15201,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125888369</v>
+        <v>125891864</v>
       </c>
       <c r="B149" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15212,39 +15212,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500310</v>
+        <v>500126</v>
       </c>
       <c r="R149" t="n">
-        <v>6792516</v>
+        <v>6792397</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15277,6 +15272,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15303,32 +15303,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125888908</v>
+        <v>125892001</v>
       </c>
       <c r="B150" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15338,10 +15338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500306</v>
+        <v>500111</v>
       </c>
       <c r="R150" t="n">
-        <v>6792466</v>
+        <v>6792428</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15400,32 +15400,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125892001</v>
+        <v>125888908</v>
       </c>
       <c r="B151" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15435,10 +15435,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500111</v>
+        <v>500306</v>
       </c>
       <c r="R151" t="n">
-        <v>6792428</v>
+        <v>6792466</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15885,10 +15885,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125895229</v>
+        <v>125888924</v>
       </c>
       <c r="B156" t="n">
-        <v>79561</v>
+        <v>78731</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15896,21 +15896,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15920,10 +15920,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>499985</v>
+        <v>500306</v>
       </c>
       <c r="R156" t="n">
-        <v>6792633</v>
+        <v>6792466</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -15982,10 +15982,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125888924</v>
+        <v>125895229</v>
       </c>
       <c r="B157" t="n">
-        <v>78731</v>
+        <v>79561</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15993,21 +15993,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16017,10 +16017,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>500306</v>
+        <v>499985</v>
       </c>
       <c r="R157" t="n">
-        <v>6792466</v>
+        <v>6792633</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -2013,32 +2013,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125684253</v>
+        <v>125684974</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500039</v>
+        <v>500076</v>
       </c>
       <c r="R15" t="n">
-        <v>6792388</v>
+        <v>6792407</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2110,10 +2110,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125684974</v>
+        <v>125693564</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2121,21 +2121,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500076</v>
+        <v>500087</v>
       </c>
       <c r="R16" t="n">
-        <v>6792407</v>
+        <v>6792574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,32 +2207,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125693564</v>
+        <v>125684253</v>
       </c>
       <c r="B17" t="n">
-        <v>78730</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500087</v>
+        <v>500039</v>
       </c>
       <c r="R17" t="n">
-        <v>6792574</v>
+        <v>6792388</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3003,50 +3003,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125693794</v>
+        <v>125689285</v>
       </c>
       <c r="B25" t="n">
-        <v>56843</v>
+        <v>79561</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500087</v>
+        <v>499942</v>
       </c>
       <c r="R25" t="n">
-        <v>6792574</v>
+        <v>6792546</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3079,6 +3074,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3105,45 +3105,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125689285</v>
+        <v>125693794</v>
       </c>
       <c r="B26" t="n">
-        <v>79561</v>
+        <v>56843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499942</v>
+        <v>500087</v>
       </c>
       <c r="R26" t="n">
-        <v>6792546</v>
+        <v>6792574</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,11 +3181,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125888195</v>
+        <v>125894731</v>
       </c>
       <c r="B68" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,34 +7274,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500310</v>
+        <v>500128</v>
       </c>
       <c r="R68" t="n">
-        <v>6792516</v>
+        <v>6792590</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,11 +7339,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7365,50 +7365,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125894731</v>
+        <v>125892998</v>
       </c>
       <c r="B69" t="n">
-        <v>57651</v>
+        <v>8447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500128</v>
+        <v>500188</v>
       </c>
       <c r="R69" t="n">
-        <v>6792590</v>
+        <v>6792496</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7467,7 +7462,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125892998</v>
+        <v>125893046</v>
       </c>
       <c r="B70" t="n">
         <v>8447</v>
@@ -7502,10 +7497,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500188</v>
+        <v>500207</v>
       </c>
       <c r="R70" t="n">
-        <v>6792496</v>
+        <v>6792488</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7564,32 +7559,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125893046</v>
+        <v>125888195</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7599,10 +7594,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500207</v>
+        <v>500310</v>
       </c>
       <c r="R71" t="n">
-        <v>6792488</v>
+        <v>6792516</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7635,6 +7630,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8830,50 +8830,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125888740</v>
+        <v>125892266</v>
       </c>
       <c r="B84" t="n">
-        <v>57811</v>
+        <v>8447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500306</v>
+        <v>500158</v>
       </c>
       <c r="R84" t="n">
-        <v>6792466</v>
+        <v>6792441</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8932,7 +8927,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125892266</v>
+        <v>125888709</v>
       </c>
       <c r="B85" t="n">
         <v>8447</v>
@@ -8967,10 +8962,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500158</v>
+        <v>500311</v>
       </c>
       <c r="R85" t="n">
-        <v>6792441</v>
+        <v>6792502</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9029,32 +9024,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125888709</v>
+        <v>125892215</v>
       </c>
       <c r="B86" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9064,10 +9059,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500311</v>
+        <v>500158</v>
       </c>
       <c r="R86" t="n">
-        <v>6792502</v>
+        <v>6792441</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9126,7 +9121,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125892215</v>
+        <v>125889155</v>
       </c>
       <c r="B87" t="n">
         <v>79561</v>
@@ -9161,10 +9156,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500158</v>
+        <v>500275</v>
       </c>
       <c r="R87" t="n">
-        <v>6792441</v>
+        <v>6792487</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9223,7 +9218,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125889155</v>
+        <v>125891598</v>
       </c>
       <c r="B88" t="n">
         <v>79561</v>
@@ -9258,10 +9253,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500275</v>
+        <v>500153</v>
       </c>
       <c r="R88" t="n">
-        <v>6792487</v>
+        <v>6792391</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9320,10 +9315,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125891598</v>
+        <v>125888740</v>
       </c>
       <c r="B89" t="n">
-        <v>79561</v>
+        <v>57811</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,34 +9326,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500153</v>
+        <v>500306</v>
       </c>
       <c r="R89" t="n">
-        <v>6792391</v>
+        <v>6792466</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10290,32 +10290,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125889725</v>
+        <v>125893327</v>
       </c>
       <c r="B99" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>500234</v>
+        <v>500271</v>
       </c>
       <c r="R99" t="n">
-        <v>6792439</v>
+        <v>6792529</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10387,32 +10387,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125894957</v>
+        <v>125892219</v>
       </c>
       <c r="B100" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>500037</v>
+        <v>500158</v>
       </c>
       <c r="R100" t="n">
-        <v>6792660</v>
+        <v>6792441</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10484,32 +10484,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125893327</v>
+        <v>125889725</v>
       </c>
       <c r="B101" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>500271</v>
+        <v>500234</v>
       </c>
       <c r="R101" t="n">
-        <v>6792529</v>
+        <v>6792439</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10581,32 +10581,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125892219</v>
+        <v>125894957</v>
       </c>
       <c r="B102" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>500158</v>
+        <v>500037</v>
       </c>
       <c r="R102" t="n">
-        <v>6792441</v>
+        <v>6792660</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125889615</v>
+        <v>125892224</v>
       </c>
       <c r="B103" t="n">
-        <v>8447</v>
+        <v>78730</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500202</v>
+        <v>500158</v>
       </c>
       <c r="R103" t="n">
-        <v>6792435</v>
+        <v>6792441</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10775,10 +10775,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125896058</v>
+        <v>125891964</v>
       </c>
       <c r="B104" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500351</v>
+        <v>500111</v>
       </c>
       <c r="R104" t="n">
-        <v>6792369</v>
+        <v>6792428</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,11 +10846,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10877,10 +10872,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125892224</v>
+        <v>125896058</v>
       </c>
       <c r="B105" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10888,21 +10883,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10912,10 +10907,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500158</v>
+        <v>500351</v>
       </c>
       <c r="R105" t="n">
-        <v>6792441</v>
+        <v>6792369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10948,6 +10943,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125891964</v>
+        <v>125889615</v>
       </c>
       <c r="B106" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500111</v>
+        <v>500202</v>
       </c>
       <c r="R106" t="n">
-        <v>6792428</v>
+        <v>6792435</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125896524</v>
+        <v>125896426</v>
       </c>
       <c r="B107" t="n">
-        <v>79590</v>
+        <v>57648</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11082,34 +11082,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500384</v>
+        <v>500351</v>
       </c>
       <c r="R107" t="n">
-        <v>6792529</v>
+        <v>6792369</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11168,10 +11173,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125889090</v>
+        <v>125889496</v>
       </c>
       <c r="B108" t="n">
-        <v>79590</v>
+        <v>57648</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11179,34 +11184,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500285</v>
+        <v>500257</v>
       </c>
       <c r="R108" t="n">
-        <v>6792489</v>
+        <v>6792475</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11265,10 +11275,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125896426</v>
+        <v>125896524</v>
       </c>
       <c r="B109" t="n">
-        <v>57648</v>
+        <v>79590</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11276,39 +11286,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500351</v>
+        <v>500384</v>
       </c>
       <c r="R109" t="n">
-        <v>6792369</v>
+        <v>6792529</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11367,10 +11372,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125889496</v>
+        <v>125889090</v>
       </c>
       <c r="B110" t="n">
-        <v>57648</v>
+        <v>79590</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11378,39 +11383,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500257</v>
+        <v>500285</v>
       </c>
       <c r="R110" t="n">
-        <v>6792475</v>
+        <v>6792489</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11469,32 +11469,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125893643</v>
+        <v>125892433</v>
       </c>
       <c r="B111" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11504,10 +11504,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500237</v>
+        <v>500160</v>
       </c>
       <c r="R111" t="n">
-        <v>6792567</v>
+        <v>6792451</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11566,32 +11566,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125892433</v>
+        <v>125893643</v>
       </c>
       <c r="B112" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11601,10 +11601,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500160</v>
+        <v>500237</v>
       </c>
       <c r="R112" t="n">
-        <v>6792451</v>
+        <v>6792567</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11858,32 +11858,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125896458</v>
+        <v>125890126</v>
       </c>
       <c r="B115" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11893,10 +11893,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500374</v>
+        <v>500242</v>
       </c>
       <c r="R115" t="n">
-        <v>6792515</v>
+        <v>6792408</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11955,32 +11955,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125889235</v>
+        <v>125892154</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11990,10 +11990,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500275</v>
+        <v>500145</v>
       </c>
       <c r="R116" t="n">
-        <v>6792487</v>
+        <v>6792446</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12052,10 +12052,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125890126</v>
+        <v>125894500</v>
       </c>
       <c r="B117" t="n">
-        <v>79590</v>
+        <v>78730</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12063,21 +12063,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12087,10 +12087,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500242</v>
+        <v>500128</v>
       </c>
       <c r="R117" t="n">
-        <v>6792408</v>
+        <v>6792590</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12149,32 +12149,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125892154</v>
+        <v>125896458</v>
       </c>
       <c r="B118" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12184,10 +12184,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>500145</v>
+        <v>500374</v>
       </c>
       <c r="R118" t="n">
-        <v>6792446</v>
+        <v>6792515</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12246,32 +12246,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125894500</v>
+        <v>125889235</v>
       </c>
       <c r="B119" t="n">
-        <v>78730</v>
+        <v>8447</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>500128</v>
+        <v>500275</v>
       </c>
       <c r="R119" t="n">
-        <v>6792590</v>
+        <v>6792487</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13236,10 +13236,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125892025</v>
+        <v>125894564</v>
       </c>
       <c r="B129" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13247,21 +13247,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13271,10 +13271,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>500111</v>
+        <v>500128</v>
       </c>
       <c r="R129" t="n">
-        <v>6792428</v>
+        <v>6792590</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13307,11 +13307,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13338,10 +13333,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125894564</v>
+        <v>125892025</v>
       </c>
       <c r="B130" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13349,21 +13344,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13373,10 +13368,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>500128</v>
+        <v>500111</v>
       </c>
       <c r="R130" t="n">
-        <v>6792590</v>
+        <v>6792428</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13409,6 +13404,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13629,32 +13629,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125890887</v>
+        <v>125892751</v>
       </c>
       <c r="B133" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500282</v>
+        <v>500151</v>
       </c>
       <c r="R133" t="n">
-        <v>6792389</v>
+        <v>6792458</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13726,45 +13726,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125893186</v>
+        <v>125891498</v>
       </c>
       <c r="B134" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500247</v>
+        <v>500166</v>
       </c>
       <c r="R134" t="n">
-        <v>6792519</v>
+        <v>6792413</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13823,32 +13828,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125892751</v>
+        <v>125890887</v>
       </c>
       <c r="B135" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13858,10 +13863,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500151</v>
+        <v>500282</v>
       </c>
       <c r="R135" t="n">
-        <v>6792458</v>
+        <v>6792389</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13920,50 +13925,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125891498</v>
+        <v>125893186</v>
       </c>
       <c r="B136" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500166</v>
+        <v>500247</v>
       </c>
       <c r="R136" t="n">
-        <v>6792413</v>
+        <v>6792519</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125896535</v>
+        <v>125896454</v>
       </c>
       <c r="B140" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500384</v>
+        <v>500374</v>
       </c>
       <c r="R140" t="n">
-        <v>6792529</v>
+        <v>6792515</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14384,6 +14384,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14410,10 +14415,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125889379</v>
+        <v>125889266</v>
       </c>
       <c r="B141" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14421,21 +14426,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14481,6 +14486,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14507,10 +14517,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125896642</v>
+        <v>125896535</v>
       </c>
       <c r="B142" t="n">
-        <v>79561</v>
+        <v>78731</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14518,21 +14528,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14604,10 +14614,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125892643</v>
+        <v>125889379</v>
       </c>
       <c r="B143" t="n">
-        <v>79561</v>
+        <v>78731</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14615,21 +14625,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14639,10 +14649,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500151</v>
+        <v>500257</v>
       </c>
       <c r="R143" t="n">
-        <v>6792458</v>
+        <v>6792475</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14701,7 +14711,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125892160</v>
+        <v>125896642</v>
       </c>
       <c r="B144" t="n">
         <v>79561</v>
@@ -14736,10 +14746,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500145</v>
+        <v>500384</v>
       </c>
       <c r="R144" t="n">
-        <v>6792446</v>
+        <v>6792529</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14798,10 +14808,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125896454</v>
+        <v>125892643</v>
       </c>
       <c r="B145" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14809,21 +14819,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14833,10 +14843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500374</v>
+        <v>500151</v>
       </c>
       <c r="R145" t="n">
-        <v>6792515</v>
+        <v>6792458</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14869,11 +14879,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14900,10 +14905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125889266</v>
+        <v>125892160</v>
       </c>
       <c r="B146" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14911,21 +14916,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14935,10 +14940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R146" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14971,11 +14976,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD146" t="b">

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -2503,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125690007</v>
+        <v>125684537</v>
       </c>
       <c r="B20" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499989</v>
+        <v>500039</v>
       </c>
       <c r="R20" t="n">
-        <v>6792563</v>
+        <v>6792388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125684537</v>
+        <v>125690007</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500039</v>
+        <v>499989</v>
       </c>
       <c r="R21" t="n">
-        <v>6792388</v>
+        <v>6792563</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125693241</v>
+        <v>125686305</v>
       </c>
       <c r="B28" t="n">
-        <v>57648</v>
+        <v>78731</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3320,21 +3320,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500047</v>
+        <v>499963</v>
       </c>
       <c r="R28" t="n">
-        <v>6792612</v>
+        <v>6792480</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3380,6 +3380,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3406,32 +3411,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125683895</v>
+        <v>125693249</v>
       </c>
       <c r="B29" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3441,10 +3446,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500326</v>
+        <v>500047</v>
       </c>
       <c r="R29" t="n">
-        <v>6792440</v>
+        <v>6792612</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3477,11 +3482,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3508,10 +3508,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125686305</v>
+        <v>125686343</v>
       </c>
       <c r="B30" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3579,11 +3579,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3610,10 +3605,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125693249</v>
+        <v>125685148</v>
       </c>
       <c r="B31" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3621,21 +3616,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3645,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500047</v>
+        <v>500040</v>
       </c>
       <c r="R31" t="n">
-        <v>6792612</v>
+        <v>6792406</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125686343</v>
+        <v>125693241</v>
       </c>
       <c r="B32" t="n">
-        <v>79590</v>
+        <v>57648</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3718,21 +3713,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3742,10 +3737,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499963</v>
+        <v>500047</v>
       </c>
       <c r="R32" t="n">
-        <v>6792480</v>
+        <v>6792612</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3804,32 +3799,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125685148</v>
+        <v>125683895</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3839,10 +3834,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500040</v>
+        <v>500326</v>
       </c>
       <c r="R33" t="n">
-        <v>6792406</v>
+        <v>6792440</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3875,6 +3870,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3901,32 +3901,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125685808</v>
+        <v>125687329</v>
       </c>
       <c r="B34" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499996</v>
+        <v>499947</v>
       </c>
       <c r="R34" t="n">
-        <v>6792435</v>
+        <v>6792525</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3972,11 +3972,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4003,10 +3998,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125684693</v>
+        <v>125685808</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4014,21 +4009,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4038,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500077</v>
+        <v>499996</v>
       </c>
       <c r="R35" t="n">
-        <v>6792400</v>
+        <v>6792435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4074,6 +4069,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4100,32 +4100,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125687329</v>
+        <v>125684693</v>
       </c>
       <c r="B36" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499947</v>
+        <v>500077</v>
       </c>
       <c r="R36" t="n">
-        <v>6792525</v>
+        <v>6792400</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5978,32 +5978,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125690170</v>
+        <v>125683878</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>500018</v>
+        <v>499954</v>
       </c>
       <c r="R55" t="n">
-        <v>6792528</v>
+        <v>6792394</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,6 +6049,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6075,10 +6080,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125685885</v>
+        <v>125685813</v>
       </c>
       <c r="B56" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6086,21 +6091,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6110,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>500002</v>
+        <v>499996</v>
       </c>
       <c r="R56" t="n">
-        <v>6792449</v>
+        <v>6792435</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6172,10 +6177,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125685813</v>
+        <v>125690170</v>
       </c>
       <c r="B57" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6183,21 +6188,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6207,10 +6212,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499996</v>
+        <v>500018</v>
       </c>
       <c r="R57" t="n">
-        <v>6792435</v>
+        <v>6792528</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6269,32 +6274,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125683878</v>
+        <v>125685885</v>
       </c>
       <c r="B58" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6304,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499954</v>
+        <v>500002</v>
       </c>
       <c r="R58" t="n">
-        <v>6792394</v>
+        <v>6792449</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6340,11 +6345,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125894731</v>
+        <v>125888195</v>
       </c>
       <c r="B68" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,39 +7274,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500128</v>
+        <v>500310</v>
       </c>
       <c r="R68" t="n">
-        <v>6792590</v>
+        <v>6792516</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7339,6 +7334,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7365,45 +7365,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125892998</v>
+        <v>125894731</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>57651</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500188</v>
+        <v>500128</v>
       </c>
       <c r="R69" t="n">
-        <v>6792496</v>
+        <v>6792590</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7462,7 +7467,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125893046</v>
+        <v>125892998</v>
       </c>
       <c r="B70" t="n">
         <v>8447</v>
@@ -7497,10 +7502,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500207</v>
+        <v>500188</v>
       </c>
       <c r="R70" t="n">
-        <v>6792488</v>
+        <v>6792496</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7559,32 +7564,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125888195</v>
+        <v>125893046</v>
       </c>
       <c r="B71" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7594,10 +7599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500310</v>
+        <v>500207</v>
       </c>
       <c r="R71" t="n">
-        <v>6792516</v>
+        <v>6792488</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7630,11 +7635,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8830,45 +8830,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125892266</v>
+        <v>125888740</v>
       </c>
       <c r="B84" t="n">
-        <v>8447</v>
+        <v>57811</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500158</v>
+        <v>500306</v>
       </c>
       <c r="R84" t="n">
-        <v>6792441</v>
+        <v>6792466</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8927,7 +8932,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125888709</v>
+        <v>125892266</v>
       </c>
       <c r="B85" t="n">
         <v>8447</v>
@@ -8962,10 +8967,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500311</v>
+        <v>500158</v>
       </c>
       <c r="R85" t="n">
-        <v>6792502</v>
+        <v>6792441</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9024,32 +9029,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125892215</v>
+        <v>125888709</v>
       </c>
       <c r="B86" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9059,10 +9064,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500158</v>
+        <v>500311</v>
       </c>
       <c r="R86" t="n">
-        <v>6792441</v>
+        <v>6792502</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9121,7 +9126,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125889155</v>
+        <v>125892215</v>
       </c>
       <c r="B87" t="n">
         <v>79561</v>
@@ -9156,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500275</v>
+        <v>500158</v>
       </c>
       <c r="R87" t="n">
-        <v>6792487</v>
+        <v>6792441</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9218,7 +9223,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125891598</v>
+        <v>125889155</v>
       </c>
       <c r="B88" t="n">
         <v>79561</v>
@@ -9253,10 +9258,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500153</v>
+        <v>500275</v>
       </c>
       <c r="R88" t="n">
-        <v>6792391</v>
+        <v>6792487</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9315,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125888740</v>
+        <v>125891598</v>
       </c>
       <c r="B89" t="n">
-        <v>57811</v>
+        <v>79561</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9326,39 +9331,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500306</v>
+        <v>500153</v>
       </c>
       <c r="R89" t="n">
-        <v>6792466</v>
+        <v>6792391</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10096,32 +10096,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125889556</v>
+        <v>125890971</v>
       </c>
       <c r="B97" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>500218</v>
+        <v>500282</v>
       </c>
       <c r="R97" t="n">
-        <v>6792438</v>
+        <v>6792389</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10193,32 +10193,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125890971</v>
+        <v>125889556</v>
       </c>
       <c r="B98" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>500282</v>
+        <v>500218</v>
       </c>
       <c r="R98" t="n">
-        <v>6792389</v>
+        <v>6792438</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125892224</v>
+        <v>125889615</v>
       </c>
       <c r="B103" t="n">
-        <v>78730</v>
+        <v>8447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500158</v>
+        <v>500202</v>
       </c>
       <c r="R103" t="n">
-        <v>6792441</v>
+        <v>6792435</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10775,10 +10775,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125891964</v>
+        <v>125896058</v>
       </c>
       <c r="B104" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500111</v>
+        <v>500351</v>
       </c>
       <c r="R104" t="n">
-        <v>6792428</v>
+        <v>6792369</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,6 +10846,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10872,10 +10877,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125896058</v>
+        <v>125892224</v>
       </c>
       <c r="B105" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10883,21 +10888,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10907,10 +10912,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500351</v>
+        <v>500158</v>
       </c>
       <c r="R105" t="n">
-        <v>6792369</v>
+        <v>6792441</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10943,11 +10948,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125889615</v>
+        <v>125891964</v>
       </c>
       <c r="B106" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500202</v>
+        <v>500111</v>
       </c>
       <c r="R106" t="n">
-        <v>6792435</v>
+        <v>6792428</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11858,32 +11858,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125890126</v>
+        <v>125896458</v>
       </c>
       <c r="B115" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11893,10 +11893,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500242</v>
+        <v>500374</v>
       </c>
       <c r="R115" t="n">
-        <v>6792408</v>
+        <v>6792515</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11955,32 +11955,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125892154</v>
+        <v>125889235</v>
       </c>
       <c r="B116" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11990,10 +11990,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500145</v>
+        <v>500275</v>
       </c>
       <c r="R116" t="n">
-        <v>6792446</v>
+        <v>6792487</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12052,10 +12052,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125894500</v>
+        <v>125890126</v>
       </c>
       <c r="B117" t="n">
-        <v>78730</v>
+        <v>79590</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12063,21 +12063,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12087,10 +12087,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500128</v>
+        <v>500242</v>
       </c>
       <c r="R117" t="n">
-        <v>6792590</v>
+        <v>6792408</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12149,32 +12149,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125896458</v>
+        <v>125892154</v>
       </c>
       <c r="B118" t="n">
-        <v>8447</v>
+        <v>79590</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12184,10 +12184,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>500374</v>
+        <v>500145</v>
       </c>
       <c r="R118" t="n">
-        <v>6792515</v>
+        <v>6792446</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12246,32 +12246,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125889235</v>
+        <v>125894500</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>78730</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>500275</v>
+        <v>500128</v>
       </c>
       <c r="R119" t="n">
-        <v>6792487</v>
+        <v>6792590</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13236,10 +13236,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125894564</v>
+        <v>125892025</v>
       </c>
       <c r="B129" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13247,21 +13247,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13271,10 +13271,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>500128</v>
+        <v>500111</v>
       </c>
       <c r="R129" t="n">
-        <v>6792590</v>
+        <v>6792428</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13307,6 +13307,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13333,10 +13338,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125892025</v>
+        <v>125894564</v>
       </c>
       <c r="B130" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13344,21 +13349,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13368,10 +13373,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>500111</v>
+        <v>500128</v>
       </c>
       <c r="R130" t="n">
-        <v>6792428</v>
+        <v>6792590</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13404,11 +13409,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13629,32 +13629,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125892751</v>
+        <v>125890887</v>
       </c>
       <c r="B133" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500151</v>
+        <v>500282</v>
       </c>
       <c r="R133" t="n">
-        <v>6792458</v>
+        <v>6792389</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13726,50 +13726,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125891498</v>
+        <v>125893186</v>
       </c>
       <c r="B134" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500166</v>
+        <v>500247</v>
       </c>
       <c r="R134" t="n">
-        <v>6792413</v>
+        <v>6792519</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13828,32 +13823,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125890887</v>
+        <v>125892751</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13863,10 +13858,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500282</v>
+        <v>500151</v>
       </c>
       <c r="R135" t="n">
-        <v>6792389</v>
+        <v>6792458</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13925,45 +13920,50 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125893186</v>
+        <v>125891498</v>
       </c>
       <c r="B136" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500247</v>
+        <v>500166</v>
       </c>
       <c r="R136" t="n">
-        <v>6792519</v>
+        <v>6792413</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14022,32 +14022,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125889773</v>
+        <v>125892352</v>
       </c>
       <c r="B137" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14057,10 +14057,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>500237</v>
+        <v>500165</v>
       </c>
       <c r="R137" t="n">
-        <v>6792422</v>
+        <v>6792432</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14119,32 +14119,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125889010</v>
+        <v>125889773</v>
       </c>
       <c r="B138" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14154,10 +14154,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>500286</v>
+        <v>500237</v>
       </c>
       <c r="R138" t="n">
-        <v>6792459</v>
+        <v>6792422</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14216,10 +14216,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125892352</v>
+        <v>125889010</v>
       </c>
       <c r="B139" t="n">
-        <v>79561</v>
+        <v>78731</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14227,21 +14227,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>500165</v>
+        <v>500286</v>
       </c>
       <c r="R139" t="n">
-        <v>6792432</v>
+        <v>6792459</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15497,32 +15497,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125888498</v>
+        <v>125889396</v>
       </c>
       <c r="B152" t="n">
-        <v>8447</v>
+        <v>79561</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500311</v>
+        <v>500257</v>
       </c>
       <c r="R152" t="n">
-        <v>6792509</v>
+        <v>6792475</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15594,10 +15594,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125889396</v>
+        <v>125891609</v>
       </c>
       <c r="B153" t="n">
-        <v>79561</v>
+        <v>78731</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15605,21 +15605,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15629,10 +15629,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500257</v>
+        <v>500153</v>
       </c>
       <c r="R153" t="n">
-        <v>6792475</v>
+        <v>6792391</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15691,32 +15691,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125891609</v>
+        <v>125888498</v>
       </c>
       <c r="B154" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500153</v>
+        <v>500311</v>
       </c>
       <c r="R154" t="n">
-        <v>6792391</v>
+        <v>6792509</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125685630</v>
+        <v>125686800</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499996</v>
+        <v>500007</v>
       </c>
       <c r="R5" t="n">
-        <v>6792394</v>
+        <v>6792490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,7 +1123,7 @@
         <v>125686732</v>
       </c>
       <c r="B6" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125686800</v>
+        <v>125685630</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500007</v>
+        <v>499996</v>
       </c>
       <c r="R7" t="n">
-        <v>6792490</v>
+        <v>6792394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1322,7 @@
         <v>125685407</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>125687486</v>
       </c>
       <c r="B13" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125684006</v>
+        <v>125684974</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1917,39 +1917,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500326</v>
+        <v>500076</v>
       </c>
       <c r="R14" t="n">
-        <v>6792440</v>
+        <v>6792407</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,11 +1977,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,10 +2003,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125684974</v>
+        <v>125693564</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,21 +2014,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2048,10 +2038,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500076</v>
+        <v>500087</v>
       </c>
       <c r="R15" t="n">
-        <v>6792407</v>
+        <v>6792574</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2110,32 +2100,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125693564</v>
+        <v>125684253</v>
       </c>
       <c r="B16" t="n">
-        <v>78730</v>
+        <v>8447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2145,10 +2135,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500087</v>
+        <v>500039</v>
       </c>
       <c r="R16" t="n">
-        <v>6792574</v>
+        <v>6792388</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,45 +2197,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125684253</v>
+        <v>125684006</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500039</v>
+        <v>500326</v>
       </c>
       <c r="R17" t="n">
-        <v>6792388</v>
+        <v>6792440</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,6 +2273,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,7 +2307,7 @@
         <v>125685313</v>
       </c>
       <c r="B18" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>125692802</v>
       </c>
       <c r="B19" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>125684537</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>125690007</v>
       </c>
       <c r="B21" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>125686316</v>
       </c>
       <c r="B22" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>125690119</v>
       </c>
       <c r="B23" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>125686792</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,45 +3003,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125689285</v>
+        <v>125693794</v>
       </c>
       <c r="B25" t="n">
-        <v>79561</v>
+        <v>56844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499942</v>
+        <v>500087</v>
       </c>
       <c r="R25" t="n">
-        <v>6792546</v>
+        <v>6792574</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3074,11 +3079,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125693794</v>
+        <v>125685512</v>
       </c>
       <c r="B26" t="n">
-        <v>56843</v>
+        <v>8447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3116,39 +3116,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500087</v>
+        <v>499996</v>
       </c>
       <c r="R26" t="n">
-        <v>6792574</v>
+        <v>6792394</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3181,6 +3176,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3207,32 +3207,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125685512</v>
+        <v>125689285</v>
       </c>
       <c r="B27" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499996</v>
+        <v>499942</v>
       </c>
       <c r="R27" t="n">
-        <v>6792394</v>
+        <v>6792546</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125686305</v>
+        <v>125686343</v>
       </c>
       <c r="B28" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3320,21 +3320,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3380,11 +3380,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3411,10 +3406,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125693249</v>
+        <v>125685148</v>
       </c>
       <c r="B29" t="n">
-        <v>79561</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3422,21 +3417,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3446,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500047</v>
+        <v>500040</v>
       </c>
       <c r="R29" t="n">
-        <v>6792612</v>
+        <v>6792406</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,10 +3503,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125686343</v>
+        <v>125693241</v>
       </c>
       <c r="B30" t="n">
-        <v>79590</v>
+        <v>57649</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3519,21 +3514,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3543,10 +3538,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499963</v>
+        <v>500047</v>
       </c>
       <c r="R30" t="n">
-        <v>6792480</v>
+        <v>6792612</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3605,32 +3600,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125685148</v>
+        <v>125683895</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3640,10 +3635,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500040</v>
+        <v>500326</v>
       </c>
       <c r="R31" t="n">
-        <v>6792406</v>
+        <v>6792440</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3676,6 +3671,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3702,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125693241</v>
+        <v>125686305</v>
       </c>
       <c r="B32" t="n">
-        <v>57648</v>
+        <v>78732</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3713,21 +3713,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500047</v>
+        <v>499963</v>
       </c>
       <c r="R32" t="n">
-        <v>6792612</v>
+        <v>6792480</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3773,6 +3773,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3799,32 +3804,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125683895</v>
+        <v>125693249</v>
       </c>
       <c r="B33" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3834,10 +3839,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500326</v>
+        <v>500047</v>
       </c>
       <c r="R33" t="n">
-        <v>6792440</v>
+        <v>6792612</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3870,11 +3875,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4001,7 +4001,7 @@
         <v>125685808</v>
       </c>
       <c r="B35" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>125684693</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4197,10 +4197,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125684984</v>
+        <v>125691930</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500076</v>
+        <v>500001</v>
       </c>
       <c r="R37" t="n">
-        <v>6792415</v>
+        <v>6792610</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,10 +4294,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125691930</v>
+        <v>125684984</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500001</v>
+        <v>500076</v>
       </c>
       <c r="R38" t="n">
-        <v>6792610</v>
+        <v>6792415</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4391,10 +4391,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687294</v>
+        <v>125686924</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4402,21 +4402,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499945</v>
+        <v>500010</v>
       </c>
       <c r="R39" t="n">
-        <v>6792497</v>
+        <v>6792501</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4488,10 +4488,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125686924</v>
+        <v>125687294</v>
       </c>
       <c r="B40" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4499,21 +4499,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500010</v>
+        <v>499945</v>
       </c>
       <c r="R40" t="n">
-        <v>6792501</v>
+        <v>6792497</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4588,7 +4588,7 @@
         <v>125690589</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>125693372</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>125688845</v>
       </c>
       <c r="B43" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>125690295</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>125686463</v>
       </c>
       <c r="B46" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>125690957</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>125689757</v>
       </c>
       <c r="B49" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>125684146</v>
       </c>
       <c r="B50" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,32 +5580,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125684626</v>
+        <v>125685693</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500047</v>
+        <v>500002</v>
       </c>
       <c r="R51" t="n">
-        <v>6792395</v>
+        <v>6792449</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5651,6 +5651,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5677,32 +5682,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125690154</v>
+        <v>125686894</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5712,10 +5717,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499990</v>
+        <v>500010</v>
       </c>
       <c r="R52" t="n">
-        <v>6792543</v>
+        <v>6792501</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5748,11 +5753,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5779,32 +5779,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685693</v>
+        <v>125684626</v>
       </c>
       <c r="B53" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500002</v>
+        <v>500047</v>
       </c>
       <c r="R53" t="n">
-        <v>6792449</v>
+        <v>6792395</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5850,11 +5850,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5881,32 +5876,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125686894</v>
+        <v>125690154</v>
       </c>
       <c r="B54" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5916,10 +5911,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>500010</v>
+        <v>499990</v>
       </c>
       <c r="R54" t="n">
-        <v>6792501</v>
+        <v>6792543</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5952,6 +5947,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5978,32 +5978,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125683878</v>
+        <v>125685885</v>
       </c>
       <c r="B55" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499954</v>
+        <v>500002</v>
       </c>
       <c r="R55" t="n">
-        <v>6792394</v>
+        <v>6792449</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,11 +6049,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6080,10 +6075,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125685813</v>
+        <v>125690170</v>
       </c>
       <c r="B56" t="n">
-        <v>79561</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6091,21 +6086,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6115,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499996</v>
+        <v>500018</v>
       </c>
       <c r="R56" t="n">
-        <v>6792435</v>
+        <v>6792528</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6177,32 +6172,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125690170</v>
+        <v>125683878</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6212,10 +6207,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>500018</v>
+        <v>499954</v>
       </c>
       <c r="R57" t="n">
-        <v>6792528</v>
+        <v>6792394</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6248,6 +6243,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125685885</v>
+        <v>125685813</v>
       </c>
       <c r="B58" t="n">
-        <v>78972</v>
+        <v>79562</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>500002</v>
+        <v>499996</v>
       </c>
       <c r="R58" t="n">
-        <v>6792449</v>
+        <v>6792435</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6374,7 +6374,7 @@
         <v>125687400</v>
       </c>
       <c r="B59" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>125686648</v>
       </c>
       <c r="B60" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>125691010</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>125685121</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>125693022</v>
       </c>
       <c r="B63" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>125693403</v>
       </c>
       <c r="B64" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6958,10 +6958,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125685660</v>
+        <v>125685734</v>
       </c>
       <c r="B65" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>499989</v>
+        <v>499996</v>
       </c>
       <c r="R65" t="n">
-        <v>6792445</v>
+        <v>6792435</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7029,6 +7029,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7055,10 +7060,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125685734</v>
+        <v>125685660</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7090,10 +7095,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>499996</v>
+        <v>499989</v>
       </c>
       <c r="R66" t="n">
-        <v>6792435</v>
+        <v>6792445</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7126,11 +7131,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7160,7 +7160,7 @@
         <v>125685335</v>
       </c>
       <c r="B67" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>125888195</v>
       </c>
       <c r="B68" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7365,10 +7365,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125894731</v>
+        <v>125889107</v>
       </c>
       <c r="B69" t="n">
-        <v>57651</v>
+        <v>79562</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7376,39 +7376,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500128</v>
+        <v>500285</v>
       </c>
       <c r="R69" t="n">
-        <v>6792590</v>
+        <v>6792489</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7467,45 +7462,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125892998</v>
+        <v>125894731</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>57652</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500188</v>
+        <v>500128</v>
       </c>
       <c r="R70" t="n">
-        <v>6792496</v>
+        <v>6792590</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7564,7 +7564,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125893046</v>
+        <v>125892998</v>
       </c>
       <c r="B71" t="n">
         <v>8447</v>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500207</v>
+        <v>500188</v>
       </c>
       <c r="R71" t="n">
-        <v>6792488</v>
+        <v>6792496</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7661,32 +7661,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125889107</v>
+        <v>125893046</v>
       </c>
       <c r="B72" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500285</v>
+        <v>500207</v>
       </c>
       <c r="R72" t="n">
-        <v>6792489</v>
+        <v>6792488</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7761,7 +7761,7 @@
         <v>125890555</v>
       </c>
       <c r="B73" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>125890092</v>
       </c>
       <c r="B78" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>125891809</v>
       </c>
       <c r="B79" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8437,10 +8437,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125890407</v>
+        <v>125888740</v>
       </c>
       <c r="B80" t="n">
-        <v>78972</v>
+        <v>57812</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8448,34 +8448,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500242</v>
+        <v>500306</v>
       </c>
       <c r="R80" t="n">
-        <v>6792408</v>
+        <v>6792466</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8508,11 +8513,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8539,32 +8539,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125892653</v>
+        <v>125892266</v>
       </c>
       <c r="B81" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8574,10 +8574,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500151</v>
+        <v>500158</v>
       </c>
       <c r="R81" t="n">
-        <v>6792458</v>
+        <v>6792441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8636,32 +8636,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125889406</v>
+        <v>125888709</v>
       </c>
       <c r="B82" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500257</v>
+        <v>500311</v>
       </c>
       <c r="R82" t="n">
-        <v>6792475</v>
+        <v>6792502</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8733,10 +8733,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125895109</v>
+        <v>125892215</v>
       </c>
       <c r="B83" t="n">
-        <v>79590</v>
+        <v>79562</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8744,21 +8744,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>499985</v>
+        <v>500158</v>
       </c>
       <c r="R83" t="n">
-        <v>6792633</v>
+        <v>6792441</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8830,10 +8830,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125888740</v>
+        <v>125890407</v>
       </c>
       <c r="B84" t="n">
-        <v>57811</v>
+        <v>78973</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8841,39 +8841,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500306</v>
+        <v>500242</v>
       </c>
       <c r="R84" t="n">
-        <v>6792466</v>
+        <v>6792408</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8906,6 +8901,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8932,32 +8932,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125892266</v>
+        <v>125892653</v>
       </c>
       <c r="B85" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8967,10 +8967,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500158</v>
+        <v>500151</v>
       </c>
       <c r="R85" t="n">
-        <v>6792441</v>
+        <v>6792458</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9029,32 +9029,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125888709</v>
+        <v>125889406</v>
       </c>
       <c r="B86" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500311</v>
+        <v>500257</v>
       </c>
       <c r="R86" t="n">
-        <v>6792502</v>
+        <v>6792475</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9126,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125892215</v>
+        <v>125895109</v>
       </c>
       <c r="B87" t="n">
-        <v>79561</v>
+        <v>79591</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9137,21 +9137,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500158</v>
+        <v>499985</v>
       </c>
       <c r="R87" t="n">
-        <v>6792441</v>
+        <v>6792633</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9226,7 +9226,7 @@
         <v>125889155</v>
       </c>
       <c r="B88" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>125891598</v>
       </c>
       <c r="B89" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125896683</v>
+        <v>125894466</v>
       </c>
       <c r="B90" t="n">
         <v>8447</v>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>500384</v>
+        <v>500128</v>
       </c>
       <c r="R90" t="n">
-        <v>6792529</v>
+        <v>6792590</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9514,7 +9514,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125894466</v>
+        <v>125896683</v>
       </c>
       <c r="B91" t="n">
         <v>8447</v>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R91" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125889879</v>
+        <v>125889889</v>
       </c>
       <c r="B93" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,21 +9719,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125895107</v>
+        <v>125896400</v>
       </c>
       <c r="B94" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>499985</v>
+        <v>500351</v>
       </c>
       <c r="R94" t="n">
-        <v>6792633</v>
+        <v>6792369</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125896400</v>
+        <v>125889879</v>
       </c>
       <c r="B95" t="n">
-        <v>79561</v>
+        <v>78732</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>500351</v>
+        <v>500237</v>
       </c>
       <c r="R95" t="n">
-        <v>6792369</v>
+        <v>6792422</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,10 +9999,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125889889</v>
+        <v>125895107</v>
       </c>
       <c r="B96" t="n">
-        <v>79590</v>
+        <v>78732</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>500237</v>
+        <v>499985</v>
       </c>
       <c r="R96" t="n">
-        <v>6792422</v>
+        <v>6792633</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10096,32 +10096,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125890971</v>
+        <v>125889556</v>
       </c>
       <c r="B97" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>500282</v>
+        <v>500218</v>
       </c>
       <c r="R97" t="n">
-        <v>6792389</v>
+        <v>6792438</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10193,32 +10193,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125889556</v>
+        <v>125890971</v>
       </c>
       <c r="B98" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>500218</v>
+        <v>500282</v>
       </c>
       <c r="R98" t="n">
-        <v>6792438</v>
+        <v>6792389</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10293,7 +10293,7 @@
         <v>125893327</v>
       </c>
       <c r="B99" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>125892219</v>
       </c>
       <c r="B100" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125889615</v>
+        <v>125892224</v>
       </c>
       <c r="B103" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500202</v>
+        <v>500158</v>
       </c>
       <c r="R103" t="n">
-        <v>6792435</v>
+        <v>6792441</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10778,7 +10778,7 @@
         <v>125896058</v>
       </c>
       <c r="B104" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10877,10 +10877,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125892224</v>
+        <v>125891964</v>
       </c>
       <c r="B105" t="n">
-        <v>78730</v>
+        <v>79591</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10888,21 +10888,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500158</v>
+        <v>500111</v>
       </c>
       <c r="R105" t="n">
-        <v>6792441</v>
+        <v>6792428</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125891964</v>
+        <v>125889615</v>
       </c>
       <c r="B106" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500111</v>
+        <v>500202</v>
       </c>
       <c r="R106" t="n">
-        <v>6792428</v>
+        <v>6792435</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11074,7 +11074,7 @@
         <v>125896426</v>
       </c>
       <c r="B107" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>125889496</v>
       </c>
       <c r="B108" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11275,32 +11275,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125896524</v>
+        <v>125893643</v>
       </c>
       <c r="B109" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500384</v>
+        <v>500237</v>
       </c>
       <c r="R109" t="n">
-        <v>6792529</v>
+        <v>6792567</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11372,10 +11372,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125889090</v>
+        <v>125896524</v>
       </c>
       <c r="B110" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11407,10 +11407,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500285</v>
+        <v>500384</v>
       </c>
       <c r="R110" t="n">
-        <v>6792489</v>
+        <v>6792529</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11469,10 +11469,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125892433</v>
+        <v>125889090</v>
       </c>
       <c r="B111" t="n">
-        <v>79561</v>
+        <v>79591</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11480,21 +11480,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11504,10 +11504,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500160</v>
+        <v>500285</v>
       </c>
       <c r="R111" t="n">
-        <v>6792451</v>
+        <v>6792489</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11566,32 +11566,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125893643</v>
+        <v>125892433</v>
       </c>
       <c r="B112" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11601,10 +11601,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500237</v>
+        <v>500160</v>
       </c>
       <c r="R112" t="n">
-        <v>6792567</v>
+        <v>6792451</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11666,7 +11666,7 @@
         <v>125894266</v>
       </c>
       <c r="B113" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11756,32 +11756,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125893637</v>
+        <v>125896458</v>
       </c>
       <c r="B114" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500246</v>
+        <v>500374</v>
       </c>
       <c r="R114" t="n">
-        <v>6792558</v>
+        <v>6792515</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11827,11 +11827,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11858,32 +11853,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125896458</v>
+        <v>125890126</v>
       </c>
       <c r="B115" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11893,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500374</v>
+        <v>500242</v>
       </c>
       <c r="R115" t="n">
-        <v>6792515</v>
+        <v>6792408</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11955,32 +11950,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125889235</v>
+        <v>125893637</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11990,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500275</v>
+        <v>500246</v>
       </c>
       <c r="R116" t="n">
-        <v>6792487</v>
+        <v>6792558</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12026,6 +12021,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12052,10 +12052,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125890126</v>
+        <v>125892154</v>
       </c>
       <c r="B117" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12087,10 +12087,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500242</v>
+        <v>500145</v>
       </c>
       <c r="R117" t="n">
-        <v>6792408</v>
+        <v>6792446</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12149,10 +12149,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125892154</v>
+        <v>125894500</v>
       </c>
       <c r="B118" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12160,21 +12160,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12184,10 +12184,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>500145</v>
+        <v>500128</v>
       </c>
       <c r="R118" t="n">
-        <v>6792446</v>
+        <v>6792590</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12246,32 +12246,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125894500</v>
+        <v>125889235</v>
       </c>
       <c r="B119" t="n">
-        <v>78730</v>
+        <v>8447</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>500128</v>
+        <v>500275</v>
       </c>
       <c r="R119" t="n">
-        <v>6792590</v>
+        <v>6792487</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125888695</v>
+        <v>125893148</v>
       </c>
       <c r="B120" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500311</v>
+        <v>500251</v>
       </c>
       <c r="R120" t="n">
-        <v>6792502</v>
+        <v>6792496</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,11 +12414,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12445,32 +12440,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125892496</v>
+        <v>125889503</v>
       </c>
       <c r="B121" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12480,10 +12475,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R121" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12516,11 +12511,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12547,32 +12537,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12582,10 +12572,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R122" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12618,6 +12608,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12644,32 +12639,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125889503</v>
+        <v>125892496</v>
       </c>
       <c r="B123" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12679,10 +12674,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R123" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12715,6 +12710,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12741,32 +12741,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125891471</v>
+        <v>125892207</v>
       </c>
       <c r="B124" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12776,10 +12776,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500181</v>
+        <v>500158</v>
       </c>
       <c r="R124" t="n">
-        <v>6792401</v>
+        <v>6792441</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12838,10 +12838,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125894132</v>
+        <v>125896030</v>
       </c>
       <c r="B125" t="n">
-        <v>78731</v>
+        <v>57652</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12849,34 +12849,39 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500128</v>
+        <v>500351</v>
       </c>
       <c r="R125" t="n">
-        <v>6792590</v>
+        <v>6792369</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12935,32 +12940,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125892207</v>
+        <v>125891471</v>
       </c>
       <c r="B126" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12970,10 +12975,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500158</v>
+        <v>500181</v>
       </c>
       <c r="R126" t="n">
-        <v>6792441</v>
+        <v>6792401</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13032,10 +13037,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125896030</v>
+        <v>125894132</v>
       </c>
       <c r="B127" t="n">
-        <v>57651</v>
+        <v>78732</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13043,39 +13048,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500351</v>
+        <v>500128</v>
       </c>
       <c r="R127" t="n">
-        <v>6792369</v>
+        <v>6792590</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13137,7 +13137,7 @@
         <v>125896611</v>
       </c>
       <c r="B128" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13236,10 +13236,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125892025</v>
+        <v>125894564</v>
       </c>
       <c r="B129" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13247,21 +13247,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13271,10 +13271,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>500111</v>
+        <v>500128</v>
       </c>
       <c r="R129" t="n">
-        <v>6792428</v>
+        <v>6792590</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13307,11 +13307,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13338,10 +13333,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125894564</v>
+        <v>125892025</v>
       </c>
       <c r="B130" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13349,21 +13344,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13373,10 +13368,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>500128</v>
+        <v>500111</v>
       </c>
       <c r="R130" t="n">
-        <v>6792590</v>
+        <v>6792428</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13409,6 +13404,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13435,32 +13435,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125893307</v>
+        <v>125890887</v>
       </c>
       <c r="B131" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>500271</v>
+        <v>500282</v>
       </c>
       <c r="R131" t="n">
-        <v>6792529</v>
+        <v>6792389</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13532,32 +13532,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125891649</v>
+        <v>125893186</v>
       </c>
       <c r="B132" t="n">
-        <v>79590</v>
+        <v>8447</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13567,10 +13567,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500166</v>
+        <v>500247</v>
       </c>
       <c r="R132" t="n">
-        <v>6792387</v>
+        <v>6792519</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13629,32 +13629,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125890887</v>
+        <v>125892751</v>
       </c>
       <c r="B133" t="n">
-        <v>8447</v>
+        <v>78732</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500282</v>
+        <v>500151</v>
       </c>
       <c r="R133" t="n">
-        <v>6792389</v>
+        <v>6792458</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13726,45 +13726,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125893186</v>
+        <v>125891498</v>
       </c>
       <c r="B134" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500247</v>
+        <v>500166</v>
       </c>
       <c r="R134" t="n">
-        <v>6792519</v>
+        <v>6792413</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13823,10 +13828,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125892751</v>
+        <v>125891649</v>
       </c>
       <c r="B135" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13834,21 +13839,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13858,10 +13863,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500151</v>
+        <v>500166</v>
       </c>
       <c r="R135" t="n">
-        <v>6792458</v>
+        <v>6792387</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13920,10 +13925,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125891498</v>
+        <v>125893307</v>
       </c>
       <c r="B136" t="n">
-        <v>57648</v>
+        <v>79591</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13931,39 +13936,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500166</v>
+        <v>500271</v>
       </c>
       <c r="R136" t="n">
-        <v>6792413</v>
+        <v>6792529</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14022,32 +14022,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125892352</v>
+        <v>125889773</v>
       </c>
       <c r="B137" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14057,10 +14057,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>500165</v>
+        <v>500237</v>
       </c>
       <c r="R137" t="n">
-        <v>6792432</v>
+        <v>6792422</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14119,32 +14119,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125889773</v>
+        <v>125892352</v>
       </c>
       <c r="B138" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14154,10 +14154,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>500237</v>
+        <v>500165</v>
       </c>
       <c r="R138" t="n">
-        <v>6792422</v>
+        <v>6792432</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14219,7 +14219,7 @@
         <v>125889010</v>
       </c>
       <c r="B139" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>125896454</v>
       </c>
       <c r="B140" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>125889266</v>
       </c>
       <c r="B141" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>125896535</v>
       </c>
       <c r="B142" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14614,10 +14614,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125889379</v>
+        <v>125896642</v>
       </c>
       <c r="B143" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14625,21 +14625,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14649,10 +14649,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500257</v>
+        <v>500384</v>
       </c>
       <c r="R143" t="n">
-        <v>6792475</v>
+        <v>6792529</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14711,10 +14711,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125896642</v>
+        <v>125892643</v>
       </c>
       <c r="B144" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14746,10 +14746,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500384</v>
+        <v>500151</v>
       </c>
       <c r="R144" t="n">
-        <v>6792529</v>
+        <v>6792458</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14808,10 +14808,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125892643</v>
+        <v>125889379</v>
       </c>
       <c r="B145" t="n">
-        <v>79561</v>
+        <v>78732</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14819,21 +14819,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500151</v>
+        <v>500257</v>
       </c>
       <c r="R145" t="n">
-        <v>6792458</v>
+        <v>6792475</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14908,7 +14908,7 @@
         <v>125892160</v>
       </c>
       <c r="B146" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15002,50 +15002,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125888369</v>
+        <v>125896772</v>
       </c>
       <c r="B147" t="n">
-        <v>57648</v>
+        <v>92524</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500310</v>
+        <v>500384</v>
       </c>
       <c r="R147" t="n">
-        <v>6792516</v>
+        <v>6792529</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15104,32 +15099,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125896772</v>
+        <v>125891864</v>
       </c>
       <c r="B148" t="n">
-        <v>92522</v>
+        <v>78973</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15139,10 +15134,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500384</v>
+        <v>500126</v>
       </c>
       <c r="R148" t="n">
-        <v>6792529</v>
+        <v>6792397</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15175,6 +15170,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15201,32 +15201,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125891864</v>
+        <v>125892001</v>
       </c>
       <c r="B149" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15236,10 +15236,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500126</v>
+        <v>500111</v>
       </c>
       <c r="R149" t="n">
-        <v>6792397</v>
+        <v>6792428</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15272,11 +15272,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15303,45 +15298,50 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125892001</v>
+        <v>125888369</v>
       </c>
       <c r="B150" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500111</v>
+        <v>500310</v>
       </c>
       <c r="R150" t="n">
-        <v>6792428</v>
+        <v>6792516</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15403,7 +15403,7 @@
         <v>125888908</v>
       </c>
       <c r="B151" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15497,32 +15497,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125889396</v>
+        <v>125888498</v>
       </c>
       <c r="B152" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500257</v>
+        <v>500311</v>
       </c>
       <c r="R152" t="n">
-        <v>6792475</v>
+        <v>6792509</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15594,10 +15594,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125891609</v>
+        <v>125889396</v>
       </c>
       <c r="B153" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15605,21 +15605,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15629,10 +15629,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500153</v>
+        <v>500257</v>
       </c>
       <c r="R153" t="n">
-        <v>6792391</v>
+        <v>6792475</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15691,32 +15691,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125888498</v>
+        <v>125891609</v>
       </c>
       <c r="B154" t="n">
-        <v>8447</v>
+        <v>78732</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500311</v>
+        <v>500153</v>
       </c>
       <c r="R154" t="n">
-        <v>6792509</v>
+        <v>6792391</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15791,7 +15791,7 @@
         <v>125895017</v>
       </c>
       <c r="B155" t="n">
-        <v>78996</v>
+        <v>78997</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15885,10 +15885,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125888924</v>
+        <v>125895229</v>
       </c>
       <c r="B156" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15896,21 +15896,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15920,10 +15920,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>500306</v>
+        <v>499985</v>
       </c>
       <c r="R156" t="n">
-        <v>6792466</v>
+        <v>6792633</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -15982,10 +15982,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125895229</v>
+        <v>125888924</v>
       </c>
       <c r="B157" t="n">
-        <v>79561</v>
+        <v>78732</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15993,21 +15993,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16017,10 +16017,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>499985</v>
+        <v>500306</v>
       </c>
       <c r="R157" t="n">
-        <v>6792633</v>
+        <v>6792466</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16082,7 +16082,7 @@
         <v>125889676</v>
       </c>
       <c r="B158" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>125892942</v>
       </c>
       <c r="B159" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>125892637</v>
       </c>
       <c r="B160" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -3003,10 +3003,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125693794</v>
+        <v>125685512</v>
       </c>
       <c r="B25" t="n">
-        <v>56844</v>
+        <v>8447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3014,39 +3014,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500087</v>
+        <v>499996</v>
       </c>
       <c r="R25" t="n">
-        <v>6792574</v>
+        <v>6792394</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3079,6 +3074,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3105,32 +3105,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125685512</v>
+        <v>125689285</v>
       </c>
       <c r="B26" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499996</v>
+        <v>499942</v>
       </c>
       <c r="R26" t="n">
-        <v>6792394</v>
+        <v>6792546</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3207,45 +3207,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125689285</v>
+        <v>125693794</v>
       </c>
       <c r="B27" t="n">
-        <v>79562</v>
+        <v>56844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499942</v>
+        <v>500087</v>
       </c>
       <c r="R27" t="n">
-        <v>6792546</v>
+        <v>6792574</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3278,11 +3283,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5978,32 +5978,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685885</v>
+        <v>125683878</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>500002</v>
+        <v>499954</v>
       </c>
       <c r="R55" t="n">
-        <v>6792449</v>
+        <v>6792394</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,6 +6049,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6075,10 +6080,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125690170</v>
+        <v>125685813</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6086,21 +6091,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6110,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>500018</v>
+        <v>499996</v>
       </c>
       <c r="R56" t="n">
-        <v>6792528</v>
+        <v>6792435</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6172,32 +6177,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125683878</v>
+        <v>125685885</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6207,10 +6212,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499954</v>
+        <v>500002</v>
       </c>
       <c r="R57" t="n">
-        <v>6792394</v>
+        <v>6792449</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6243,11 +6248,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125685813</v>
+        <v>125690170</v>
       </c>
       <c r="B58" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499996</v>
+        <v>500018</v>
       </c>
       <c r="R58" t="n">
-        <v>6792435</v>
+        <v>6792528</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7365,32 +7365,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125889107</v>
+        <v>125892998</v>
       </c>
       <c r="B69" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500285</v>
+        <v>500188</v>
       </c>
       <c r="R69" t="n">
-        <v>6792489</v>
+        <v>6792496</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7462,50 +7462,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125894731</v>
+        <v>125893046</v>
       </c>
       <c r="B70" t="n">
-        <v>57652</v>
+        <v>8447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500128</v>
+        <v>500207</v>
       </c>
       <c r="R70" t="n">
-        <v>6792590</v>
+        <v>6792488</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7564,32 +7559,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125892998</v>
+        <v>125889107</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7599,10 +7594,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500188</v>
+        <v>500285</v>
       </c>
       <c r="R71" t="n">
-        <v>6792496</v>
+        <v>6792489</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7661,45 +7656,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125893046</v>
+        <v>125894731</v>
       </c>
       <c r="B72" t="n">
-        <v>8447</v>
+        <v>57652</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500207</v>
+        <v>500128</v>
       </c>
       <c r="R72" t="n">
-        <v>6792488</v>
+        <v>6792590</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7758,32 +7758,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125890555</v>
+        <v>125893261</v>
       </c>
       <c r="B73" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>500282</v>
+        <v>500271</v>
       </c>
       <c r="R73" t="n">
-        <v>6792389</v>
+        <v>6792529</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7855,7 +7855,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125893261</v>
+        <v>125896279</v>
       </c>
       <c r="B74" t="n">
         <v>8447</v>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500271</v>
+        <v>500351</v>
       </c>
       <c r="R74" t="n">
-        <v>6792529</v>
+        <v>6792369</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7952,7 +7952,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125896279</v>
+        <v>125895125</v>
       </c>
       <c r="B75" t="n">
         <v>8447</v>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>500351</v>
+        <v>499985</v>
       </c>
       <c r="R75" t="n">
-        <v>6792369</v>
+        <v>6792633</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125895125</v>
+        <v>125890234</v>
       </c>
       <c r="B76" t="n">
         <v>8447</v>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>499985</v>
+        <v>500242</v>
       </c>
       <c r="R76" t="n">
-        <v>6792633</v>
+        <v>6792408</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8146,32 +8146,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125890234</v>
+        <v>125890092</v>
       </c>
       <c r="B77" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8243,7 +8243,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125890092</v>
+        <v>125891809</v>
       </c>
       <c r="B78" t="n">
         <v>79562</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>500242</v>
+        <v>500166</v>
       </c>
       <c r="R78" t="n">
-        <v>6792408</v>
+        <v>6792387</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8340,10 +8340,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125891809</v>
+        <v>125890555</v>
       </c>
       <c r="B79" t="n">
-        <v>79562</v>
+        <v>79591</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8351,21 +8351,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500166</v>
+        <v>500282</v>
       </c>
       <c r="R79" t="n">
-        <v>6792387</v>
+        <v>6792389</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9611,32 +9611,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125888352</v>
+        <v>125889889</v>
       </c>
       <c r="B92" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>500310</v>
+        <v>500237</v>
       </c>
       <c r="R92" t="n">
-        <v>6792516</v>
+        <v>6792422</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125889889</v>
+        <v>125896400</v>
       </c>
       <c r="B93" t="n">
-        <v>79591</v>
+        <v>79562</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,21 +9719,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>500237</v>
+        <v>500351</v>
       </c>
       <c r="R93" t="n">
-        <v>6792422</v>
+        <v>6792369</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125896400</v>
+        <v>125889879</v>
       </c>
       <c r="B94" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>500351</v>
+        <v>500237</v>
       </c>
       <c r="R94" t="n">
-        <v>6792369</v>
+        <v>6792422</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,7 +9902,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125889879</v>
+        <v>125895107</v>
       </c>
       <c r="B95" t="n">
         <v>78732</v>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>500237</v>
+        <v>499985</v>
       </c>
       <c r="R95" t="n">
-        <v>6792422</v>
+        <v>6792633</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,32 +9999,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125895107</v>
+        <v>125888352</v>
       </c>
       <c r="B96" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>499985</v>
+        <v>500310</v>
       </c>
       <c r="R96" t="n">
-        <v>6792633</v>
+        <v>6792516</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10290,32 +10290,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125893327</v>
+        <v>125889725</v>
       </c>
       <c r="B99" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>500271</v>
+        <v>500234</v>
       </c>
       <c r="R99" t="n">
-        <v>6792529</v>
+        <v>6792439</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10387,32 +10387,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125892219</v>
+        <v>125894957</v>
       </c>
       <c r="B100" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>500158</v>
+        <v>500037</v>
       </c>
       <c r="R100" t="n">
-        <v>6792441</v>
+        <v>6792660</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10484,32 +10484,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125889725</v>
+        <v>125893327</v>
       </c>
       <c r="B101" t="n">
-        <v>8447</v>
+        <v>78732</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>500234</v>
+        <v>500271</v>
       </c>
       <c r="R101" t="n">
-        <v>6792439</v>
+        <v>6792529</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10581,32 +10581,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125894957</v>
+        <v>125892219</v>
       </c>
       <c r="B102" t="n">
-        <v>8447</v>
+        <v>78732</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>500037</v>
+        <v>500158</v>
       </c>
       <c r="R102" t="n">
-        <v>6792660</v>
+        <v>6792441</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125896426</v>
+        <v>125896524</v>
       </c>
       <c r="B107" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11082,39 +11082,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500351</v>
+        <v>500384</v>
       </c>
       <c r="R107" t="n">
-        <v>6792369</v>
+        <v>6792529</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11173,10 +11168,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125889496</v>
+        <v>125889090</v>
       </c>
       <c r="B108" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11184,39 +11179,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500257</v>
+        <v>500285</v>
       </c>
       <c r="R108" t="n">
-        <v>6792475</v>
+        <v>6792489</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11275,45 +11265,50 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125893643</v>
+        <v>125896426</v>
       </c>
       <c r="B109" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500237</v>
+        <v>500351</v>
       </c>
       <c r="R109" t="n">
-        <v>6792567</v>
+        <v>6792369</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11372,10 +11367,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125896524</v>
+        <v>125889496</v>
       </c>
       <c r="B110" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11383,34 +11378,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500384</v>
+        <v>500257</v>
       </c>
       <c r="R110" t="n">
-        <v>6792529</v>
+        <v>6792475</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11469,10 +11469,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125889090</v>
+        <v>125892433</v>
       </c>
       <c r="B111" t="n">
-        <v>79591</v>
+        <v>79562</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11480,21 +11480,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11504,10 +11504,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500285</v>
+        <v>500160</v>
       </c>
       <c r="R111" t="n">
-        <v>6792489</v>
+        <v>6792451</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11566,34 +11566,30 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125892433</v>
+        <v>125894266</v>
       </c>
       <c r="B112" t="n">
-        <v>79562</v>
+        <v>98261</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>223597</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11601,10 +11597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500160</v>
+        <v>500128</v>
       </c>
       <c r="R112" t="n">
-        <v>6792451</v>
+        <v>6792590</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11663,10 +11659,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125894266</v>
+        <v>125893643</v>
       </c>
       <c r="B113" t="n">
-        <v>98261</v>
+        <v>8447</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11674,19 +11670,23 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>223597</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500128</v>
+        <v>500237</v>
       </c>
       <c r="R113" t="n">
-        <v>6792590</v>
+        <v>6792567</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,32 +11756,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125896458</v>
+        <v>125890126</v>
       </c>
       <c r="B114" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500374</v>
+        <v>500242</v>
       </c>
       <c r="R114" t="n">
-        <v>6792515</v>
+        <v>6792408</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11853,10 +11853,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125890126</v>
+        <v>125893637</v>
       </c>
       <c r="B115" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11864,21 +11864,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500242</v>
+        <v>500246</v>
       </c>
       <c r="R115" t="n">
-        <v>6792408</v>
+        <v>6792558</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11924,6 +11924,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11950,10 +11955,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125893637</v>
+        <v>125892154</v>
       </c>
       <c r="B116" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11961,21 +11966,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11985,10 +11990,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500246</v>
+        <v>500145</v>
       </c>
       <c r="R116" t="n">
-        <v>6792558</v>
+        <v>6792446</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12021,11 +12026,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12052,10 +12052,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125892154</v>
+        <v>125894500</v>
       </c>
       <c r="B117" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12063,21 +12063,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12087,10 +12087,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500145</v>
+        <v>500128</v>
       </c>
       <c r="R117" t="n">
-        <v>6792446</v>
+        <v>6792590</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12149,32 +12149,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125894500</v>
+        <v>125896458</v>
       </c>
       <c r="B118" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12184,10 +12184,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>500128</v>
+        <v>500374</v>
       </c>
       <c r="R118" t="n">
-        <v>6792590</v>
+        <v>6792515</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1023,32 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125686800</v>
+        <v>125686874</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500007</v>
+        <v>500013</v>
       </c>
       <c r="R5" t="n">
-        <v>6792490</v>
+        <v>6792493</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,6 +1094,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,32 +1125,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125686732</v>
+        <v>125693671</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499990</v>
+        <v>500087</v>
       </c>
       <c r="R6" t="n">
-        <v>6792488</v>
+        <v>6792574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,11 +1196,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,32 +1222,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125685630</v>
+        <v>125687215</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499996</v>
+        <v>499945</v>
       </c>
       <c r="R7" t="n">
-        <v>6792394</v>
+        <v>6792497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,32 +1319,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125685407</v>
+        <v>125689836</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500063</v>
+        <v>499951</v>
       </c>
       <c r="R8" t="n">
-        <v>6792381</v>
+        <v>6792574</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,32 +1416,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125686874</v>
+        <v>125686800</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500013</v>
+        <v>500007</v>
       </c>
       <c r="R9" t="n">
-        <v>6792493</v>
+        <v>6792490</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,11 +1487,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,32 +1513,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125693671</v>
+        <v>125686732</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500087</v>
+        <v>499990</v>
       </c>
       <c r="R10" t="n">
-        <v>6792574</v>
+        <v>6792488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,6 +1584,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,32 +1615,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125687215</v>
+        <v>125685630</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499945</v>
+        <v>499996</v>
       </c>
       <c r="R11" t="n">
-        <v>6792497</v>
+        <v>6792394</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,32 +1712,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125689836</v>
+        <v>125685407</v>
       </c>
       <c r="B12" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499951</v>
+        <v>500063</v>
       </c>
       <c r="R12" t="n">
-        <v>6792574</v>
+        <v>6792381</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2100,45 +2100,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125684253</v>
+        <v>125684006</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500039</v>
+        <v>500326</v>
       </c>
       <c r="R16" t="n">
-        <v>6792388</v>
+        <v>6792440</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2171,6 +2176,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2197,50 +2207,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125684006</v>
+        <v>125684253</v>
       </c>
       <c r="B17" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500326</v>
+        <v>500039</v>
       </c>
       <c r="R17" t="n">
-        <v>6792440</v>
+        <v>6792388</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,11 +2278,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2707,10 +2707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125686316</v>
+        <v>125686792</v>
       </c>
       <c r="B22" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2718,21 +2718,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499963</v>
+        <v>499990</v>
       </c>
       <c r="R22" t="n">
-        <v>6792480</v>
+        <v>6792488</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125690119</v>
+        <v>125686316</v>
       </c>
       <c r="B23" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2815,21 +2815,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499990</v>
+        <v>499963</v>
       </c>
       <c r="R23" t="n">
-        <v>6792543</v>
+        <v>6792480</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2875,11 +2875,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2906,10 +2901,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125686792</v>
+        <v>125690119</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2917,21 +2912,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2944,7 +2939,7 @@
         <v>499990</v>
       </c>
       <c r="R24" t="n">
-        <v>6792488</v>
+        <v>6792543</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,6 +2972,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,10 +3309,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125686343</v>
+        <v>125686305</v>
       </c>
       <c r="B28" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3320,21 +3320,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3380,6 +3380,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3406,10 +3411,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125685148</v>
+        <v>125693249</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3417,21 +3422,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3441,10 +3446,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500040</v>
+        <v>500047</v>
       </c>
       <c r="R29" t="n">
-        <v>6792406</v>
+        <v>6792612</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3503,10 +3508,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125693241</v>
+        <v>125686343</v>
       </c>
       <c r="B30" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,21 +3519,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3538,10 +3543,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500047</v>
+        <v>499963</v>
       </c>
       <c r="R30" t="n">
-        <v>6792612</v>
+        <v>6792480</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,32 +3605,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125683895</v>
+        <v>125685148</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3635,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500326</v>
+        <v>500040</v>
       </c>
       <c r="R31" t="n">
-        <v>6792440</v>
+        <v>6792406</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3671,11 +3676,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3702,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125686305</v>
+        <v>125693241</v>
       </c>
       <c r="B32" t="n">
-        <v>78732</v>
+        <v>57649</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3713,21 +3713,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499963</v>
+        <v>500047</v>
       </c>
       <c r="R32" t="n">
-        <v>6792480</v>
+        <v>6792612</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3773,11 +3773,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3804,32 +3799,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125693249</v>
+        <v>125683895</v>
       </c>
       <c r="B33" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3839,10 +3834,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500047</v>
+        <v>500326</v>
       </c>
       <c r="R33" t="n">
-        <v>6792612</v>
+        <v>6792440</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3875,6 +3870,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3901,32 +3901,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125687329</v>
+        <v>125684693</v>
       </c>
       <c r="B34" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499947</v>
+        <v>500077</v>
       </c>
       <c r="R34" t="n">
-        <v>6792525</v>
+        <v>6792400</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3998,32 +3998,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125685808</v>
+        <v>125687329</v>
       </c>
       <c r="B35" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499996</v>
+        <v>499947</v>
       </c>
       <c r="R35" t="n">
-        <v>6792435</v>
+        <v>6792525</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4069,11 +4069,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4100,10 +4095,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125684693</v>
+        <v>125685808</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4111,21 +4106,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4135,10 +4130,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500077</v>
+        <v>499996</v>
       </c>
       <c r="R36" t="n">
-        <v>6792400</v>
+        <v>6792435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4171,6 +4166,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5279,32 +5279,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125685110</v>
+        <v>125689757</v>
       </c>
       <c r="B48" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>500063</v>
+        <v>499951</v>
       </c>
       <c r="R48" t="n">
-        <v>6792423</v>
+        <v>6792574</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,32 +5381,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125689757</v>
+        <v>125685110</v>
       </c>
       <c r="B49" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499951</v>
+        <v>500063</v>
       </c>
       <c r="R49" t="n">
-        <v>6792574</v>
+        <v>6792423</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5978,32 +5978,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125683878</v>
+        <v>125685885</v>
       </c>
       <c r="B55" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499954</v>
+        <v>500002</v>
       </c>
       <c r="R55" t="n">
-        <v>6792394</v>
+        <v>6792449</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,11 +6049,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6080,10 +6075,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125685813</v>
+        <v>125690170</v>
       </c>
       <c r="B56" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6091,21 +6086,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6115,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499996</v>
+        <v>500018</v>
       </c>
       <c r="R56" t="n">
-        <v>6792435</v>
+        <v>6792528</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6177,32 +6172,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125685885</v>
+        <v>125683878</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6212,10 +6207,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>500002</v>
+        <v>499954</v>
       </c>
       <c r="R57" t="n">
-        <v>6792449</v>
+        <v>6792394</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6248,6 +6243,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125690170</v>
+        <v>125685813</v>
       </c>
       <c r="B58" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>500018</v>
+        <v>499996</v>
       </c>
       <c r="R58" t="n">
-        <v>6792528</v>
+        <v>6792435</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7263,32 +7263,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125888195</v>
+        <v>125892998</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500310</v>
+        <v>500188</v>
       </c>
       <c r="R68" t="n">
-        <v>6792516</v>
+        <v>6792496</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,11 +7334,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7365,7 +7360,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125892998</v>
+        <v>125893046</v>
       </c>
       <c r="B69" t="n">
         <v>8447</v>
@@ -7400,10 +7395,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500188</v>
+        <v>500207</v>
       </c>
       <c r="R69" t="n">
-        <v>6792496</v>
+        <v>6792488</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7462,32 +7457,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125893046</v>
+        <v>125888195</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7497,10 +7492,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500207</v>
+        <v>500310</v>
       </c>
       <c r="R70" t="n">
-        <v>6792488</v>
+        <v>6792516</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7533,6 +7528,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7559,10 +7559,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125889107</v>
+        <v>125894731</v>
       </c>
       <c r="B71" t="n">
-        <v>79562</v>
+        <v>57652</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7570,34 +7570,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500285</v>
+        <v>500128</v>
       </c>
       <c r="R71" t="n">
-        <v>6792489</v>
+        <v>6792590</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7656,10 +7661,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125894731</v>
+        <v>125889107</v>
       </c>
       <c r="B72" t="n">
-        <v>57652</v>
+        <v>79562</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7667,39 +7672,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500128</v>
+        <v>500285</v>
       </c>
       <c r="R72" t="n">
-        <v>6792590</v>
+        <v>6792489</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7758,32 +7758,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125893261</v>
+        <v>125890092</v>
       </c>
       <c r="B73" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>500271</v>
+        <v>500242</v>
       </c>
       <c r="R73" t="n">
-        <v>6792529</v>
+        <v>6792408</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7855,32 +7855,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125896279</v>
+        <v>125891809</v>
       </c>
       <c r="B74" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500351</v>
+        <v>500166</v>
       </c>
       <c r="R74" t="n">
-        <v>6792369</v>
+        <v>6792387</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7952,32 +7952,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125895125</v>
+        <v>125890555</v>
       </c>
       <c r="B75" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>499985</v>
+        <v>500282</v>
       </c>
       <c r="R75" t="n">
-        <v>6792633</v>
+        <v>6792389</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125890234</v>
+        <v>125893261</v>
       </c>
       <c r="B76" t="n">
         <v>8447</v>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>500242</v>
+        <v>500271</v>
       </c>
       <c r="R76" t="n">
-        <v>6792408</v>
+        <v>6792529</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8146,32 +8146,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125890092</v>
+        <v>125896279</v>
       </c>
       <c r="B77" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>500242</v>
+        <v>500351</v>
       </c>
       <c r="R77" t="n">
-        <v>6792408</v>
+        <v>6792369</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8243,32 +8243,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125891809</v>
+        <v>125895125</v>
       </c>
       <c r="B78" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>500166</v>
+        <v>499985</v>
       </c>
       <c r="R78" t="n">
-        <v>6792387</v>
+        <v>6792633</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8340,32 +8340,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125890555</v>
+        <v>125890234</v>
       </c>
       <c r="B79" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500282</v>
+        <v>500242</v>
       </c>
       <c r="R79" t="n">
-        <v>6792389</v>
+        <v>6792408</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8830,10 +8830,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125890407</v>
+        <v>125889155</v>
       </c>
       <c r="B84" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8841,21 +8841,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500242</v>
+        <v>500275</v>
       </c>
       <c r="R84" t="n">
-        <v>6792408</v>
+        <v>6792487</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8901,11 +8901,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8932,10 +8927,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125892653</v>
+        <v>125891598</v>
       </c>
       <c r="B85" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8943,21 +8938,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8967,10 +8962,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500151</v>
+        <v>500153</v>
       </c>
       <c r="R85" t="n">
-        <v>6792458</v>
+        <v>6792391</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9029,10 +9024,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125889406</v>
+        <v>125890407</v>
       </c>
       <c r="B86" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9040,21 +9035,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9064,10 +9059,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500257</v>
+        <v>500242</v>
       </c>
       <c r="R86" t="n">
-        <v>6792475</v>
+        <v>6792408</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9100,6 +9095,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9126,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125895109</v>
+        <v>125892653</v>
       </c>
       <c r="B87" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9137,21 +9137,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>499985</v>
+        <v>500151</v>
       </c>
       <c r="R87" t="n">
-        <v>6792633</v>
+        <v>6792458</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125889155</v>
+        <v>125889406</v>
       </c>
       <c r="B88" t="n">
-        <v>79562</v>
+        <v>79591</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9234,21 +9234,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9258,10 +9258,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500275</v>
+        <v>500257</v>
       </c>
       <c r="R88" t="n">
-        <v>6792487</v>
+        <v>6792475</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9320,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125891598</v>
+        <v>125895109</v>
       </c>
       <c r="B89" t="n">
-        <v>79562</v>
+        <v>79591</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,21 +9331,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500153</v>
+        <v>499985</v>
       </c>
       <c r="R89" t="n">
-        <v>6792391</v>
+        <v>6792633</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10096,32 +10096,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125889556</v>
+        <v>125890971</v>
       </c>
       <c r="B97" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>500218</v>
+        <v>500282</v>
       </c>
       <c r="R97" t="n">
-        <v>6792438</v>
+        <v>6792389</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10193,32 +10193,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125890971</v>
+        <v>125889556</v>
       </c>
       <c r="B98" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>500282</v>
+        <v>500218</v>
       </c>
       <c r="R98" t="n">
-        <v>6792389</v>
+        <v>6792438</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125896524</v>
+        <v>125896426</v>
       </c>
       <c r="B107" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11082,34 +11082,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500384</v>
+        <v>500351</v>
       </c>
       <c r="R107" t="n">
-        <v>6792529</v>
+        <v>6792369</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11168,7 +11173,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125889090</v>
+        <v>125896524</v>
       </c>
       <c r="B108" t="n">
         <v>79591</v>
@@ -11203,10 +11208,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500285</v>
+        <v>500384</v>
       </c>
       <c r="R108" t="n">
-        <v>6792489</v>
+        <v>6792529</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11265,10 +11270,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125896426</v>
+        <v>125889090</v>
       </c>
       <c r="B109" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11276,39 +11281,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500351</v>
+        <v>500285</v>
       </c>
       <c r="R109" t="n">
-        <v>6792369</v>
+        <v>6792489</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11469,32 +11469,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125892433</v>
+        <v>125893643</v>
       </c>
       <c r="B111" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11504,10 +11504,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500160</v>
+        <v>500237</v>
       </c>
       <c r="R111" t="n">
-        <v>6792451</v>
+        <v>6792567</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11566,30 +11566,34 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125894266</v>
+        <v>125892433</v>
       </c>
       <c r="B112" t="n">
-        <v>98261</v>
+        <v>79562</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>223597</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11597,10 +11601,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500128</v>
+        <v>500160</v>
       </c>
       <c r="R112" t="n">
-        <v>6792590</v>
+        <v>6792451</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11659,10 +11663,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125893643</v>
+        <v>125894266</v>
       </c>
       <c r="B113" t="n">
-        <v>8447</v>
+        <v>98263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11670,23 +11674,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>223597</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500237</v>
+        <v>500128</v>
       </c>
       <c r="R113" t="n">
-        <v>6792567</v>
+        <v>6792590</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,10 +11756,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125890126</v>
+        <v>125893637</v>
       </c>
       <c r="B114" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500242</v>
+        <v>500246</v>
       </c>
       <c r="R114" t="n">
-        <v>6792408</v>
+        <v>6792558</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11827,6 +11827,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11853,10 +11858,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125893637</v>
+        <v>125892154</v>
       </c>
       <c r="B115" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11864,21 +11869,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11893,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500246</v>
+        <v>500145</v>
       </c>
       <c r="R115" t="n">
-        <v>6792558</v>
+        <v>6792446</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11924,11 +11929,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11955,10 +11955,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125892154</v>
+        <v>125894500</v>
       </c>
       <c r="B116" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11966,21 +11966,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11990,10 +11990,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500145</v>
+        <v>500128</v>
       </c>
       <c r="R116" t="n">
-        <v>6792446</v>
+        <v>6792590</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12052,10 +12052,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125894500</v>
+        <v>125890126</v>
       </c>
       <c r="B117" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12063,21 +12063,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12087,10 +12087,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500128</v>
+        <v>500242</v>
       </c>
       <c r="R117" t="n">
-        <v>6792590</v>
+        <v>6792408</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B120" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R120" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,6 +12414,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12440,32 +12445,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125889503</v>
+        <v>125892496</v>
       </c>
       <c r="B121" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12475,10 +12480,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R121" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12511,6 +12516,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12537,32 +12547,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125888695</v>
+        <v>125893148</v>
       </c>
       <c r="B122" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12572,10 +12582,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500311</v>
+        <v>500251</v>
       </c>
       <c r="R122" t="n">
-        <v>6792502</v>
+        <v>6792496</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12608,11 +12618,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12639,32 +12644,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125892496</v>
+        <v>125889503</v>
       </c>
       <c r="B123" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12674,10 +12679,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R123" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12710,11 +12715,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12741,32 +12741,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125892207</v>
+        <v>125891471</v>
       </c>
       <c r="B124" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12776,10 +12776,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500158</v>
+        <v>500181</v>
       </c>
       <c r="R124" t="n">
-        <v>6792441</v>
+        <v>6792401</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12838,10 +12838,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125896030</v>
+        <v>125896611</v>
       </c>
       <c r="B125" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12849,39 +12849,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500351</v>
+        <v>500384</v>
       </c>
       <c r="R125" t="n">
-        <v>6792369</v>
+        <v>6792529</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12914,6 +12909,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12940,32 +12940,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125891471</v>
+        <v>125892207</v>
       </c>
       <c r="B126" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12975,10 +12975,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500181</v>
+        <v>500158</v>
       </c>
       <c r="R126" t="n">
-        <v>6792401</v>
+        <v>6792441</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13037,10 +13037,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125894132</v>
+        <v>125896030</v>
       </c>
       <c r="B127" t="n">
-        <v>78732</v>
+        <v>57652</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13048,34 +13048,39 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500128</v>
+        <v>500351</v>
       </c>
       <c r="R127" t="n">
-        <v>6792590</v>
+        <v>6792369</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13134,10 +13139,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125896611</v>
+        <v>125894132</v>
       </c>
       <c r="B128" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13145,21 +13150,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13169,10 +13174,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>500384</v>
+        <v>500128</v>
       </c>
       <c r="R128" t="n">
-        <v>6792529</v>
+        <v>6792590</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13205,11 +13210,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13435,45 +13435,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125890887</v>
+        <v>125891498</v>
       </c>
       <c r="B131" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>500282</v>
+        <v>500166</v>
       </c>
       <c r="R131" t="n">
-        <v>6792389</v>
+        <v>6792413</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13532,7 +13537,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125893186</v>
+        <v>125890887</v>
       </c>
       <c r="B132" t="n">
         <v>8447</v>
@@ -13567,10 +13572,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500247</v>
+        <v>500282</v>
       </c>
       <c r="R132" t="n">
-        <v>6792519</v>
+        <v>6792389</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13629,32 +13634,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125892751</v>
+        <v>125893186</v>
       </c>
       <c r="B133" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13664,10 +13669,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500151</v>
+        <v>500247</v>
       </c>
       <c r="R133" t="n">
-        <v>6792458</v>
+        <v>6792519</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13726,10 +13731,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125891498</v>
+        <v>125893307</v>
       </c>
       <c r="B134" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13737,39 +13742,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500166</v>
+        <v>500271</v>
       </c>
       <c r="R134" t="n">
-        <v>6792413</v>
+        <v>6792529</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13925,10 +13925,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125893307</v>
+        <v>125892751</v>
       </c>
       <c r="B136" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13936,21 +13936,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13960,10 +13960,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500271</v>
+        <v>500151</v>
       </c>
       <c r="R136" t="n">
-        <v>6792529</v>
+        <v>6792458</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14022,32 +14022,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125889773</v>
+        <v>125892352</v>
       </c>
       <c r="B137" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14057,10 +14057,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>500237</v>
+        <v>500165</v>
       </c>
       <c r="R137" t="n">
-        <v>6792422</v>
+        <v>6792432</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14119,10 +14119,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125892352</v>
+        <v>125889010</v>
       </c>
       <c r="B138" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14130,21 +14130,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14154,10 +14154,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>500165</v>
+        <v>500286</v>
       </c>
       <c r="R138" t="n">
-        <v>6792432</v>
+        <v>6792459</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14216,32 +14216,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125889010</v>
+        <v>125889773</v>
       </c>
       <c r="B139" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>500286</v>
+        <v>500237</v>
       </c>
       <c r="R139" t="n">
-        <v>6792459</v>
+        <v>6792422</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15005,7 +15005,7 @@
         <v>125896772</v>
       </c>
       <c r="B147" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>125892942</v>
       </c>
       <c r="B159" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1023,32 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125686874</v>
+        <v>125686800</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500013</v>
+        <v>500007</v>
       </c>
       <c r="R5" t="n">
-        <v>6792493</v>
+        <v>6792490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,11 +1094,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,32 +1120,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125693671</v>
+        <v>125686732</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500087</v>
+        <v>499990</v>
       </c>
       <c r="R6" t="n">
-        <v>6792574</v>
+        <v>6792488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1191,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,32 +1222,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125687215</v>
+        <v>125685630</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499945</v>
+        <v>499996</v>
       </c>
       <c r="R7" t="n">
-        <v>6792497</v>
+        <v>6792394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,32 +1319,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125689836</v>
+        <v>125685407</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499951</v>
+        <v>500063</v>
       </c>
       <c r="R8" t="n">
-        <v>6792574</v>
+        <v>6792381</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,32 +1416,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125686800</v>
+        <v>125686874</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500007</v>
+        <v>500013</v>
       </c>
       <c r="R9" t="n">
-        <v>6792490</v>
+        <v>6792493</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,6 +1487,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,32 +1518,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125686732</v>
+        <v>125693671</v>
       </c>
       <c r="B10" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499990</v>
+        <v>500087</v>
       </c>
       <c r="R10" t="n">
-        <v>6792488</v>
+        <v>6792574</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,11 +1589,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,32 +1615,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125685630</v>
+        <v>125687215</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499996</v>
+        <v>499945</v>
       </c>
       <c r="R11" t="n">
-        <v>6792394</v>
+        <v>6792497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,32 +1712,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125685407</v>
+        <v>125689836</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500063</v>
+        <v>499951</v>
       </c>
       <c r="R12" t="n">
-        <v>6792381</v>
+        <v>6792574</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125685512</v>
+        <v>125693794</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>56844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3014,34 +3014,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499996</v>
+        <v>500087</v>
       </c>
       <c r="R25" t="n">
-        <v>6792394</v>
+        <v>6792574</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3074,11 +3079,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3105,32 +3105,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125689285</v>
+        <v>125685512</v>
       </c>
       <c r="B26" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499942</v>
+        <v>499996</v>
       </c>
       <c r="R26" t="n">
-        <v>6792546</v>
+        <v>6792394</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3207,50 +3207,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125693794</v>
+        <v>125689285</v>
       </c>
       <c r="B27" t="n">
-        <v>56844</v>
+        <v>79562</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500087</v>
+        <v>499942</v>
       </c>
       <c r="R27" t="n">
-        <v>6792574</v>
+        <v>6792546</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3283,6 +3278,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3309,10 +3309,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125686305</v>
+        <v>125686343</v>
       </c>
       <c r="B28" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3320,21 +3320,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3380,11 +3380,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3411,10 +3406,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125693249</v>
+        <v>125685148</v>
       </c>
       <c r="B29" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3422,21 +3417,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3446,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500047</v>
+        <v>500040</v>
       </c>
       <c r="R29" t="n">
-        <v>6792612</v>
+        <v>6792406</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,10 +3503,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125686343</v>
+        <v>125693241</v>
       </c>
       <c r="B30" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3519,21 +3514,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3543,10 +3538,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499963</v>
+        <v>500047</v>
       </c>
       <c r="R30" t="n">
-        <v>6792480</v>
+        <v>6792612</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3605,32 +3600,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125685148</v>
+        <v>125683895</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3640,10 +3635,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500040</v>
+        <v>500326</v>
       </c>
       <c r="R31" t="n">
-        <v>6792406</v>
+        <v>6792440</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3676,6 +3671,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3702,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125693241</v>
+        <v>125686305</v>
       </c>
       <c r="B32" t="n">
-        <v>57649</v>
+        <v>78732</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3713,21 +3713,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500047</v>
+        <v>499963</v>
       </c>
       <c r="R32" t="n">
-        <v>6792612</v>
+        <v>6792480</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3773,6 +3773,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3799,32 +3804,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125683895</v>
+        <v>125693249</v>
       </c>
       <c r="B33" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3834,10 +3839,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500326</v>
+        <v>500047</v>
       </c>
       <c r="R33" t="n">
-        <v>6792440</v>
+        <v>6792612</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3870,11 +3875,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5279,32 +5279,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125689757</v>
+        <v>125685110</v>
       </c>
       <c r="B48" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499951</v>
+        <v>500063</v>
       </c>
       <c r="R48" t="n">
-        <v>6792574</v>
+        <v>6792423</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,32 +5381,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125685110</v>
+        <v>125689757</v>
       </c>
       <c r="B49" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500063</v>
+        <v>499951</v>
       </c>
       <c r="R49" t="n">
-        <v>6792423</v>
+        <v>6792574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7263,32 +7263,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125892998</v>
+        <v>125888195</v>
       </c>
       <c r="B68" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500188</v>
+        <v>500310</v>
       </c>
       <c r="R68" t="n">
-        <v>6792496</v>
+        <v>6792516</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,6 +7334,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7360,45 +7365,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125893046</v>
+        <v>125894731</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>57652</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500207</v>
+        <v>500128</v>
       </c>
       <c r="R69" t="n">
-        <v>6792488</v>
+        <v>6792590</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7457,32 +7467,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125888195</v>
+        <v>125892998</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7492,10 +7502,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500310</v>
+        <v>500188</v>
       </c>
       <c r="R70" t="n">
-        <v>6792516</v>
+        <v>6792496</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7528,11 +7538,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7559,50 +7564,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125894731</v>
+        <v>125893046</v>
       </c>
       <c r="B71" t="n">
-        <v>57652</v>
+        <v>8447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500128</v>
+        <v>500207</v>
       </c>
       <c r="R71" t="n">
-        <v>6792590</v>
+        <v>6792488</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7758,10 +7758,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125890092</v>
+        <v>125890555</v>
       </c>
       <c r="B73" t="n">
-        <v>79562</v>
+        <v>79591</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7769,21 +7769,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>500242</v>
+        <v>500282</v>
       </c>
       <c r="R73" t="n">
-        <v>6792408</v>
+        <v>6792389</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7855,32 +7855,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125891809</v>
+        <v>125893261</v>
       </c>
       <c r="B74" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500166</v>
+        <v>500271</v>
       </c>
       <c r="R74" t="n">
-        <v>6792387</v>
+        <v>6792529</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7952,32 +7952,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125890555</v>
+        <v>125896279</v>
       </c>
       <c r="B75" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>500282</v>
+        <v>500351</v>
       </c>
       <c r="R75" t="n">
-        <v>6792389</v>
+        <v>6792369</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125893261</v>
+        <v>125895125</v>
       </c>
       <c r="B76" t="n">
         <v>8447</v>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>500271</v>
+        <v>499985</v>
       </c>
       <c r="R76" t="n">
-        <v>6792529</v>
+        <v>6792633</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125896279</v>
+        <v>125890234</v>
       </c>
       <c r="B77" t="n">
         <v>8447</v>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>500351</v>
+        <v>500242</v>
       </c>
       <c r="R77" t="n">
-        <v>6792369</v>
+        <v>6792408</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8243,32 +8243,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125895125</v>
+        <v>125890092</v>
       </c>
       <c r="B78" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>499985</v>
+        <v>500242</v>
       </c>
       <c r="R78" t="n">
-        <v>6792633</v>
+        <v>6792408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8340,32 +8340,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125890234</v>
+        <v>125891809</v>
       </c>
       <c r="B79" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500242</v>
+        <v>500166</v>
       </c>
       <c r="R79" t="n">
-        <v>6792408</v>
+        <v>6792387</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125894466</v>
+        <v>125896683</v>
       </c>
       <c r="B90" t="n">
         <v>8447</v>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R90" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9514,7 +9514,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125896683</v>
+        <v>125894466</v>
       </c>
       <c r="B91" t="n">
         <v>8447</v>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>500384</v>
+        <v>500128</v>
       </c>
       <c r="R91" t="n">
-        <v>6792529</v>
+        <v>6792590</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10096,32 +10096,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125890971</v>
+        <v>125889556</v>
       </c>
       <c r="B97" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>500282</v>
+        <v>500218</v>
       </c>
       <c r="R97" t="n">
-        <v>6792389</v>
+        <v>6792438</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10193,32 +10193,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125889556</v>
+        <v>125890971</v>
       </c>
       <c r="B98" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>500218</v>
+        <v>500282</v>
       </c>
       <c r="R98" t="n">
-        <v>6792438</v>
+        <v>6792389</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10484,7 +10484,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125893327</v>
+        <v>125892219</v>
       </c>
       <c r="B101" t="n">
         <v>78732</v>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>500271</v>
+        <v>500158</v>
       </c>
       <c r="R101" t="n">
-        <v>6792529</v>
+        <v>6792441</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10581,7 +10581,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125892219</v>
+        <v>125893327</v>
       </c>
       <c r="B102" t="n">
         <v>78732</v>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>500158</v>
+        <v>500271</v>
       </c>
       <c r="R102" t="n">
-        <v>6792441</v>
+        <v>6792529</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125896426</v>
+        <v>125896524</v>
       </c>
       <c r="B107" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11082,39 +11082,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500351</v>
+        <v>500384</v>
       </c>
       <c r="R107" t="n">
-        <v>6792369</v>
+        <v>6792529</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11173,10 +11168,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125896524</v>
+        <v>125896426</v>
       </c>
       <c r="B108" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11184,34 +11179,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500384</v>
+        <v>500351</v>
       </c>
       <c r="R108" t="n">
-        <v>6792529</v>
+        <v>6792369</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11270,10 +11270,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125889090</v>
+        <v>125889496</v>
       </c>
       <c r="B109" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11281,34 +11281,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500285</v>
+        <v>500257</v>
       </c>
       <c r="R109" t="n">
-        <v>6792489</v>
+        <v>6792475</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11367,50 +11372,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125889496</v>
+        <v>125893643</v>
       </c>
       <c r="B110" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500257</v>
+        <v>500237</v>
       </c>
       <c r="R110" t="n">
-        <v>6792475</v>
+        <v>6792567</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11469,32 +11469,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125893643</v>
+        <v>125889090</v>
       </c>
       <c r="B111" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11504,10 +11504,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500237</v>
+        <v>500285</v>
       </c>
       <c r="R111" t="n">
-        <v>6792567</v>
+        <v>6792489</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15002,45 +15002,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125896772</v>
+        <v>125888369</v>
       </c>
       <c r="B147" t="n">
-        <v>92526</v>
+        <v>57649</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500384</v>
+        <v>500310</v>
       </c>
       <c r="R147" t="n">
-        <v>6792529</v>
+        <v>6792516</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15099,10 +15104,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125891864</v>
+        <v>125888908</v>
       </c>
       <c r="B148" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15110,21 +15115,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15134,10 +15139,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500126</v>
+        <v>500306</v>
       </c>
       <c r="R148" t="n">
-        <v>6792397</v>
+        <v>6792466</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15170,11 +15175,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15201,10 +15201,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125892001</v>
+        <v>125896772</v>
       </c>
       <c r="B149" t="n">
-        <v>8447</v>
+        <v>92526</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15212,21 +15212,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15236,10 +15236,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500111</v>
+        <v>500384</v>
       </c>
       <c r="R149" t="n">
-        <v>6792428</v>
+        <v>6792529</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15298,10 +15298,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125888369</v>
+        <v>125891864</v>
       </c>
       <c r="B150" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15309,39 +15309,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500310</v>
+        <v>500126</v>
       </c>
       <c r="R150" t="n">
-        <v>6792516</v>
+        <v>6792397</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15374,6 +15369,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15400,32 +15400,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125888908</v>
+        <v>125892001</v>
       </c>
       <c r="B151" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15435,10 +15435,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500306</v>
+        <v>500111</v>
       </c>
       <c r="R151" t="n">
-        <v>6792466</v>
+        <v>6792428</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1906,10 +1906,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125684974</v>
+        <v>125684006</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1917,34 +1917,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500076</v>
+        <v>500326</v>
       </c>
       <c r="R14" t="n">
-        <v>6792407</v>
+        <v>6792440</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1977,6 +1982,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125693564</v>
+        <v>125684974</v>
       </c>
       <c r="B15" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2014,21 +2024,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2038,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500087</v>
+        <v>500076</v>
       </c>
       <c r="R15" t="n">
-        <v>6792574</v>
+        <v>6792407</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2100,10 +2110,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125684006</v>
+        <v>125693564</v>
       </c>
       <c r="B16" t="n">
-        <v>57649</v>
+        <v>78731</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2111,39 +2121,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500326</v>
+        <v>500087</v>
       </c>
       <c r="R16" t="n">
-        <v>6792440</v>
+        <v>6792574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,11 +2181,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3309,10 +3309,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125686343</v>
+        <v>125693241</v>
       </c>
       <c r="B28" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3320,21 +3320,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499963</v>
+        <v>500047</v>
       </c>
       <c r="R28" t="n">
-        <v>6792480</v>
+        <v>6792612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125685148</v>
+        <v>125686305</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500040</v>
+        <v>499963</v>
       </c>
       <c r="R29" t="n">
-        <v>6792406</v>
+        <v>6792480</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3477,6 +3477,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3503,10 +3508,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125693241</v>
+        <v>125693249</v>
       </c>
       <c r="B30" t="n">
-        <v>57649</v>
+        <v>79562</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,21 +3519,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3600,32 +3605,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125683895</v>
+        <v>125686343</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3635,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500326</v>
+        <v>499963</v>
       </c>
       <c r="R31" t="n">
-        <v>6792440</v>
+        <v>6792480</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3671,11 +3676,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3702,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125686305</v>
+        <v>125685148</v>
       </c>
       <c r="B32" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3713,21 +3713,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499963</v>
+        <v>500040</v>
       </c>
       <c r="R32" t="n">
-        <v>6792480</v>
+        <v>6792406</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3773,11 +3773,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3804,32 +3799,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125693249</v>
+        <v>125683895</v>
       </c>
       <c r="B33" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3839,10 +3834,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500047</v>
+        <v>500326</v>
       </c>
       <c r="R33" t="n">
-        <v>6792612</v>
+        <v>6792440</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3875,6 +3870,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5580,32 +5580,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125685693</v>
+        <v>125684626</v>
       </c>
       <c r="B51" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500002</v>
+        <v>500047</v>
       </c>
       <c r="R51" t="n">
-        <v>6792449</v>
+        <v>6792395</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5651,11 +5651,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5682,32 +5677,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125686894</v>
+        <v>125690154</v>
       </c>
       <c r="B52" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5717,10 +5712,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500010</v>
+        <v>499990</v>
       </c>
       <c r="R52" t="n">
-        <v>6792501</v>
+        <v>6792543</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5753,6 +5748,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5779,32 +5779,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125684626</v>
+        <v>125685693</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500047</v>
+        <v>500002</v>
       </c>
       <c r="R53" t="n">
-        <v>6792395</v>
+        <v>6792449</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5850,6 +5850,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5876,32 +5881,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125690154</v>
+        <v>125686894</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5911,10 +5916,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499990</v>
+        <v>500010</v>
       </c>
       <c r="R54" t="n">
-        <v>6792543</v>
+        <v>6792501</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5947,11 +5952,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5978,10 +5978,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685885</v>
+        <v>125685813</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5989,21 +5989,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>500002</v>
+        <v>499996</v>
       </c>
       <c r="R55" t="n">
-        <v>6792449</v>
+        <v>6792435</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6075,7 +6075,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125690170</v>
+        <v>125685885</v>
       </c>
       <c r="B56" t="n">
         <v>78973</v>
@@ -6110,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>500018</v>
+        <v>500002</v>
       </c>
       <c r="R56" t="n">
-        <v>6792528</v>
+        <v>6792449</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6172,32 +6172,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125683878</v>
+        <v>125690170</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499954</v>
+        <v>500018</v>
       </c>
       <c r="R57" t="n">
-        <v>6792394</v>
+        <v>6792528</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6243,11 +6243,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6274,32 +6269,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125685813</v>
+        <v>125683878</v>
       </c>
       <c r="B58" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6304,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499996</v>
+        <v>499954</v>
       </c>
       <c r="R58" t="n">
-        <v>6792435</v>
+        <v>6792394</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6345,6 +6340,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6371,10 +6371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125687400</v>
+        <v>125686648</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6382,21 +6382,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499947</v>
+        <v>499990</v>
       </c>
       <c r="R59" t="n">
-        <v>6792525</v>
+        <v>6792488</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6442,6 +6442,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6468,10 +6473,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125686648</v>
+        <v>125687400</v>
       </c>
       <c r="B60" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6479,21 +6484,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6503,10 +6508,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>499990</v>
+        <v>499947</v>
       </c>
       <c r="R60" t="n">
-        <v>6792488</v>
+        <v>6792525</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6539,11 +6544,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6958,7 +6958,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125685734</v>
+        <v>125685660</v>
       </c>
       <c r="B65" t="n">
         <v>78973</v>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>499996</v>
+        <v>499989</v>
       </c>
       <c r="R65" t="n">
-        <v>6792435</v>
+        <v>6792445</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7029,11 +7029,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7060,7 +7055,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125685660</v>
+        <v>125685734</v>
       </c>
       <c r="B66" t="n">
         <v>78973</v>
@@ -7095,10 +7090,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>499989</v>
+        <v>499996</v>
       </c>
       <c r="R66" t="n">
-        <v>6792445</v>
+        <v>6792435</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7131,6 +7126,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125888195</v>
+        <v>125894731</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,34 +7274,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500310</v>
+        <v>500128</v>
       </c>
       <c r="R68" t="n">
-        <v>6792516</v>
+        <v>6792590</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,11 +7339,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7365,50 +7365,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125894731</v>
+        <v>125892998</v>
       </c>
       <c r="B69" t="n">
-        <v>57652</v>
+        <v>8447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500128</v>
+        <v>500188</v>
       </c>
       <c r="R69" t="n">
-        <v>6792590</v>
+        <v>6792496</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7467,7 +7462,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125892998</v>
+        <v>125893046</v>
       </c>
       <c r="B70" t="n">
         <v>8447</v>
@@ -7502,10 +7497,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500188</v>
+        <v>500207</v>
       </c>
       <c r="R70" t="n">
-        <v>6792496</v>
+        <v>6792488</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7564,32 +7559,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125893046</v>
+        <v>125888195</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7599,10 +7594,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500207</v>
+        <v>500310</v>
       </c>
       <c r="R71" t="n">
-        <v>6792488</v>
+        <v>6792516</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7635,6 +7630,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7758,10 +7758,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125890555</v>
+        <v>125890092</v>
       </c>
       <c r="B73" t="n">
-        <v>79591</v>
+        <v>79562</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7769,21 +7769,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>500282</v>
+        <v>500242</v>
       </c>
       <c r="R73" t="n">
-        <v>6792389</v>
+        <v>6792408</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7855,32 +7855,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125893261</v>
+        <v>125891809</v>
       </c>
       <c r="B74" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500271</v>
+        <v>500166</v>
       </c>
       <c r="R74" t="n">
-        <v>6792529</v>
+        <v>6792387</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7952,32 +7952,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125896279</v>
+        <v>125890555</v>
       </c>
       <c r="B75" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>500351</v>
+        <v>500282</v>
       </c>
       <c r="R75" t="n">
-        <v>6792369</v>
+        <v>6792389</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125895125</v>
+        <v>125893261</v>
       </c>
       <c r="B76" t="n">
         <v>8447</v>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>499985</v>
+        <v>500271</v>
       </c>
       <c r="R76" t="n">
-        <v>6792633</v>
+        <v>6792529</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125890234</v>
+        <v>125896279</v>
       </c>
       <c r="B77" t="n">
         <v>8447</v>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>500242</v>
+        <v>500351</v>
       </c>
       <c r="R77" t="n">
-        <v>6792408</v>
+        <v>6792369</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8243,32 +8243,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125890092</v>
+        <v>125895125</v>
       </c>
       <c r="B78" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>500242</v>
+        <v>499985</v>
       </c>
       <c r="R78" t="n">
-        <v>6792408</v>
+        <v>6792633</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8340,32 +8340,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125891809</v>
+        <v>125890234</v>
       </c>
       <c r="B79" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500166</v>
+        <v>500242</v>
       </c>
       <c r="R79" t="n">
-        <v>6792387</v>
+        <v>6792408</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8437,10 +8437,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125888740</v>
+        <v>125892215</v>
       </c>
       <c r="B80" t="n">
-        <v>57812</v>
+        <v>79562</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8448,39 +8448,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500306</v>
+        <v>500158</v>
       </c>
       <c r="R80" t="n">
-        <v>6792466</v>
+        <v>6792441</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8539,32 +8534,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125892266</v>
+        <v>125889155</v>
       </c>
       <c r="B81" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8574,10 +8569,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500158</v>
+        <v>500275</v>
       </c>
       <c r="R81" t="n">
-        <v>6792441</v>
+        <v>6792487</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8636,32 +8631,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125888709</v>
+        <v>125891598</v>
       </c>
       <c r="B82" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8671,10 +8666,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500311</v>
+        <v>500153</v>
       </c>
       <c r="R82" t="n">
-        <v>6792502</v>
+        <v>6792391</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8733,10 +8728,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125892215</v>
+        <v>125890407</v>
       </c>
       <c r="B83" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8744,21 +8739,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8768,10 +8763,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>500158</v>
+        <v>500242</v>
       </c>
       <c r="R83" t="n">
-        <v>6792441</v>
+        <v>6792408</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8804,6 +8799,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8830,10 +8830,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125889155</v>
+        <v>125892653</v>
       </c>
       <c r="B84" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8841,21 +8841,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500275</v>
+        <v>500151</v>
       </c>
       <c r="R84" t="n">
-        <v>6792487</v>
+        <v>6792458</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8927,10 +8927,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125891598</v>
+        <v>125889406</v>
       </c>
       <c r="B85" t="n">
-        <v>79562</v>
+        <v>79591</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8938,21 +8938,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500153</v>
+        <v>500257</v>
       </c>
       <c r="R85" t="n">
-        <v>6792391</v>
+        <v>6792475</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9024,10 +9024,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125890407</v>
+        <v>125895109</v>
       </c>
       <c r="B86" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9035,21 +9035,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500242</v>
+        <v>499985</v>
       </c>
       <c r="R86" t="n">
-        <v>6792408</v>
+        <v>6792633</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9095,11 +9095,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9126,32 +9121,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125892653</v>
+        <v>125892266</v>
       </c>
       <c r="B87" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9161,10 +9156,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500151</v>
+        <v>500158</v>
       </c>
       <c r="R87" t="n">
-        <v>6792458</v>
+        <v>6792441</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9223,32 +9218,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125889406</v>
+        <v>125888709</v>
       </c>
       <c r="B88" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9258,10 +9253,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500257</v>
+        <v>500311</v>
       </c>
       <c r="R88" t="n">
-        <v>6792475</v>
+        <v>6792502</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9320,10 +9315,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125895109</v>
+        <v>125888740</v>
       </c>
       <c r="B89" t="n">
-        <v>79591</v>
+        <v>57812</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,34 +9326,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>499985</v>
+        <v>500306</v>
       </c>
       <c r="R89" t="n">
-        <v>6792633</v>
+        <v>6792466</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9611,10 +9611,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125889889</v>
+        <v>125896400</v>
       </c>
       <c r="B92" t="n">
-        <v>79591</v>
+        <v>79562</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9622,21 +9622,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>500237</v>
+        <v>500351</v>
       </c>
       <c r="R92" t="n">
-        <v>6792422</v>
+        <v>6792369</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125896400</v>
+        <v>125889879</v>
       </c>
       <c r="B93" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,21 +9719,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>500351</v>
+        <v>500237</v>
       </c>
       <c r="R93" t="n">
-        <v>6792369</v>
+        <v>6792422</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,7 +9805,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125889879</v>
+        <v>125895107</v>
       </c>
       <c r="B94" t="n">
         <v>78732</v>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>500237</v>
+        <v>499985</v>
       </c>
       <c r="R94" t="n">
-        <v>6792422</v>
+        <v>6792633</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125895107</v>
+        <v>125889889</v>
       </c>
       <c r="B95" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>499985</v>
+        <v>500237</v>
       </c>
       <c r="R95" t="n">
-        <v>6792633</v>
+        <v>6792422</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10484,7 +10484,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125892219</v>
+        <v>125893327</v>
       </c>
       <c r="B101" t="n">
         <v>78732</v>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>500158</v>
+        <v>500271</v>
       </c>
       <c r="R101" t="n">
-        <v>6792441</v>
+        <v>6792529</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10581,7 +10581,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125893327</v>
+        <v>125892219</v>
       </c>
       <c r="B102" t="n">
         <v>78732</v>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>500271</v>
+        <v>500158</v>
       </c>
       <c r="R102" t="n">
-        <v>6792529</v>
+        <v>6792441</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125892224</v>
+        <v>125889615</v>
       </c>
       <c r="B103" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500158</v>
+        <v>500202</v>
       </c>
       <c r="R103" t="n">
-        <v>6792441</v>
+        <v>6792435</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10775,10 +10775,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125896058</v>
+        <v>125892224</v>
       </c>
       <c r="B104" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500351</v>
+        <v>500158</v>
       </c>
       <c r="R104" t="n">
-        <v>6792369</v>
+        <v>6792441</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,11 +10846,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10877,10 +10872,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125891964</v>
+        <v>125896058</v>
       </c>
       <c r="B105" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10888,21 +10883,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10912,10 +10907,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500111</v>
+        <v>500351</v>
       </c>
       <c r="R105" t="n">
-        <v>6792428</v>
+        <v>6792369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10948,6 +10943,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125889615</v>
+        <v>125891964</v>
       </c>
       <c r="B106" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500202</v>
+        <v>500111</v>
       </c>
       <c r="R106" t="n">
-        <v>6792435</v>
+        <v>6792428</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11168,10 +11168,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125896426</v>
+        <v>125889090</v>
       </c>
       <c r="B108" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11179,39 +11179,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500351</v>
+        <v>500285</v>
       </c>
       <c r="R108" t="n">
-        <v>6792369</v>
+        <v>6792489</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11270,7 +11265,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125889496</v>
+        <v>125896426</v>
       </c>
       <c r="B109" t="n">
         <v>57649</v>
@@ -11301,7 +11296,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -11310,10 +11305,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500257</v>
+        <v>500351</v>
       </c>
       <c r="R109" t="n">
-        <v>6792475</v>
+        <v>6792369</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11372,45 +11367,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125893643</v>
+        <v>125889496</v>
       </c>
       <c r="B110" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500237</v>
+        <v>500257</v>
       </c>
       <c r="R110" t="n">
-        <v>6792567</v>
+        <v>6792475</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11469,32 +11469,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125889090</v>
+        <v>125893643</v>
       </c>
       <c r="B111" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11504,10 +11504,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500285</v>
+        <v>500237</v>
       </c>
       <c r="R111" t="n">
-        <v>6792489</v>
+        <v>6792567</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11566,34 +11566,30 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125892433</v>
+        <v>125894266</v>
       </c>
       <c r="B112" t="n">
-        <v>79562</v>
+        <v>98265</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>223597</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11601,10 +11597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500160</v>
+        <v>500128</v>
       </c>
       <c r="R112" t="n">
-        <v>6792451</v>
+        <v>6792590</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11663,30 +11659,34 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125894266</v>
+        <v>125892433</v>
       </c>
       <c r="B113" t="n">
-        <v>98263</v>
+        <v>79562</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>223597</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500128</v>
+        <v>500160</v>
       </c>
       <c r="R113" t="n">
-        <v>6792590</v>
+        <v>6792451</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,10 +11756,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125893637</v>
+        <v>125890126</v>
       </c>
       <c r="B114" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500246</v>
+        <v>500242</v>
       </c>
       <c r="R114" t="n">
-        <v>6792558</v>
+        <v>6792408</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11827,11 +11827,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11858,10 +11853,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125892154</v>
+        <v>125893637</v>
       </c>
       <c r="B115" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11869,21 +11864,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11893,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500145</v>
+        <v>500246</v>
       </c>
       <c r="R115" t="n">
-        <v>6792446</v>
+        <v>6792558</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11929,6 +11924,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11955,10 +11955,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125894500</v>
+        <v>125892154</v>
       </c>
       <c r="B116" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11966,21 +11966,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11990,10 +11990,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500128</v>
+        <v>500145</v>
       </c>
       <c r="R116" t="n">
-        <v>6792590</v>
+        <v>6792446</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12052,10 +12052,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125890126</v>
+        <v>125894500</v>
       </c>
       <c r="B117" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12063,21 +12063,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12087,10 +12087,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500242</v>
+        <v>500128</v>
       </c>
       <c r="R117" t="n">
-        <v>6792408</v>
+        <v>6792590</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125888695</v>
+        <v>125893148</v>
       </c>
       <c r="B120" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500311</v>
+        <v>500251</v>
       </c>
       <c r="R120" t="n">
-        <v>6792502</v>
+        <v>6792496</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,11 +12414,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12445,32 +12440,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125892496</v>
+        <v>125889503</v>
       </c>
       <c r="B121" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12480,10 +12475,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R121" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12516,11 +12511,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12547,32 +12537,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12582,10 +12572,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R122" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12618,6 +12608,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12644,32 +12639,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125889503</v>
+        <v>125892496</v>
       </c>
       <c r="B123" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12679,10 +12674,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R123" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12715,6 +12710,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13537,32 +13537,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125890887</v>
+        <v>125893307</v>
       </c>
       <c r="B132" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13572,10 +13572,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500282</v>
+        <v>500271</v>
       </c>
       <c r="R132" t="n">
-        <v>6792389</v>
+        <v>6792529</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13634,32 +13634,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125893186</v>
+        <v>125891649</v>
       </c>
       <c r="B133" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13669,10 +13669,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500247</v>
+        <v>500166</v>
       </c>
       <c r="R133" t="n">
-        <v>6792519</v>
+        <v>6792387</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13731,32 +13731,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125893307</v>
+        <v>125890887</v>
       </c>
       <c r="B134" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500271</v>
+        <v>500282</v>
       </c>
       <c r="R134" t="n">
-        <v>6792529</v>
+        <v>6792389</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13828,32 +13828,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125891649</v>
+        <v>125893186</v>
       </c>
       <c r="B135" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13863,10 +13863,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500166</v>
+        <v>500247</v>
       </c>
       <c r="R135" t="n">
-        <v>6792387</v>
+        <v>6792519</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14022,32 +14022,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125892352</v>
+        <v>125889773</v>
       </c>
       <c r="B137" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14057,10 +14057,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>500165</v>
+        <v>500237</v>
       </c>
       <c r="R137" t="n">
-        <v>6792432</v>
+        <v>6792422</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14119,10 +14119,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125889010</v>
+        <v>125892352</v>
       </c>
       <c r="B138" t="n">
-        <v>78732</v>
+        <v>79562</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14130,21 +14130,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14154,10 +14154,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>500286</v>
+        <v>500165</v>
       </c>
       <c r="R138" t="n">
-        <v>6792459</v>
+        <v>6792432</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14216,32 +14216,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125889773</v>
+        <v>125889010</v>
       </c>
       <c r="B139" t="n">
-        <v>8447</v>
+        <v>78732</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>500237</v>
+        <v>500286</v>
       </c>
       <c r="R139" t="n">
-        <v>6792422</v>
+        <v>6792459</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15002,50 +15002,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125888369</v>
+        <v>125896772</v>
       </c>
       <c r="B147" t="n">
-        <v>57649</v>
+        <v>92528</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500310</v>
+        <v>500384</v>
       </c>
       <c r="R147" t="n">
-        <v>6792516</v>
+        <v>6792529</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15104,10 +15099,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125888908</v>
+        <v>125888369</v>
       </c>
       <c r="B148" t="n">
-        <v>79562</v>
+        <v>57649</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15115,34 +15110,39 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500306</v>
+        <v>500310</v>
       </c>
       <c r="R148" t="n">
-        <v>6792466</v>
+        <v>6792516</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15201,32 +15201,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125896772</v>
+        <v>125891864</v>
       </c>
       <c r="B149" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15236,10 +15236,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500384</v>
+        <v>500126</v>
       </c>
       <c r="R149" t="n">
-        <v>6792529</v>
+        <v>6792397</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15272,6 +15272,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15298,10 +15303,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125891864</v>
+        <v>125888908</v>
       </c>
       <c r="B150" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15309,21 +15314,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15333,10 +15338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500126</v>
+        <v>500306</v>
       </c>
       <c r="R150" t="n">
-        <v>6792397</v>
+        <v>6792466</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15369,11 +15374,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16184,7 +16184,7 @@
         <v>125892942</v>
       </c>
       <c r="B159" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -2503,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125684537</v>
+        <v>125690007</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500039</v>
+        <v>499989</v>
       </c>
       <c r="R20" t="n">
-        <v>6792388</v>
+        <v>6792563</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125690007</v>
+        <v>125684537</v>
       </c>
       <c r="B21" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499989</v>
+        <v>500039</v>
       </c>
       <c r="R21" t="n">
-        <v>6792563</v>
+        <v>6792388</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -5978,10 +5978,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685813</v>
+        <v>125685885</v>
       </c>
       <c r="B55" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5989,21 +5989,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499996</v>
+        <v>500002</v>
       </c>
       <c r="R55" t="n">
-        <v>6792435</v>
+        <v>6792449</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6075,7 +6075,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125685885</v>
+        <v>125690170</v>
       </c>
       <c r="B56" t="n">
         <v>78973</v>
@@ -6110,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>500002</v>
+        <v>500018</v>
       </c>
       <c r="R56" t="n">
-        <v>6792449</v>
+        <v>6792528</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6172,32 +6172,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125690170</v>
+        <v>125683878</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>500018</v>
+        <v>499954</v>
       </c>
       <c r="R57" t="n">
-        <v>6792528</v>
+        <v>6792394</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6243,6 +6243,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6269,32 +6274,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125683878</v>
+        <v>125685813</v>
       </c>
       <c r="B58" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6304,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499954</v>
+        <v>499996</v>
       </c>
       <c r="R58" t="n">
-        <v>6792394</v>
+        <v>6792435</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6340,11 +6345,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6371,10 +6371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125686648</v>
+        <v>125687400</v>
       </c>
       <c r="B59" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6382,21 +6382,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499990</v>
+        <v>499947</v>
       </c>
       <c r="R59" t="n">
-        <v>6792488</v>
+        <v>6792525</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6442,11 +6442,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6473,10 +6468,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125687400</v>
+        <v>125686648</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6484,21 +6479,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6508,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>499947</v>
+        <v>499990</v>
       </c>
       <c r="R60" t="n">
-        <v>6792525</v>
+        <v>6792488</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6544,6 +6539,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7365,32 +7365,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125892998</v>
+        <v>125889107</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500188</v>
+        <v>500285</v>
       </c>
       <c r="R69" t="n">
-        <v>6792496</v>
+        <v>6792489</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7462,32 +7462,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125893046</v>
+        <v>125888195</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500207</v>
+        <v>500310</v>
       </c>
       <c r="R70" t="n">
-        <v>6792488</v>
+        <v>6792516</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7533,6 +7533,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7559,32 +7564,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125888195</v>
+        <v>125892998</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7594,10 +7599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500310</v>
+        <v>500188</v>
       </c>
       <c r="R71" t="n">
-        <v>6792516</v>
+        <v>6792496</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7630,11 +7635,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7661,32 +7661,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125889107</v>
+        <v>125893046</v>
       </c>
       <c r="B72" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500285</v>
+        <v>500207</v>
       </c>
       <c r="R72" t="n">
-        <v>6792489</v>
+        <v>6792488</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8437,10 +8437,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125892215</v>
+        <v>125890407</v>
       </c>
       <c r="B80" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8448,21 +8448,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8472,10 +8472,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500158</v>
+        <v>500242</v>
       </c>
       <c r="R80" t="n">
-        <v>6792441</v>
+        <v>6792408</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8508,6 +8508,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8534,10 +8539,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125889155</v>
+        <v>125892653</v>
       </c>
       <c r="B81" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8545,21 +8550,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8569,10 +8574,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500275</v>
+        <v>500151</v>
       </c>
       <c r="R81" t="n">
-        <v>6792487</v>
+        <v>6792458</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8631,10 +8636,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125891598</v>
+        <v>125889406</v>
       </c>
       <c r="B82" t="n">
-        <v>79562</v>
+        <v>79591</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8642,21 +8647,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8666,10 +8671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500153</v>
+        <v>500257</v>
       </c>
       <c r="R82" t="n">
-        <v>6792391</v>
+        <v>6792475</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8728,10 +8733,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125890407</v>
+        <v>125895109</v>
       </c>
       <c r="B83" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8739,21 +8744,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8763,10 +8768,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>500242</v>
+        <v>499985</v>
       </c>
       <c r="R83" t="n">
-        <v>6792408</v>
+        <v>6792633</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8799,11 +8804,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8830,10 +8830,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125892653</v>
+        <v>125888740</v>
       </c>
       <c r="B84" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8841,34 +8841,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500151</v>
+        <v>500306</v>
       </c>
       <c r="R84" t="n">
-        <v>6792458</v>
+        <v>6792466</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8927,32 +8932,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125889406</v>
+        <v>125892266</v>
       </c>
       <c r="B85" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8962,10 +8967,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500257</v>
+        <v>500158</v>
       </c>
       <c r="R85" t="n">
-        <v>6792475</v>
+        <v>6792441</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9024,32 +9029,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125895109</v>
+        <v>125888709</v>
       </c>
       <c r="B86" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9059,10 +9064,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>499985</v>
+        <v>500311</v>
       </c>
       <c r="R86" t="n">
-        <v>6792633</v>
+        <v>6792502</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9121,32 +9126,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125892266</v>
+        <v>125892215</v>
       </c>
       <c r="B87" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9218,32 +9223,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125888709</v>
+        <v>125889155</v>
       </c>
       <c r="B88" t="n">
-        <v>8447</v>
+        <v>79562</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9253,10 +9258,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500311</v>
+        <v>500275</v>
       </c>
       <c r="R88" t="n">
-        <v>6792502</v>
+        <v>6792487</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9315,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125888740</v>
+        <v>125891598</v>
       </c>
       <c r="B89" t="n">
-        <v>57812</v>
+        <v>79562</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9326,39 +9331,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500306</v>
+        <v>500153</v>
       </c>
       <c r="R89" t="n">
-        <v>6792466</v>
+        <v>6792391</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125896524</v>
+        <v>125896426</v>
       </c>
       <c r="B107" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11082,34 +11082,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500384</v>
+        <v>500351</v>
       </c>
       <c r="R107" t="n">
-        <v>6792529</v>
+        <v>6792369</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11168,10 +11173,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125889090</v>
+        <v>125889496</v>
       </c>
       <c r="B108" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11179,34 +11184,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500285</v>
+        <v>500257</v>
       </c>
       <c r="R108" t="n">
-        <v>6792489</v>
+        <v>6792475</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11265,10 +11275,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125896426</v>
+        <v>125896524</v>
       </c>
       <c r="B109" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11276,39 +11286,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500351</v>
+        <v>500384</v>
       </c>
       <c r="R109" t="n">
-        <v>6792369</v>
+        <v>6792529</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11367,10 +11372,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125889496</v>
+        <v>125889090</v>
       </c>
       <c r="B110" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11378,39 +11383,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500257</v>
+        <v>500285</v>
       </c>
       <c r="R110" t="n">
-        <v>6792475</v>
+        <v>6792489</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125686800</v>
+        <v>125687486</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>79566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500007</v>
+        <v>499947</v>
       </c>
       <c r="R5" t="n">
-        <v>6792490</v>
+        <v>6792525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125686732</v>
+        <v>125686800</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499990</v>
+        <v>500007</v>
       </c>
       <c r="R6" t="n">
-        <v>6792488</v>
+        <v>6792490</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,11 +1191,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125685630</v>
+        <v>125686732</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499996</v>
+        <v>499990</v>
       </c>
       <c r="R7" t="n">
-        <v>6792394</v>
+        <v>6792488</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,6 +1288,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125685407</v>
+        <v>125685630</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500063</v>
+        <v>499996</v>
       </c>
       <c r="R8" t="n">
-        <v>6792381</v>
+        <v>6792394</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,32 +1416,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125686874</v>
+        <v>125685407</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500013</v>
+        <v>500063</v>
       </c>
       <c r="R9" t="n">
-        <v>6792493</v>
+        <v>6792381</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,11 +1487,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,7 +1513,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125693671</v>
+        <v>125686874</v>
       </c>
       <c r="B10" t="n">
         <v>8447</v>
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500087</v>
+        <v>500013</v>
       </c>
       <c r="R10" t="n">
-        <v>6792574</v>
+        <v>6792493</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,6 +1584,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,7 +1615,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125687215</v>
+        <v>125693671</v>
       </c>
       <c r="B11" t="n">
         <v>8447</v>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499945</v>
+        <v>500087</v>
       </c>
       <c r="R11" t="n">
-        <v>6792497</v>
+        <v>6792574</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125689836</v>
+        <v>125687215</v>
       </c>
       <c r="B12" t="n">
         <v>8447</v>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499951</v>
+        <v>499945</v>
       </c>
       <c r="R12" t="n">
-        <v>6792574</v>
+        <v>6792497</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1809,32 +1809,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125687486</v>
+        <v>125689836</v>
       </c>
       <c r="B13" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499947</v>
+        <v>499951</v>
       </c>
       <c r="R13" t="n">
-        <v>6792525</v>
+        <v>6792574</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125684006</v>
+        <v>125684974</v>
       </c>
       <c r="B14" t="n">
-        <v>57649</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1917,39 +1917,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500326</v>
+        <v>500076</v>
       </c>
       <c r="R14" t="n">
-        <v>6792440</v>
+        <v>6792407</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,11 +1977,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,10 +2003,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125684974</v>
+        <v>125693564</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,21 +2014,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2048,10 +2038,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500076</v>
+        <v>500087</v>
       </c>
       <c r="R15" t="n">
-        <v>6792407</v>
+        <v>6792574</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2110,32 +2100,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125693564</v>
+        <v>125684253</v>
       </c>
       <c r="B16" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2145,10 +2135,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500087</v>
+        <v>500039</v>
       </c>
       <c r="R16" t="n">
-        <v>6792574</v>
+        <v>6792388</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,32 +2197,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125684253</v>
+        <v>125692802</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2242,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500039</v>
+        <v>499954</v>
       </c>
       <c r="R17" t="n">
-        <v>6792388</v>
+        <v>6792650</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125685313</v>
+        <v>125684006</v>
       </c>
       <c r="B18" t="n">
-        <v>78732</v>
+        <v>57653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2315,34 +2305,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500063</v>
+        <v>500326</v>
       </c>
       <c r="R18" t="n">
-        <v>6792381</v>
+        <v>6792440</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,7 +2374,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Muljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,10 +2401,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125692802</v>
+        <v>125685313</v>
       </c>
       <c r="B19" t="n">
-        <v>79562</v>
+        <v>78736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,21 +2412,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2441,10 +2436,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499954</v>
+        <v>500063</v>
       </c>
       <c r="R19" t="n">
-        <v>6792650</v>
+        <v>6792381</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2477,6 +2472,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Muljöbilder</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2503,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125690007</v>
+        <v>125684537</v>
       </c>
       <c r="B20" t="n">
-        <v>79562</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499989</v>
+        <v>500039</v>
       </c>
       <c r="R20" t="n">
-        <v>6792563</v>
+        <v>6792388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125684537</v>
+        <v>125690007</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>79566</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500039</v>
+        <v>499989</v>
       </c>
       <c r="R21" t="n">
-        <v>6792388</v>
+        <v>6792563</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,7 +2710,7 @@
         <v>125686792</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>125686316</v>
       </c>
       <c r="B23" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>125690119</v>
       </c>
       <c r="B24" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125693794</v>
+        <v>125685512</v>
       </c>
       <c r="B25" t="n">
-        <v>56844</v>
+        <v>8447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3014,39 +3014,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500087</v>
+        <v>499996</v>
       </c>
       <c r="R25" t="n">
-        <v>6792574</v>
+        <v>6792394</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3079,6 +3074,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125685512</v>
+        <v>125693794</v>
       </c>
       <c r="B26" t="n">
-        <v>8447</v>
+        <v>56848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3116,34 +3116,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499996</v>
+        <v>500087</v>
       </c>
       <c r="R26" t="n">
-        <v>6792394</v>
+        <v>6792574</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,11 +3181,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3210,7 +3210,7 @@
         <v>125689285</v>
       </c>
       <c r="B27" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3309,32 +3309,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125693241</v>
+        <v>125683895</v>
       </c>
       <c r="B28" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500047</v>
+        <v>500326</v>
       </c>
       <c r="R28" t="n">
-        <v>6792612</v>
+        <v>6792440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3380,6 +3380,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3409,7 +3414,7 @@
         <v>125686305</v>
       </c>
       <c r="B29" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3516,7 @@
         <v>125693249</v>
       </c>
       <c r="B30" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3608,7 +3613,7 @@
         <v>125686343</v>
       </c>
       <c r="B31" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,7 +3710,7 @@
         <v>125685148</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3799,32 +3804,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125683895</v>
+        <v>125693241</v>
       </c>
       <c r="B33" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3834,10 +3839,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500326</v>
+        <v>500047</v>
       </c>
       <c r="R33" t="n">
-        <v>6792440</v>
+        <v>6792612</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3870,11 +3875,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3904,7 +3904,7 @@
         <v>125684693</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>125685808</v>
       </c>
       <c r="B36" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>125691930</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>125684984</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>125686924</v>
       </c>
       <c r="B39" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>125687294</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>125690589</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>125693372</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>125688845</v>
       </c>
       <c r="B43" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>125690295</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>125686463</v>
       </c>
       <c r="B46" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>125690957</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>125689757</v>
       </c>
       <c r="B49" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>125684146</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>125684626</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>125690154</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5978,32 +5978,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685885</v>
+        <v>125683878</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>500002</v>
+        <v>499954</v>
       </c>
       <c r="R55" t="n">
-        <v>6792449</v>
+        <v>6792394</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,6 +6049,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6075,10 +6080,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125690170</v>
+        <v>125685813</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>79566</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6086,21 +6091,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6110,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>500018</v>
+        <v>499996</v>
       </c>
       <c r="R56" t="n">
-        <v>6792528</v>
+        <v>6792435</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6172,32 +6177,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125683878</v>
+        <v>125685885</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6207,10 +6212,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499954</v>
+        <v>500002</v>
       </c>
       <c r="R57" t="n">
-        <v>6792394</v>
+        <v>6792449</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6243,11 +6248,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125685813</v>
+        <v>125690170</v>
       </c>
       <c r="B58" t="n">
-        <v>79562</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499996</v>
+        <v>500018</v>
       </c>
       <c r="R58" t="n">
-        <v>6792435</v>
+        <v>6792528</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125687400</v>
+        <v>125686648</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6382,21 +6382,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499947</v>
+        <v>499990</v>
       </c>
       <c r="R59" t="n">
-        <v>6792525</v>
+        <v>6792488</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6442,6 +6442,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6468,10 +6473,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125686648</v>
+        <v>125687400</v>
       </c>
       <c r="B60" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6479,21 +6484,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6503,10 +6508,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>499990</v>
+        <v>499947</v>
       </c>
       <c r="R60" t="n">
-        <v>6792488</v>
+        <v>6792525</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6539,11 +6544,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6573,7 +6573,7 @@
         <v>125691010</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>125685121</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>125693022</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>125693403</v>
       </c>
       <c r="B64" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6958,10 +6958,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125685660</v>
+        <v>125685734</v>
       </c>
       <c r="B65" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>499989</v>
+        <v>499996</v>
       </c>
       <c r="R65" t="n">
-        <v>6792445</v>
+        <v>6792435</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7029,6 +7029,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7055,10 +7060,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125685734</v>
+        <v>125685660</v>
       </c>
       <c r="B66" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7090,10 +7095,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>499996</v>
+        <v>499989</v>
       </c>
       <c r="R66" t="n">
-        <v>6792435</v>
+        <v>6792445</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7126,11 +7131,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7160,7 +7160,7 @@
         <v>125685335</v>
       </c>
       <c r="B67" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7263,10 +7263,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125894731</v>
+        <v>125889107</v>
       </c>
       <c r="B68" t="n">
-        <v>57652</v>
+        <v>79566</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,39 +7274,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500128</v>
+        <v>500285</v>
       </c>
       <c r="R68" t="n">
-        <v>6792590</v>
+        <v>6792489</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7365,32 +7360,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125889107</v>
+        <v>125892998</v>
       </c>
       <c r="B69" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7400,10 +7395,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500285</v>
+        <v>500188</v>
       </c>
       <c r="R69" t="n">
-        <v>6792489</v>
+        <v>6792496</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7462,32 +7457,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125888195</v>
+        <v>125893046</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7497,10 +7492,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500310</v>
+        <v>500207</v>
       </c>
       <c r="R70" t="n">
-        <v>6792516</v>
+        <v>6792488</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7533,11 +7528,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7564,45 +7554,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125892998</v>
+        <v>125894731</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>57656</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500188</v>
+        <v>500128</v>
       </c>
       <c r="R71" t="n">
-        <v>6792496</v>
+        <v>6792590</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7661,32 +7656,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125893046</v>
+        <v>125888195</v>
       </c>
       <c r="B72" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7691,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500207</v>
+        <v>500310</v>
       </c>
       <c r="R72" t="n">
-        <v>6792488</v>
+        <v>6792516</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7732,6 +7727,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7758,10 +7758,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125890092</v>
+        <v>125890555</v>
       </c>
       <c r="B73" t="n">
-        <v>79562</v>
+        <v>79595</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7769,21 +7769,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>500242</v>
+        <v>500282</v>
       </c>
       <c r="R73" t="n">
-        <v>6792408</v>
+        <v>6792389</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7855,32 +7855,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125891809</v>
+        <v>125893261</v>
       </c>
       <c r="B74" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500166</v>
+        <v>500271</v>
       </c>
       <c r="R74" t="n">
-        <v>6792387</v>
+        <v>6792529</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7952,32 +7952,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125890555</v>
+        <v>125896279</v>
       </c>
       <c r="B75" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>500282</v>
+        <v>500351</v>
       </c>
       <c r="R75" t="n">
-        <v>6792389</v>
+        <v>6792369</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125893261</v>
+        <v>125895125</v>
       </c>
       <c r="B76" t="n">
         <v>8447</v>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>500271</v>
+        <v>499985</v>
       </c>
       <c r="R76" t="n">
-        <v>6792529</v>
+        <v>6792633</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125896279</v>
+        <v>125890234</v>
       </c>
       <c r="B77" t="n">
         <v>8447</v>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>500351</v>
+        <v>500242</v>
       </c>
       <c r="R77" t="n">
-        <v>6792369</v>
+        <v>6792408</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8243,32 +8243,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125895125</v>
+        <v>125890092</v>
       </c>
       <c r="B78" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>499985</v>
+        <v>500242</v>
       </c>
       <c r="R78" t="n">
-        <v>6792633</v>
+        <v>6792408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8340,32 +8340,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125890234</v>
+        <v>125891809</v>
       </c>
       <c r="B79" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500242</v>
+        <v>500166</v>
       </c>
       <c r="R79" t="n">
-        <v>6792408</v>
+        <v>6792387</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8437,10 +8437,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125890407</v>
+        <v>125888740</v>
       </c>
       <c r="B80" t="n">
-        <v>78973</v>
+        <v>57816</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8448,34 +8448,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500242</v>
+        <v>500306</v>
       </c>
       <c r="R80" t="n">
-        <v>6792408</v>
+        <v>6792466</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8508,11 +8513,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8539,32 +8539,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125892653</v>
+        <v>125892266</v>
       </c>
       <c r="B81" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8574,10 +8574,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500151</v>
+        <v>500158</v>
       </c>
       <c r="R81" t="n">
-        <v>6792458</v>
+        <v>6792441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8636,10 +8636,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125889406</v>
+        <v>125892215</v>
       </c>
       <c r="B82" t="n">
-        <v>79591</v>
+        <v>79566</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8647,21 +8647,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500257</v>
+        <v>500158</v>
       </c>
       <c r="R82" t="n">
-        <v>6792475</v>
+        <v>6792441</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8733,10 +8733,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125895109</v>
+        <v>125889155</v>
       </c>
       <c r="B83" t="n">
-        <v>79591</v>
+        <v>79566</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8744,21 +8744,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>499985</v>
+        <v>500275</v>
       </c>
       <c r="R83" t="n">
-        <v>6792633</v>
+        <v>6792487</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8830,10 +8830,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125888740</v>
+        <v>125891598</v>
       </c>
       <c r="B84" t="n">
-        <v>57812</v>
+        <v>79566</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8841,39 +8841,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500306</v>
+        <v>500153</v>
       </c>
       <c r="R84" t="n">
-        <v>6792466</v>
+        <v>6792391</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8932,7 +8927,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125892266</v>
+        <v>125888709</v>
       </c>
       <c r="B85" t="n">
         <v>8447</v>
@@ -8967,10 +8962,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500158</v>
+        <v>500311</v>
       </c>
       <c r="R85" t="n">
-        <v>6792441</v>
+        <v>6792502</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9029,32 +9024,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125888709</v>
+        <v>125890407</v>
       </c>
       <c r="B86" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9064,10 +9059,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500311</v>
+        <v>500242</v>
       </c>
       <c r="R86" t="n">
-        <v>6792502</v>
+        <v>6792408</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9100,6 +9095,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9126,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125892215</v>
+        <v>125892653</v>
       </c>
       <c r="B87" t="n">
-        <v>79562</v>
+        <v>78977</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9137,21 +9137,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500158</v>
+        <v>500151</v>
       </c>
       <c r="R87" t="n">
-        <v>6792441</v>
+        <v>6792458</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125889155</v>
+        <v>125889406</v>
       </c>
       <c r="B88" t="n">
-        <v>79562</v>
+        <v>79595</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9234,21 +9234,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9258,10 +9258,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500275</v>
+        <v>500257</v>
       </c>
       <c r="R88" t="n">
-        <v>6792487</v>
+        <v>6792475</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9320,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125891598</v>
+        <v>125895109</v>
       </c>
       <c r="B89" t="n">
-        <v>79562</v>
+        <v>79595</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,21 +9331,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500153</v>
+        <v>499985</v>
       </c>
       <c r="R89" t="n">
-        <v>6792391</v>
+        <v>6792633</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125896683</v>
+        <v>125894466</v>
       </c>
       <c r="B90" t="n">
         <v>8447</v>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>500384</v>
+        <v>500128</v>
       </c>
       <c r="R90" t="n">
-        <v>6792529</v>
+        <v>6792590</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9514,7 +9514,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125894466</v>
+        <v>125896683</v>
       </c>
       <c r="B91" t="n">
         <v>8447</v>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R91" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9611,10 +9611,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125896400</v>
+        <v>125889889</v>
       </c>
       <c r="B92" t="n">
-        <v>79562</v>
+        <v>79595</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9622,21 +9622,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>500351</v>
+        <v>500237</v>
       </c>
       <c r="R92" t="n">
-        <v>6792369</v>
+        <v>6792422</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,32 +9708,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125889879</v>
+        <v>125888352</v>
       </c>
       <c r="B93" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>500237</v>
+        <v>500310</v>
       </c>
       <c r="R93" t="n">
-        <v>6792422</v>
+        <v>6792516</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125895107</v>
+        <v>125896400</v>
       </c>
       <c r="B94" t="n">
-        <v>78732</v>
+        <v>79566</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>499985</v>
+        <v>500351</v>
       </c>
       <c r="R94" t="n">
-        <v>6792633</v>
+        <v>6792369</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125889889</v>
+        <v>125889879</v>
       </c>
       <c r="B95" t="n">
-        <v>79591</v>
+        <v>78736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9999,32 +9999,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125888352</v>
+        <v>125895107</v>
       </c>
       <c r="B96" t="n">
-        <v>8447</v>
+        <v>78736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>500310</v>
+        <v>499985</v>
       </c>
       <c r="R96" t="n">
-        <v>6792516</v>
+        <v>6792633</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10096,32 +10096,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125889556</v>
+        <v>125890971</v>
       </c>
       <c r="B97" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>500218</v>
+        <v>500282</v>
       </c>
       <c r="R97" t="n">
-        <v>6792438</v>
+        <v>6792389</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10193,32 +10193,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125890971</v>
+        <v>125889556</v>
       </c>
       <c r="B98" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>500282</v>
+        <v>500218</v>
       </c>
       <c r="R98" t="n">
-        <v>6792389</v>
+        <v>6792438</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10290,7 +10290,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125889725</v>
+        <v>125894957</v>
       </c>
       <c r="B99" t="n">
         <v>8447</v>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>500234</v>
+        <v>500037</v>
       </c>
       <c r="R99" t="n">
-        <v>6792439</v>
+        <v>6792660</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10387,32 +10387,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125894957</v>
+        <v>125893327</v>
       </c>
       <c r="B100" t="n">
-        <v>8447</v>
+        <v>78736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>500037</v>
+        <v>500271</v>
       </c>
       <c r="R100" t="n">
-        <v>6792660</v>
+        <v>6792529</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10484,10 +10484,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125893327</v>
+        <v>125892219</v>
       </c>
       <c r="B101" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>500271</v>
+        <v>500158</v>
       </c>
       <c r="R101" t="n">
-        <v>6792529</v>
+        <v>6792441</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10581,32 +10581,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125892219</v>
+        <v>125889725</v>
       </c>
       <c r="B102" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>500158</v>
+        <v>500234</v>
       </c>
       <c r="R102" t="n">
-        <v>6792441</v>
+        <v>6792439</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125889615</v>
+        <v>125892224</v>
       </c>
       <c r="B103" t="n">
-        <v>8447</v>
+        <v>78735</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500202</v>
+        <v>500158</v>
       </c>
       <c r="R103" t="n">
-        <v>6792435</v>
+        <v>6792441</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10775,32 +10775,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125892224</v>
+        <v>125889615</v>
       </c>
       <c r="B104" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500158</v>
+        <v>500202</v>
       </c>
       <c r="R104" t="n">
-        <v>6792441</v>
+        <v>6792435</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10875,7 +10875,7 @@
         <v>125896058</v>
       </c>
       <c r="B105" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>125891964</v>
       </c>
       <c r="B106" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125896426</v>
+        <v>125896524</v>
       </c>
       <c r="B107" t="n">
-        <v>57649</v>
+        <v>79595</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11082,39 +11082,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500351</v>
+        <v>500384</v>
       </c>
       <c r="R107" t="n">
-        <v>6792369</v>
+        <v>6792529</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11173,10 +11168,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125889496</v>
+        <v>125889090</v>
       </c>
       <c r="B108" t="n">
-        <v>57649</v>
+        <v>79595</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11184,39 +11179,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500257</v>
+        <v>500285</v>
       </c>
       <c r="R108" t="n">
-        <v>6792475</v>
+        <v>6792489</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11275,34 +11265,30 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125896524</v>
+        <v>125894266</v>
       </c>
       <c r="B109" t="n">
-        <v>79591</v>
+        <v>98269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>223597</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11310,10 +11296,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500384</v>
+        <v>500128</v>
       </c>
       <c r="R109" t="n">
-        <v>6792529</v>
+        <v>6792590</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11372,32 +11358,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125889090</v>
+        <v>125893643</v>
       </c>
       <c r="B110" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11407,10 +11393,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500285</v>
+        <v>500237</v>
       </c>
       <c r="R110" t="n">
-        <v>6792489</v>
+        <v>6792567</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11469,32 +11455,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125893643</v>
+        <v>125892433</v>
       </c>
       <c r="B111" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11504,10 +11490,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500237</v>
+        <v>500160</v>
       </c>
       <c r="R111" t="n">
-        <v>6792567</v>
+        <v>6792451</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11566,41 +11552,50 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125894266</v>
+        <v>125896426</v>
       </c>
       <c r="B112" t="n">
-        <v>98265</v>
+        <v>57653</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>223597</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500128</v>
+        <v>500351</v>
       </c>
       <c r="R112" t="n">
-        <v>6792590</v>
+        <v>6792369</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11659,10 +11654,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125892433</v>
+        <v>125889496</v>
       </c>
       <c r="B113" t="n">
-        <v>79562</v>
+        <v>57653</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11670,34 +11665,39 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500160</v>
+        <v>500257</v>
       </c>
       <c r="R113" t="n">
-        <v>6792451</v>
+        <v>6792475</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11759,7 +11759,7 @@
         <v>125890126</v>
       </c>
       <c r="B114" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>125893637</v>
       </c>
       <c r="B115" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>125892154</v>
       </c>
       <c r="B116" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>125894500</v>
       </c>
       <c r="B117" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B120" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R120" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,6 +12414,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12440,32 +12445,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125889503</v>
+        <v>125892496</v>
       </c>
       <c r="B121" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12475,10 +12480,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R121" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12511,6 +12516,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12537,32 +12547,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125888695</v>
+        <v>125893148</v>
       </c>
       <c r="B122" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12572,10 +12582,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500311</v>
+        <v>500251</v>
       </c>
       <c r="R122" t="n">
-        <v>6792502</v>
+        <v>6792496</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12608,11 +12618,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12639,32 +12644,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125892496</v>
+        <v>125889503</v>
       </c>
       <c r="B123" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12674,10 +12679,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R123" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12710,11 +12715,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12741,45 +12741,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125891471</v>
+        <v>125896030</v>
       </c>
       <c r="B124" t="n">
-        <v>8447</v>
+        <v>57656</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500181</v>
+        <v>500351</v>
       </c>
       <c r="R124" t="n">
-        <v>6792401</v>
+        <v>6792369</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12841,7 +12846,7 @@
         <v>125896611</v>
       </c>
       <c r="B125" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12943,7 +12948,7 @@
         <v>125892207</v>
       </c>
       <c r="B126" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13037,50 +13042,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125896030</v>
+        <v>125891471</v>
       </c>
       <c r="B127" t="n">
-        <v>57652</v>
+        <v>8447</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500351</v>
+        <v>500181</v>
       </c>
       <c r="R127" t="n">
-        <v>6792369</v>
+        <v>6792401</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13142,7 +13142,7 @@
         <v>125894132</v>
       </c>
       <c r="B128" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>125894564</v>
       </c>
       <c r="B129" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>125892025</v>
       </c>
       <c r="B130" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>125891498</v>
       </c>
       <c r="B131" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>125893307</v>
       </c>
       <c r="B132" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>125891649</v>
       </c>
       <c r="B133" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13731,32 +13731,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125890887</v>
+        <v>125892751</v>
       </c>
       <c r="B134" t="n">
-        <v>8447</v>
+        <v>78736</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500282</v>
+        <v>500151</v>
       </c>
       <c r="R134" t="n">
-        <v>6792389</v>
+        <v>6792458</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13828,7 +13828,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125893186</v>
+        <v>125890887</v>
       </c>
       <c r="B135" t="n">
         <v>8447</v>
@@ -13863,10 +13863,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500247</v>
+        <v>500282</v>
       </c>
       <c r="R135" t="n">
-        <v>6792519</v>
+        <v>6792389</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13925,32 +13925,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125892751</v>
+        <v>125893186</v>
       </c>
       <c r="B136" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13960,10 +13960,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500151</v>
+        <v>500247</v>
       </c>
       <c r="R136" t="n">
-        <v>6792458</v>
+        <v>6792519</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14122,7 +14122,7 @@
         <v>125892352</v>
       </c>
       <c r="B138" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>125889010</v>
       </c>
       <c r="B139" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125896454</v>
+        <v>125896535</v>
       </c>
       <c r="B140" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500374</v>
+        <v>500384</v>
       </c>
       <c r="R140" t="n">
-        <v>6792515</v>
+        <v>6792529</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14384,11 +14384,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14415,10 +14410,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125889266</v>
+        <v>125896642</v>
       </c>
       <c r="B141" t="n">
-        <v>78973</v>
+        <v>79566</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14426,21 +14421,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14450,10 +14445,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500257</v>
+        <v>500384</v>
       </c>
       <c r="R141" t="n">
-        <v>6792475</v>
+        <v>6792529</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14486,11 +14481,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14517,10 +14507,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125896535</v>
+        <v>125892643</v>
       </c>
       <c r="B142" t="n">
-        <v>78732</v>
+        <v>79566</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14528,21 +14518,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14552,10 +14542,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>500384</v>
+        <v>500151</v>
       </c>
       <c r="R142" t="n">
-        <v>6792529</v>
+        <v>6792458</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14614,10 +14604,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125896642</v>
+        <v>125889379</v>
       </c>
       <c r="B143" t="n">
-        <v>79562</v>
+        <v>78736</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14625,21 +14615,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14649,10 +14639,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500384</v>
+        <v>500257</v>
       </c>
       <c r="R143" t="n">
-        <v>6792529</v>
+        <v>6792475</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14711,10 +14701,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125892643</v>
+        <v>125892160</v>
       </c>
       <c r="B144" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14746,10 +14736,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500151</v>
+        <v>500145</v>
       </c>
       <c r="R144" t="n">
-        <v>6792458</v>
+        <v>6792446</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14808,10 +14798,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125889379</v>
+        <v>125896454</v>
       </c>
       <c r="B145" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14819,21 +14809,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14843,10 +14833,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500257</v>
+        <v>500374</v>
       </c>
       <c r="R145" t="n">
-        <v>6792475</v>
+        <v>6792515</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14879,6 +14869,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14905,10 +14900,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125892160</v>
+        <v>125889266</v>
       </c>
       <c r="B146" t="n">
-        <v>79562</v>
+        <v>78977</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14916,21 +14911,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14940,10 +14935,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R146" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14976,6 +14971,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15002,45 +15002,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125896772</v>
+        <v>125888369</v>
       </c>
       <c r="B147" t="n">
-        <v>92528</v>
+        <v>57653</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500384</v>
+        <v>500310</v>
       </c>
       <c r="R147" t="n">
-        <v>6792529</v>
+        <v>6792516</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15099,50 +15104,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125888369</v>
+        <v>125896772</v>
       </c>
       <c r="B148" t="n">
-        <v>57649</v>
+        <v>92532</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500310</v>
+        <v>500384</v>
       </c>
       <c r="R148" t="n">
-        <v>6792516</v>
+        <v>6792529</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15204,7 +15204,7 @@
         <v>125891864</v>
       </c>
       <c r="B149" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15303,32 +15303,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125888908</v>
+        <v>125892001</v>
       </c>
       <c r="B150" t="n">
-        <v>79562</v>
+        <v>8447</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15338,10 +15338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500306</v>
+        <v>500111</v>
       </c>
       <c r="R150" t="n">
-        <v>6792466</v>
+        <v>6792428</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15400,32 +15400,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125892001</v>
+        <v>125888908</v>
       </c>
       <c r="B151" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15435,10 +15435,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500111</v>
+        <v>500306</v>
       </c>
       <c r="R151" t="n">
-        <v>6792428</v>
+        <v>6792466</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15597,7 +15597,7 @@
         <v>125889396</v>
       </c>
       <c r="B153" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>125891609</v>
       </c>
       <c r="B154" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15788,32 +15788,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125895017</v>
+        <v>125895229</v>
       </c>
       <c r="B155" t="n">
-        <v>78997</v>
+        <v>79566</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15885,10 +15885,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125895229</v>
+        <v>125888924</v>
       </c>
       <c r="B156" t="n">
-        <v>79562</v>
+        <v>78736</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15896,21 +15896,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15920,10 +15920,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>499985</v>
+        <v>500306</v>
       </c>
       <c r="R156" t="n">
-        <v>6792633</v>
+        <v>6792466</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -15982,32 +15982,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125888924</v>
+        <v>125895017</v>
       </c>
       <c r="B157" t="n">
-        <v>78732</v>
+        <v>79001</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16017,10 +16017,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>500306</v>
+        <v>499985</v>
       </c>
       <c r="R157" t="n">
-        <v>6792466</v>
+        <v>6792633</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16079,10 +16079,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125889676</v>
+        <v>125892942</v>
       </c>
       <c r="B158" t="n">
-        <v>78973</v>
+        <v>91262</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16090,21 +16090,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16114,10 +16114,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500202</v>
+        <v>500171</v>
       </c>
       <c r="R158" t="n">
-        <v>6792435</v>
+        <v>6792489</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16150,11 +16150,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16181,10 +16176,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125892942</v>
+        <v>125889676</v>
       </c>
       <c r="B159" t="n">
-        <v>91258</v>
+        <v>78977</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16192,21 +16187,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16216,10 +16211,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500171</v>
+        <v>500202</v>
       </c>
       <c r="R159" t="n">
-        <v>6792489</v>
+        <v>6792435</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16252,6 +16247,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16281,7 +16281,7 @@
         <v>125892637</v>
       </c>
       <c r="B160" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125687486</v>
+        <v>125686800</v>
       </c>
       <c r="B5" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499947</v>
+        <v>500007</v>
       </c>
       <c r="R5" t="n">
-        <v>6792525</v>
+        <v>6792490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125686800</v>
+        <v>125686732</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500007</v>
+        <v>499990</v>
       </c>
       <c r="R6" t="n">
-        <v>6792490</v>
+        <v>6792488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,6 +1191,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125686732</v>
+        <v>125685630</v>
       </c>
       <c r="B7" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,21 +1233,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499990</v>
+        <v>499996</v>
       </c>
       <c r="R7" t="n">
-        <v>6792488</v>
+        <v>6792394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,11 +1293,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,7 +1319,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125685630</v>
+        <v>125685407</v>
       </c>
       <c r="B8" t="n">
         <v>78977</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499996</v>
+        <v>500063</v>
       </c>
       <c r="R8" t="n">
-        <v>6792394</v>
+        <v>6792381</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125685407</v>
+        <v>125687486</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,21 +1427,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500063</v>
+        <v>499947</v>
       </c>
       <c r="R9" t="n">
-        <v>6792381</v>
+        <v>6792525</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125685512</v>
+        <v>125693794</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>56848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3014,34 +3014,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499996</v>
+        <v>500087</v>
       </c>
       <c r="R25" t="n">
-        <v>6792394</v>
+        <v>6792574</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3074,11 +3079,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3105,50 +3105,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125693794</v>
+        <v>125689285</v>
       </c>
       <c r="B26" t="n">
-        <v>56848</v>
+        <v>79566</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500087</v>
+        <v>499942</v>
       </c>
       <c r="R26" t="n">
-        <v>6792574</v>
+        <v>6792546</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3181,6 +3176,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3207,32 +3207,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125689285</v>
+        <v>125685512</v>
       </c>
       <c r="B27" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499942</v>
+        <v>499996</v>
       </c>
       <c r="R27" t="n">
-        <v>6792546</v>
+        <v>6792394</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125686463</v>
+        <v>125685110</v>
       </c>
       <c r="B46" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499969</v>
+        <v>500063</v>
       </c>
       <c r="R46" t="n">
-        <v>6792489</v>
+        <v>6792423</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5156,6 +5156,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5182,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125690957</v>
+        <v>125689757</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5193,21 +5198,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5217,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>500003</v>
+        <v>499951</v>
       </c>
       <c r="R47" t="n">
-        <v>6792577</v>
+        <v>6792574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5253,6 +5258,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5279,32 +5289,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125685110</v>
+        <v>125686463</v>
       </c>
       <c r="B48" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5314,10 +5324,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>500063</v>
+        <v>499969</v>
       </c>
       <c r="R48" t="n">
-        <v>6792423</v>
+        <v>6792489</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5350,11 +5360,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5381,10 +5386,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125689757</v>
+        <v>125690957</v>
       </c>
       <c r="B49" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,21 +5397,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5421,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499951</v>
+        <v>500003</v>
       </c>
       <c r="R49" t="n">
-        <v>6792574</v>
+        <v>6792577</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5452,11 +5457,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125889107</v>
+        <v>125888195</v>
       </c>
       <c r="B68" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,21 +7274,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500285</v>
+        <v>500310</v>
       </c>
       <c r="R68" t="n">
-        <v>6792489</v>
+        <v>6792516</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,6 +7334,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7360,45 +7365,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125892998</v>
+        <v>125894731</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>57656</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500188</v>
+        <v>500128</v>
       </c>
       <c r="R69" t="n">
-        <v>6792496</v>
+        <v>6792590</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7457,7 +7467,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125893046</v>
+        <v>125892998</v>
       </c>
       <c r="B70" t="n">
         <v>8447</v>
@@ -7492,10 +7502,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500207</v>
+        <v>500188</v>
       </c>
       <c r="R70" t="n">
-        <v>6792488</v>
+        <v>6792496</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7554,50 +7564,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125894731</v>
+        <v>125893046</v>
       </c>
       <c r="B71" t="n">
-        <v>57656</v>
+        <v>8447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500128</v>
+        <v>500207</v>
       </c>
       <c r="R71" t="n">
-        <v>6792590</v>
+        <v>6792488</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7656,10 +7661,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125888195</v>
+        <v>125889107</v>
       </c>
       <c r="B72" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7667,21 +7672,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7691,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500310</v>
+        <v>500285</v>
       </c>
       <c r="R72" t="n">
-        <v>6792516</v>
+        <v>6792489</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7727,11 +7732,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9611,32 +9611,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125889889</v>
+        <v>125888352</v>
       </c>
       <c r="B92" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>500237</v>
+        <v>500310</v>
       </c>
       <c r="R92" t="n">
-        <v>6792422</v>
+        <v>6792516</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,32 +9708,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125888352</v>
+        <v>125896400</v>
       </c>
       <c r="B93" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>500310</v>
+        <v>500351</v>
       </c>
       <c r="R93" t="n">
-        <v>6792516</v>
+        <v>6792369</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125896400</v>
+        <v>125889879</v>
       </c>
       <c r="B94" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>500351</v>
+        <v>500237</v>
       </c>
       <c r="R94" t="n">
-        <v>6792369</v>
+        <v>6792422</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,7 +9902,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125889879</v>
+        <v>125895107</v>
       </c>
       <c r="B95" t="n">
         <v>78736</v>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>500237</v>
+        <v>499985</v>
       </c>
       <c r="R95" t="n">
-        <v>6792422</v>
+        <v>6792633</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,10 +9999,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125895107</v>
+        <v>125889889</v>
       </c>
       <c r="B96" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>499985</v>
+        <v>500237</v>
       </c>
       <c r="R96" t="n">
-        <v>6792633</v>
+        <v>6792422</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10096,32 +10096,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125890971</v>
+        <v>125889556</v>
       </c>
       <c r="B97" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>500282</v>
+        <v>500218</v>
       </c>
       <c r="R97" t="n">
-        <v>6792389</v>
+        <v>6792438</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10193,32 +10193,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125889556</v>
+        <v>125890971</v>
       </c>
       <c r="B98" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>500218</v>
+        <v>500282</v>
       </c>
       <c r="R98" t="n">
-        <v>6792438</v>
+        <v>6792389</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10775,32 +10775,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125889615</v>
+        <v>125896058</v>
       </c>
       <c r="B104" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500202</v>
+        <v>500351</v>
       </c>
       <c r="R104" t="n">
-        <v>6792435</v>
+        <v>6792369</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,6 +10846,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10872,10 +10877,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125896058</v>
+        <v>125891964</v>
       </c>
       <c r="B105" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10883,21 +10888,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10907,10 +10912,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500351</v>
+        <v>500111</v>
       </c>
       <c r="R105" t="n">
-        <v>6792369</v>
+        <v>6792428</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10943,11 +10948,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125891964</v>
+        <v>125889615</v>
       </c>
       <c r="B106" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500111</v>
+        <v>500202</v>
       </c>
       <c r="R106" t="n">
-        <v>6792428</v>
+        <v>6792435</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11071,32 +11071,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125896524</v>
+        <v>125893643</v>
       </c>
       <c r="B107" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500384</v>
+        <v>500237</v>
       </c>
       <c r="R107" t="n">
-        <v>6792529</v>
+        <v>6792567</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125889090</v>
+        <v>125896524</v>
       </c>
       <c r="B108" t="n">
         <v>79595</v>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500285</v>
+        <v>500384</v>
       </c>
       <c r="R108" t="n">
-        <v>6792489</v>
+        <v>6792529</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11265,30 +11265,34 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125894266</v>
+        <v>125889090</v>
       </c>
       <c r="B109" t="n">
-        <v>98269</v>
+        <v>79595</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>223597</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11296,10 +11300,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500128</v>
+        <v>500285</v>
       </c>
       <c r="R109" t="n">
-        <v>6792590</v>
+        <v>6792489</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11358,45 +11362,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125893643</v>
+        <v>125896426</v>
       </c>
       <c r="B110" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500237</v>
+        <v>500351</v>
       </c>
       <c r="R110" t="n">
-        <v>6792567</v>
+        <v>6792369</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11455,10 +11464,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125892433</v>
+        <v>125889496</v>
       </c>
       <c r="B111" t="n">
-        <v>79566</v>
+        <v>57653</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11466,34 +11475,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500160</v>
+        <v>500257</v>
       </c>
       <c r="R111" t="n">
-        <v>6792451</v>
+        <v>6792475</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11552,50 +11566,41 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125896426</v>
+        <v>125894266</v>
       </c>
       <c r="B112" t="n">
-        <v>57653</v>
+        <v>98269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>223597</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500351</v>
+        <v>500128</v>
       </c>
       <c r="R112" t="n">
-        <v>6792369</v>
+        <v>6792590</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11654,10 +11659,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125889496</v>
+        <v>125892433</v>
       </c>
       <c r="B113" t="n">
-        <v>57653</v>
+        <v>79566</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11665,39 +11670,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500257</v>
+        <v>500160</v>
       </c>
       <c r="R113" t="n">
-        <v>6792475</v>
+        <v>6792451</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12149,7 +12149,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125896458</v>
+        <v>125889235</v>
       </c>
       <c r="B118" t="n">
         <v>8447</v>
@@ -12184,10 +12184,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>500374</v>
+        <v>500275</v>
       </c>
       <c r="R118" t="n">
-        <v>6792515</v>
+        <v>6792487</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125889235</v>
+        <v>125896458</v>
       </c>
       <c r="B119" t="n">
         <v>8447</v>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>500275</v>
+        <v>500374</v>
       </c>
       <c r="R119" t="n">
-        <v>6792487</v>
+        <v>6792515</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15788,32 +15788,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125895229</v>
+        <v>125895017</v>
       </c>
       <c r="B155" t="n">
-        <v>79566</v>
+        <v>79001</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15885,10 +15885,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125888924</v>
+        <v>125895229</v>
       </c>
       <c r="B156" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15896,21 +15896,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15920,10 +15920,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>500306</v>
+        <v>499985</v>
       </c>
       <c r="R156" t="n">
-        <v>6792466</v>
+        <v>6792633</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -15982,32 +15982,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125895017</v>
+        <v>125888924</v>
       </c>
       <c r="B157" t="n">
-        <v>79001</v>
+        <v>78736</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16017,10 +16017,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>499985</v>
+        <v>500306</v>
       </c>
       <c r="R157" t="n">
-        <v>6792633</v>
+        <v>6792466</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -1416,32 +1416,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125687486</v>
+        <v>125686874</v>
       </c>
       <c r="B9" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499947</v>
+        <v>500013</v>
       </c>
       <c r="R9" t="n">
-        <v>6792525</v>
+        <v>6792493</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,6 +1487,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125686874</v>
+        <v>125693671</v>
       </c>
       <c r="B10" t="n">
         <v>8447</v>
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500013</v>
+        <v>500087</v>
       </c>
       <c r="R10" t="n">
-        <v>6792493</v>
+        <v>6792574</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,11 +1589,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,7 +1615,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125693671</v>
+        <v>125687215</v>
       </c>
       <c r="B11" t="n">
         <v>8447</v>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500087</v>
+        <v>499945</v>
       </c>
       <c r="R11" t="n">
-        <v>6792574</v>
+        <v>6792497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125687215</v>
+        <v>125689836</v>
       </c>
       <c r="B12" t="n">
         <v>8447</v>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499945</v>
+        <v>499951</v>
       </c>
       <c r="R12" t="n">
-        <v>6792497</v>
+        <v>6792574</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1809,32 +1809,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125689836</v>
+        <v>125687486</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499951</v>
+        <v>499947</v>
       </c>
       <c r="R13" t="n">
-        <v>6792574</v>
+        <v>6792525</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2100,32 +2100,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125684253</v>
+        <v>125692802</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500039</v>
+        <v>499954</v>
       </c>
       <c r="R16" t="n">
-        <v>6792388</v>
+        <v>6792650</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,32 +2197,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125692802</v>
+        <v>125684253</v>
       </c>
       <c r="B17" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499954</v>
+        <v>500039</v>
       </c>
       <c r="R17" t="n">
-        <v>6792650</v>
+        <v>6792388</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125684006</v>
+        <v>125685313</v>
       </c>
       <c r="B18" t="n">
-        <v>57653</v>
+        <v>78736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,39 +2305,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500326</v>
+        <v>500063</v>
       </c>
       <c r="R18" t="n">
-        <v>6792440</v>
+        <v>6792381</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,7 +2369,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Muljöbilder</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2401,10 +2396,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125685313</v>
+        <v>125684006</v>
       </c>
       <c r="B19" t="n">
-        <v>78736</v>
+        <v>57653</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2412,34 +2407,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500063</v>
+        <v>500326</v>
       </c>
       <c r="R19" t="n">
-        <v>6792381</v>
+        <v>6792440</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Muljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2503,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125684537</v>
+        <v>125690007</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500039</v>
+        <v>499989</v>
       </c>
       <c r="R20" t="n">
-        <v>6792388</v>
+        <v>6792563</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125690007</v>
+        <v>125684537</v>
       </c>
       <c r="B21" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499989</v>
+        <v>500039</v>
       </c>
       <c r="R21" t="n">
-        <v>6792563</v>
+        <v>6792388</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3105,32 +3105,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125689285</v>
+        <v>125685512</v>
       </c>
       <c r="B26" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499942</v>
+        <v>499996</v>
       </c>
       <c r="R26" t="n">
-        <v>6792546</v>
+        <v>6792394</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3207,32 +3207,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125685512</v>
+        <v>125689285</v>
       </c>
       <c r="B27" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499996</v>
+        <v>499942</v>
       </c>
       <c r="R27" t="n">
-        <v>6792394</v>
+        <v>6792546</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,32 +3309,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125683895</v>
+        <v>125693241</v>
       </c>
       <c r="B28" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500326</v>
+        <v>500047</v>
       </c>
       <c r="R28" t="n">
-        <v>6792440</v>
+        <v>6792612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3380,11 +3380,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3411,10 +3406,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125686305</v>
+        <v>125686343</v>
       </c>
       <c r="B29" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3422,21 +3417,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3482,11 +3477,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3513,10 +3503,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125693249</v>
+        <v>125685148</v>
       </c>
       <c r="B30" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3514,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3538,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500047</v>
+        <v>500040</v>
       </c>
       <c r="R30" t="n">
-        <v>6792612</v>
+        <v>6792406</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,10 +3600,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125686343</v>
+        <v>125693249</v>
       </c>
       <c r="B31" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3621,21 +3611,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3645,10 +3635,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499963</v>
+        <v>500047</v>
       </c>
       <c r="R31" t="n">
-        <v>6792480</v>
+        <v>6792612</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,32 +3697,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125685148</v>
+        <v>125683895</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3742,10 +3732,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500040</v>
+        <v>500326</v>
       </c>
       <c r="R32" t="n">
-        <v>6792406</v>
+        <v>6792440</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3778,6 +3768,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3804,10 +3799,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125693241</v>
+        <v>125686305</v>
       </c>
       <c r="B33" t="n">
-        <v>57653</v>
+        <v>78736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3815,21 +3810,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3839,10 +3834,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500047</v>
+        <v>499963</v>
       </c>
       <c r="R33" t="n">
-        <v>6792612</v>
+        <v>6792480</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3875,6 +3870,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3901,32 +3901,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125684693</v>
+        <v>125687329</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500077</v>
+        <v>499947</v>
       </c>
       <c r="R34" t="n">
-        <v>6792400</v>
+        <v>6792525</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3998,32 +3998,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125687329</v>
+        <v>125685808</v>
       </c>
       <c r="B35" t="n">
-        <v>8447</v>
+        <v>78736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499947</v>
+        <v>499996</v>
       </c>
       <c r="R35" t="n">
-        <v>6792525</v>
+        <v>6792435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4069,6 +4069,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,10 +4100,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125685808</v>
+        <v>125684693</v>
       </c>
       <c r="B36" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4106,21 +4111,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4130,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499996</v>
+        <v>500077</v>
       </c>
       <c r="R36" t="n">
-        <v>6792435</v>
+        <v>6792400</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4166,11 +4171,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5085,32 +5085,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125685110</v>
+        <v>125686463</v>
       </c>
       <c r="B46" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500063</v>
+        <v>499969</v>
       </c>
       <c r="R46" t="n">
-        <v>6792423</v>
+        <v>6792489</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5156,11 +5156,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5187,10 +5182,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125689757</v>
+        <v>125690957</v>
       </c>
       <c r="B47" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,21 +5193,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499951</v>
+        <v>500003</v>
       </c>
       <c r="R47" t="n">
-        <v>6792574</v>
+        <v>6792577</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5258,11 +5253,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5289,32 +5279,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125686463</v>
+        <v>125685110</v>
       </c>
       <c r="B48" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5324,10 +5314,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499969</v>
+        <v>500063</v>
       </c>
       <c r="R48" t="n">
-        <v>6792489</v>
+        <v>6792423</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5360,6 +5350,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5386,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125690957</v>
+        <v>125689757</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5397,21 +5392,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5421,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500003</v>
+        <v>499951</v>
       </c>
       <c r="R49" t="n">
-        <v>6792577</v>
+        <v>6792574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5457,6 +5452,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5978,32 +5978,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125683878</v>
+        <v>125685885</v>
       </c>
       <c r="B55" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499954</v>
+        <v>500002</v>
       </c>
       <c r="R55" t="n">
-        <v>6792394</v>
+        <v>6792449</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,11 +6049,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6080,10 +6075,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125685813</v>
+        <v>125690170</v>
       </c>
       <c r="B56" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6091,21 +6086,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6115,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499996</v>
+        <v>500018</v>
       </c>
       <c r="R56" t="n">
-        <v>6792435</v>
+        <v>6792528</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6177,10 +6172,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125685885</v>
+        <v>125685813</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6188,21 +6183,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6212,10 +6207,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>500002</v>
+        <v>499996</v>
       </c>
       <c r="R57" t="n">
-        <v>6792449</v>
+        <v>6792435</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6274,32 +6269,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125690170</v>
+        <v>125683878</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6304,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>500018</v>
+        <v>499954</v>
       </c>
       <c r="R58" t="n">
-        <v>6792528</v>
+        <v>6792394</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6345,6 +6340,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6371,10 +6371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125686648</v>
+        <v>125687400</v>
       </c>
       <c r="B59" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6382,21 +6382,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499990</v>
+        <v>499947</v>
       </c>
       <c r="R59" t="n">
-        <v>6792488</v>
+        <v>6792525</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6442,11 +6442,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6473,10 +6468,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125687400</v>
+        <v>125686648</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6484,21 +6479,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6508,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>499947</v>
+        <v>499990</v>
       </c>
       <c r="R60" t="n">
-        <v>6792525</v>
+        <v>6792488</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6544,6 +6539,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125888195</v>
+        <v>125889107</v>
       </c>
       <c r="B68" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,21 +7274,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500310</v>
+        <v>500285</v>
       </c>
       <c r="R68" t="n">
-        <v>6792516</v>
+        <v>6792489</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,11 +7334,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7365,10 +7360,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125894731</v>
+        <v>125888195</v>
       </c>
       <c r="B69" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7376,39 +7371,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500128</v>
+        <v>500310</v>
       </c>
       <c r="R69" t="n">
-        <v>6792590</v>
+        <v>6792516</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7441,6 +7431,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7467,45 +7462,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125892998</v>
+        <v>125894731</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>57656</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500188</v>
+        <v>500128</v>
       </c>
       <c r="R70" t="n">
-        <v>6792496</v>
+        <v>6792590</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7564,7 +7564,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125893046</v>
+        <v>125892998</v>
       </c>
       <c r="B71" t="n">
         <v>8447</v>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500207</v>
+        <v>500188</v>
       </c>
       <c r="R71" t="n">
-        <v>6792488</v>
+        <v>6792496</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7661,32 +7661,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125889107</v>
+        <v>125893046</v>
       </c>
       <c r="B72" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500285</v>
+        <v>500207</v>
       </c>
       <c r="R72" t="n">
-        <v>6792489</v>
+        <v>6792488</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8437,10 +8437,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125888740</v>
+        <v>125890407</v>
       </c>
       <c r="B80" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8448,39 +8448,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500306</v>
+        <v>500242</v>
       </c>
       <c r="R80" t="n">
-        <v>6792466</v>
+        <v>6792408</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8513,6 +8508,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8539,32 +8539,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125892266</v>
+        <v>125892653</v>
       </c>
       <c r="B81" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8574,10 +8574,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500158</v>
+        <v>500151</v>
       </c>
       <c r="R81" t="n">
-        <v>6792441</v>
+        <v>6792458</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8636,10 +8636,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125892215</v>
+        <v>125889406</v>
       </c>
       <c r="B82" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8647,21 +8647,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500158</v>
+        <v>500257</v>
       </c>
       <c r="R82" t="n">
-        <v>6792441</v>
+        <v>6792475</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8733,10 +8733,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125889155</v>
+        <v>125895109</v>
       </c>
       <c r="B83" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8744,21 +8744,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>500275</v>
+        <v>499985</v>
       </c>
       <c r="R83" t="n">
-        <v>6792487</v>
+        <v>6792633</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8830,32 +8830,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125891598</v>
+        <v>125892266</v>
       </c>
       <c r="B84" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500153</v>
+        <v>500158</v>
       </c>
       <c r="R84" t="n">
-        <v>6792391</v>
+        <v>6792441</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8927,45 +8927,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125888709</v>
+        <v>125888740</v>
       </c>
       <c r="B85" t="n">
-        <v>8447</v>
+        <v>57816</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500311</v>
+        <v>500306</v>
       </c>
       <c r="R85" t="n">
-        <v>6792502</v>
+        <v>6792466</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9024,32 +9029,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125890407</v>
+        <v>125888709</v>
       </c>
       <c r="B86" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9059,10 +9064,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500242</v>
+        <v>500311</v>
       </c>
       <c r="R86" t="n">
-        <v>6792408</v>
+        <v>6792502</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9095,11 +9100,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9126,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125892653</v>
+        <v>125892215</v>
       </c>
       <c r="B87" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9137,21 +9137,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500151</v>
+        <v>500158</v>
       </c>
       <c r="R87" t="n">
-        <v>6792458</v>
+        <v>6792441</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125889406</v>
+        <v>125889155</v>
       </c>
       <c r="B88" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9234,21 +9234,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9258,10 +9258,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500257</v>
+        <v>500275</v>
       </c>
       <c r="R88" t="n">
-        <v>6792475</v>
+        <v>6792487</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9320,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125895109</v>
+        <v>125891598</v>
       </c>
       <c r="B89" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,21 +9331,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>499985</v>
+        <v>500153</v>
       </c>
       <c r="R89" t="n">
-        <v>6792633</v>
+        <v>6792391</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125894466</v>
+        <v>125896683</v>
       </c>
       <c r="B90" t="n">
         <v>8447</v>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R90" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9514,7 +9514,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125896683</v>
+        <v>125894466</v>
       </c>
       <c r="B91" t="n">
         <v>8447</v>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>500384</v>
+        <v>500128</v>
       </c>
       <c r="R91" t="n">
-        <v>6792529</v>
+        <v>6792590</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9611,32 +9611,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125888352</v>
+        <v>125889889</v>
       </c>
       <c r="B92" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>500310</v>
+        <v>500237</v>
       </c>
       <c r="R92" t="n">
-        <v>6792516</v>
+        <v>6792422</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,32 +9708,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125896400</v>
+        <v>125888352</v>
       </c>
       <c r="B93" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>500351</v>
+        <v>500310</v>
       </c>
       <c r="R93" t="n">
-        <v>6792369</v>
+        <v>6792516</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125889879</v>
+        <v>125896400</v>
       </c>
       <c r="B94" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>500237</v>
+        <v>500351</v>
       </c>
       <c r="R94" t="n">
-        <v>6792422</v>
+        <v>6792369</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,7 +9902,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125895107</v>
+        <v>125889879</v>
       </c>
       <c r="B95" t="n">
         <v>78736</v>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>499985</v>
+        <v>500237</v>
       </c>
       <c r="R95" t="n">
-        <v>6792633</v>
+        <v>6792422</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,10 +9999,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125889889</v>
+        <v>125895107</v>
       </c>
       <c r="B96" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>500237</v>
+        <v>499985</v>
       </c>
       <c r="R96" t="n">
-        <v>6792422</v>
+        <v>6792633</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10290,7 +10290,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125894957</v>
+        <v>125889725</v>
       </c>
       <c r="B99" t="n">
         <v>8447</v>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>500037</v>
+        <v>500234</v>
       </c>
       <c r="R99" t="n">
-        <v>6792660</v>
+        <v>6792439</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10387,32 +10387,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125893327</v>
+        <v>125894957</v>
       </c>
       <c r="B100" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>500271</v>
+        <v>500037</v>
       </c>
       <c r="R100" t="n">
-        <v>6792529</v>
+        <v>6792660</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10484,7 +10484,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125892219</v>
+        <v>125893327</v>
       </c>
       <c r="B101" t="n">
         <v>78736</v>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>500158</v>
+        <v>500271</v>
       </c>
       <c r="R101" t="n">
-        <v>6792441</v>
+        <v>6792529</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10581,32 +10581,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125889725</v>
+        <v>125892219</v>
       </c>
       <c r="B102" t="n">
-        <v>8447</v>
+        <v>78736</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>500234</v>
+        <v>500158</v>
       </c>
       <c r="R102" t="n">
-        <v>6792439</v>
+        <v>6792441</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125892224</v>
+        <v>125889615</v>
       </c>
       <c r="B103" t="n">
-        <v>78735</v>
+        <v>8447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500158</v>
+        <v>500202</v>
       </c>
       <c r="R103" t="n">
-        <v>6792441</v>
+        <v>6792435</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10775,10 +10775,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125896058</v>
+        <v>125892224</v>
       </c>
       <c r="B104" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500351</v>
+        <v>500158</v>
       </c>
       <c r="R104" t="n">
-        <v>6792369</v>
+        <v>6792441</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,11 +10846,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10877,10 +10872,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125891964</v>
+        <v>125896058</v>
       </c>
       <c r="B105" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10888,21 +10883,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10912,10 +10907,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500111</v>
+        <v>500351</v>
       </c>
       <c r="R105" t="n">
-        <v>6792428</v>
+        <v>6792369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10948,6 +10943,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125889615</v>
+        <v>125891964</v>
       </c>
       <c r="B106" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500202</v>
+        <v>500111</v>
       </c>
       <c r="R106" t="n">
-        <v>6792435</v>
+        <v>6792428</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11071,32 +11071,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125893643</v>
+        <v>125896524</v>
       </c>
       <c r="B107" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500237</v>
+        <v>500384</v>
       </c>
       <c r="R107" t="n">
-        <v>6792567</v>
+        <v>6792529</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125896524</v>
+        <v>125889090</v>
       </c>
       <c r="B108" t="n">
         <v>79595</v>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500384</v>
+        <v>500285</v>
       </c>
       <c r="R108" t="n">
-        <v>6792529</v>
+        <v>6792489</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11265,10 +11265,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125889090</v>
+        <v>125896426</v>
       </c>
       <c r="B109" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11276,34 +11276,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500285</v>
+        <v>500351</v>
       </c>
       <c r="R109" t="n">
-        <v>6792489</v>
+        <v>6792369</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11362,7 +11367,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125896426</v>
+        <v>125889496</v>
       </c>
       <c r="B110" t="n">
         <v>57653</v>
@@ -11393,7 +11398,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -11402,10 +11407,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500351</v>
+        <v>500257</v>
       </c>
       <c r="R110" t="n">
-        <v>6792369</v>
+        <v>6792475</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11464,50 +11469,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125889496</v>
+        <v>125893643</v>
       </c>
       <c r="B111" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500257</v>
+        <v>500237</v>
       </c>
       <c r="R111" t="n">
-        <v>6792475</v>
+        <v>6792567</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11569,7 +11569,7 @@
         <v>125894266</v>
       </c>
       <c r="B112" t="n">
-        <v>98269</v>
+        <v>98272</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11756,32 +11756,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125890126</v>
+        <v>125896458</v>
       </c>
       <c r="B114" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500242</v>
+        <v>500374</v>
       </c>
       <c r="R114" t="n">
-        <v>6792408</v>
+        <v>6792515</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11853,32 +11853,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125893637</v>
+        <v>125889235</v>
       </c>
       <c r="B115" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500246</v>
+        <v>500275</v>
       </c>
       <c r="R115" t="n">
-        <v>6792558</v>
+        <v>6792487</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11924,11 +11924,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11955,7 +11950,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125892154</v>
+        <v>125890126</v>
       </c>
       <c r="B116" t="n">
         <v>79595</v>
@@ -11990,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500145</v>
+        <v>500242</v>
       </c>
       <c r="R116" t="n">
-        <v>6792446</v>
+        <v>6792408</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12052,10 +12047,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125894500</v>
+        <v>125893637</v>
       </c>
       <c r="B117" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12063,21 +12058,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12087,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500128</v>
+        <v>500246</v>
       </c>
       <c r="R117" t="n">
-        <v>6792590</v>
+        <v>6792558</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12123,6 +12118,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12149,32 +12149,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125889235</v>
+        <v>125892154</v>
       </c>
       <c r="B118" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12184,10 +12184,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>500275</v>
+        <v>500145</v>
       </c>
       <c r="R118" t="n">
-        <v>6792487</v>
+        <v>6792446</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12246,32 +12246,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125896458</v>
+        <v>125894500</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>78735</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>500374</v>
+        <v>500128</v>
       </c>
       <c r="R119" t="n">
-        <v>6792515</v>
+        <v>6792590</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12741,10 +12741,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125896030</v>
+        <v>125896611</v>
       </c>
       <c r="B124" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12752,39 +12752,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500351</v>
+        <v>500384</v>
       </c>
       <c r="R124" t="n">
-        <v>6792369</v>
+        <v>6792529</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12817,6 +12812,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12843,10 +12843,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125896611</v>
+        <v>125892207</v>
       </c>
       <c r="B125" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12854,21 +12854,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12878,10 +12878,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500384</v>
+        <v>500158</v>
       </c>
       <c r="R125" t="n">
-        <v>6792529</v>
+        <v>6792441</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12914,11 +12914,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Sparsamt till måttligt i radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12945,10 +12940,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125892207</v>
+        <v>125896030</v>
       </c>
       <c r="B126" t="n">
-        <v>79595</v>
+        <v>57656</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12956,34 +12951,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500158</v>
+        <v>500351</v>
       </c>
       <c r="R126" t="n">
-        <v>6792441</v>
+        <v>6792369</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13435,50 +13435,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125891498</v>
+        <v>125890887</v>
       </c>
       <c r="B131" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>500166</v>
+        <v>500282</v>
       </c>
       <c r="R131" t="n">
-        <v>6792413</v>
+        <v>6792389</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13537,10 +13532,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125893307</v>
+        <v>125892751</v>
       </c>
       <c r="B132" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13548,21 +13543,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13572,10 +13567,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500271</v>
+        <v>500151</v>
       </c>
       <c r="R132" t="n">
-        <v>6792529</v>
+        <v>6792458</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13634,10 +13629,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125891649</v>
+        <v>125891498</v>
       </c>
       <c r="B133" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13645,24 +13640,29 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
@@ -13672,7 +13672,7 @@
         <v>500166</v>
       </c>
       <c r="R133" t="n">
-        <v>6792387</v>
+        <v>6792413</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13731,10 +13731,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125892751</v>
+        <v>125893307</v>
       </c>
       <c r="B134" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13742,21 +13742,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500151</v>
+        <v>500271</v>
       </c>
       <c r="R134" t="n">
-        <v>6792458</v>
+        <v>6792529</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13828,32 +13828,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125890887</v>
+        <v>125891649</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13863,10 +13863,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500282</v>
+        <v>500166</v>
       </c>
       <c r="R135" t="n">
-        <v>6792389</v>
+        <v>6792387</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15002,50 +15002,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125888369</v>
+        <v>125896772</v>
       </c>
       <c r="B147" t="n">
-        <v>57653</v>
+        <v>92532</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500310</v>
+        <v>500384</v>
       </c>
       <c r="R147" t="n">
-        <v>6792516</v>
+        <v>6792529</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15104,32 +15099,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125896772</v>
+        <v>125891864</v>
       </c>
       <c r="B148" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15139,10 +15134,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500384</v>
+        <v>500126</v>
       </c>
       <c r="R148" t="n">
-        <v>6792529</v>
+        <v>6792397</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15175,6 +15170,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15201,32 +15201,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125891864</v>
+        <v>125892001</v>
       </c>
       <c r="B149" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15236,10 +15236,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500126</v>
+        <v>500111</v>
       </c>
       <c r="R149" t="n">
-        <v>6792397</v>
+        <v>6792428</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15272,11 +15272,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15303,45 +15298,50 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125892001</v>
+        <v>125888369</v>
       </c>
       <c r="B150" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500111</v>
+        <v>500310</v>
       </c>
       <c r="R150" t="n">
-        <v>6792428</v>
+        <v>6792516</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15788,32 +15788,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125895017</v>
+        <v>125895229</v>
       </c>
       <c r="B155" t="n">
-        <v>79001</v>
+        <v>79566</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15885,10 +15885,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125895229</v>
+        <v>125888924</v>
       </c>
       <c r="B156" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15896,21 +15896,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15920,10 +15920,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>499985</v>
+        <v>500306</v>
       </c>
       <c r="R156" t="n">
-        <v>6792633</v>
+        <v>6792466</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -15982,32 +15982,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125888924</v>
+        <v>125895017</v>
       </c>
       <c r="B157" t="n">
-        <v>78736</v>
+        <v>79001</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16017,10 +16017,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>500306</v>
+        <v>499985</v>
       </c>
       <c r="R157" t="n">
-        <v>6792466</v>
+        <v>6792633</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16079,10 +16079,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125892942</v>
+        <v>125889676</v>
       </c>
       <c r="B158" t="n">
-        <v>91262</v>
+        <v>78977</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16090,21 +16090,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16114,10 +16114,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500171</v>
+        <v>500202</v>
       </c>
       <c r="R158" t="n">
-        <v>6792489</v>
+        <v>6792435</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16150,6 +16150,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16176,10 +16181,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125889676</v>
+        <v>125892942</v>
       </c>
       <c r="B159" t="n">
-        <v>78977</v>
+        <v>91262</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16187,21 +16192,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16211,10 +16216,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500202</v>
+        <v>500171</v>
       </c>
       <c r="R159" t="n">
-        <v>6792435</v>
+        <v>6792489</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16247,11 +16252,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -8437,10 +8437,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125890407</v>
+        <v>125888740</v>
       </c>
       <c r="B80" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8448,34 +8448,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500242</v>
+        <v>500306</v>
       </c>
       <c r="R80" t="n">
-        <v>6792408</v>
+        <v>6792466</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8508,11 +8513,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8539,32 +8539,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125892653</v>
+        <v>125888709</v>
       </c>
       <c r="B81" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8574,10 +8574,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500151</v>
+        <v>500311</v>
       </c>
       <c r="R81" t="n">
-        <v>6792458</v>
+        <v>6792502</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8636,10 +8636,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125889406</v>
+        <v>125892215</v>
       </c>
       <c r="B82" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8647,21 +8647,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500257</v>
+        <v>500158</v>
       </c>
       <c r="R82" t="n">
-        <v>6792475</v>
+        <v>6792441</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8733,10 +8733,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125895109</v>
+        <v>125889155</v>
       </c>
       <c r="B83" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8744,21 +8744,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>499985</v>
+        <v>500275</v>
       </c>
       <c r="R83" t="n">
-        <v>6792633</v>
+        <v>6792487</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8830,32 +8830,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125892266</v>
+        <v>125891598</v>
       </c>
       <c r="B84" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500158</v>
+        <v>500153</v>
       </c>
       <c r="R84" t="n">
-        <v>6792441</v>
+        <v>6792391</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8927,10 +8927,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125888740</v>
+        <v>125890407</v>
       </c>
       <c r="B85" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8938,39 +8938,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500306</v>
+        <v>500242</v>
       </c>
       <c r="R85" t="n">
-        <v>6792466</v>
+        <v>6792408</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9003,6 +8998,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9029,32 +9029,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125888709</v>
+        <v>125892653</v>
       </c>
       <c r="B86" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500311</v>
+        <v>500151</v>
       </c>
       <c r="R86" t="n">
-        <v>6792502</v>
+        <v>6792458</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9126,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125892215</v>
+        <v>125889406</v>
       </c>
       <c r="B87" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9137,21 +9137,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500158</v>
+        <v>500257</v>
       </c>
       <c r="R87" t="n">
-        <v>6792441</v>
+        <v>6792475</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125889155</v>
+        <v>125895109</v>
       </c>
       <c r="B88" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9234,21 +9234,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9258,10 +9258,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500275</v>
+        <v>499985</v>
       </c>
       <c r="R88" t="n">
-        <v>6792487</v>
+        <v>6792633</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9320,32 +9320,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125891598</v>
+        <v>125892266</v>
       </c>
       <c r="B89" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500153</v>
+        <v>500158</v>
       </c>
       <c r="R89" t="n">
-        <v>6792391</v>
+        <v>6792441</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125889615</v>
+        <v>125892224</v>
       </c>
       <c r="B103" t="n">
-        <v>8447</v>
+        <v>78735</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500202</v>
+        <v>500158</v>
       </c>
       <c r="R103" t="n">
-        <v>6792435</v>
+        <v>6792441</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10775,10 +10775,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125892224</v>
+        <v>125896058</v>
       </c>
       <c r="B104" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500158</v>
+        <v>500351</v>
       </c>
       <c r="R104" t="n">
-        <v>6792441</v>
+        <v>6792369</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,6 +10846,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10872,10 +10877,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125896058</v>
+        <v>125891964</v>
       </c>
       <c r="B105" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10883,21 +10888,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10907,10 +10912,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500351</v>
+        <v>500111</v>
       </c>
       <c r="R105" t="n">
-        <v>6792369</v>
+        <v>6792428</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10943,11 +10948,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125891964</v>
+        <v>125889615</v>
       </c>
       <c r="B106" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500111</v>
+        <v>500202</v>
       </c>
       <c r="R106" t="n">
-        <v>6792428</v>
+        <v>6792435</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125896524</v>
+        <v>125896426</v>
       </c>
       <c r="B107" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11082,34 +11082,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500384</v>
+        <v>500351</v>
       </c>
       <c r="R107" t="n">
-        <v>6792529</v>
+        <v>6792369</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11168,10 +11173,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125889090</v>
+        <v>125892433</v>
       </c>
       <c r="B108" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11179,21 +11184,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11203,10 +11208,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500285</v>
+        <v>500160</v>
       </c>
       <c r="R108" t="n">
-        <v>6792489</v>
+        <v>6792451</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11265,10 +11270,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125896426</v>
+        <v>125896524</v>
       </c>
       <c r="B109" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11276,39 +11281,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500351</v>
+        <v>500384</v>
       </c>
       <c r="R109" t="n">
-        <v>6792369</v>
+        <v>6792529</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125889496</v>
+        <v>125889090</v>
       </c>
       <c r="B110" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11378,39 +11378,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500257</v>
+        <v>500285</v>
       </c>
       <c r="R110" t="n">
-        <v>6792475</v>
+        <v>6792489</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11469,45 +11464,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125893643</v>
+        <v>125889496</v>
       </c>
       <c r="B111" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500237</v>
+        <v>500257</v>
       </c>
       <c r="R111" t="n">
-        <v>6792567</v>
+        <v>6792475</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11566,10 +11566,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125894266</v>
+        <v>125893643</v>
       </c>
       <c r="B112" t="n">
-        <v>98272</v>
+        <v>8447</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11577,19 +11577,23 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>223597</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11597,10 +11601,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500128</v>
+        <v>500237</v>
       </c>
       <c r="R112" t="n">
-        <v>6792590</v>
+        <v>6792567</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11659,34 +11663,30 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125892433</v>
+        <v>125894266</v>
       </c>
       <c r="B113" t="n">
-        <v>79566</v>
+        <v>98272</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>223597</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500160</v>
+        <v>500128</v>
       </c>
       <c r="R113" t="n">
-        <v>6792451</v>
+        <v>6792590</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125888695</v>
+        <v>125893148</v>
       </c>
       <c r="B120" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500311</v>
+        <v>500251</v>
       </c>
       <c r="R120" t="n">
-        <v>6792502</v>
+        <v>6792496</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,11 +12414,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12445,32 +12440,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125892496</v>
+        <v>125889503</v>
       </c>
       <c r="B121" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12480,10 +12475,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R121" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12516,11 +12511,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12547,32 +12537,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12582,10 +12572,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R122" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12618,6 +12608,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12644,32 +12639,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125889503</v>
+        <v>125892496</v>
       </c>
       <c r="B123" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12679,10 +12674,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R123" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12715,6 +12710,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12940,10 +12940,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125896030</v>
+        <v>125894132</v>
       </c>
       <c r="B126" t="n">
-        <v>57656</v>
+        <v>78736</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12951,39 +12951,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500351</v>
+        <v>500128</v>
       </c>
       <c r="R126" t="n">
-        <v>6792369</v>
+        <v>6792590</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13042,45 +13037,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125891471</v>
+        <v>125896030</v>
       </c>
       <c r="B127" t="n">
-        <v>8447</v>
+        <v>57656</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500181</v>
+        <v>500351</v>
       </c>
       <c r="R127" t="n">
-        <v>6792401</v>
+        <v>6792369</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13139,32 +13139,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125894132</v>
+        <v>125891471</v>
       </c>
       <c r="B128" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13174,10 +13174,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>500128</v>
+        <v>500181</v>
       </c>
       <c r="R128" t="n">
-        <v>6792590</v>
+        <v>6792401</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13435,45 +13435,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125890887</v>
+        <v>125891498</v>
       </c>
       <c r="B131" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>500282</v>
+        <v>500166</v>
       </c>
       <c r="R131" t="n">
-        <v>6792389</v>
+        <v>6792413</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13532,32 +13537,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125892751</v>
+        <v>125893186</v>
       </c>
       <c r="B132" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13567,10 +13572,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500151</v>
+        <v>500247</v>
       </c>
       <c r="R132" t="n">
-        <v>6792458</v>
+        <v>6792519</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13629,10 +13634,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125891498</v>
+        <v>125892751</v>
       </c>
       <c r="B133" t="n">
-        <v>57653</v>
+        <v>78736</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13640,39 +13645,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500166</v>
+        <v>500151</v>
       </c>
       <c r="R133" t="n">
-        <v>6792413</v>
+        <v>6792458</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13925,7 +13925,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125893186</v>
+        <v>125890887</v>
       </c>
       <c r="B136" t="n">
         <v>8447</v>
@@ -13960,10 +13960,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500247</v>
+        <v>500282</v>
       </c>
       <c r="R136" t="n">
-        <v>6792519</v>
+        <v>6792389</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15002,45 +15002,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125896772</v>
+        <v>125888369</v>
       </c>
       <c r="B147" t="n">
-        <v>92532</v>
+        <v>57653</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500384</v>
+        <v>500310</v>
       </c>
       <c r="R147" t="n">
-        <v>6792529</v>
+        <v>6792516</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15099,32 +15104,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125891864</v>
+        <v>125892001</v>
       </c>
       <c r="B148" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15134,10 +15139,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500126</v>
+        <v>500111</v>
       </c>
       <c r="R148" t="n">
-        <v>6792397</v>
+        <v>6792428</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15170,11 +15175,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15201,32 +15201,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125892001</v>
+        <v>125888908</v>
       </c>
       <c r="B149" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15236,10 +15236,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500111</v>
+        <v>500306</v>
       </c>
       <c r="R149" t="n">
-        <v>6792428</v>
+        <v>6792466</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15298,50 +15298,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125888369</v>
+        <v>125896772</v>
       </c>
       <c r="B150" t="n">
-        <v>57653</v>
+        <v>92532</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500310</v>
+        <v>500384</v>
       </c>
       <c r="R150" t="n">
-        <v>6792516</v>
+        <v>6792529</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15400,10 +15395,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125888908</v>
+        <v>125891864</v>
       </c>
       <c r="B151" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15411,21 +15406,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15435,10 +15430,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500306</v>
+        <v>500126</v>
       </c>
       <c r="R151" t="n">
-        <v>6792466</v>
+        <v>6792397</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15471,6 +15466,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15497,32 +15497,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125888498</v>
+        <v>125889396</v>
       </c>
       <c r="B152" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500311</v>
+        <v>500257</v>
       </c>
       <c r="R152" t="n">
-        <v>6792509</v>
+        <v>6792475</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15594,10 +15594,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125889396</v>
+        <v>125891609</v>
       </c>
       <c r="B153" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15605,21 +15605,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15629,10 +15629,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500257</v>
+        <v>500153</v>
       </c>
       <c r="R153" t="n">
-        <v>6792475</v>
+        <v>6792391</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15691,32 +15691,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125891609</v>
+        <v>125888498</v>
       </c>
       <c r="B154" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500153</v>
+        <v>500311</v>
       </c>
       <c r="R154" t="n">
-        <v>6792391</v>
+        <v>6792509</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -8539,7 +8539,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125888709</v>
+        <v>125892266</v>
       </c>
       <c r="B81" t="n">
         <v>8447</v>
@@ -8574,10 +8574,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500311</v>
+        <v>500158</v>
       </c>
       <c r="R81" t="n">
-        <v>6792502</v>
+        <v>6792441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8636,32 +8636,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125892215</v>
+        <v>125888709</v>
       </c>
       <c r="B82" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500158</v>
+        <v>500311</v>
       </c>
       <c r="R82" t="n">
-        <v>6792441</v>
+        <v>6792502</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125891598</v>
+        <v>125892215</v>
       </c>
       <c r="B84" t="n">
         <v>79566</v>
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500153</v>
+        <v>500158</v>
       </c>
       <c r="R84" t="n">
-        <v>6792391</v>
+        <v>6792441</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8927,10 +8927,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125890407</v>
+        <v>125891598</v>
       </c>
       <c r="B85" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8938,21 +8938,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500242</v>
+        <v>500153</v>
       </c>
       <c r="R85" t="n">
-        <v>6792408</v>
+        <v>6792391</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8998,11 +8998,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9029,7 +9024,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125892653</v>
+        <v>125890407</v>
       </c>
       <c r="B86" t="n">
         <v>78977</v>
@@ -9064,10 +9059,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500151</v>
+        <v>500242</v>
       </c>
       <c r="R86" t="n">
-        <v>6792458</v>
+        <v>6792408</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9100,6 +9095,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9126,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125889406</v>
+        <v>125892653</v>
       </c>
       <c r="B87" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9137,21 +9137,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500257</v>
+        <v>500151</v>
       </c>
       <c r="R87" t="n">
-        <v>6792475</v>
+        <v>6792458</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9320,32 +9320,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125892266</v>
+        <v>125889406</v>
       </c>
       <c r="B89" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500158</v>
+        <v>500257</v>
       </c>
       <c r="R89" t="n">
-        <v>6792441</v>
+        <v>6792475</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9708,32 +9708,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125888352</v>
+        <v>125889879</v>
       </c>
       <c r="B93" t="n">
-        <v>8447</v>
+        <v>78736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>500310</v>
+        <v>500237</v>
       </c>
       <c r="R93" t="n">
-        <v>6792516</v>
+        <v>6792422</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125896400</v>
+        <v>125895107</v>
       </c>
       <c r="B94" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>500351</v>
+        <v>499985</v>
       </c>
       <c r="R94" t="n">
-        <v>6792369</v>
+        <v>6792633</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125889879</v>
+        <v>125896400</v>
       </c>
       <c r="B95" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>500237</v>
+        <v>500351</v>
       </c>
       <c r="R95" t="n">
-        <v>6792422</v>
+        <v>6792369</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,32 +9999,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125895107</v>
+        <v>125888352</v>
       </c>
       <c r="B96" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>499985</v>
+        <v>500310</v>
       </c>
       <c r="R96" t="n">
-        <v>6792633</v>
+        <v>6792516</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10096,32 +10096,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125889556</v>
+        <v>125890971</v>
       </c>
       <c r="B97" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>500218</v>
+        <v>500282</v>
       </c>
       <c r="R97" t="n">
-        <v>6792438</v>
+        <v>6792389</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10193,32 +10193,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125890971</v>
+        <v>125889556</v>
       </c>
       <c r="B98" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>500282</v>
+        <v>500218</v>
       </c>
       <c r="R98" t="n">
-        <v>6792389</v>
+        <v>6792438</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10484,7 +10484,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125893327</v>
+        <v>125892219</v>
       </c>
       <c r="B101" t="n">
         <v>78736</v>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>500271</v>
+        <v>500158</v>
       </c>
       <c r="R101" t="n">
-        <v>6792529</v>
+        <v>6792441</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10581,7 +10581,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125892219</v>
+        <v>125893327</v>
       </c>
       <c r="B102" t="n">
         <v>78736</v>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>500158</v>
+        <v>500271</v>
       </c>
       <c r="R102" t="n">
-        <v>6792441</v>
+        <v>6792529</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11173,10 +11173,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125892433</v>
+        <v>125889496</v>
       </c>
       <c r="B108" t="n">
-        <v>79566</v>
+        <v>57653</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11184,34 +11184,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500160</v>
+        <v>500257</v>
       </c>
       <c r="R108" t="n">
-        <v>6792451</v>
+        <v>6792475</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11464,50 +11469,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125889496</v>
+        <v>125893643</v>
       </c>
       <c r="B111" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500257</v>
+        <v>500237</v>
       </c>
       <c r="R111" t="n">
-        <v>6792475</v>
+        <v>6792567</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11566,10 +11566,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125893643</v>
+        <v>125894266</v>
       </c>
       <c r="B112" t="n">
-        <v>8447</v>
+        <v>98272</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11577,23 +11577,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>223597</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11601,10 +11597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500237</v>
+        <v>500128</v>
       </c>
       <c r="R112" t="n">
-        <v>6792567</v>
+        <v>6792590</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11663,30 +11659,34 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125894266</v>
+        <v>125892433</v>
       </c>
       <c r="B113" t="n">
-        <v>98272</v>
+        <v>79566</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>223597</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500128</v>
+        <v>500160</v>
       </c>
       <c r="R113" t="n">
-        <v>6792590</v>
+        <v>6792451</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,32 +11756,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125896458</v>
+        <v>125892154</v>
       </c>
       <c r="B114" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500374</v>
+        <v>500145</v>
       </c>
       <c r="R114" t="n">
-        <v>6792515</v>
+        <v>6792446</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11853,32 +11853,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125889235</v>
+        <v>125890126</v>
       </c>
       <c r="B115" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500275</v>
+        <v>500242</v>
       </c>
       <c r="R115" t="n">
-        <v>6792487</v>
+        <v>6792408</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11950,32 +11950,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125890126</v>
+        <v>125896458</v>
       </c>
       <c r="B116" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500242</v>
+        <v>500374</v>
       </c>
       <c r="R116" t="n">
-        <v>6792408</v>
+        <v>6792515</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12047,32 +12047,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125893637</v>
+        <v>125889235</v>
       </c>
       <c r="B117" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500246</v>
+        <v>500275</v>
       </c>
       <c r="R117" t="n">
-        <v>6792558</v>
+        <v>6792487</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12118,11 +12118,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12149,10 +12144,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125892154</v>
+        <v>125893637</v>
       </c>
       <c r="B118" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12160,21 +12155,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12184,10 +12179,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>500145</v>
+        <v>500246</v>
       </c>
       <c r="R118" t="n">
-        <v>6792446</v>
+        <v>6792558</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12220,6 +12215,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B120" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R120" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,6 +12414,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12440,32 +12445,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125889503</v>
+        <v>125892496</v>
       </c>
       <c r="B121" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12475,10 +12480,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R121" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12511,6 +12516,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12537,32 +12547,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125888695</v>
+        <v>125893148</v>
       </c>
       <c r="B122" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12572,10 +12582,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500311</v>
+        <v>500251</v>
       </c>
       <c r="R122" t="n">
-        <v>6792502</v>
+        <v>6792496</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12608,11 +12618,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12639,32 +12644,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125892496</v>
+        <v>125889503</v>
       </c>
       <c r="B123" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12674,10 +12679,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R123" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12710,11 +12715,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12843,10 +12843,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125892207</v>
+        <v>125896030</v>
       </c>
       <c r="B125" t="n">
-        <v>79595</v>
+        <v>57656</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12854,34 +12854,39 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500158</v>
+        <v>500351</v>
       </c>
       <c r="R125" t="n">
-        <v>6792441</v>
+        <v>6792369</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12940,32 +12945,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125894132</v>
+        <v>125891471</v>
       </c>
       <c r="B126" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12975,10 +12980,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500128</v>
+        <v>500181</v>
       </c>
       <c r="R126" t="n">
-        <v>6792590</v>
+        <v>6792401</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13037,10 +13042,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125896030</v>
+        <v>125894132</v>
       </c>
       <c r="B127" t="n">
-        <v>57656</v>
+        <v>78736</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13048,39 +13053,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500351</v>
+        <v>500128</v>
       </c>
       <c r="R127" t="n">
-        <v>6792369</v>
+        <v>6792590</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13139,32 +13139,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125891471</v>
+        <v>125892207</v>
       </c>
       <c r="B128" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13174,10 +13174,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>500181</v>
+        <v>500158</v>
       </c>
       <c r="R128" t="n">
-        <v>6792401</v>
+        <v>6792441</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13435,50 +13435,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125891498</v>
+        <v>125890887</v>
       </c>
       <c r="B131" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>500166</v>
+        <v>500282</v>
       </c>
       <c r="R131" t="n">
-        <v>6792413</v>
+        <v>6792389</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13634,10 +13629,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125892751</v>
+        <v>125891649</v>
       </c>
       <c r="B133" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13645,21 +13640,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13669,10 +13664,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500151</v>
+        <v>500166</v>
       </c>
       <c r="R133" t="n">
-        <v>6792458</v>
+        <v>6792387</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13828,10 +13823,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125891649</v>
+        <v>125891498</v>
       </c>
       <c r="B135" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13839,24 +13834,29 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
@@ -13866,7 +13866,7 @@
         <v>500166</v>
       </c>
       <c r="R135" t="n">
-        <v>6792387</v>
+        <v>6792413</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13925,32 +13925,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125890887</v>
+        <v>125892751</v>
       </c>
       <c r="B136" t="n">
-        <v>8447</v>
+        <v>78736</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13960,10 +13960,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500282</v>
+        <v>500151</v>
       </c>
       <c r="R136" t="n">
-        <v>6792389</v>
+        <v>6792458</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125896535</v>
+        <v>125892643</v>
       </c>
       <c r="B140" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500384</v>
+        <v>500151</v>
       </c>
       <c r="R140" t="n">
-        <v>6792529</v>
+        <v>6792458</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14410,7 +14410,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125896642</v>
+        <v>125892160</v>
       </c>
       <c r="B141" t="n">
         <v>79566</v>
@@ -14445,10 +14445,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500384</v>
+        <v>500145</v>
       </c>
       <c r="R141" t="n">
-        <v>6792529</v>
+        <v>6792446</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14507,10 +14507,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125892643</v>
+        <v>125889379</v>
       </c>
       <c r="B142" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14518,21 +14518,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14542,10 +14542,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>500151</v>
+        <v>500257</v>
       </c>
       <c r="R142" t="n">
-        <v>6792458</v>
+        <v>6792475</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14604,7 +14604,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125889379</v>
+        <v>125896535</v>
       </c>
       <c r="B143" t="n">
         <v>78736</v>
@@ -14639,10 +14639,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500257</v>
+        <v>500384</v>
       </c>
       <c r="R143" t="n">
-        <v>6792475</v>
+        <v>6792529</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14701,7 +14701,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125892160</v>
+        <v>125896642</v>
       </c>
       <c r="B144" t="n">
         <v>79566</v>
@@ -14736,10 +14736,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500145</v>
+        <v>500384</v>
       </c>
       <c r="R144" t="n">
-        <v>6792446</v>
+        <v>6792529</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15002,50 +15002,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125888369</v>
+        <v>125896772</v>
       </c>
       <c r="B147" t="n">
-        <v>57653</v>
+        <v>92532</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500310</v>
+        <v>500384</v>
       </c>
       <c r="R147" t="n">
-        <v>6792516</v>
+        <v>6792529</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15104,32 +15099,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125892001</v>
+        <v>125891864</v>
       </c>
       <c r="B148" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15139,10 +15134,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500111</v>
+        <v>500126</v>
       </c>
       <c r="R148" t="n">
-        <v>6792428</v>
+        <v>6792397</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15175,6 +15170,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15201,10 +15201,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125888908</v>
+        <v>125888369</v>
       </c>
       <c r="B149" t="n">
-        <v>79566</v>
+        <v>57653</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15212,34 +15212,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500306</v>
+        <v>500310</v>
       </c>
       <c r="R149" t="n">
-        <v>6792466</v>
+        <v>6792516</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15298,10 +15303,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125896772</v>
+        <v>125892001</v>
       </c>
       <c r="B150" t="n">
-        <v>92532</v>
+        <v>8447</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15309,21 +15314,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15333,10 +15338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500384</v>
+        <v>500111</v>
       </c>
       <c r="R150" t="n">
-        <v>6792529</v>
+        <v>6792428</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15395,10 +15400,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125891864</v>
+        <v>125888908</v>
       </c>
       <c r="B151" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15406,21 +15411,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15430,10 +15435,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500126</v>
+        <v>500306</v>
       </c>
       <c r="R151" t="n">
-        <v>6792397</v>
+        <v>6792466</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15466,11 +15471,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15497,32 +15497,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125889396</v>
+        <v>125888498</v>
       </c>
       <c r="B152" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500257</v>
+        <v>500311</v>
       </c>
       <c r="R152" t="n">
-        <v>6792475</v>
+        <v>6792509</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15691,32 +15691,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125888498</v>
+        <v>125889396</v>
       </c>
       <c r="B154" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500311</v>
+        <v>500257</v>
       </c>
       <c r="R154" t="n">
-        <v>6792509</v>
+        <v>6792475</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16079,10 +16079,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125889676</v>
+        <v>125892637</v>
       </c>
       <c r="B158" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16090,21 +16090,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16114,10 +16114,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500202</v>
+        <v>500151</v>
       </c>
       <c r="R158" t="n">
-        <v>6792435</v>
+        <v>6792458</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16150,11 +16150,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16181,10 +16176,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125892942</v>
+        <v>125889676</v>
       </c>
       <c r="B159" t="n">
-        <v>91262</v>
+        <v>78977</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16192,21 +16187,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16216,10 +16211,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500171</v>
+        <v>500202</v>
       </c>
       <c r="R159" t="n">
-        <v>6792489</v>
+        <v>6792435</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16252,6 +16247,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16278,10 +16278,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125892637</v>
+        <v>125892942</v>
       </c>
       <c r="B160" t="n">
-        <v>79595</v>
+        <v>91262</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16289,21 +16289,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16313,10 +16313,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>500151</v>
+        <v>500171</v>
       </c>
       <c r="R160" t="n">
-        <v>6792458</v>
+        <v>6792489</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -7263,10 +7263,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125889107</v>
+        <v>125894731</v>
       </c>
       <c r="B68" t="n">
-        <v>79566</v>
+        <v>57656</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,34 +7274,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500285</v>
+        <v>500128</v>
       </c>
       <c r="R68" t="n">
-        <v>6792489</v>
+        <v>6792590</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7360,32 +7365,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125888195</v>
+        <v>125892998</v>
       </c>
       <c r="B69" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7395,10 +7400,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500310</v>
+        <v>500188</v>
       </c>
       <c r="R69" t="n">
-        <v>6792516</v>
+        <v>6792496</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7431,11 +7436,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7462,50 +7462,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125894731</v>
+        <v>125893046</v>
       </c>
       <c r="B70" t="n">
-        <v>57656</v>
+        <v>8447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500128</v>
+        <v>500207</v>
       </c>
       <c r="R70" t="n">
-        <v>6792590</v>
+        <v>6792488</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7564,32 +7559,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125892998</v>
+        <v>125888195</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7599,10 +7594,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500188</v>
+        <v>500310</v>
       </c>
       <c r="R71" t="n">
-        <v>6792496</v>
+        <v>6792516</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7635,6 +7630,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7661,32 +7661,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125893046</v>
+        <v>125889107</v>
       </c>
       <c r="B72" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500207</v>
+        <v>500285</v>
       </c>
       <c r="R72" t="n">
-        <v>6792488</v>
+        <v>6792489</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8437,10 +8437,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125888740</v>
+        <v>125890407</v>
       </c>
       <c r="B80" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8448,39 +8448,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500306</v>
+        <v>500242</v>
       </c>
       <c r="R80" t="n">
-        <v>6792466</v>
+        <v>6792408</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8513,6 +8508,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8539,32 +8539,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125892266</v>
+        <v>125892653</v>
       </c>
       <c r="B81" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8574,10 +8574,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500158</v>
+        <v>500151</v>
       </c>
       <c r="R81" t="n">
-        <v>6792441</v>
+        <v>6792458</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8636,32 +8636,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125888709</v>
+        <v>125895109</v>
       </c>
       <c r="B82" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500311</v>
+        <v>499985</v>
       </c>
       <c r="R82" t="n">
-        <v>6792502</v>
+        <v>6792633</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8733,10 +8733,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125889155</v>
+        <v>125889406</v>
       </c>
       <c r="B83" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8744,21 +8744,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>500275</v>
+        <v>500257</v>
       </c>
       <c r="R83" t="n">
-        <v>6792487</v>
+        <v>6792475</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8830,10 +8830,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125892215</v>
+        <v>125888740</v>
       </c>
       <c r="B84" t="n">
-        <v>79566</v>
+        <v>57816</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8841,34 +8841,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500158</v>
+        <v>500306</v>
       </c>
       <c r="R84" t="n">
-        <v>6792441</v>
+        <v>6792466</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8927,32 +8932,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125891598</v>
+        <v>125892266</v>
       </c>
       <c r="B85" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8962,10 +8967,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500153</v>
+        <v>500158</v>
       </c>
       <c r="R85" t="n">
-        <v>6792391</v>
+        <v>6792441</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9024,32 +9029,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125890407</v>
+        <v>125888709</v>
       </c>
       <c r="B86" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9059,10 +9064,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500242</v>
+        <v>500311</v>
       </c>
       <c r="R86" t="n">
-        <v>6792408</v>
+        <v>6792502</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9095,11 +9100,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9126,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125892653</v>
+        <v>125889155</v>
       </c>
       <c r="B87" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9137,21 +9137,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500151</v>
+        <v>500275</v>
       </c>
       <c r="R87" t="n">
-        <v>6792458</v>
+        <v>6792487</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125895109</v>
+        <v>125892215</v>
       </c>
       <c r="B88" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9234,21 +9234,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9258,10 +9258,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>499985</v>
+        <v>500158</v>
       </c>
       <c r="R88" t="n">
-        <v>6792633</v>
+        <v>6792441</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9320,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125889406</v>
+        <v>125891598</v>
       </c>
       <c r="B89" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,21 +9331,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500257</v>
+        <v>500153</v>
       </c>
       <c r="R89" t="n">
-        <v>6792475</v>
+        <v>6792391</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10096,32 +10096,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125890971</v>
+        <v>125889556</v>
       </c>
       <c r="B97" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>500282</v>
+        <v>500218</v>
       </c>
       <c r="R97" t="n">
-        <v>6792389</v>
+        <v>6792438</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10193,32 +10193,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125889556</v>
+        <v>125890971</v>
       </c>
       <c r="B98" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>500218</v>
+        <v>500282</v>
       </c>
       <c r="R98" t="n">
-        <v>6792438</v>
+        <v>6792389</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125888695</v>
+        <v>125893148</v>
       </c>
       <c r="B120" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500311</v>
+        <v>500251</v>
       </c>
       <c r="R120" t="n">
-        <v>6792502</v>
+        <v>6792496</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,11 +12414,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12445,32 +12440,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125892496</v>
+        <v>125889503</v>
       </c>
       <c r="B121" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12480,10 +12475,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R121" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12516,11 +12511,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12547,32 +12537,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12582,10 +12572,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R122" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12618,6 +12608,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12644,32 +12639,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125889503</v>
+        <v>125892496</v>
       </c>
       <c r="B123" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12679,10 +12674,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R123" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12715,6 +12710,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12843,10 +12843,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125896030</v>
+        <v>125892207</v>
       </c>
       <c r="B125" t="n">
-        <v>57656</v>
+        <v>79595</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12854,39 +12854,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500351</v>
+        <v>500158</v>
       </c>
       <c r="R125" t="n">
-        <v>6792369</v>
+        <v>6792441</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12945,45 +12940,50 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125891471</v>
+        <v>125896030</v>
       </c>
       <c r="B126" t="n">
-        <v>8447</v>
+        <v>57656</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500181</v>
+        <v>500351</v>
       </c>
       <c r="R126" t="n">
-        <v>6792401</v>
+        <v>6792369</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13042,32 +13042,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125894132</v>
+        <v>125891471</v>
       </c>
       <c r="B127" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13077,10 +13077,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500128</v>
+        <v>500181</v>
       </c>
       <c r="R127" t="n">
-        <v>6792590</v>
+        <v>6792401</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13139,10 +13139,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125892207</v>
+        <v>125894132</v>
       </c>
       <c r="B128" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13150,21 +13150,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13174,10 +13174,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>500158</v>
+        <v>500128</v>
       </c>
       <c r="R128" t="n">
-        <v>6792441</v>
+        <v>6792590</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13435,45 +13435,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125890887</v>
+        <v>125891498</v>
       </c>
       <c r="B131" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>500282</v>
+        <v>500166</v>
       </c>
       <c r="R131" t="n">
-        <v>6792389</v>
+        <v>6792413</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13532,32 +13537,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125893186</v>
+        <v>125891649</v>
       </c>
       <c r="B132" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13567,10 +13572,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500247</v>
+        <v>500166</v>
       </c>
       <c r="R132" t="n">
-        <v>6792519</v>
+        <v>6792387</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13629,7 +13634,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125891649</v>
+        <v>125893307</v>
       </c>
       <c r="B133" t="n">
         <v>79595</v>
@@ -13664,10 +13669,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500166</v>
+        <v>500271</v>
       </c>
       <c r="R133" t="n">
-        <v>6792387</v>
+        <v>6792529</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13726,32 +13731,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125893307</v>
+        <v>125890887</v>
       </c>
       <c r="B134" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13761,10 +13766,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500271</v>
+        <v>500282</v>
       </c>
       <c r="R134" t="n">
-        <v>6792529</v>
+        <v>6792389</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13823,50 +13828,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125891498</v>
+        <v>125893186</v>
       </c>
       <c r="B135" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500166</v>
+        <v>500247</v>
       </c>
       <c r="R135" t="n">
-        <v>6792413</v>
+        <v>6792519</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125892643</v>
+        <v>125896454</v>
       </c>
       <c r="B140" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500151</v>
+        <v>500374</v>
       </c>
       <c r="R140" t="n">
-        <v>6792458</v>
+        <v>6792515</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14384,6 +14384,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14410,10 +14415,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125892160</v>
+        <v>125889266</v>
       </c>
       <c r="B141" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14421,21 +14426,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14445,10 +14450,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R141" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14481,6 +14486,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14507,10 +14517,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125889379</v>
+        <v>125892643</v>
       </c>
       <c r="B142" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14518,21 +14528,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14542,10 +14552,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>500257</v>
+        <v>500151</v>
       </c>
       <c r="R142" t="n">
-        <v>6792475</v>
+        <v>6792458</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14604,10 +14614,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125896535</v>
+        <v>125892160</v>
       </c>
       <c r="B143" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14615,21 +14625,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14639,10 +14649,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500384</v>
+        <v>500145</v>
       </c>
       <c r="R143" t="n">
-        <v>6792529</v>
+        <v>6792446</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14701,10 +14711,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125896642</v>
+        <v>125889379</v>
       </c>
       <c r="B144" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14712,21 +14722,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14736,10 +14746,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500384</v>
+        <v>500257</v>
       </c>
       <c r="R144" t="n">
-        <v>6792529</v>
+        <v>6792475</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14798,10 +14808,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125896454</v>
+        <v>125896535</v>
       </c>
       <c r="B145" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14809,21 +14819,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14833,10 +14843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500374</v>
+        <v>500384</v>
       </c>
       <c r="R145" t="n">
-        <v>6792515</v>
+        <v>6792529</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14869,11 +14879,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14900,10 +14905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125889266</v>
+        <v>125896642</v>
       </c>
       <c r="B146" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14911,21 +14916,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14935,10 +14940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500257</v>
+        <v>500384</v>
       </c>
       <c r="R146" t="n">
-        <v>6792475</v>
+        <v>6792529</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14971,11 +14976,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD146" t="b">

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -7266,7 +7266,7 @@
         <v>125894731</v>
       </c>
       <c r="B68" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7365,32 +7365,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125892998</v>
+        <v>125889107</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500188</v>
+        <v>500285</v>
       </c>
       <c r="R69" t="n">
-        <v>6792496</v>
+        <v>6792489</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7462,32 +7462,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125893046</v>
+        <v>125888195</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500207</v>
+        <v>500310</v>
       </c>
       <c r="R70" t="n">
-        <v>6792488</v>
+        <v>6792516</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7533,6 +7533,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7559,32 +7564,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125888195</v>
+        <v>125893046</v>
       </c>
       <c r="B71" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7594,10 +7599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500310</v>
+        <v>500207</v>
       </c>
       <c r="R71" t="n">
-        <v>6792516</v>
+        <v>6792488</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7630,11 +7635,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7661,32 +7661,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125889107</v>
+        <v>125892998</v>
       </c>
       <c r="B72" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500285</v>
+        <v>500188</v>
       </c>
       <c r="R72" t="n">
-        <v>6792489</v>
+        <v>6792496</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7761,7 +7761,7 @@
         <v>125890555</v>
       </c>
       <c r="B73" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7855,32 +7855,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125893261</v>
+        <v>125890092</v>
       </c>
       <c r="B74" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500271</v>
+        <v>500242</v>
       </c>
       <c r="R74" t="n">
-        <v>6792529</v>
+        <v>6792408</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7952,32 +7952,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125896279</v>
+        <v>125891809</v>
       </c>
       <c r="B75" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>500351</v>
+        <v>500166</v>
       </c>
       <c r="R75" t="n">
-        <v>6792369</v>
+        <v>6792387</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125895125</v>
+        <v>125890234</v>
       </c>
       <c r="B76" t="n">
         <v>8447</v>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>499985</v>
+        <v>500242</v>
       </c>
       <c r="R76" t="n">
-        <v>6792633</v>
+        <v>6792408</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125890234</v>
+        <v>125895125</v>
       </c>
       <c r="B77" t="n">
         <v>8447</v>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>500242</v>
+        <v>499985</v>
       </c>
       <c r="R77" t="n">
-        <v>6792408</v>
+        <v>6792633</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8243,32 +8243,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125890092</v>
+        <v>125896279</v>
       </c>
       <c r="B78" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>500242</v>
+        <v>500351</v>
       </c>
       <c r="R78" t="n">
-        <v>6792408</v>
+        <v>6792369</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8340,32 +8340,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125891809</v>
+        <v>125893261</v>
       </c>
       <c r="B79" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500166</v>
+        <v>500271</v>
       </c>
       <c r="R79" t="n">
-        <v>6792387</v>
+        <v>6792529</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8440,7 +8440,7 @@
         <v>125890407</v>
       </c>
       <c r="B80" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>125892653</v>
       </c>
       <c r="B81" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8636,10 +8636,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125895109</v>
+        <v>125889406</v>
       </c>
       <c r="B82" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>499985</v>
+        <v>500257</v>
       </c>
       <c r="R82" t="n">
-        <v>6792633</v>
+        <v>6792475</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8733,10 +8733,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125889406</v>
+        <v>125895109</v>
       </c>
       <c r="B83" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>500257</v>
+        <v>499985</v>
       </c>
       <c r="R83" t="n">
-        <v>6792475</v>
+        <v>6792633</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8830,50 +8830,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125888740</v>
+        <v>125892266</v>
       </c>
       <c r="B84" t="n">
-        <v>57816</v>
+        <v>8447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500306</v>
+        <v>500158</v>
       </c>
       <c r="R84" t="n">
-        <v>6792466</v>
+        <v>6792441</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8932,7 +8927,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125892266</v>
+        <v>125888709</v>
       </c>
       <c r="B85" t="n">
         <v>8447</v>
@@ -8967,10 +8962,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500158</v>
+        <v>500311</v>
       </c>
       <c r="R85" t="n">
-        <v>6792441</v>
+        <v>6792502</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9029,32 +9024,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125888709</v>
+        <v>125892215</v>
       </c>
       <c r="B86" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9064,10 +9059,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500311</v>
+        <v>500158</v>
       </c>
       <c r="R86" t="n">
-        <v>6792502</v>
+        <v>6792441</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9129,7 +9124,7 @@
         <v>125889155</v>
       </c>
       <c r="B87" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9223,10 +9218,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125892215</v>
+        <v>125891598</v>
       </c>
       <c r="B88" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9258,10 +9253,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500158</v>
+        <v>500153</v>
       </c>
       <c r="R88" t="n">
-        <v>6792441</v>
+        <v>6792391</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9320,10 +9315,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125891598</v>
+        <v>125888740</v>
       </c>
       <c r="B89" t="n">
-        <v>79566</v>
+        <v>57817</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,34 +9326,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500153</v>
+        <v>500306</v>
       </c>
       <c r="R89" t="n">
-        <v>6792391</v>
+        <v>6792466</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125896683</v>
+        <v>125894466</v>
       </c>
       <c r="B90" t="n">
         <v>8447</v>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>500384</v>
+        <v>500128</v>
       </c>
       <c r="R90" t="n">
-        <v>6792529</v>
+        <v>6792590</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9514,7 +9514,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125894466</v>
+        <v>125896683</v>
       </c>
       <c r="B91" t="n">
         <v>8447</v>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R91" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9614,7 +9614,7 @@
         <v>125889889</v>
       </c>
       <c r="B92" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9708,32 +9708,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125889879</v>
+        <v>125888352</v>
       </c>
       <c r="B93" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>500237</v>
+        <v>500310</v>
       </c>
       <c r="R93" t="n">
-        <v>6792422</v>
+        <v>6792516</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125895107</v>
+        <v>125889879</v>
       </c>
       <c r="B94" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>499985</v>
+        <v>500237</v>
       </c>
       <c r="R94" t="n">
-        <v>6792633</v>
+        <v>6792422</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125896400</v>
+        <v>125895107</v>
       </c>
       <c r="B95" t="n">
-        <v>79566</v>
+        <v>78739</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>500351</v>
+        <v>499985</v>
       </c>
       <c r="R95" t="n">
-        <v>6792369</v>
+        <v>6792633</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,32 +9999,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125888352</v>
+        <v>125896400</v>
       </c>
       <c r="B96" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>500310</v>
+        <v>500351</v>
       </c>
       <c r="R96" t="n">
-        <v>6792516</v>
+        <v>6792369</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10196,7 +10196,7 @@
         <v>125890971</v>
       </c>
       <c r="B98" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10290,32 +10290,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125889725</v>
+        <v>125893327</v>
       </c>
       <c r="B99" t="n">
-        <v>8447</v>
+        <v>78739</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>500234</v>
+        <v>500271</v>
       </c>
       <c r="R99" t="n">
-        <v>6792439</v>
+        <v>6792529</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10387,32 +10387,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125894957</v>
+        <v>125892219</v>
       </c>
       <c r="B100" t="n">
-        <v>8447</v>
+        <v>78739</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>500037</v>
+        <v>500158</v>
       </c>
       <c r="R100" t="n">
-        <v>6792660</v>
+        <v>6792441</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10484,32 +10484,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125892219</v>
+        <v>125894957</v>
       </c>
       <c r="B101" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>500158</v>
+        <v>500037</v>
       </c>
       <c r="R101" t="n">
-        <v>6792441</v>
+        <v>6792660</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10581,32 +10581,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125893327</v>
+        <v>125889725</v>
       </c>
       <c r="B102" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>500271</v>
+        <v>500234</v>
       </c>
       <c r="R102" t="n">
-        <v>6792529</v>
+        <v>6792439</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125892224</v>
+        <v>125889615</v>
       </c>
       <c r="B103" t="n">
-        <v>78735</v>
+        <v>8447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500158</v>
+        <v>500202</v>
       </c>
       <c r="R103" t="n">
-        <v>6792441</v>
+        <v>6792435</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10775,10 +10775,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125896058</v>
+        <v>125892224</v>
       </c>
       <c r="B104" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500351</v>
+        <v>500158</v>
       </c>
       <c r="R104" t="n">
-        <v>6792369</v>
+        <v>6792441</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,11 +10846,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10877,10 +10872,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125891964</v>
+        <v>125896058</v>
       </c>
       <c r="B105" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10888,21 +10883,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10912,10 +10907,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500111</v>
+        <v>500351</v>
       </c>
       <c r="R105" t="n">
-        <v>6792428</v>
+        <v>6792369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10948,6 +10943,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125889615</v>
+        <v>125891964</v>
       </c>
       <c r="B106" t="n">
-        <v>8447</v>
+        <v>79598</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500202</v>
+        <v>500111</v>
       </c>
       <c r="R106" t="n">
-        <v>6792435</v>
+        <v>6792428</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11071,50 +11071,41 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125896426</v>
+        <v>125894266</v>
       </c>
       <c r="B107" t="n">
-        <v>57653</v>
+        <v>98281</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>223597</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500351</v>
+        <v>500128</v>
       </c>
       <c r="R107" t="n">
-        <v>6792369</v>
+        <v>6792590</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11173,10 +11164,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125889496</v>
+        <v>125896524</v>
       </c>
       <c r="B108" t="n">
-        <v>57653</v>
+        <v>79598</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11184,39 +11175,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500257</v>
+        <v>500384</v>
       </c>
       <c r="R108" t="n">
-        <v>6792475</v>
+        <v>6792529</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11275,10 +11261,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125896524</v>
+        <v>125889090</v>
       </c>
       <c r="B109" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11310,10 +11296,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500384</v>
+        <v>500285</v>
       </c>
       <c r="R109" t="n">
-        <v>6792529</v>
+        <v>6792489</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11372,10 +11358,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125889090</v>
+        <v>125896426</v>
       </c>
       <c r="B110" t="n">
-        <v>79595</v>
+        <v>57654</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11383,34 +11369,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500285</v>
+        <v>500351</v>
       </c>
       <c r="R110" t="n">
-        <v>6792489</v>
+        <v>6792369</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11469,45 +11460,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125893643</v>
+        <v>125889496</v>
       </c>
       <c r="B111" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500237</v>
+        <v>500257</v>
       </c>
       <c r="R111" t="n">
-        <v>6792567</v>
+        <v>6792475</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11566,10 +11562,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125894266</v>
+        <v>125893643</v>
       </c>
       <c r="B112" t="n">
-        <v>98272</v>
+        <v>8447</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11577,19 +11573,23 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>223597</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11597,10 +11597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500128</v>
+        <v>500237</v>
       </c>
       <c r="R112" t="n">
-        <v>6792590</v>
+        <v>6792567</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11662,7 +11662,7 @@
         <v>125892433</v>
       </c>
       <c r="B113" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11756,10 +11756,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125892154</v>
+        <v>125890126</v>
       </c>
       <c r="B114" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500145</v>
+        <v>500242</v>
       </c>
       <c r="R114" t="n">
-        <v>6792446</v>
+        <v>6792408</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11853,10 +11853,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125890126</v>
+        <v>125893637</v>
       </c>
       <c r="B115" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11864,21 +11864,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500242</v>
+        <v>500246</v>
       </c>
       <c r="R115" t="n">
-        <v>6792408</v>
+        <v>6792558</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11924,6 +11924,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11950,32 +11955,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125896458</v>
+        <v>125892154</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>79598</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11985,10 +11990,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500374</v>
+        <v>500145</v>
       </c>
       <c r="R116" t="n">
-        <v>6792515</v>
+        <v>6792446</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12047,32 +12052,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125889235</v>
+        <v>125894500</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>78738</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12082,10 +12087,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500275</v>
+        <v>500128</v>
       </c>
       <c r="R117" t="n">
-        <v>6792487</v>
+        <v>6792590</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12144,32 +12149,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125893637</v>
+        <v>125896458</v>
       </c>
       <c r="B118" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12179,10 +12184,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>500246</v>
+        <v>500374</v>
       </c>
       <c r="R118" t="n">
-        <v>6792558</v>
+        <v>6792515</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12215,11 +12220,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12246,32 +12246,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125894500</v>
+        <v>125889235</v>
       </c>
       <c r="B119" t="n">
-        <v>78735</v>
+        <v>8447</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>500128</v>
+        <v>500275</v>
       </c>
       <c r="R119" t="n">
-        <v>6792590</v>
+        <v>6792487</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B120" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R120" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,6 +12414,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12440,32 +12445,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125889503</v>
+        <v>125892496</v>
       </c>
       <c r="B121" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12475,10 +12480,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R121" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12511,6 +12516,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12537,32 +12547,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125888695</v>
+        <v>125893148</v>
       </c>
       <c r="B122" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12572,10 +12582,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500311</v>
+        <v>500251</v>
       </c>
       <c r="R122" t="n">
-        <v>6792502</v>
+        <v>6792496</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12608,11 +12618,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12639,32 +12644,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125892496</v>
+        <v>125889503</v>
       </c>
       <c r="B123" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12674,10 +12679,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R123" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12710,11 +12715,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12744,7 +12744,7 @@
         <v>125896611</v>
       </c>
       <c r="B124" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>125892207</v>
       </c>
       <c r="B125" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>125896030</v>
       </c>
       <c r="B126" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>125894132</v>
       </c>
       <c r="B128" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>125894564</v>
       </c>
       <c r="B129" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>125892025</v>
       </c>
       <c r="B130" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>125891498</v>
       </c>
       <c r="B131" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13537,10 +13537,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125891649</v>
+        <v>125892751</v>
       </c>
       <c r="B132" t="n">
-        <v>79595</v>
+        <v>78739</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13548,21 +13548,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13572,10 +13572,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500166</v>
+        <v>500151</v>
       </c>
       <c r="R132" t="n">
-        <v>6792387</v>
+        <v>6792458</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13637,7 +13637,7 @@
         <v>125893307</v>
       </c>
       <c r="B133" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13731,32 +13731,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125890887</v>
+        <v>125891649</v>
       </c>
       <c r="B134" t="n">
-        <v>8447</v>
+        <v>79598</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500282</v>
+        <v>500166</v>
       </c>
       <c r="R134" t="n">
-        <v>6792389</v>
+        <v>6792387</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13925,32 +13925,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125892751</v>
+        <v>125890887</v>
       </c>
       <c r="B136" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13960,10 +13960,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500151</v>
+        <v>500282</v>
       </c>
       <c r="R136" t="n">
-        <v>6792458</v>
+        <v>6792389</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14022,32 +14022,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125889773</v>
+        <v>125892352</v>
       </c>
       <c r="B137" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14057,10 +14057,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>500237</v>
+        <v>500165</v>
       </c>
       <c r="R137" t="n">
-        <v>6792422</v>
+        <v>6792432</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14119,32 +14119,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125892352</v>
+        <v>125889773</v>
       </c>
       <c r="B138" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14154,10 +14154,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>500165</v>
+        <v>500237</v>
       </c>
       <c r="R138" t="n">
-        <v>6792432</v>
+        <v>6792422</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14219,7 +14219,7 @@
         <v>125889010</v>
       </c>
       <c r="B139" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>125896454</v>
       </c>
       <c r="B140" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>125889266</v>
       </c>
       <c r="B141" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14517,10 +14517,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125892643</v>
+        <v>125896535</v>
       </c>
       <c r="B142" t="n">
-        <v>79566</v>
+        <v>78739</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14528,21 +14528,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14552,10 +14552,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>500151</v>
+        <v>500384</v>
       </c>
       <c r="R142" t="n">
-        <v>6792458</v>
+        <v>6792529</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14614,10 +14614,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125892160</v>
+        <v>125889379</v>
       </c>
       <c r="B143" t="n">
-        <v>79566</v>
+        <v>78739</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14625,21 +14625,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14649,10 +14649,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R143" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14711,10 +14711,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125889379</v>
+        <v>125896642</v>
       </c>
       <c r="B144" t="n">
-        <v>78736</v>
+        <v>79569</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14722,21 +14722,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14746,10 +14746,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500257</v>
+        <v>500384</v>
       </c>
       <c r="R144" t="n">
-        <v>6792475</v>
+        <v>6792529</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14808,10 +14808,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125896535</v>
+        <v>125892643</v>
       </c>
       <c r="B145" t="n">
-        <v>78736</v>
+        <v>79569</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14819,21 +14819,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500384</v>
+        <v>500151</v>
       </c>
       <c r="R145" t="n">
-        <v>6792529</v>
+        <v>6792458</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14905,10 +14905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125896642</v>
+        <v>125892160</v>
       </c>
       <c r="B146" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14940,10 +14940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500384</v>
+        <v>500145</v>
       </c>
       <c r="R146" t="n">
-        <v>6792529</v>
+        <v>6792446</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15002,45 +15002,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125896772</v>
+        <v>125888369</v>
       </c>
       <c r="B147" t="n">
-        <v>92532</v>
+        <v>57654</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500384</v>
+        <v>500310</v>
       </c>
       <c r="R147" t="n">
-        <v>6792529</v>
+        <v>6792516</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15099,10 +15104,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125891864</v>
+        <v>125888908</v>
       </c>
       <c r="B148" t="n">
-        <v>78977</v>
+        <v>79569</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15110,21 +15115,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15134,10 +15139,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500126</v>
+        <v>500306</v>
       </c>
       <c r="R148" t="n">
-        <v>6792397</v>
+        <v>6792466</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15170,11 +15175,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15201,50 +15201,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125888369</v>
+        <v>125892001</v>
       </c>
       <c r="B149" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500310</v>
+        <v>500111</v>
       </c>
       <c r="R149" t="n">
-        <v>6792516</v>
+        <v>6792428</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15303,10 +15298,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125892001</v>
+        <v>125896772</v>
       </c>
       <c r="B150" t="n">
-        <v>8447</v>
+        <v>92535</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15314,21 +15309,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15338,10 +15333,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500111</v>
+        <v>500384</v>
       </c>
       <c r="R150" t="n">
-        <v>6792428</v>
+        <v>6792529</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15400,10 +15395,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125888908</v>
+        <v>125891864</v>
       </c>
       <c r="B151" t="n">
-        <v>79566</v>
+        <v>78980</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15411,21 +15406,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15435,10 +15430,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500306</v>
+        <v>500126</v>
       </c>
       <c r="R151" t="n">
-        <v>6792466</v>
+        <v>6792397</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15471,6 +15466,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15597,7 +15597,7 @@
         <v>125891609</v>
       </c>
       <c r="B153" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>125889396</v>
       </c>
       <c r="B154" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15788,32 +15788,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125895229</v>
+        <v>125895017</v>
       </c>
       <c r="B155" t="n">
-        <v>79566</v>
+        <v>79004</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15888,7 +15888,7 @@
         <v>125888924</v>
       </c>
       <c r="B156" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15982,32 +15982,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125895017</v>
+        <v>125895229</v>
       </c>
       <c r="B157" t="n">
-        <v>79001</v>
+        <v>79569</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16079,10 +16079,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125892637</v>
+        <v>125889676</v>
       </c>
       <c r="B158" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16090,21 +16090,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16114,10 +16114,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500151</v>
+        <v>500202</v>
       </c>
       <c r="R158" t="n">
-        <v>6792458</v>
+        <v>6792435</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16150,6 +16150,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16176,10 +16181,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125889676</v>
+        <v>125892942</v>
       </c>
       <c r="B159" t="n">
-        <v>78977</v>
+        <v>91265</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16187,21 +16192,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16211,10 +16216,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500202</v>
+        <v>500171</v>
       </c>
       <c r="R159" t="n">
-        <v>6792435</v>
+        <v>6792489</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16247,11 +16252,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16278,10 +16278,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125892942</v>
+        <v>125892637</v>
       </c>
       <c r="B160" t="n">
-        <v>91262</v>
+        <v>79598</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16289,21 +16289,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16313,10 +16313,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>500171</v>
+        <v>500151</v>
       </c>
       <c r="R160" t="n">
-        <v>6792489</v>
+        <v>6792458</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -7263,10 +7263,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125894731</v>
+        <v>125889107</v>
       </c>
       <c r="B68" t="n">
-        <v>57657</v>
+        <v>79569</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,39 +7274,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500128</v>
+        <v>500285</v>
       </c>
       <c r="R68" t="n">
-        <v>6792590</v>
+        <v>6792489</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7365,10 +7360,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125889107</v>
+        <v>125888195</v>
       </c>
       <c r="B69" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7376,21 +7371,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7400,10 +7395,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500285</v>
+        <v>500310</v>
       </c>
       <c r="R69" t="n">
-        <v>6792489</v>
+        <v>6792516</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,6 +7431,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7462,10 +7462,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125888195</v>
+        <v>125894731</v>
       </c>
       <c r="B70" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7473,34 +7473,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500310</v>
+        <v>500128</v>
       </c>
       <c r="R70" t="n">
-        <v>6792516</v>
+        <v>6792590</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7533,11 +7538,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8437,32 +8437,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125890407</v>
+        <v>125892266</v>
       </c>
       <c r="B80" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8472,10 +8472,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500242</v>
+        <v>500158</v>
       </c>
       <c r="R80" t="n">
-        <v>6792408</v>
+        <v>6792441</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8508,11 +8508,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8539,32 +8534,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125892653</v>
+        <v>125888709</v>
       </c>
       <c r="B81" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8574,10 +8569,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500151</v>
+        <v>500311</v>
       </c>
       <c r="R81" t="n">
-        <v>6792458</v>
+        <v>6792502</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8636,10 +8631,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125889406</v>
+        <v>125892215</v>
       </c>
       <c r="B82" t="n">
-        <v>79598</v>
+        <v>79569</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8647,21 +8642,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8671,10 +8666,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>500257</v>
+        <v>500158</v>
       </c>
       <c r="R82" t="n">
-        <v>6792475</v>
+        <v>6792441</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8733,10 +8728,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125895109</v>
+        <v>125889155</v>
       </c>
       <c r="B83" t="n">
-        <v>79598</v>
+        <v>79569</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8744,21 +8739,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8768,10 +8763,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>499985</v>
+        <v>500275</v>
       </c>
       <c r="R83" t="n">
-        <v>6792633</v>
+        <v>6792487</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8830,32 +8825,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125892266</v>
+        <v>125891598</v>
       </c>
       <c r="B84" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8865,10 +8860,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500158</v>
+        <v>500153</v>
       </c>
       <c r="R84" t="n">
-        <v>6792441</v>
+        <v>6792391</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8927,32 +8922,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125888709</v>
+        <v>125890407</v>
       </c>
       <c r="B85" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8962,10 +8957,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500311</v>
+        <v>500242</v>
       </c>
       <c r="R85" t="n">
-        <v>6792502</v>
+        <v>6792408</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8998,6 +8993,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9024,10 +9024,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125892215</v>
+        <v>125892653</v>
       </c>
       <c r="B86" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9035,21 +9035,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500158</v>
+        <v>500151</v>
       </c>
       <c r="R86" t="n">
-        <v>6792441</v>
+        <v>6792458</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125889155</v>
+        <v>125889406</v>
       </c>
       <c r="B87" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9132,21 +9132,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500275</v>
+        <v>500257</v>
       </c>
       <c r="R87" t="n">
-        <v>6792487</v>
+        <v>6792475</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9218,10 +9218,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125891598</v>
+        <v>125895109</v>
       </c>
       <c r="B88" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9229,21 +9229,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500153</v>
+        <v>499985</v>
       </c>
       <c r="R88" t="n">
-        <v>6792391</v>
+        <v>6792633</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10290,32 +10290,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125893327</v>
+        <v>125894957</v>
       </c>
       <c r="B99" t="n">
-        <v>78739</v>
+        <v>8447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>500271</v>
+        <v>500037</v>
       </c>
       <c r="R99" t="n">
-        <v>6792529</v>
+        <v>6792660</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10387,32 +10387,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125892219</v>
+        <v>125889725</v>
       </c>
       <c r="B100" t="n">
-        <v>78739</v>
+        <v>8447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>500158</v>
+        <v>500234</v>
       </c>
       <c r="R100" t="n">
-        <v>6792441</v>
+        <v>6792439</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10484,32 +10484,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125894957</v>
+        <v>125893327</v>
       </c>
       <c r="B101" t="n">
-        <v>8447</v>
+        <v>78739</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>500037</v>
+        <v>500271</v>
       </c>
       <c r="R101" t="n">
-        <v>6792660</v>
+        <v>6792529</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10581,32 +10581,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125889725</v>
+        <v>125892219</v>
       </c>
       <c r="B102" t="n">
-        <v>8447</v>
+        <v>78739</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>500234</v>
+        <v>500158</v>
       </c>
       <c r="R102" t="n">
-        <v>6792439</v>
+        <v>6792441</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10678,32 +10678,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125889615</v>
+        <v>125892224</v>
       </c>
       <c r="B103" t="n">
-        <v>8447</v>
+        <v>78738</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>500202</v>
+        <v>500158</v>
       </c>
       <c r="R103" t="n">
-        <v>6792435</v>
+        <v>6792441</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10775,10 +10775,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125892224</v>
+        <v>125896058</v>
       </c>
       <c r="B104" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>500158</v>
+        <v>500351</v>
       </c>
       <c r="R104" t="n">
-        <v>6792441</v>
+        <v>6792369</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10846,6 +10846,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10872,10 +10877,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125896058</v>
+        <v>125891964</v>
       </c>
       <c r="B105" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10883,21 +10888,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10907,10 +10912,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>500351</v>
+        <v>500111</v>
       </c>
       <c r="R105" t="n">
-        <v>6792369</v>
+        <v>6792428</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10943,11 +10948,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125891964</v>
+        <v>125889615</v>
       </c>
       <c r="B106" t="n">
-        <v>79598</v>
+        <v>8447</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500111</v>
+        <v>500202</v>
       </c>
       <c r="R106" t="n">
-        <v>6792428</v>
+        <v>6792435</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11071,30 +11071,34 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125894266</v>
+        <v>125896524</v>
       </c>
       <c r="B107" t="n">
-        <v>98281</v>
+        <v>79598</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>223597</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11102,10 +11106,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500128</v>
+        <v>500384</v>
       </c>
       <c r="R107" t="n">
-        <v>6792590</v>
+        <v>6792529</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11164,7 +11168,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125896524</v>
+        <v>125889090</v>
       </c>
       <c r="B108" t="n">
         <v>79598</v>
@@ -11199,10 +11203,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500384</v>
+        <v>500285</v>
       </c>
       <c r="R108" t="n">
-        <v>6792529</v>
+        <v>6792489</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11261,10 +11265,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125889090</v>
+        <v>125896426</v>
       </c>
       <c r="B109" t="n">
-        <v>79598</v>
+        <v>57654</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11272,34 +11276,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500285</v>
+        <v>500351</v>
       </c>
       <c r="R109" t="n">
-        <v>6792489</v>
+        <v>6792369</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11358,7 +11367,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125896426</v>
+        <v>125889496</v>
       </c>
       <c r="B110" t="n">
         <v>57654</v>
@@ -11389,7 +11398,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -11398,10 +11407,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>500351</v>
+        <v>500257</v>
       </c>
       <c r="R110" t="n">
-        <v>6792369</v>
+        <v>6792475</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11460,50 +11469,41 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125889496</v>
+        <v>125894266</v>
       </c>
       <c r="B111" t="n">
-        <v>57654</v>
+        <v>98281</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>223597</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>500257</v>
+        <v>500128</v>
       </c>
       <c r="R111" t="n">
-        <v>6792475</v>
+        <v>6792590</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11562,32 +11562,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125893643</v>
+        <v>125892433</v>
       </c>
       <c r="B112" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11597,10 +11597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500237</v>
+        <v>500160</v>
       </c>
       <c r="R112" t="n">
-        <v>6792567</v>
+        <v>6792451</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11659,32 +11659,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125892433</v>
+        <v>125893643</v>
       </c>
       <c r="B113" t="n">
-        <v>79569</v>
+        <v>8447</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500160</v>
+        <v>500237</v>
       </c>
       <c r="R113" t="n">
-        <v>6792451</v>
+        <v>6792567</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12343,32 +12343,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125888695</v>
+        <v>125893148</v>
       </c>
       <c r="B120" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500311</v>
+        <v>500251</v>
       </c>
       <c r="R120" t="n">
-        <v>6792502</v>
+        <v>6792496</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12414,11 +12414,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12445,32 +12440,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125892496</v>
+        <v>125889503</v>
       </c>
       <c r="B121" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12480,10 +12475,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500145</v>
+        <v>500257</v>
       </c>
       <c r="R121" t="n">
-        <v>6792446</v>
+        <v>6792475</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12516,11 +12511,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12547,32 +12537,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125893148</v>
+        <v>125888695</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12582,10 +12572,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500251</v>
+        <v>500311</v>
       </c>
       <c r="R122" t="n">
-        <v>6792496</v>
+        <v>6792502</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12618,6 +12608,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12644,32 +12639,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125889503</v>
+        <v>125892496</v>
       </c>
       <c r="B123" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12679,10 +12674,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500257</v>
+        <v>500145</v>
       </c>
       <c r="R123" t="n">
-        <v>6792475</v>
+        <v>6792446</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12715,6 +12710,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14022,10 +14022,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125892352</v>
+        <v>125889010</v>
       </c>
       <c r="B137" t="n">
-        <v>79569</v>
+        <v>78739</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14033,21 +14033,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14057,10 +14057,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>500165</v>
+        <v>500286</v>
       </c>
       <c r="R137" t="n">
-        <v>6792432</v>
+        <v>6792459</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14216,10 +14216,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125889010</v>
+        <v>125892352</v>
       </c>
       <c r="B139" t="n">
-        <v>78739</v>
+        <v>79569</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14227,21 +14227,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>500286</v>
+        <v>500165</v>
       </c>
       <c r="R139" t="n">
-        <v>6792459</v>
+        <v>6792432</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15002,50 +15002,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125888369</v>
+        <v>125896772</v>
       </c>
       <c r="B147" t="n">
-        <v>57654</v>
+        <v>92535</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500310</v>
+        <v>500384</v>
       </c>
       <c r="R147" t="n">
-        <v>6792516</v>
+        <v>6792529</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15104,10 +15099,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125888908</v>
+        <v>125891864</v>
       </c>
       <c r="B148" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15115,21 +15110,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15139,10 +15134,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500306</v>
+        <v>500126</v>
       </c>
       <c r="R148" t="n">
-        <v>6792466</v>
+        <v>6792397</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15175,6 +15170,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15201,45 +15201,50 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125892001</v>
+        <v>125888369</v>
       </c>
       <c r="B149" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500111</v>
+        <v>500310</v>
       </c>
       <c r="R149" t="n">
-        <v>6792428</v>
+        <v>6792516</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15298,32 +15303,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125896772</v>
+        <v>125888908</v>
       </c>
       <c r="B150" t="n">
-        <v>92535</v>
+        <v>79569</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15333,10 +15338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500384</v>
+        <v>500306</v>
       </c>
       <c r="R150" t="n">
-        <v>6792529</v>
+        <v>6792466</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15395,32 +15400,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125891864</v>
+        <v>125892001</v>
       </c>
       <c r="B151" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15430,10 +15435,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500126</v>
+        <v>500111</v>
       </c>
       <c r="R151" t="n">
-        <v>6792397</v>
+        <v>6792428</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15466,11 +15471,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15497,32 +15497,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125888498</v>
+        <v>125889396</v>
       </c>
       <c r="B152" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500311</v>
+        <v>500257</v>
       </c>
       <c r="R152" t="n">
-        <v>6792509</v>
+        <v>6792475</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15594,32 +15594,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125891609</v>
+        <v>125888498</v>
       </c>
       <c r="B153" t="n">
-        <v>78739</v>
+        <v>8447</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15629,10 +15629,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500153</v>
+        <v>500311</v>
       </c>
       <c r="R153" t="n">
-        <v>6792391</v>
+        <v>6792509</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15691,10 +15691,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125889396</v>
+        <v>125891609</v>
       </c>
       <c r="B154" t="n">
-        <v>79569</v>
+        <v>78739</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15702,21 +15702,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500257</v>
+        <v>500153</v>
       </c>
       <c r="R154" t="n">
-        <v>6792475</v>
+        <v>6792391</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>

--- a/artfynd/A 22650-2025 artfynd.xlsx
+++ b/artfynd/A 22650-2025 artfynd.xlsx
@@ -7263,32 +7263,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125889107</v>
+        <v>125892998</v>
       </c>
       <c r="B68" t="n">
-        <v>79569</v>
+        <v>8447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500285</v>
+        <v>500188</v>
       </c>
       <c r="R68" t="n">
-        <v>6792489</v>
+        <v>6792496</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7360,32 +7360,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125888195</v>
+        <v>125893046</v>
       </c>
       <c r="B69" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500310</v>
+        <v>500207</v>
       </c>
       <c r="R69" t="n">
-        <v>6792516</v>
+        <v>6792488</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7431,11 +7431,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7462,10 +7457,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125894731</v>
+        <v>125888195</v>
       </c>
       <c r="B70" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7473,39 +7468,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500128</v>
+        <v>500310</v>
       </c>
       <c r="R70" t="n">
-        <v>6792590</v>
+        <v>6792516</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7538,6 +7528,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie på ca 30 meter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7564,45 +7559,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125893046</v>
+        <v>125894731</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>57657</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500207</v>
+        <v>500128</v>
       </c>
       <c r="R71" t="n">
-        <v>6792488</v>
+        <v>6792590</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7661,32 +7661,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125892998</v>
+        <v>125889107</v>
       </c>
       <c r="B72" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500188</v>
+        <v>500285</v>
       </c>
       <c r="R72" t="n">
-        <v>6792496</v>
+        <v>6792489</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7855,32 +7855,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125890092</v>
+        <v>125896279</v>
       </c>
       <c r="B74" t="n">
-        <v>79569</v>
+        <v>8447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500242</v>
+        <v>500351</v>
       </c>
       <c r="R74" t="n">
-        <v>6792408</v>
+        <v>6792369</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7952,32 +7952,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125891809</v>
+        <v>125893261</v>
       </c>
       <c r="B75" t="n">
-        <v>79569</v>
+        <v>8447</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>500166</v>
+        <v>500271</v>
       </c>
       <c r="R75" t="n">
-        <v>6792387</v>
+        <v>6792529</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8243,32 +8243,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125896279</v>
+        <v>125890092</v>
       </c>
       <c r="B78" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>500351</v>
+        <v>500242</v>
       </c>
       <c r="R78" t="n">
-        <v>6792369</v>
+        <v>6792408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8340,32 +8340,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125893261</v>
+        <v>125891809</v>
       </c>
       <c r="B79" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500271</v>
+        <v>500166</v>
       </c>
       <c r="R79" t="n">
-        <v>6792529</v>
+        <v>6792387</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8922,10 +8922,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125890407</v>
+        <v>125888740</v>
       </c>
       <c r="B85" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8933,34 +8933,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500242</v>
+        <v>500306</v>
       </c>
       <c r="R85" t="n">
-        <v>6792408</v>
+        <v>6792466</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8993,11 +8998,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9024,7 +9024,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125892653</v>
+        <v>125890407</v>
       </c>
       <c r="B86" t="n">
         <v>78980</v>
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500151</v>
+        <v>500242</v>
       </c>
       <c r="R86" t="n">
-        <v>6792458</v>
+        <v>6792408</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ 